--- a/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5C88F4-A801-4145-9193-CA1FC9E285B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27B1693-4A93-4988-94D1-C228425ABD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="146">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -733,6 +733,10 @@
   <si>
     <t>Up to 6000 rubs                    Every 1000 rubs</t>
     <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sample  Unit(gf)</t>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1170,7 +1174,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1316,6 +1320,15 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1370,36 +1383,54 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1427,110 +1458,86 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1825,25 +1832,25 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="70"/>
+      <c r="T1" s="70"/>
+      <c r="U1" s="70"/>
+      <c r="V1" s="70"/>
+      <c r="W1" s="70"/>
+      <c r="X1" s="70"/>
+      <c r="Y1" s="70"/>
+      <c r="Z1" s="70"/>
+      <c r="AA1" s="70"/>
+      <c r="AB1" s="70"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
@@ -1875,14 +1882,14 @@
       <c r="AB2" s="3"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="84"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2079,86 +2086,86 @@
       <c r="AB9" s="3"/>
     </row>
     <row r="10" spans="1:28" ht="16.75" x14ac:dyDescent="0.35">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="68" t="s">
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="70" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="71"/>
-      <c r="AB10" s="72"/>
+      <c r="Z10" s="74"/>
+      <c r="AA10" s="74"/>
+      <c r="AB10" s="75"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="68" t="s">
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="68" t="s">
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="68" t="s">
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="68" t="s">
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="82"/>
-      <c r="U11" s="68" t="s">
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="69"/>
-      <c r="W11" s="69"/>
-      <c r="X11" s="83"/>
-      <c r="Y11" s="73"/>
-      <c r="Z11" s="74"/>
-      <c r="AA11" s="74"/>
-      <c r="AB11" s="75"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="72"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="76"/>
+      <c r="Z11" s="77"/>
+      <c r="AA11" s="77"/>
+      <c r="AB11" s="78"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A12" s="85"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="87"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2185,10 +2192,10 @@
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A13" s="85"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="87"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -2215,10 +2222,10 @@
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A14" s="85"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="87"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2245,10 +2252,10 @@
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A15" s="85"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="87"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2275,10 +2282,10 @@
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A16" s="85"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="87"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -2445,11 +2452,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="E10:X10"/>
     <mergeCell ref="Y10:AB11"/>
@@ -2460,6 +2462,11 @@
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2500,32 +2507,32 @@
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="88"/>
-      <c r="Z1" s="88"/>
-      <c r="AA1" s="88"/>
-      <c r="AB1" s="88"/>
-      <c r="AC1" s="88"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="88"/>
-      <c r="AF1" s="88"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="88"/>
-      <c r="AJ1" s="88"/>
-      <c r="AK1" s="88"/>
-      <c r="AL1" s="88"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="103"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
+      <c r="Z1" s="103"/>
+      <c r="AA1" s="103"/>
+      <c r="AB1" s="103"/>
+      <c r="AC1" s="103"/>
+      <c r="AD1" s="103"/>
+      <c r="AE1" s="103"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="103"/>
+      <c r="AH1" s="103"/>
+      <c r="AI1" s="103"/>
+      <c r="AJ1" s="103"/>
+      <c r="AK1" s="103"/>
+      <c r="AL1" s="103"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" s="41" t="s">
@@ -2561,17 +2568,17 @@
       <c r="AF2" s="21"/>
     </row>
     <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="103"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -2788,45 +2795,45 @@
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="95" t="s">
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="95" t="s">
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="96"/>
-      <c r="Y10" s="96"/>
-      <c r="Z10" s="96"/>
-      <c r="AA10" s="96"/>
-      <c r="AB10" s="96"/>
-      <c r="AC10" s="96"/>
-      <c r="AD10" s="96"/>
-      <c r="AE10" s="96"/>
-      <c r="AF10" s="96"/>
-      <c r="AG10" s="96"/>
-      <c r="AH10" s="96"/>
-      <c r="AI10" s="96"/>
-      <c r="AJ10" s="96"/>
-      <c r="AK10" s="96"/>
-      <c r="AL10" s="97"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="105"/>
+      <c r="S10" s="105"/>
+      <c r="T10" s="105"/>
+      <c r="U10" s="105"/>
+      <c r="V10" s="105"/>
+      <c r="W10" s="105"/>
+      <c r="X10" s="105"/>
+      <c r="Y10" s="105"/>
+      <c r="Z10" s="105"/>
+      <c r="AA10" s="105"/>
+      <c r="AB10" s="105"/>
+      <c r="AC10" s="105"/>
+      <c r="AD10" s="105"/>
+      <c r="AE10" s="105"/>
+      <c r="AF10" s="105"/>
+      <c r="AG10" s="105"/>
+      <c r="AH10" s="105"/>
+      <c r="AI10" s="105"/>
+      <c r="AJ10" s="105"/>
+      <c r="AK10" s="105"/>
+      <c r="AL10" s="106"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
@@ -2836,62 +2843,62 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="27"/>
-      <c r="F11" s="95" t="s">
+      <c r="F11" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="95" t="s">
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="95" t="s">
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="105"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="97"/>
-      <c r="U11" s="95" t="s">
+      <c r="Q11" s="105"/>
+      <c r="R11" s="105"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="106"/>
+      <c r="U11" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="96"/>
-      <c r="W11" s="96"/>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="97"/>
-      <c r="Z11" s="95" t="s">
+      <c r="V11" s="105"/>
+      <c r="W11" s="105"/>
+      <c r="X11" s="105"/>
+      <c r="Y11" s="106"/>
+      <c r="Z11" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="97"/>
-      <c r="AE11" s="95" t="s">
+      <c r="AA11" s="105"/>
+      <c r="AB11" s="105"/>
+      <c r="AC11" s="105"/>
+      <c r="AD11" s="106"/>
+      <c r="AE11" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="96"/>
-      <c r="AG11" s="96"/>
-      <c r="AH11" s="96"/>
-      <c r="AI11" s="97"/>
-      <c r="AJ11" s="98" t="s">
+      <c r="AF11" s="105"/>
+      <c r="AG11" s="105"/>
+      <c r="AH11" s="105"/>
+      <c r="AI11" s="106"/>
+      <c r="AJ11" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="99"/>
-      <c r="AL11" s="100"/>
+      <c r="AK11" s="108"/>
+      <c r="AL11" s="109"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="91"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="90"/>
       <c r="F12" s="28"/>
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
@@ -2927,11 +2934,11 @@
       <c r="AL12" s="33"/>
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="92"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="94"/>
+      <c r="A13" s="91"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
       <c r="F13" s="34"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
@@ -2967,13 +2974,13 @@
       <c r="AL13" s="38"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="91"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="90"/>
       <c r="F14" s="28"/>
       <c r="G14" s="29"/>
       <c r="H14" s="29"/>
@@ -3009,11 +3016,11 @@
       <c r="AL14" s="33"/>
     </row>
     <row r="15" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="92"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="94"/>
+      <c r="A15" s="91"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="93"/>
       <c r="F15" s="34"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
@@ -3049,13 +3056,13 @@
       <c r="AL15" s="38"/>
     </row>
     <row r="16" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="89" t="s">
+      <c r="A16" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="91"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="90"/>
       <c r="F16" s="28"/>
       <c r="G16" s="29"/>
       <c r="H16" s="29"/>
@@ -3091,11 +3098,11 @@
       <c r="AL16" s="33"/>
     </row>
     <row r="17" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="92"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94"/>
+      <c r="A17" s="91"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93"/>
       <c r="F17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
@@ -3131,13 +3138,13 @@
       <c r="AL17" s="38"/>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="90"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="90"/>
-      <c r="E18" s="91"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="90"/>
       <c r="F18" s="28"/>
       <c r="G18" s="29"/>
       <c r="H18" s="29"/>
@@ -3173,11 +3180,11 @@
       <c r="AL18" s="33"/>
     </row>
     <row r="19" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="92"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="94"/>
+      <c r="A19" s="91"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="93"/>
       <c r="F19" s="34"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
@@ -3213,13 +3220,13 @@
       <c r="AL19" s="38"/>
     </row>
     <row r="20" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="91"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="90"/>
       <c r="F20" s="28"/>
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
@@ -3255,11 +3262,11 @@
       <c r="AL20" s="33"/>
     </row>
     <row r="21" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="92"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="94"/>
+      <c r="A21" s="91"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93"/>
       <c r="F21" s="34"/>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
@@ -3295,13 +3302,13 @@
       <c r="AL21" s="38"/>
     </row>
     <row r="22" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="91"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="90"/>
       <c r="F22" s="28"/>
       <c r="G22" s="29"/>
       <c r="H22" s="29"/>
@@ -3337,11 +3344,11 @@
       <c r="AL22" s="33"/>
     </row>
     <row r="23" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="92"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="94"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="93"/>
       <c r="F23" s="34"/>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
@@ -3377,13 +3384,13 @@
       <c r="AL23" s="38"/>
     </row>
     <row r="24" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="91"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="90"/>
       <c r="F24" s="28"/>
       <c r="G24" s="29"/>
       <c r="H24" s="29"/>
@@ -3419,11 +3426,11 @@
       <c r="AL24" s="33"/>
     </row>
     <row r="25" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="92"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="94"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="93"/>
       <c r="F25" s="34"/>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
@@ -3459,13 +3466,13 @@
       <c r="AL25" s="38"/>
     </row>
     <row r="26" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="91"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="90"/>
       <c r="F26" s="28"/>
       <c r="G26" s="29"/>
       <c r="H26" s="29"/>
@@ -3501,11 +3508,11 @@
       <c r="AL26" s="33"/>
     </row>
     <row r="27" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="92"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="94"/>
+      <c r="A27" s="91"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="93"/>
       <c r="F27" s="34"/>
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
@@ -3541,13 +3548,13 @@
       <c r="AL27" s="38"/>
     </row>
     <row r="28" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="91"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="28"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
@@ -3583,11 +3590,11 @@
       <c r="AL28" s="33"/>
     </row>
     <row r="29" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="92"/>
-      <c r="B29" s="93"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="94"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="93"/>
       <c r="F29" s="34"/>
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
@@ -3623,13 +3630,13 @@
       <c r="AL29" s="38"/>
     </row>
     <row r="30" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="89" t="s">
+      <c r="A30" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="91"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="28"/>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -3665,11 +3672,11 @@
       <c r="AL30" s="33"/>
     </row>
     <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="92"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="94"/>
+      <c r="A31" s="91"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="93"/>
       <c r="F31" s="34"/>
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
@@ -3705,13 +3712,13 @@
       <c r="AL31" s="38"/>
     </row>
     <row r="32" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="89" t="s">
+      <c r="A32" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
       <c r="F32" s="28"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
@@ -3747,11 +3754,11 @@
       <c r="AL32" s="33"/>
     </row>
     <row r="33" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="92"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
       <c r="F33" s="34"/>
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
@@ -3787,13 +3794,13 @@
       <c r="AL33" s="38"/>
     </row>
     <row r="34" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="89" t="s">
+      <c r="A34" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="90"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
       <c r="F34" s="28"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29"/>
@@ -3829,11 +3836,11 @@
       <c r="AL34" s="33"/>
     </row>
     <row r="35" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="92"/>
-      <c r="B35" s="93"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="94"/>
+      <c r="A35" s="91"/>
+      <c r="B35" s="92"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="93"/>
       <c r="F35" s="34"/>
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
@@ -3869,13 +3876,13 @@
       <c r="AL35" s="38"/>
     </row>
     <row r="36" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="104" t="s">
+      <c r="A36" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="105"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="106"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="96"/>
       <c r="F36" s="28"/>
       <c r="G36" s="29"/>
       <c r="H36" s="29"/>
@@ -3911,11 +3918,11 @@
       <c r="AL36" s="33"/>
     </row>
     <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="109"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="99"/>
       <c r="F37" s="34"/>
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
@@ -3984,21 +3991,21 @@
       <c r="AF38" s="21"/>
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A39" s="110" t="s">
+      <c r="A39" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="110"/>
-      <c r="C39" s="110"/>
-      <c r="D39" s="111" t="s">
+      <c r="B39" s="100"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="111"/>
-      <c r="F39" s="111"/>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
-      <c r="I39" s="111"/>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="101"/>
+      <c r="H39" s="101"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
       <c r="L39" s="21"/>
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
@@ -4022,19 +4029,19 @@
       <c r="AF39" s="21"/>
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
-      <c r="B40" s="110"/>
-      <c r="C40" s="110"/>
-      <c r="D40" s="112" t="s">
+      <c r="A40" s="100"/>
+      <c r="B40" s="100"/>
+      <c r="C40" s="100"/>
+      <c r="D40" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="112"/>
-      <c r="F40" s="112"/>
-      <c r="G40" s="112"/>
-      <c r="H40" s="112"/>
-      <c r="I40" s="112"/>
-      <c r="J40" s="112"/>
-      <c r="K40" s="112"/>
+      <c r="E40" s="102"/>
+      <c r="F40" s="102"/>
+      <c r="G40" s="102"/>
+      <c r="H40" s="102"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="102"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
@@ -4253,18 +4260,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="A24:E25"/>
-    <mergeCell ref="A26:E27"/>
-    <mergeCell ref="A28:E29"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="A22:E23"/>
@@ -4281,6 +4276,18 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="A24:E25"/>
+    <mergeCell ref="A26:E27"/>
+    <mergeCell ref="A28:E29"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4320,32 +4327,32 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="119"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
@@ -4385,18 +4392,18 @@
         <v>45</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -4417,13 +4424,13 @@
       <c r="A4" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -4482,216 +4489,216 @@
       <c r="AK5" s="7"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="115" t="s">
+      <c r="B6" s="117"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115" t="s">
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115"/>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115"/>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115"/>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115"/>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
+      <c r="S6" s="118"/>
+      <c r="T6" s="118"/>
+      <c r="U6" s="118"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="118"/>
+      <c r="X6" s="118"/>
+      <c r="Y6" s="118"/>
+      <c r="Z6" s="118"/>
+      <c r="AA6" s="118"/>
+      <c r="AB6" s="118"/>
+      <c r="AC6" s="118"/>
+      <c r="AD6" s="118"/>
+      <c r="AE6" s="118"/>
+      <c r="AF6" s="118"/>
+      <c r="AG6" s="118"/>
+      <c r="AH6" s="118"/>
+      <c r="AI6" s="118"/>
+      <c r="AJ6" s="118"/>
+      <c r="AK6" s="118"/>
+      <c r="AL6" s="118"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="118"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="121" t="s">
+      <c r="A7" s="117"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="122"/>
-      <c r="Q7" s="122"/>
-      <c r="R7" s="122"/>
-      <c r="S7" s="122"/>
-      <c r="T7" s="122"/>
-      <c r="U7" s="123"/>
-      <c r="V7" s="121" t="s">
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="123"/>
+      <c r="U7" s="124"/>
+      <c r="V7" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="W7" s="122"/>
-      <c r="X7" s="122"/>
-      <c r="Y7" s="122"/>
-      <c r="Z7" s="122"/>
-      <c r="AA7" s="122"/>
-      <c r="AB7" s="122"/>
-      <c r="AC7" s="122"/>
-      <c r="AD7" s="123"/>
-      <c r="AE7" s="124" t="s">
+      <c r="W7" s="123"/>
+      <c r="X7" s="123"/>
+      <c r="Y7" s="123"/>
+      <c r="Z7" s="123"/>
+      <c r="AA7" s="123"/>
+      <c r="AB7" s="123"/>
+      <c r="AC7" s="123"/>
+      <c r="AD7" s="124"/>
+      <c r="AE7" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="AF7" s="124"/>
-      <c r="AG7" s="124"/>
-      <c r="AH7" s="124"/>
-      <c r="AI7" s="124"/>
-      <c r="AJ7" s="124"/>
-      <c r="AK7" s="124"/>
-      <c r="AL7" s="124"/>
+      <c r="AF7" s="119"/>
+      <c r="AG7" s="119"/>
+      <c r="AH7" s="119"/>
+      <c r="AI7" s="119"/>
+      <c r="AJ7" s="119"/>
+      <c r="AK7" s="119"/>
+      <c r="AL7" s="119"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="125"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="120"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="82"/>
-      <c r="V8" s="120"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="83"/>
-      <c r="Y8" s="83"/>
-      <c r="Z8" s="83"/>
-      <c r="AA8" s="83"/>
-      <c r="AB8" s="83"/>
-      <c r="AC8" s="83"/>
-      <c r="AD8" s="82"/>
-      <c r="AE8" s="113"/>
-      <c r="AF8" s="113"/>
-      <c r="AG8" s="113"/>
-      <c r="AH8" s="113"/>
-      <c r="AI8" s="113"/>
-      <c r="AJ8" s="113"/>
-      <c r="AK8" s="113"/>
-      <c r="AL8" s="113"/>
+      <c r="A8" s="116"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="86"/>
+      <c r="O8" s="86"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="86"/>
+      <c r="R8" s="86"/>
+      <c r="S8" s="86"/>
+      <c r="T8" s="86"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="121"/>
+      <c r="W8" s="86"/>
+      <c r="X8" s="86"/>
+      <c r="Y8" s="86"/>
+      <c r="Z8" s="86"/>
+      <c r="AA8" s="86"/>
+      <c r="AB8" s="86"/>
+      <c r="AC8" s="86"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="114"/>
+      <c r="AF8" s="114"/>
+      <c r="AG8" s="114"/>
+      <c r="AH8" s="114"/>
+      <c r="AI8" s="114"/>
+      <c r="AJ8" s="114"/>
+      <c r="AK8" s="114"/>
+      <c r="AL8" s="114"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="125"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="113"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
-      <c r="L9" s="113"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="83"/>
-      <c r="U9" s="82"/>
-      <c r="V9" s="120"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="83"/>
-      <c r="Y9" s="83"/>
-      <c r="Z9" s="83"/>
-      <c r="AA9" s="83"/>
-      <c r="AB9" s="83"/>
-      <c r="AC9" s="83"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="113"/>
-      <c r="AF9" s="113"/>
-      <c r="AG9" s="113"/>
-      <c r="AH9" s="113"/>
-      <c r="AI9" s="113"/>
-      <c r="AJ9" s="113"/>
-      <c r="AK9" s="113"/>
-      <c r="AL9" s="113"/>
+      <c r="A9" s="116"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="114"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="86"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="86"/>
+      <c r="S9" s="86"/>
+      <c r="T9" s="86"/>
+      <c r="U9" s="85"/>
+      <c r="V9" s="121"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="86"/>
+      <c r="Z9" s="86"/>
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="86"/>
+      <c r="AC9" s="86"/>
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="114"/>
+      <c r="AF9" s="114"/>
+      <c r="AG9" s="114"/>
+      <c r="AH9" s="114"/>
+      <c r="AI9" s="114"/>
+      <c r="AJ9" s="114"/>
+      <c r="AK9" s="114"/>
+      <c r="AL9" s="114"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="126"/>
-      <c r="B10" s="126"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="126"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="113"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="83"/>
-      <c r="S10" s="83"/>
-      <c r="T10" s="83"/>
-      <c r="U10" s="82"/>
-      <c r="V10" s="120"/>
-      <c r="W10" s="83"/>
-      <c r="X10" s="83"/>
-      <c r="Y10" s="83"/>
-      <c r="Z10" s="83"/>
-      <c r="AA10" s="83"/>
-      <c r="AB10" s="83"/>
-      <c r="AC10" s="83"/>
-      <c r="AD10" s="82"/>
-      <c r="AE10" s="113"/>
-      <c r="AF10" s="113"/>
-      <c r="AG10" s="113"/>
-      <c r="AH10" s="113"/>
-      <c r="AI10" s="113"/>
-      <c r="AJ10" s="113"/>
-      <c r="AK10" s="113"/>
-      <c r="AL10" s="113"/>
+      <c r="A10" s="125"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="86"/>
+      <c r="O10" s="86"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="86"/>
+      <c r="R10" s="86"/>
+      <c r="S10" s="86"/>
+      <c r="T10" s="86"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="121"/>
+      <c r="W10" s="86"/>
+      <c r="X10" s="86"/>
+      <c r="Y10" s="86"/>
+      <c r="Z10" s="86"/>
+      <c r="AA10" s="86"/>
+      <c r="AB10" s="86"/>
+      <c r="AC10" s="86"/>
+      <c r="AD10" s="85"/>
+      <c r="AE10" s="114"/>
+      <c r="AF10" s="114"/>
+      <c r="AG10" s="114"/>
+      <c r="AH10" s="114"/>
+      <c r="AI10" s="114"/>
+      <c r="AJ10" s="114"/>
+      <c r="AK10" s="114"/>
+      <c r="AL10" s="114"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
@@ -4759,20 +4766,20 @@
       <c r="A13" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="117"/>
-      <c r="N13" s="117"/>
-      <c r="O13" s="117"/>
-      <c r="P13" s="117"/>
-      <c r="Q13" s="117"/>
-      <c r="R13" s="117"/>
-      <c r="S13" s="117"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="127"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="127"/>
+      <c r="O13" s="127"/>
+      <c r="P13" s="127"/>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -4790,13 +4797,13 @@
       <c r="A14" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -4862,238 +4869,238 @@
       <c r="AL15" s="3"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="115" t="s">
+      <c r="B16" s="117"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="115"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="124" t="s">
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="M16" s="124"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="124"/>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="124"/>
-      <c r="R16" s="124"/>
-      <c r="S16" s="124"/>
-      <c r="T16" s="124"/>
-      <c r="U16" s="124"/>
-      <c r="V16" s="124"/>
-      <c r="W16" s="124"/>
-      <c r="X16" s="115" t="s">
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="119"/>
+      <c r="R16" s="119"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="119"/>
+      <c r="U16" s="119"/>
+      <c r="V16" s="119"/>
+      <c r="W16" s="119"/>
+      <c r="X16" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="Y16" s="115"/>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="115"/>
-      <c r="AB16" s="124" t="s">
+      <c r="Y16" s="118"/>
+      <c r="Z16" s="118"/>
+      <c r="AA16" s="118"/>
+      <c r="AB16" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="AC16" s="124"/>
-      <c r="AD16" s="124"/>
-      <c r="AE16" s="124"/>
-      <c r="AF16" s="124"/>
-      <c r="AG16" s="124"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="124"/>
-      <c r="AJ16" s="124"/>
-      <c r="AK16" s="124"/>
-      <c r="AL16" s="124"/>
+      <c r="AC16" s="119"/>
+      <c r="AD16" s="119"/>
+      <c r="AE16" s="119"/>
+      <c r="AF16" s="119"/>
+      <c r="AG16" s="119"/>
+      <c r="AH16" s="119"/>
+      <c r="AI16" s="119"/>
+      <c r="AJ16" s="119"/>
+      <c r="AK16" s="119"/>
+      <c r="AL16" s="119"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="118"/>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="124" t="s">
+      <c r="A17" s="117"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124" t="s">
+      <c r="M17" s="119"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
+      <c r="P17" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124" t="s">
+      <c r="Q17" s="119"/>
+      <c r="R17" s="119"/>
+      <c r="S17" s="119"/>
+      <c r="T17" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="U17" s="124"/>
-      <c r="V17" s="124"/>
-      <c r="W17" s="124"/>
-      <c r="X17" s="115"/>
-      <c r="Y17" s="115"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="115"/>
-      <c r="AB17" s="124" t="s">
+      <c r="U17" s="119"/>
+      <c r="V17" s="119"/>
+      <c r="W17" s="119"/>
+      <c r="X17" s="118"/>
+      <c r="Y17" s="118"/>
+      <c r="Z17" s="118"/>
+      <c r="AA17" s="118"/>
+      <c r="AB17" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="AC17" s="124"/>
-      <c r="AD17" s="124"/>
-      <c r="AE17" s="124"/>
-      <c r="AF17" s="124" t="s">
+      <c r="AC17" s="119"/>
+      <c r="AD17" s="119"/>
+      <c r="AE17" s="119"/>
+      <c r="AF17" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="AG17" s="124"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="124"/>
-      <c r="AJ17" s="124" t="s">
+      <c r="AG17" s="119"/>
+      <c r="AH17" s="119"/>
+      <c r="AI17" s="119"/>
+      <c r="AJ17" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="AK17" s="124"/>
-      <c r="AL17" s="124"/>
+      <c r="AK17" s="119"/>
+      <c r="AL17" s="119"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="125"/>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="116">
+      <c r="A18" s="116"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="115">
         <v>125</v>
       </c>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="N18" s="113"/>
-      <c r="O18" s="113"/>
-      <c r="P18" s="113"/>
-      <c r="Q18" s="113"/>
-      <c r="R18" s="113"/>
-      <c r="S18" s="113"/>
-      <c r="T18" s="113"/>
-      <c r="U18" s="113"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="113"/>
-      <c r="X18" s="116">
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
+      <c r="U18" s="114"/>
+      <c r="V18" s="114"/>
+      <c r="W18" s="114"/>
+      <c r="X18" s="115">
         <v>2000</v>
       </c>
-      <c r="Y18" s="116"/>
-      <c r="Z18" s="116"/>
-      <c r="AA18" s="116"/>
-      <c r="AB18" s="113"/>
-      <c r="AC18" s="113"/>
-      <c r="AD18" s="113"/>
-      <c r="AE18" s="113"/>
-      <c r="AF18" s="113"/>
-      <c r="AG18" s="113"/>
-      <c r="AH18" s="113"/>
-      <c r="AI18" s="113"/>
-      <c r="AJ18" s="113"/>
-      <c r="AK18" s="113"/>
-      <c r="AL18" s="113"/>
+      <c r="Y18" s="115"/>
+      <c r="Z18" s="115"/>
+      <c r="AA18" s="115"/>
+      <c r="AB18" s="114"/>
+      <c r="AC18" s="114"/>
+      <c r="AD18" s="114"/>
+      <c r="AE18" s="114"/>
+      <c r="AF18" s="114"/>
+      <c r="AG18" s="114"/>
+      <c r="AH18" s="114"/>
+      <c r="AI18" s="114"/>
+      <c r="AJ18" s="114"/>
+      <c r="AK18" s="114"/>
+      <c r="AL18" s="114"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="125"/>
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="116">
+      <c r="A19" s="116"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="115">
         <v>500</v>
       </c>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="113"/>
-      <c r="N19" s="113"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="113"/>
-      <c r="Q19" s="113"/>
-      <c r="R19" s="113"/>
-      <c r="S19" s="113"/>
-      <c r="T19" s="113"/>
-      <c r="U19" s="113"/>
-      <c r="V19" s="113"/>
-      <c r="W19" s="113"/>
-      <c r="X19" s="116">
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="114"/>
+      <c r="V19" s="114"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="115">
         <v>5000</v>
       </c>
-      <c r="Y19" s="116"/>
-      <c r="Z19" s="116"/>
-      <c r="AA19" s="116"/>
-      <c r="AB19" s="113"/>
-      <c r="AC19" s="113"/>
-      <c r="AD19" s="113"/>
-      <c r="AE19" s="113"/>
-      <c r="AF19" s="113"/>
-      <c r="AG19" s="113"/>
-      <c r="AH19" s="113"/>
-      <c r="AI19" s="113"/>
-      <c r="AJ19" s="113"/>
-      <c r="AK19" s="113"/>
-      <c r="AL19" s="113"/>
+      <c r="Y19" s="115"/>
+      <c r="Z19" s="115"/>
+      <c r="AA19" s="115"/>
+      <c r="AB19" s="114"/>
+      <c r="AC19" s="114"/>
+      <c r="AD19" s="114"/>
+      <c r="AE19" s="114"/>
+      <c r="AF19" s="114"/>
+      <c r="AG19" s="114"/>
+      <c r="AH19" s="114"/>
+      <c r="AI19" s="114"/>
+      <c r="AJ19" s="114"/>
+      <c r="AK19" s="114"/>
+      <c r="AL19" s="114"/>
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="125"/>
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="116">
+      <c r="A20" s="116"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="115">
         <v>1000</v>
       </c>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="113"/>
-      <c r="R20" s="113"/>
-      <c r="S20" s="113"/>
-      <c r="T20" s="113"/>
-      <c r="U20" s="113"/>
-      <c r="V20" s="113"/>
-      <c r="W20" s="113"/>
-      <c r="X20" s="116">
+      <c r="I20" s="115"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="114"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="114"/>
+      <c r="V20" s="114"/>
+      <c r="W20" s="114"/>
+      <c r="X20" s="115">
         <v>7000</v>
       </c>
-      <c r="Y20" s="116"/>
-      <c r="Z20" s="116"/>
-      <c r="AA20" s="116"/>
-      <c r="AB20" s="113"/>
-      <c r="AC20" s="113"/>
-      <c r="AD20" s="113"/>
-      <c r="AE20" s="113"/>
-      <c r="AF20" s="113"/>
-      <c r="AG20" s="113"/>
-      <c r="AH20" s="113"/>
-      <c r="AI20" s="113"/>
-      <c r="AJ20" s="113"/>
-      <c r="AK20" s="113"/>
-      <c r="AL20" s="113"/>
+      <c r="Y20" s="115"/>
+      <c r="Z20" s="115"/>
+      <c r="AA20" s="115"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="114"/>
+      <c r="AD20" s="114"/>
+      <c r="AE20" s="114"/>
+      <c r="AF20" s="114"/>
+      <c r="AG20" s="114"/>
+      <c r="AH20" s="114"/>
+      <c r="AI20" s="114"/>
+      <c r="AJ20" s="114"/>
+      <c r="AK20" s="114"/>
+      <c r="AL20" s="114"/>
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
@@ -5172,238 +5179,238 @@
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="118" t="s">
+      <c r="A23" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="115" t="s">
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="124" t="s">
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="M23" s="124"/>
-      <c r="N23" s="124"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="124"/>
-      <c r="R23" s="124"/>
-      <c r="S23" s="124"/>
-      <c r="T23" s="124"/>
-      <c r="U23" s="124"/>
-      <c r="V23" s="124"/>
-      <c r="W23" s="124"/>
-      <c r="X23" s="115" t="s">
+      <c r="M23" s="119"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="119"/>
+      <c r="S23" s="119"/>
+      <c r="T23" s="119"/>
+      <c r="U23" s="119"/>
+      <c r="V23" s="119"/>
+      <c r="W23" s="119"/>
+      <c r="X23" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="Y23" s="115"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="115"/>
-      <c r="AB23" s="124" t="s">
+      <c r="Y23" s="118"/>
+      <c r="Z23" s="118"/>
+      <c r="AA23" s="118"/>
+      <c r="AB23" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="AC23" s="124"/>
-      <c r="AD23" s="124"/>
-      <c r="AE23" s="124"/>
-      <c r="AF23" s="124"/>
-      <c r="AG23" s="124"/>
-      <c r="AH23" s="124"/>
-      <c r="AI23" s="124"/>
-      <c r="AJ23" s="124"/>
-      <c r="AK23" s="124"/>
-      <c r="AL23" s="124"/>
+      <c r="AC23" s="119"/>
+      <c r="AD23" s="119"/>
+      <c r="AE23" s="119"/>
+      <c r="AF23" s="119"/>
+      <c r="AG23" s="119"/>
+      <c r="AH23" s="119"/>
+      <c r="AI23" s="119"/>
+      <c r="AJ23" s="119"/>
+      <c r="AK23" s="119"/>
+      <c r="AL23" s="119"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="118"/>
-      <c r="B24" s="118"/>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="115"/>
-      <c r="L24" s="124" t="s">
+      <c r="A24" s="117"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124" t="s">
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124" t="s">
+      <c r="Q24" s="119"/>
+      <c r="R24" s="119"/>
+      <c r="S24" s="119"/>
+      <c r="T24" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
-      <c r="X24" s="115"/>
-      <c r="Y24" s="115"/>
-      <c r="Z24" s="115"/>
-      <c r="AA24" s="115"/>
-      <c r="AB24" s="124" t="s">
+      <c r="U24" s="119"/>
+      <c r="V24" s="119"/>
+      <c r="W24" s="119"/>
+      <c r="X24" s="118"/>
+      <c r="Y24" s="118"/>
+      <c r="Z24" s="118"/>
+      <c r="AA24" s="118"/>
+      <c r="AB24" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="AC24" s="124"/>
-      <c r="AD24" s="124"/>
-      <c r="AE24" s="124"/>
-      <c r="AF24" s="124" t="s">
+      <c r="AC24" s="119"/>
+      <c r="AD24" s="119"/>
+      <c r="AE24" s="119"/>
+      <c r="AF24" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="AG24" s="124"/>
-      <c r="AH24" s="124"/>
-      <c r="AI24" s="124"/>
-      <c r="AJ24" s="124" t="s">
+      <c r="AG24" s="119"/>
+      <c r="AH24" s="119"/>
+      <c r="AI24" s="119"/>
+      <c r="AJ24" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="AK24" s="124"/>
-      <c r="AL24" s="124"/>
+      <c r="AK24" s="119"/>
+      <c r="AL24" s="119"/>
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="125"/>
-      <c r="B25" s="125"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="125"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="116">
+      <c r="A25" s="116"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="115">
         <v>125</v>
       </c>
-      <c r="I25" s="116"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="113"/>
-      <c r="N25" s="113"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="113"/>
-      <c r="S25" s="113"/>
-      <c r="T25" s="113"/>
-      <c r="U25" s="113"/>
-      <c r="V25" s="113"/>
-      <c r="W25" s="113"/>
-      <c r="X25" s="116">
+      <c r="I25" s="115"/>
+      <c r="J25" s="115"/>
+      <c r="K25" s="115"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
+      <c r="U25" s="114"/>
+      <c r="V25" s="114"/>
+      <c r="W25" s="114"/>
+      <c r="X25" s="115">
         <v>2000</v>
       </c>
-      <c r="Y25" s="116"/>
-      <c r="Z25" s="116"/>
-      <c r="AA25" s="116"/>
-      <c r="AB25" s="113"/>
-      <c r="AC25" s="113"/>
-      <c r="AD25" s="113"/>
-      <c r="AE25" s="113"/>
-      <c r="AF25" s="113"/>
-      <c r="AG25" s="113"/>
-      <c r="AH25" s="113"/>
-      <c r="AI25" s="113"/>
-      <c r="AJ25" s="113"/>
-      <c r="AK25" s="113"/>
-      <c r="AL25" s="113"/>
+      <c r="Y25" s="115"/>
+      <c r="Z25" s="115"/>
+      <c r="AA25" s="115"/>
+      <c r="AB25" s="114"/>
+      <c r="AC25" s="114"/>
+      <c r="AD25" s="114"/>
+      <c r="AE25" s="114"/>
+      <c r="AF25" s="114"/>
+      <c r="AG25" s="114"/>
+      <c r="AH25" s="114"/>
+      <c r="AI25" s="114"/>
+      <c r="AJ25" s="114"/>
+      <c r="AK25" s="114"/>
+      <c r="AL25" s="114"/>
     </row>
     <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="125"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="125"/>
-      <c r="G26" s="125"/>
-      <c r="H26" s="116">
+      <c r="A26" s="116"/>
+      <c r="B26" s="116"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="115">
         <v>500</v>
       </c>
-      <c r="I26" s="116"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="113"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="113"/>
-      <c r="S26" s="113"/>
-      <c r="T26" s="113"/>
-      <c r="U26" s="113"/>
-      <c r="V26" s="113"/>
-      <c r="W26" s="113"/>
-      <c r="X26" s="116">
+      <c r="I26" s="115"/>
+      <c r="J26" s="115"/>
+      <c r="K26" s="115"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="114"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="114"/>
+      <c r="T26" s="114"/>
+      <c r="U26" s="114"/>
+      <c r="V26" s="114"/>
+      <c r="W26" s="114"/>
+      <c r="X26" s="115">
         <v>5000</v>
       </c>
-      <c r="Y26" s="116"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="116"/>
-      <c r="AB26" s="113"/>
-      <c r="AC26" s="113"/>
-      <c r="AD26" s="113"/>
-      <c r="AE26" s="113"/>
-      <c r="AF26" s="113"/>
-      <c r="AG26" s="113"/>
-      <c r="AH26" s="113"/>
-      <c r="AI26" s="113"/>
-      <c r="AJ26" s="113"/>
-      <c r="AK26" s="113"/>
-      <c r="AL26" s="113"/>
+      <c r="Y26" s="115"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="115"/>
+      <c r="AB26" s="114"/>
+      <c r="AC26" s="114"/>
+      <c r="AD26" s="114"/>
+      <c r="AE26" s="114"/>
+      <c r="AF26" s="114"/>
+      <c r="AG26" s="114"/>
+      <c r="AH26" s="114"/>
+      <c r="AI26" s="114"/>
+      <c r="AJ26" s="114"/>
+      <c r="AK26" s="114"/>
+      <c r="AL26" s="114"/>
     </row>
     <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="125"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="125"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="116">
+      <c r="A27" s="116"/>
+      <c r="B27" s="116"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="115">
         <v>1000</v>
       </c>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="113"/>
-      <c r="M27" s="113"/>
-      <c r="N27" s="113"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="113"/>
-      <c r="R27" s="113"/>
-      <c r="S27" s="113"/>
-      <c r="T27" s="113"/>
-      <c r="U27" s="113"/>
-      <c r="V27" s="113"/>
-      <c r="W27" s="113"/>
-      <c r="X27" s="116">
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
+      <c r="U27" s="114"/>
+      <c r="V27" s="114"/>
+      <c r="W27" s="114"/>
+      <c r="X27" s="115">
         <v>7000</v>
       </c>
-      <c r="Y27" s="116"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="116"/>
-      <c r="AB27" s="113"/>
-      <c r="AC27" s="113"/>
-      <c r="AD27" s="113"/>
-      <c r="AE27" s="113"/>
-      <c r="AF27" s="113"/>
-      <c r="AG27" s="113"/>
-      <c r="AH27" s="113"/>
-      <c r="AI27" s="113"/>
-      <c r="AJ27" s="113"/>
-      <c r="AK27" s="113"/>
-      <c r="AL27" s="113"/>
+      <c r="Y27" s="115"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="115"/>
+      <c r="AB27" s="114"/>
+      <c r="AC27" s="114"/>
+      <c r="AD27" s="114"/>
+      <c r="AE27" s="114"/>
+      <c r="AF27" s="114"/>
+      <c r="AG27" s="114"/>
+      <c r="AH27" s="114"/>
+      <c r="AI27" s="114"/>
+      <c r="AJ27" s="114"/>
+      <c r="AK27" s="114"/>
+      <c r="AL27" s="114"/>
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7"/>
@@ -6395,6 +6402,88 @@
     </row>
   </sheetData>
   <mergeCells count="98">
+    <mergeCell ref="AE8:AL8"/>
+    <mergeCell ref="AE9:AL9"/>
+    <mergeCell ref="AE10:AL10"/>
+    <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="X16:AA17"/>
+    <mergeCell ref="X18:AA18"/>
+    <mergeCell ref="X19:AA19"/>
+    <mergeCell ref="X20:AA20"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="X25:AA25"/>
+    <mergeCell ref="AB25:AE25"/>
+    <mergeCell ref="F13:S13"/>
+    <mergeCell ref="A6:E7"/>
+    <mergeCell ref="F6:L7"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="M6:AL6"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AL7"/>
+    <mergeCell ref="V10:AD10"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A16:G17"/>
+    <mergeCell ref="A18:G20"/>
+    <mergeCell ref="AB16:AL16"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AB18:AE18"/>
+    <mergeCell ref="AB19:AE19"/>
+    <mergeCell ref="AB20:AE20"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="H16:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="L16:W16"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="A23:G24"/>
+    <mergeCell ref="H23:K24"/>
+    <mergeCell ref="L23:W23"/>
+    <mergeCell ref="X23:AA24"/>
+    <mergeCell ref="AB23:AL23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="AB24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="AJ24:AL24"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:W26"/>
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="AF26:AI26"/>
@@ -6411,88 +6500,6 @@
     <mergeCell ref="AB26:AE26"/>
     <mergeCell ref="A25:G27"/>
     <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="A23:G24"/>
-    <mergeCell ref="H23:K24"/>
-    <mergeCell ref="L23:W23"/>
-    <mergeCell ref="X23:AA24"/>
-    <mergeCell ref="AB23:AL23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="AB24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="H16:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="L16:W16"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A16:G17"/>
-    <mergeCell ref="A18:G20"/>
-    <mergeCell ref="AB16:AL16"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AB18:AE18"/>
-    <mergeCell ref="AB19:AE19"/>
-    <mergeCell ref="AB20:AE20"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="A6:E7"/>
-    <mergeCell ref="F6:L7"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="M6:AL6"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="V7:AD7"/>
-    <mergeCell ref="AE7:AL7"/>
-    <mergeCell ref="V10:AD10"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="V8:AD8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V9:AD9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="AE8:AL8"/>
-    <mergeCell ref="AE9:AL9"/>
-    <mergeCell ref="AE10:AL10"/>
-    <mergeCell ref="F3:Q3"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="X16:AA17"/>
-    <mergeCell ref="X18:AA18"/>
-    <mergeCell ref="X19:AA19"/>
-    <mergeCell ref="X20:AA20"/>
-    <mergeCell ref="F8:L8"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="F10:L10"/>
-    <mergeCell ref="X25:AA25"/>
-    <mergeCell ref="AB25:AE25"/>
-    <mergeCell ref="F13:S13"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6532,32 +6539,32 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="119"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
@@ -6593,17 +6600,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="84"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
       <c r="N3" s="3"/>
@@ -6764,268 +6771,268 @@
       <c r="AL7" s="15"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="118" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="128" t="s">
+      <c r="A8" s="140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="117"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="128"/>
-      <c r="L8" s="128"/>
-      <c r="M8" s="128"/>
-      <c r="N8" s="128"/>
-      <c r="O8" s="128"/>
-      <c r="P8" s="128"/>
-      <c r="Q8" s="128"/>
-      <c r="R8" s="128"/>
-      <c r="S8" s="128"/>
-      <c r="T8" s="128"/>
-      <c r="U8" s="128"/>
-      <c r="V8" s="128"/>
-      <c r="W8" s="128"/>
-      <c r="X8" s="128"/>
-      <c r="Y8" s="128"/>
-      <c r="Z8" s="128"/>
-      <c r="AA8" s="128"/>
-      <c r="AB8" s="128"/>
-      <c r="AC8" s="128"/>
-      <c r="AD8" s="128"/>
-      <c r="AE8" s="128"/>
-      <c r="AF8" s="128"/>
-      <c r="AG8" s="128"/>
-      <c r="AH8" s="128"/>
-      <c r="AI8" s="118" t="s">
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
+      <c r="M8" s="131"/>
+      <c r="N8" s="131"/>
+      <c r="O8" s="131"/>
+      <c r="P8" s="131"/>
+      <c r="Q8" s="131"/>
+      <c r="R8" s="131"/>
+      <c r="S8" s="131"/>
+      <c r="T8" s="131"/>
+      <c r="U8" s="131"/>
+      <c r="V8" s="131"/>
+      <c r="W8" s="131"/>
+      <c r="X8" s="131"/>
+      <c r="Y8" s="131"/>
+      <c r="Z8" s="131"/>
+      <c r="AA8" s="131"/>
+      <c r="AB8" s="131"/>
+      <c r="AC8" s="131"/>
+      <c r="AD8" s="131"/>
+      <c r="AE8" s="131"/>
+      <c r="AF8" s="131"/>
+      <c r="AG8" s="131"/>
+      <c r="AH8" s="131"/>
+      <c r="AI8" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="AJ8" s="118"/>
-      <c r="AK8" s="118"/>
-      <c r="AL8" s="118"/>
+      <c r="AJ8" s="117"/>
+      <c r="AK8" s="117"/>
+      <c r="AL8" s="117"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="118"/>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="128" t="s">
+      <c r="A9" s="117"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="131" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="128"/>
-      <c r="L9" s="128"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="128" t="s">
+      <c r="K9" s="131"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="131"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="131" t="s">
         <v>80</v>
       </c>
-      <c r="P9" s="128"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="128"/>
-      <c r="S9" s="128"/>
-      <c r="T9" s="128" t="s">
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="131"/>
+      <c r="S9" s="131"/>
+      <c r="T9" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="U9" s="128"/>
-      <c r="V9" s="128"/>
-      <c r="W9" s="128"/>
-      <c r="X9" s="128"/>
-      <c r="Y9" s="128" t="s">
+      <c r="U9" s="131"/>
+      <c r="V9" s="131"/>
+      <c r="W9" s="131"/>
+      <c r="X9" s="131"/>
+      <c r="Y9" s="131" t="s">
         <v>82</v>
       </c>
-      <c r="Z9" s="128"/>
-      <c r="AA9" s="128"/>
-      <c r="AB9" s="128"/>
-      <c r="AC9" s="128"/>
-      <c r="AD9" s="128" t="s">
+      <c r="Z9" s="131"/>
+      <c r="AA9" s="131"/>
+      <c r="AB9" s="131"/>
+      <c r="AC9" s="131"/>
+      <c r="AD9" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="AE9" s="128"/>
-      <c r="AF9" s="128"/>
-      <c r="AG9" s="128"/>
-      <c r="AH9" s="128"/>
-      <c r="AI9" s="118"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="118"/>
-      <c r="AL9" s="118"/>
+      <c r="AE9" s="131"/>
+      <c r="AF9" s="131"/>
+      <c r="AG9" s="131"/>
+      <c r="AH9" s="131"/>
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="129" t="s">
+      <c r="A10" s="116"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
-      <c r="P10" s="128"/>
-      <c r="Q10" s="128"/>
-      <c r="R10" s="128"/>
-      <c r="S10" s="128"/>
-      <c r="T10" s="128"/>
-      <c r="U10" s="128"/>
-      <c r="V10" s="128"/>
-      <c r="W10" s="128"/>
-      <c r="X10" s="128"/>
-      <c r="Y10" s="128"/>
-      <c r="Z10" s="128"/>
-      <c r="AA10" s="128"/>
-      <c r="AB10" s="128"/>
-      <c r="AC10" s="128"/>
-      <c r="AD10" s="128"/>
-      <c r="AE10" s="128"/>
-      <c r="AF10" s="128"/>
-      <c r="AG10" s="128"/>
-      <c r="AH10" s="128"/>
-      <c r="AI10" s="118"/>
-      <c r="AJ10" s="118"/>
-      <c r="AK10" s="118"/>
-      <c r="AL10" s="118"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="131"/>
+      <c r="T10" s="131"/>
+      <c r="U10" s="131"/>
+      <c r="V10" s="131"/>
+      <c r="W10" s="131"/>
+      <c r="X10" s="131"/>
+      <c r="Y10" s="131"/>
+      <c r="Z10" s="131"/>
+      <c r="AA10" s="131"/>
+      <c r="AB10" s="131"/>
+      <c r="AC10" s="131"/>
+      <c r="AD10" s="131"/>
+      <c r="AE10" s="131"/>
+      <c r="AF10" s="131"/>
+      <c r="AG10" s="131"/>
+      <c r="AH10" s="131"/>
+      <c r="AI10" s="117"/>
+      <c r="AJ10" s="117"/>
+      <c r="AK10" s="117"/>
+      <c r="AL10" s="117"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="125"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="129" t="s">
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="128"/>
-      <c r="N11" s="128"/>
-      <c r="O11" s="128"/>
-      <c r="P11" s="128"/>
-      <c r="Q11" s="128"/>
-      <c r="R11" s="128"/>
-      <c r="S11" s="128"/>
-      <c r="T11" s="128"/>
-      <c r="U11" s="128"/>
-      <c r="V11" s="128"/>
-      <c r="W11" s="128"/>
-      <c r="X11" s="128"/>
-      <c r="Y11" s="128"/>
-      <c r="Z11" s="128"/>
-      <c r="AA11" s="128"/>
-      <c r="AB11" s="128"/>
-      <c r="AC11" s="128"/>
-      <c r="AD11" s="128"/>
-      <c r="AE11" s="128"/>
-      <c r="AF11" s="128"/>
-      <c r="AG11" s="128"/>
-      <c r="AH11" s="128"/>
-      <c r="AI11" s="118"/>
-      <c r="AJ11" s="118"/>
-      <c r="AK11" s="118"/>
-      <c r="AL11" s="118"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="131"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="131"/>
+      <c r="U11" s="131"/>
+      <c r="V11" s="131"/>
+      <c r="W11" s="131"/>
+      <c r="X11" s="131"/>
+      <c r="Y11" s="131"/>
+      <c r="Z11" s="131"/>
+      <c r="AA11" s="131"/>
+      <c r="AB11" s="131"/>
+      <c r="AC11" s="131"/>
+      <c r="AD11" s="131"/>
+      <c r="AE11" s="131"/>
+      <c r="AF11" s="131"/>
+      <c r="AG11" s="131"/>
+      <c r="AH11" s="131"/>
+      <c r="AI11" s="117"/>
+      <c r="AJ11" s="117"/>
+      <c r="AK11" s="117"/>
+      <c r="AL11" s="117"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="125"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="129" t="s">
+      <c r="A12" s="116"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="128"/>
-      <c r="O12" s="128"/>
-      <c r="P12" s="128"/>
-      <c r="Q12" s="128"/>
-      <c r="R12" s="128"/>
-      <c r="S12" s="128"/>
-      <c r="T12" s="128"/>
-      <c r="U12" s="128"/>
-      <c r="V12" s="128"/>
-      <c r="W12" s="128"/>
-      <c r="X12" s="128"/>
-      <c r="Y12" s="128"/>
-      <c r="Z12" s="128"/>
-      <c r="AA12" s="128"/>
-      <c r="AB12" s="128"/>
-      <c r="AC12" s="128"/>
-      <c r="AD12" s="128"/>
-      <c r="AE12" s="128"/>
-      <c r="AF12" s="128"/>
-      <c r="AG12" s="128"/>
-      <c r="AH12" s="128"/>
-      <c r="AI12" s="118"/>
-      <c r="AJ12" s="118"/>
-      <c r="AK12" s="118"/>
-      <c r="AL12" s="118"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="131"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="131"/>
+      <c r="Q12" s="131"/>
+      <c r="R12" s="131"/>
+      <c r="S12" s="131"/>
+      <c r="T12" s="131"/>
+      <c r="U12" s="131"/>
+      <c r="V12" s="131"/>
+      <c r="W12" s="131"/>
+      <c r="X12" s="131"/>
+      <c r="Y12" s="131"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="131"/>
+      <c r="AB12" s="131"/>
+      <c r="AC12" s="131"/>
+      <c r="AD12" s="131"/>
+      <c r="AE12" s="131"/>
+      <c r="AF12" s="131"/>
+      <c r="AG12" s="131"/>
+      <c r="AH12" s="131"/>
+      <c r="AI12" s="117"/>
+      <c r="AJ12" s="117"/>
+      <c r="AK12" s="117"/>
+      <c r="AL12" s="117"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="125"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="129" t="s">
+      <c r="A13" s="116"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="128"/>
-      <c r="U13" s="128"/>
-      <c r="V13" s="128"/>
-      <c r="W13" s="128"/>
-      <c r="X13" s="128"/>
-      <c r="Y13" s="128"/>
-      <c r="Z13" s="128"/>
-      <c r="AA13" s="128"/>
-      <c r="AB13" s="128"/>
-      <c r="AC13" s="128"/>
-      <c r="AD13" s="128"/>
-      <c r="AE13" s="128"/>
-      <c r="AF13" s="128"/>
-      <c r="AG13" s="128"/>
-      <c r="AH13" s="128"/>
-      <c r="AI13" s="118"/>
-      <c r="AJ13" s="118"/>
-      <c r="AK13" s="118"/>
-      <c r="AL13" s="118"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="131"/>
+      <c r="P13" s="131"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="131"/>
+      <c r="S13" s="131"/>
+      <c r="T13" s="131"/>
+      <c r="U13" s="131"/>
+      <c r="V13" s="131"/>
+      <c r="W13" s="131"/>
+      <c r="X13" s="131"/>
+      <c r="Y13" s="131"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="131"/>
+      <c r="AB13" s="131"/>
+      <c r="AC13" s="131"/>
+      <c r="AD13" s="131"/>
+      <c r="AE13" s="131"/>
+      <c r="AF13" s="131"/>
+      <c r="AG13" s="131"/>
+      <c r="AH13" s="131"/>
+      <c r="AI13" s="117"/>
+      <c r="AJ13" s="117"/>
+      <c r="AK13" s="117"/>
+      <c r="AL13" s="117"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="44"/>
@@ -7726,6 +7733,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A12:C13"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="AI13:AL13"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="J11:N11"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="D10:I10"/>
@@ -7742,30 +7773,6 @@
     <mergeCell ref="A8:I9"/>
     <mergeCell ref="A10:C11"/>
     <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="A12:C13"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="AI13:AL13"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="O12:S12"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7805,32 +7812,32 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="119"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
       <c r="AM1" s="56"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8051,360 +8058,360 @@
       <c r="AM7" s="17"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="117" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118"/>
-      <c r="K8" s="118"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="118"/>
-      <c r="N8" s="118"/>
-      <c r="O8" s="118"/>
-      <c r="P8" s="118" t="s">
+      <c r="B8" s="117"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="117"/>
+      <c r="O8" s="117"/>
+      <c r="P8" s="117" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="118"/>
-      <c r="R8" s="118"/>
-      <c r="S8" s="118"/>
-      <c r="T8" s="118"/>
-      <c r="U8" s="118"/>
-      <c r="V8" s="118"/>
-      <c r="W8" s="118"/>
-      <c r="X8" s="118"/>
-      <c r="Y8" s="118"/>
-      <c r="Z8" s="118"/>
-      <c r="AA8" s="118"/>
-      <c r="AB8" s="118"/>
-      <c r="AC8" s="118"/>
-      <c r="AD8" s="118"/>
-      <c r="AE8" s="118"/>
-      <c r="AF8" s="118"/>
-      <c r="AG8" s="118"/>
-      <c r="AH8" s="118"/>
-      <c r="AI8" s="118"/>
-      <c r="AJ8" s="118" t="s">
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
+      <c r="U8" s="117"/>
+      <c r="V8" s="117"/>
+      <c r="W8" s="117"/>
+      <c r="X8" s="117"/>
+      <c r="Y8" s="117"/>
+      <c r="Z8" s="117"/>
+      <c r="AA8" s="117"/>
+      <c r="AB8" s="117"/>
+      <c r="AC8" s="117"/>
+      <c r="AD8" s="117"/>
+      <c r="AE8" s="117"/>
+      <c r="AF8" s="117"/>
+      <c r="AG8" s="117"/>
+      <c r="AH8" s="117"/>
+      <c r="AI8" s="117"/>
+      <c r="AJ8" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="AK8" s="118"/>
-      <c r="AL8" s="118"/>
-      <c r="AM8" s="118"/>
+      <c r="AK8" s="117"/>
+      <c r="AL8" s="117"/>
+      <c r="AM8" s="117"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="118"/>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="118" t="s">
+      <c r="A9" s="117"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118" t="s">
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117"/>
+      <c r="S9" s="117"/>
+      <c r="T9" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118" t="s">
+      <c r="U9" s="117"/>
+      <c r="V9" s="117"/>
+      <c r="W9" s="117"/>
+      <c r="X9" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118"/>
-      <c r="AA9" s="118"/>
-      <c r="AB9" s="118" t="s">
+      <c r="Y9" s="117"/>
+      <c r="Z9" s="117"/>
+      <c r="AA9" s="117"/>
+      <c r="AB9" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AC9" s="118"/>
-      <c r="AD9" s="118"/>
-      <c r="AE9" s="118"/>
-      <c r="AF9" s="118" t="s">
+      <c r="AC9" s="117"/>
+      <c r="AD9" s="117"/>
+      <c r="AE9" s="117"/>
+      <c r="AF9" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="AG9" s="118"/>
-      <c r="AH9" s="118"/>
-      <c r="AI9" s="118"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="118"/>
-      <c r="AL9" s="118"/>
-      <c r="AM9" s="118"/>
+      <c r="AG9" s="117"/>
+      <c r="AH9" s="117"/>
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
+      <c r="AM9" s="117"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="118" t="s">
+      <c r="A10" s="116"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="118"/>
-      <c r="O10" s="118"/>
-      <c r="P10" s="118"/>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="118"/>
-      <c r="S10" s="118"/>
-      <c r="T10" s="118"/>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
-      <c r="W10" s="118"/>
-      <c r="X10" s="118"/>
-      <c r="Y10" s="118"/>
-      <c r="Z10" s="118"/>
-      <c r="AA10" s="118"/>
-      <c r="AB10" s="118"/>
-      <c r="AC10" s="118"/>
-      <c r="AD10" s="118"/>
-      <c r="AE10" s="118"/>
-      <c r="AF10" s="118"/>
-      <c r="AG10" s="118"/>
-      <c r="AH10" s="118"/>
-      <c r="AI10" s="118"/>
-      <c r="AJ10" s="118"/>
-      <c r="AK10" s="118"/>
-      <c r="AL10" s="118"/>
-      <c r="AM10" s="118"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="117"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="117"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="117"/>
+      <c r="S10" s="117"/>
+      <c r="T10" s="117"/>
+      <c r="U10" s="117"/>
+      <c r="V10" s="117"/>
+      <c r="W10" s="117"/>
+      <c r="X10" s="117"/>
+      <c r="Y10" s="117"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="117"/>
+      <c r="AB10" s="117"/>
+      <c r="AC10" s="117"/>
+      <c r="AD10" s="117"/>
+      <c r="AE10" s="117"/>
+      <c r="AF10" s="117"/>
+      <c r="AG10" s="117"/>
+      <c r="AH10" s="117"/>
+      <c r="AI10" s="117"/>
+      <c r="AJ10" s="117"/>
+      <c r="AK10" s="117"/>
+      <c r="AL10" s="117"/>
+      <c r="AM10" s="117"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="125"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="118" t="s">
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="118"/>
-      <c r="N11" s="118"/>
-      <c r="O11" s="118"/>
-      <c r="P11" s="118"/>
-      <c r="Q11" s="118"/>
-      <c r="R11" s="118"/>
-      <c r="S11" s="118"/>
-      <c r="T11" s="118"/>
-      <c r="U11" s="118"/>
-      <c r="V11" s="118"/>
-      <c r="W11" s="118"/>
-      <c r="X11" s="118"/>
-      <c r="Y11" s="118"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="118"/>
-      <c r="AB11" s="118"/>
-      <c r="AC11" s="118"/>
-      <c r="AD11" s="118"/>
-      <c r="AE11" s="118"/>
-      <c r="AF11" s="118"/>
-      <c r="AG11" s="118"/>
-      <c r="AH11" s="118"/>
-      <c r="AI11" s="118"/>
-      <c r="AJ11" s="118"/>
-      <c r="AK11" s="118"/>
-      <c r="AL11" s="118"/>
-      <c r="AM11" s="118"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="117"/>
+      <c r="O11" s="117"/>
+      <c r="P11" s="117"/>
+      <c r="Q11" s="117"/>
+      <c r="R11" s="117"/>
+      <c r="S11" s="117"/>
+      <c r="T11" s="117"/>
+      <c r="U11" s="117"/>
+      <c r="V11" s="117"/>
+      <c r="W11" s="117"/>
+      <c r="X11" s="117"/>
+      <c r="Y11" s="117"/>
+      <c r="Z11" s="117"/>
+      <c r="AA11" s="117"/>
+      <c r="AB11" s="117"/>
+      <c r="AC11" s="117"/>
+      <c r="AD11" s="117"/>
+      <c r="AE11" s="117"/>
+      <c r="AF11" s="117"/>
+      <c r="AG11" s="117"/>
+      <c r="AH11" s="117"/>
+      <c r="AI11" s="117"/>
+      <c r="AJ11" s="117"/>
+      <c r="AK11" s="117"/>
+      <c r="AL11" s="117"/>
+      <c r="AM11" s="117"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="125"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="118" t="s">
+      <c r="A12" s="116"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="118"/>
-      <c r="L12" s="118"/>
-      <c r="M12" s="118"/>
-      <c r="N12" s="118"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="118"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
-      <c r="S12" s="118"/>
-      <c r="T12" s="118"/>
-      <c r="U12" s="118"/>
-      <c r="V12" s="118"/>
-      <c r="W12" s="118"/>
-      <c r="X12" s="118"/>
-      <c r="Y12" s="118"/>
-      <c r="Z12" s="118"/>
-      <c r="AA12" s="118"/>
-      <c r="AB12" s="118"/>
-      <c r="AC12" s="118"/>
-      <c r="AD12" s="118"/>
-      <c r="AE12" s="118"/>
-      <c r="AF12" s="118"/>
-      <c r="AG12" s="118"/>
-      <c r="AH12" s="118"/>
-      <c r="AI12" s="118"/>
-      <c r="AJ12" s="118"/>
-      <c r="AK12" s="118"/>
-      <c r="AL12" s="118"/>
-      <c r="AM12" s="118"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="117"/>
+      <c r="O12" s="117"/>
+      <c r="P12" s="117"/>
+      <c r="Q12" s="117"/>
+      <c r="R12" s="117"/>
+      <c r="S12" s="117"/>
+      <c r="T12" s="117"/>
+      <c r="U12" s="117"/>
+      <c r="V12" s="117"/>
+      <c r="W12" s="117"/>
+      <c r="X12" s="117"/>
+      <c r="Y12" s="117"/>
+      <c r="Z12" s="117"/>
+      <c r="AA12" s="117"/>
+      <c r="AB12" s="117"/>
+      <c r="AC12" s="117"/>
+      <c r="AD12" s="117"/>
+      <c r="AE12" s="117"/>
+      <c r="AF12" s="117"/>
+      <c r="AG12" s="117"/>
+      <c r="AH12" s="117"/>
+      <c r="AI12" s="117"/>
+      <c r="AJ12" s="117"/>
+      <c r="AK12" s="117"/>
+      <c r="AL12" s="117"/>
+      <c r="AM12" s="117"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="125"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="118" t="s">
+      <c r="A13" s="116"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="118"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="118"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
-      <c r="U13" s="118"/>
-      <c r="V13" s="118"/>
-      <c r="W13" s="118"/>
-      <c r="X13" s="118"/>
-      <c r="Y13" s="118"/>
-      <c r="Z13" s="118"/>
-      <c r="AA13" s="118"/>
-      <c r="AB13" s="118"/>
-      <c r="AC13" s="118"/>
-      <c r="AD13" s="118"/>
-      <c r="AE13" s="118"/>
-      <c r="AF13" s="118"/>
-      <c r="AG13" s="118"/>
-      <c r="AH13" s="118"/>
-      <c r="AI13" s="118"/>
-      <c r="AJ13" s="118"/>
-      <c r="AK13" s="118"/>
-      <c r="AL13" s="118"/>
-      <c r="AM13" s="118"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
+      <c r="O13" s="117"/>
+      <c r="P13" s="117"/>
+      <c r="Q13" s="117"/>
+      <c r="R13" s="117"/>
+      <c r="S13" s="117"/>
+      <c r="T13" s="117"/>
+      <c r="U13" s="117"/>
+      <c r="V13" s="117"/>
+      <c r="W13" s="117"/>
+      <c r="X13" s="117"/>
+      <c r="Y13" s="117"/>
+      <c r="Z13" s="117"/>
+      <c r="AA13" s="117"/>
+      <c r="AB13" s="117"/>
+      <c r="AC13" s="117"/>
+      <c r="AD13" s="117"/>
+      <c r="AE13" s="117"/>
+      <c r="AF13" s="117"/>
+      <c r="AG13" s="117"/>
+      <c r="AH13" s="117"/>
+      <c r="AI13" s="117"/>
+      <c r="AJ13" s="117"/>
+      <c r="AK13" s="117"/>
+      <c r="AL13" s="117"/>
+      <c r="AM13" s="117"/>
     </row>
     <row r="14" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="125"/>
-      <c r="B14" s="125"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="118" t="s">
+      <c r="A14" s="116"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="118"/>
-      <c r="N14" s="118"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="118"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
-      <c r="U14" s="118"/>
-      <c r="V14" s="118"/>
-      <c r="W14" s="118"/>
-      <c r="X14" s="118"/>
-      <c r="Y14" s="118"/>
-      <c r="Z14" s="118"/>
-      <c r="AA14" s="118"/>
-      <c r="AB14" s="118"/>
-      <c r="AC14" s="118"/>
-      <c r="AD14" s="118"/>
-      <c r="AE14" s="118"/>
-      <c r="AF14" s="118"/>
-      <c r="AG14" s="118"/>
-      <c r="AH14" s="118"/>
-      <c r="AI14" s="118"/>
-      <c r="AJ14" s="118"/>
-      <c r="AK14" s="118"/>
-      <c r="AL14" s="118"/>
-      <c r="AM14" s="118"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="117"/>
+      <c r="O14" s="117"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="117"/>
+      <c r="R14" s="117"/>
+      <c r="S14" s="117"/>
+      <c r="T14" s="117"/>
+      <c r="U14" s="117"/>
+      <c r="V14" s="117"/>
+      <c r="W14" s="117"/>
+      <c r="X14" s="117"/>
+      <c r="Y14" s="117"/>
+      <c r="Z14" s="117"/>
+      <c r="AA14" s="117"/>
+      <c r="AB14" s="117"/>
+      <c r="AC14" s="117"/>
+      <c r="AD14" s="117"/>
+      <c r="AE14" s="117"/>
+      <c r="AF14" s="117"/>
+      <c r="AG14" s="117"/>
+      <c r="AH14" s="117"/>
+      <c r="AI14" s="117"/>
+      <c r="AJ14" s="117"/>
+      <c r="AK14" s="117"/>
+      <c r="AL14" s="117"/>
+      <c r="AM14" s="117"/>
     </row>
     <row r="15" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="125"/>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="118" t="s">
+      <c r="A15" s="116"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
-      <c r="M15" s="118"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
-      <c r="U15" s="118"/>
-      <c r="V15" s="118"/>
-      <c r="W15" s="118"/>
-      <c r="X15" s="118"/>
-      <c r="Y15" s="118"/>
-      <c r="Z15" s="118"/>
-      <c r="AA15" s="118"/>
-      <c r="AB15" s="118"/>
-      <c r="AC15" s="118"/>
-      <c r="AD15" s="118"/>
-      <c r="AE15" s="118"/>
-      <c r="AF15" s="118"/>
-      <c r="AG15" s="118"/>
-      <c r="AH15" s="118"/>
-      <c r="AI15" s="118"/>
-      <c r="AJ15" s="118"/>
-      <c r="AK15" s="118"/>
-      <c r="AL15" s="118"/>
-      <c r="AM15" s="118"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="117"/>
+      <c r="V15" s="117"/>
+      <c r="W15" s="117"/>
+      <c r="X15" s="117"/>
+      <c r="Y15" s="117"/>
+      <c r="Z15" s="117"/>
+      <c r="AA15" s="117"/>
+      <c r="AB15" s="117"/>
+      <c r="AC15" s="117"/>
+      <c r="AD15" s="117"/>
+      <c r="AE15" s="117"/>
+      <c r="AF15" s="117"/>
+      <c r="AG15" s="117"/>
+      <c r="AH15" s="117"/>
+      <c r="AI15" s="117"/>
+      <c r="AJ15" s="117"/>
+      <c r="AK15" s="117"/>
+      <c r="AL15" s="117"/>
+      <c r="AM15" s="117"/>
     </row>
     <row r="16" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
@@ -8983,45 +8990,6 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A8:O9"/>
-    <mergeCell ref="P8:AI8"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ8:AM9"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="AJ11:AM11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="F11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:W11"/>
-    <mergeCell ref="X11:AA11"/>
-    <mergeCell ref="AB11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:W12"/>
-    <mergeCell ref="X12:AA12"/>
-    <mergeCell ref="AB13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="AB12:AE12"/>
-    <mergeCell ref="AJ12:AM12"/>
-    <mergeCell ref="AJ13:AM13"/>
-    <mergeCell ref="A14:E15"/>
-    <mergeCell ref="F14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="X14:AA14"/>
     <mergeCell ref="AJ14:AM14"/>
     <mergeCell ref="AJ15:AM15"/>
     <mergeCell ref="F3:R3"/>
@@ -9038,6 +9006,45 @@
     <mergeCell ref="P13:S13"/>
     <mergeCell ref="T13:W13"/>
     <mergeCell ref="X13:AA13"/>
+    <mergeCell ref="A14:E15"/>
+    <mergeCell ref="F14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X14:AA14"/>
+    <mergeCell ref="AB13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="AB12:AE12"/>
+    <mergeCell ref="AJ12:AM12"/>
+    <mergeCell ref="AJ13:AM13"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:O12"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="T12:W12"/>
+    <mergeCell ref="X12:AA12"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="AJ11:AM11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="F11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:W11"/>
+    <mergeCell ref="X11:AA11"/>
+    <mergeCell ref="AB11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A8:O9"/>
+    <mergeCell ref="P8:AI8"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ8:AM9"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9108,16 +9115,16 @@
       <c r="AL1" s="135"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="136" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -9356,85 +9363,85 @@
       <c r="AL7" s="3"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="133"/>
-      <c r="K8" s="133"/>
-      <c r="L8" s="133"/>
-      <c r="M8" s="133"/>
-      <c r="N8" s="133"/>
-      <c r="O8" s="133"/>
-      <c r="P8" s="133"/>
-      <c r="Q8" s="133"/>
-      <c r="R8" s="133"/>
-      <c r="S8" s="133"/>
-      <c r="T8" s="133"/>
-      <c r="U8" s="133"/>
-      <c r="V8" s="133"/>
-      <c r="W8" s="133"/>
-      <c r="X8" s="133"/>
-      <c r="Y8" s="133"/>
-      <c r="Z8" s="133"/>
-      <c r="AA8" s="133"/>
-      <c r="AB8" s="133"/>
-      <c r="AC8" s="133"/>
-      <c r="AD8" s="133"/>
-      <c r="AE8" s="133"/>
-      <c r="AF8" s="133"/>
-      <c r="AG8" s="133"/>
-      <c r="AH8" s="133"/>
-      <c r="AI8" s="133"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="138"/>
+      <c r="K8" s="138"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="138"/>
+      <c r="N8" s="138"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="138"/>
+      <c r="Q8" s="138"/>
+      <c r="R8" s="138"/>
+      <c r="S8" s="138"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="138"/>
+      <c r="W8" s="138"/>
+      <c r="X8" s="138"/>
+      <c r="Y8" s="138"/>
+      <c r="Z8" s="138"/>
+      <c r="AA8" s="138"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="138"/>
+      <c r="AD8" s="138"/>
+      <c r="AE8" s="138"/>
+      <c r="AF8" s="138"/>
+      <c r="AG8" s="138"/>
+      <c r="AH8" s="138"/>
+      <c r="AI8" s="138"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="134" t="s">
+      <c r="A9" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="134"/>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
-      <c r="L9" s="113"/>
-      <c r="M9" s="113"/>
-      <c r="N9" s="113"/>
-      <c r="O9" s="113"/>
-      <c r="P9" s="113"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="113"/>
-      <c r="S9" s="113"/>
-      <c r="T9" s="113"/>
-      <c r="U9" s="113"/>
-      <c r="V9" s="113"/>
-      <c r="W9" s="113"/>
-      <c r="X9" s="113"/>
-      <c r="Y9" s="113"/>
-      <c r="Z9" s="113"/>
-      <c r="AA9" s="113"/>
-      <c r="AB9" s="113"/>
-      <c r="AC9" s="113"/>
-      <c r="AD9" s="113"/>
-      <c r="AE9" s="113"/>
-      <c r="AF9" s="113"/>
-      <c r="AG9" s="113"/>
-      <c r="AH9" s="113"/>
-      <c r="AI9" s="113"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="114"/>
+      <c r="M9" s="114"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="114"/>
+      <c r="Q9" s="114"/>
+      <c r="R9" s="114"/>
+      <c r="S9" s="114"/>
+      <c r="T9" s="114"/>
+      <c r="U9" s="114"/>
+      <c r="V9" s="114"/>
+      <c r="W9" s="114"/>
+      <c r="X9" s="114"/>
+      <c r="Y9" s="114"/>
+      <c r="Z9" s="114"/>
+      <c r="AA9" s="114"/>
+      <c r="AB9" s="114"/>
+      <c r="AC9" s="114"/>
+      <c r="AD9" s="114"/>
+      <c r="AE9" s="114"/>
+      <c r="AF9" s="114"/>
+      <c r="AG9" s="114"/>
+      <c r="AH9" s="114"/>
+      <c r="AI9" s="114"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
@@ -10031,20 +10038,20 @@
       <c r="G24" s="59"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="138"/>
-      <c r="L24" s="138"/>
-      <c r="M24" s="138"/>
-      <c r="N24" s="138"/>
-      <c r="O24" s="138"/>
-      <c r="P24" s="138"/>
-      <c r="Q24" s="138"/>
-      <c r="R24" s="138"/>
-      <c r="S24" s="138"/>
-      <c r="T24" s="138"/>
-      <c r="U24" s="138"/>
-      <c r="V24" s="138"/>
-      <c r="W24" s="138"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="134"/>
+      <c r="N24" s="134"/>
+      <c r="O24" s="134"/>
+      <c r="P24" s="134"/>
+      <c r="Q24" s="134"/>
+      <c r="R24" s="134"/>
+      <c r="S24" s="134"/>
+      <c r="T24" s="134"/>
+      <c r="U24" s="134"/>
+      <c r="V24" s="134"/>
+      <c r="W24" s="134"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
@@ -10089,8 +10096,8 @@
       <c r="A26" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
       <c r="E26" s="59" t="s">
         <v>132</v>
       </c>
@@ -10156,250 +10163,250 @@
       <c r="AK27" s="58"/>
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="139" t="s">
+      <c r="A28" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="139"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="125"/>
-      <c r="L28" s="125"/>
-      <c r="M28" s="125"/>
-      <c r="N28" s="125"/>
-      <c r="O28" s="125"/>
-      <c r="P28" s="125"/>
-      <c r="Q28" s="125"/>
-      <c r="R28" s="125"/>
-      <c r="S28" s="125"/>
-      <c r="T28" s="125"/>
-      <c r="U28" s="125"/>
-      <c r="V28" s="125"/>
-      <c r="W28" s="125"/>
-      <c r="X28" s="125"/>
-      <c r="Y28" s="125"/>
-      <c r="Z28" s="125"/>
-      <c r="AA28" s="125"/>
-      <c r="AB28" s="125"/>
-      <c r="AC28" s="125"/>
-      <c r="AD28" s="125"/>
-      <c r="AE28" s="125"/>
-      <c r="AF28" s="125"/>
-      <c r="AG28" s="125"/>
-      <c r="AH28" s="125"/>
-      <c r="AI28" s="125"/>
-      <c r="AJ28" s="125"/>
-      <c r="AK28" s="125"/>
-      <c r="AL28" s="125"/>
+      <c r="B28" s="133"/>
+      <c r="C28" s="133"/>
+      <c r="D28" s="133"/>
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="116"/>
+      <c r="N28" s="116"/>
+      <c r="O28" s="116"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="116"/>
+      <c r="S28" s="116"/>
+      <c r="T28" s="116"/>
+      <c r="U28" s="116"/>
+      <c r="V28" s="116"/>
+      <c r="W28" s="116"/>
+      <c r="X28" s="116"/>
+      <c r="Y28" s="116"/>
+      <c r="Z28" s="116"/>
+      <c r="AA28" s="116"/>
+      <c r="AB28" s="116"/>
+      <c r="AC28" s="116"/>
+      <c r="AD28" s="116"/>
+      <c r="AE28" s="116"/>
+      <c r="AF28" s="116"/>
+      <c r="AG28" s="116"/>
+      <c r="AH28" s="116"/>
+      <c r="AI28" s="116"/>
+      <c r="AJ28" s="116"/>
+      <c r="AK28" s="116"/>
+      <c r="AL28" s="116"/>
     </row>
     <row r="29" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="139"/>
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="139"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="125"/>
-      <c r="L29" s="125"/>
-      <c r="M29" s="125"/>
-      <c r="N29" s="125"/>
-      <c r="O29" s="125"/>
-      <c r="P29" s="125"/>
-      <c r="Q29" s="125"/>
-      <c r="R29" s="125"/>
-      <c r="S29" s="125"/>
-      <c r="T29" s="125"/>
-      <c r="U29" s="125"/>
-      <c r="V29" s="125"/>
-      <c r="W29" s="125"/>
-      <c r="X29" s="125"/>
-      <c r="Y29" s="125"/>
-      <c r="Z29" s="125"/>
-      <c r="AA29" s="125"/>
-      <c r="AB29" s="125"/>
-      <c r="AC29" s="125"/>
-      <c r="AD29" s="125"/>
-      <c r="AE29" s="125"/>
-      <c r="AF29" s="125"/>
-      <c r="AG29" s="125"/>
-      <c r="AH29" s="125"/>
-      <c r="AI29" s="125"/>
-      <c r="AJ29" s="125"/>
-      <c r="AK29" s="125"/>
-      <c r="AL29" s="125"/>
+      <c r="A29" s="133"/>
+      <c r="B29" s="133"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="133"/>
+      <c r="I29" s="133"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="116"/>
+      <c r="L29" s="116"/>
+      <c r="M29" s="116"/>
+      <c r="N29" s="116"/>
+      <c r="O29" s="116"/>
+      <c r="P29" s="116"/>
+      <c r="Q29" s="116"/>
+      <c r="R29" s="116"/>
+      <c r="S29" s="116"/>
+      <c r="T29" s="116"/>
+      <c r="U29" s="116"/>
+      <c r="V29" s="116"/>
+      <c r="W29" s="116"/>
+      <c r="X29" s="116"/>
+      <c r="Y29" s="116"/>
+      <c r="Z29" s="116"/>
+      <c r="AA29" s="116"/>
+      <c r="AB29" s="116"/>
+      <c r="AC29" s="116"/>
+      <c r="AD29" s="116"/>
+      <c r="AE29" s="116"/>
+      <c r="AF29" s="116"/>
+      <c r="AG29" s="116"/>
+      <c r="AH29" s="116"/>
+      <c r="AI29" s="116"/>
+      <c r="AJ29" s="116"/>
+      <c r="AK29" s="116"/>
+      <c r="AL29" s="116"/>
     </row>
     <row r="30" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="139" t="s">
+      <c r="A30" s="133" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="139"/>
-      <c r="C30" s="139"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="139"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="139"/>
-      <c r="L30" s="139"/>
-      <c r="M30" s="139"/>
-      <c r="N30" s="139"/>
-      <c r="O30" s="139"/>
-      <c r="P30" s="139"/>
-      <c r="Q30" s="139"/>
-      <c r="R30" s="139"/>
-      <c r="S30" s="139"/>
-      <c r="T30" s="139"/>
-      <c r="U30" s="139"/>
-      <c r="V30" s="139"/>
-      <c r="W30" s="139"/>
-      <c r="X30" s="139"/>
-      <c r="Y30" s="139"/>
-      <c r="Z30" s="139"/>
-      <c r="AA30" s="139"/>
-      <c r="AB30" s="139"/>
-      <c r="AC30" s="139"/>
-      <c r="AD30" s="139"/>
-      <c r="AE30" s="139"/>
-      <c r="AF30" s="139"/>
-      <c r="AG30" s="139"/>
-      <c r="AH30" s="139"/>
-      <c r="AI30" s="139"/>
-      <c r="AJ30" s="139"/>
-      <c r="AK30" s="139"/>
-      <c r="AL30" s="139"/>
+      <c r="B30" s="133"/>
+      <c r="C30" s="133"/>
+      <c r="D30" s="133"/>
+      <c r="E30" s="133"/>
+      <c r="F30" s="133"/>
+      <c r="G30" s="133"/>
+      <c r="H30" s="133"/>
+      <c r="I30" s="133"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="133"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="133"/>
+      <c r="N30" s="133"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="133"/>
+      <c r="Q30" s="133"/>
+      <c r="R30" s="133"/>
+      <c r="S30" s="133"/>
+      <c r="T30" s="133"/>
+      <c r="U30" s="133"/>
+      <c r="V30" s="133"/>
+      <c r="W30" s="133"/>
+      <c r="X30" s="133"/>
+      <c r="Y30" s="133"/>
+      <c r="Z30" s="133"/>
+      <c r="AA30" s="133"/>
+      <c r="AB30" s="133"/>
+      <c r="AC30" s="133"/>
+      <c r="AD30" s="133"/>
+      <c r="AE30" s="133"/>
+      <c r="AF30" s="133"/>
+      <c r="AG30" s="133"/>
+      <c r="AH30" s="133"/>
+      <c r="AI30" s="133"/>
+      <c r="AJ30" s="133"/>
+      <c r="AK30" s="133"/>
+      <c r="AL30" s="133"/>
     </row>
     <row r="31" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="139"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
-      <c r="J31" s="139"/>
-      <c r="K31" s="139"/>
-      <c r="L31" s="139"/>
-      <c r="M31" s="139"/>
-      <c r="N31" s="139"/>
-      <c r="O31" s="139"/>
-      <c r="P31" s="139"/>
-      <c r="Q31" s="139"/>
-      <c r="R31" s="139"/>
-      <c r="S31" s="139"/>
-      <c r="T31" s="139"/>
-      <c r="U31" s="139"/>
-      <c r="V31" s="139"/>
-      <c r="W31" s="139"/>
-      <c r="X31" s="139"/>
-      <c r="Y31" s="139"/>
-      <c r="Z31" s="139"/>
-      <c r="AA31" s="139"/>
-      <c r="AB31" s="139"/>
-      <c r="AC31" s="139"/>
-      <c r="AD31" s="139"/>
-      <c r="AE31" s="139"/>
-      <c r="AF31" s="139"/>
-      <c r="AG31" s="139"/>
-      <c r="AH31" s="139"/>
-      <c r="AI31" s="139"/>
-      <c r="AJ31" s="139"/>
-      <c r="AK31" s="139"/>
-      <c r="AL31" s="139"/>
+      <c r="A31" s="133"/>
+      <c r="B31" s="133"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="133"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="133"/>
+      <c r="G31" s="133"/>
+      <c r="H31" s="133"/>
+      <c r="I31" s="133"/>
+      <c r="J31" s="133"/>
+      <c r="K31" s="133"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="133"/>
+      <c r="N31" s="133"/>
+      <c r="O31" s="133"/>
+      <c r="P31" s="133"/>
+      <c r="Q31" s="133"/>
+      <c r="R31" s="133"/>
+      <c r="S31" s="133"/>
+      <c r="T31" s="133"/>
+      <c r="U31" s="133"/>
+      <c r="V31" s="133"/>
+      <c r="W31" s="133"/>
+      <c r="X31" s="133"/>
+      <c r="Y31" s="133"/>
+      <c r="Z31" s="133"/>
+      <c r="AA31" s="133"/>
+      <c r="AB31" s="133"/>
+      <c r="AC31" s="133"/>
+      <c r="AD31" s="133"/>
+      <c r="AE31" s="133"/>
+      <c r="AF31" s="133"/>
+      <c r="AG31" s="133"/>
+      <c r="AH31" s="133"/>
+      <c r="AI31" s="133"/>
+      <c r="AJ31" s="133"/>
+      <c r="AK31" s="133"/>
+      <c r="AL31" s="133"/>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="139"/>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="139"/>
-      <c r="L32" s="139"/>
-      <c r="M32" s="139"/>
-      <c r="N32" s="139"/>
-      <c r="O32" s="139"/>
-      <c r="P32" s="139"/>
-      <c r="Q32" s="139"/>
-      <c r="R32" s="139"/>
-      <c r="S32" s="139"/>
-      <c r="T32" s="139"/>
-      <c r="U32" s="139"/>
-      <c r="V32" s="139"/>
-      <c r="W32" s="139"/>
-      <c r="X32" s="139"/>
-      <c r="Y32" s="139"/>
-      <c r="Z32" s="139"/>
-      <c r="AA32" s="139"/>
-      <c r="AB32" s="139"/>
-      <c r="AC32" s="139"/>
-      <c r="AD32" s="139"/>
-      <c r="AE32" s="139"/>
-      <c r="AF32" s="139"/>
-      <c r="AG32" s="139"/>
-      <c r="AH32" s="139"/>
-      <c r="AI32" s="139"/>
-      <c r="AJ32" s="139"/>
-      <c r="AK32" s="139"/>
-      <c r="AL32" s="139"/>
+      <c r="B32" s="133"/>
+      <c r="C32" s="133"/>
+      <c r="D32" s="133"/>
+      <c r="E32" s="133"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="133"/>
+      <c r="H32" s="133"/>
+      <c r="I32" s="133"/>
+      <c r="J32" s="133"/>
+      <c r="K32" s="133"/>
+      <c r="L32" s="133"/>
+      <c r="M32" s="133"/>
+      <c r="N32" s="133"/>
+      <c r="O32" s="133"/>
+      <c r="P32" s="133"/>
+      <c r="Q32" s="133"/>
+      <c r="R32" s="133"/>
+      <c r="S32" s="133"/>
+      <c r="T32" s="133"/>
+      <c r="U32" s="133"/>
+      <c r="V32" s="133"/>
+      <c r="W32" s="133"/>
+      <c r="X32" s="133"/>
+      <c r="Y32" s="133"/>
+      <c r="Z32" s="133"/>
+      <c r="AA32" s="133"/>
+      <c r="AB32" s="133"/>
+      <c r="AC32" s="133"/>
+      <c r="AD32" s="133"/>
+      <c r="AE32" s="133"/>
+      <c r="AF32" s="133"/>
+      <c r="AG32" s="133"/>
+      <c r="AH32" s="133"/>
+      <c r="AI32" s="133"/>
+      <c r="AJ32" s="133"/>
+      <c r="AK32" s="133"/>
+      <c r="AL32" s="133"/>
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A33" s="139"/>
-      <c r="B33" s="139"/>
-      <c r="C33" s="139"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="139"/>
-      <c r="K33" s="139"/>
-      <c r="L33" s="139"/>
-      <c r="M33" s="139"/>
-      <c r="N33" s="139"/>
-      <c r="O33" s="139"/>
-      <c r="P33" s="139"/>
-      <c r="Q33" s="139"/>
-      <c r="R33" s="139"/>
-      <c r="S33" s="139"/>
-      <c r="T33" s="139"/>
-      <c r="U33" s="139"/>
-      <c r="V33" s="139"/>
-      <c r="W33" s="139"/>
-      <c r="X33" s="139"/>
-      <c r="Y33" s="139"/>
-      <c r="Z33" s="139"/>
-      <c r="AA33" s="139"/>
-      <c r="AB33" s="139"/>
-      <c r="AC33" s="139"/>
-      <c r="AD33" s="139"/>
-      <c r="AE33" s="139"/>
-      <c r="AF33" s="139"/>
-      <c r="AG33" s="139"/>
-      <c r="AH33" s="139"/>
-      <c r="AI33" s="139"/>
-      <c r="AJ33" s="139"/>
-      <c r="AK33" s="139"/>
-      <c r="AL33" s="139"/>
+      <c r="A33" s="133"/>
+      <c r="B33" s="133"/>
+      <c r="C33" s="133"/>
+      <c r="D33" s="133"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="133"/>
+      <c r="I33" s="133"/>
+      <c r="J33" s="133"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
+      <c r="M33" s="133"/>
+      <c r="N33" s="133"/>
+      <c r="O33" s="133"/>
+      <c r="P33" s="133"/>
+      <c r="Q33" s="133"/>
+      <c r="R33" s="133"/>
+      <c r="S33" s="133"/>
+      <c r="T33" s="133"/>
+      <c r="U33" s="133"/>
+      <c r="V33" s="133"/>
+      <c r="W33" s="133"/>
+      <c r="X33" s="133"/>
+      <c r="Y33" s="133"/>
+      <c r="Z33" s="133"/>
+      <c r="AA33" s="133"/>
+      <c r="AB33" s="133"/>
+      <c r="AC33" s="133"/>
+      <c r="AD33" s="133"/>
+      <c r="AE33" s="133"/>
+      <c r="AF33" s="133"/>
+      <c r="AG33" s="133"/>
+      <c r="AH33" s="133"/>
+      <c r="AI33" s="133"/>
+      <c r="AJ33" s="133"/>
+      <c r="AK33" s="133"/>
+      <c r="AL33" s="133"/>
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" s="59"/>
@@ -10766,11 +10773,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A32:J33"/>
-    <mergeCell ref="K32:Q33"/>
-    <mergeCell ref="R32:X33"/>
-    <mergeCell ref="Y32:AE33"/>
-    <mergeCell ref="AF32:AL33"/>
+    <mergeCell ref="AC8:AI8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="V9:AB9"/>
+    <mergeCell ref="AC9:AI9"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:U8"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="J24:W24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A28:J29"/>
+    <mergeCell ref="K28:Q29"/>
+    <mergeCell ref="R28:X29"/>
     <mergeCell ref="Y28:AE29"/>
     <mergeCell ref="AF28:AL29"/>
     <mergeCell ref="A30:J31"/>
@@ -10778,27 +10801,11 @@
     <mergeCell ref="R30:X31"/>
     <mergeCell ref="Y30:AE31"/>
     <mergeCell ref="AF30:AL31"/>
-    <mergeCell ref="J24:W24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A28:J29"/>
-    <mergeCell ref="K28:Q29"/>
-    <mergeCell ref="R28:X29"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:U8"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="AC8:AI8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="V9:AB9"/>
-    <mergeCell ref="AC9:AI9"/>
+    <mergeCell ref="A32:J33"/>
+    <mergeCell ref="K32:Q33"/>
+    <mergeCell ref="R32:X33"/>
+    <mergeCell ref="Y32:AE33"/>
+    <mergeCell ref="AF32:AL33"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27B1693-4A93-4988-94D1-C228425ABD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919BBC50-4755-4954-9940-827955AA76E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -462,9 +462,6 @@
     <t>seam // weft</t>
   </si>
   <si>
-    <t>Sample  Unit(N)</t>
-  </si>
-  <si>
     <t># 1</t>
   </si>
   <si>
@@ -541,12 +538,6 @@
   </si>
   <si>
     <t>Elmendorf:</t>
-  </si>
-  <si>
-    <t>Warp /Length yarns torn (N)</t>
-  </si>
-  <si>
-    <t>Weft / Width yarns torn (N)</t>
   </si>
   <si>
     <t xml:space="preserve">Warp/Length yarns torn </t>
@@ -735,8 +726,20 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
+    <t>Sample  Unit(N)</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
     <t>Sample  Unit(gf)</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warp /Length yarns torn (gf)</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weft / Width yarns torn (gf)</t>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -996,6 +999,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1174,7 +1178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1320,6 +1324,60 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1329,59 +1387,8 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1401,6 +1408,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1428,80 +1462,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1512,33 +1519,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1818,12 +1825,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="28" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1832,27 +1839,27 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="70"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="70"/>
-      <c r="AB1" s="70"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1881,15 +1888,15 @@
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="84"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -1911,7 +1918,7 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
-    <row r="4" spans="1:28" ht="16.75" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -1940,7 +1947,7 @@
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
@@ -1969,7 +1976,7 @@
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
@@ -1998,7 +2005,7 @@
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>4</v>
       </c>
@@ -2027,7 +2034,7 @@
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -2054,7 +2061,7 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
     </row>
-    <row r="9" spans="1:28" ht="16.75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
@@ -2085,87 +2092,87 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
     </row>
-    <row r="10" spans="1:28" ht="16.75" x14ac:dyDescent="0.35">
-      <c r="A10" s="79" t="s">
+    <row r="10" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="71" t="s">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="73" t="s">
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="69"/>
+      <c r="T10" s="69"/>
+      <c r="U10" s="69"/>
+      <c r="V10" s="69"/>
+      <c r="W10" s="69"/>
+      <c r="X10" s="69"/>
+      <c r="Y10" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="74"/>
-      <c r="AA10" s="74"/>
-      <c r="AB10" s="75"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="71" t="s">
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="71"/>
+      <c r="AB10" s="72"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="79"/>
+      <c r="B11" s="80"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="71" t="s">
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="71" t="s">
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="71" t="s">
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="85"/>
-      <c r="U11" s="71" t="s">
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="86"/>
-      <c r="Y11" s="76"/>
-      <c r="Z11" s="77"/>
-      <c r="AA11" s="77"/>
-      <c r="AB11" s="78"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A12" s="67"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
+      <c r="V11" s="69"/>
+      <c r="W11" s="69"/>
+      <c r="X11" s="83"/>
+      <c r="Y11" s="73"/>
+      <c r="Z11" s="74"/>
+      <c r="AA11" s="74"/>
+      <c r="AB11" s="75"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="85"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="87"/>
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2191,11 +2198,11 @@
       <c r="AA12" s="4"/>
       <c r="AB12" s="2"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A13" s="67"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="85"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="87"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -2221,11 +2228,11 @@
       <c r="AA13" s="4"/>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A14" s="67"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="69"/>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="85"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2251,11 +2258,11 @@
       <c r="AA14" s="4"/>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A15" s="67"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="85"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="87"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2281,11 +2288,11 @@
       <c r="AA15" s="4"/>
       <c r="AB15" s="2"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A16" s="67"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="85"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="87"/>
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -2311,7 +2318,7 @@
       <c r="AA16" s="4"/>
       <c r="AB16" s="2"/>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>16</v>
       </c>
@@ -2340,7 +2347,7 @@
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2367,7 +2374,7 @@
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>17</v>
       </c>
@@ -2396,7 +2403,7 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2423,7 +2430,7 @@
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2452,6 +2459,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="E10:X10"/>
     <mergeCell ref="Y10:AB11"/>
@@ -2462,11 +2474,6 @@
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2486,16 +2493,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD6E72E-6B16-4A5A-8E3F-434228BD81B4}">
   <dimension ref="A1:AL48"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" style="22" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" style="22" customWidth="1"/>
     <col min="8" max="8" width="2" style="22" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" style="22" customWidth="1"/>
-    <col min="32" max="38" width="2.35546875" style="22" customWidth="1"/>
-    <col min="39" max="16384" width="8.85546875" style="22"/>
+    <col min="9" max="31" width="2.109375" style="22" customWidth="1"/>
+    <col min="32" max="38" width="2.33203125" style="22" customWidth="1"/>
+    <col min="39" max="16384" width="8.88671875" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -2507,34 +2514,34 @@
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="103"/>
-      <c r="AH1" s="103"/>
-      <c r="AI1" s="103"/>
-      <c r="AJ1" s="103"/>
-      <c r="AK1" s="103"/>
-      <c r="AL1" s="103"/>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="88"/>
+      <c r="AA1" s="88"/>
+      <c r="AB1" s="88"/>
+      <c r="AC1" s="88"/>
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="88"/>
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
+      <c r="AI1" s="88"/>
+      <c r="AJ1" s="88"/>
+      <c r="AK1" s="88"/>
+      <c r="AL1" s="88"/>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
         <v>19</v>
       </c>
@@ -2567,18 +2574,18 @@
       <c r="AE2" s="21"/>
       <c r="AF2" s="21"/>
     </row>
-    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="112"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
+    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="103"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -2601,7 +2608,7 @@
       <c r="AE3" s="21"/>
       <c r="AF3" s="21"/>
     </row>
-    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
@@ -2632,7 +2639,7 @@
       <c r="AE4" s="21"/>
       <c r="AF4" s="21"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
         <v>20</v>
       </c>
@@ -2664,7 +2671,7 @@
       <c r="AF5" s="21"/>
       <c r="AK5" s="21"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>21</v>
       </c>
@@ -2696,7 +2703,7 @@
       <c r="AF6" s="21"/>
       <c r="AK6" s="21"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -2726,7 +2733,7 @@
       <c r="AF7" s="21"/>
       <c r="AK7" s="21"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>22</v>
       </c>
@@ -2758,7 +2765,7 @@
       <c r="AF8" s="21"/>
       <c r="AK8" s="21"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="21"/>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
@@ -2789,53 +2796,53 @@
       <c r="AE9" s="21"/>
       <c r="AF9" s="21"/>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="104" t="s">
+      <c r="D10" s="101"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="105"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="104" t="s">
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="Q10" s="105"/>
-      <c r="R10" s="105"/>
-      <c r="S10" s="105"/>
-      <c r="T10" s="105"/>
-      <c r="U10" s="105"/>
-      <c r="V10" s="105"/>
-      <c r="W10" s="105"/>
-      <c r="X10" s="105"/>
-      <c r="Y10" s="105"/>
-      <c r="Z10" s="105"/>
-      <c r="AA10" s="105"/>
-      <c r="AB10" s="105"/>
-      <c r="AC10" s="105"/>
-      <c r="AD10" s="105"/>
-      <c r="AE10" s="105"/>
-      <c r="AF10" s="105"/>
-      <c r="AG10" s="105"/>
-      <c r="AH10" s="105"/>
-      <c r="AI10" s="105"/>
-      <c r="AJ10" s="105"/>
-      <c r="AK10" s="105"/>
-      <c r="AL10" s="106"/>
-    </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="Q10" s="96"/>
+      <c r="R10" s="96"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="96"/>
+      <c r="V10" s="96"/>
+      <c r="W10" s="96"/>
+      <c r="X10" s="96"/>
+      <c r="Y10" s="96"/>
+      <c r="Z10" s="96"/>
+      <c r="AA10" s="96"/>
+      <c r="AB10" s="96"/>
+      <c r="AC10" s="96"/>
+      <c r="AD10" s="96"/>
+      <c r="AE10" s="96"/>
+      <c r="AF10" s="96"/>
+      <c r="AG10" s="96"/>
+      <c r="AH10" s="96"/>
+      <c r="AI10" s="96"/>
+      <c r="AJ10" s="96"/>
+      <c r="AK10" s="96"/>
+      <c r="AL10" s="97"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>26</v>
       </c>
@@ -2843,62 +2850,62 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="27"/>
-      <c r="F11" s="104" t="s">
+      <c r="F11" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="104" t="s">
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="105"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="105"/>
-      <c r="O11" s="106"/>
-      <c r="P11" s="104" t="s">
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="97"/>
+      <c r="P11" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="106"/>
-      <c r="U11" s="104" t="s">
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="S11" s="96"/>
+      <c r="T11" s="97"/>
+      <c r="U11" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="105"/>
-      <c r="W11" s="105"/>
-      <c r="X11" s="105"/>
-      <c r="Y11" s="106"/>
-      <c r="Z11" s="104" t="s">
+      <c r="V11" s="96"/>
+      <c r="W11" s="96"/>
+      <c r="X11" s="96"/>
+      <c r="Y11" s="97"/>
+      <c r="Z11" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="105"/>
-      <c r="AB11" s="105"/>
-      <c r="AC11" s="105"/>
-      <c r="AD11" s="106"/>
-      <c r="AE11" s="104" t="s">
+      <c r="AA11" s="96"/>
+      <c r="AB11" s="96"/>
+      <c r="AC11" s="96"/>
+      <c r="AD11" s="97"/>
+      <c r="AE11" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="105"/>
-      <c r="AG11" s="105"/>
-      <c r="AH11" s="105"/>
-      <c r="AI11" s="106"/>
-      <c r="AJ11" s="107" t="s">
+      <c r="AF11" s="96"/>
+      <c r="AG11" s="96"/>
+      <c r="AH11" s="96"/>
+      <c r="AI11" s="97"/>
+      <c r="AJ11" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="108"/>
-      <c r="AL11" s="109"/>
-    </row>
-    <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="88" t="s">
+      <c r="AK11" s="99"/>
+      <c r="AL11" s="100"/>
+    </row>
+    <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="90"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="91"/>
       <c r="F12" s="28"/>
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
@@ -2933,12 +2940,12 @@
       <c r="AK12" s="32"/>
       <c r="AL12" s="33"/>
     </row>
-    <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="91"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
+    <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="94"/>
       <c r="F13" s="34"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
@@ -2973,14 +2980,14 @@
       <c r="AK13" s="24"/>
       <c r="AL13" s="38"/>
     </row>
-    <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="88" t="s">
+    <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="90"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="91"/>
       <c r="F14" s="28"/>
       <c r="G14" s="29"/>
       <c r="H14" s="29"/>
@@ -3015,12 +3022,12 @@
       <c r="AK14" s="32"/>
       <c r="AL14" s="33"/>
     </row>
-    <row r="15" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="93"/>
+    <row r="15" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="92"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="94"/>
       <c r="F15" s="34"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
@@ -3055,14 +3062,14 @@
       <c r="AK15" s="24"/>
       <c r="AL15" s="38"/>
     </row>
-    <row r="16" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="88" t="s">
+    <row r="16" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="90"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="91"/>
       <c r="F16" s="28"/>
       <c r="G16" s="29"/>
       <c r="H16" s="29"/>
@@ -3097,12 +3104,12 @@
       <c r="AK16" s="32"/>
       <c r="AL16" s="33"/>
     </row>
-    <row r="17" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="93"/>
+    <row r="17" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="92"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="94"/>
       <c r="F17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
@@ -3137,14 +3144,14 @@
       <c r="AK17" s="24"/>
       <c r="AL17" s="38"/>
     </row>
-    <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="88" t="s">
+    <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="90"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="91"/>
       <c r="F18" s="28"/>
       <c r="G18" s="29"/>
       <c r="H18" s="29"/>
@@ -3179,12 +3186,12 @@
       <c r="AK18" s="32"/>
       <c r="AL18" s="33"/>
     </row>
-    <row r="19" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="91"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="93"/>
+    <row r="19" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="92"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="94"/>
       <c r="F19" s="34"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
@@ -3219,14 +3226,14 @@
       <c r="AK19" s="24"/>
       <c r="AL19" s="38"/>
     </row>
-    <row r="20" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="88" t="s">
+    <row r="20" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="90"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="91"/>
       <c r="F20" s="28"/>
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
@@ -3261,12 +3268,12 @@
       <c r="AK20" s="32"/>
       <c r="AL20" s="33"/>
     </row>
-    <row r="21" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="93"/>
+    <row r="21" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="92"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="94"/>
       <c r="F21" s="34"/>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
@@ -3301,14 +3308,14 @@
       <c r="AK21" s="24"/>
       <c r="AL21" s="38"/>
     </row>
-    <row r="22" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="88" t="s">
+    <row r="22" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="90"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="91"/>
       <c r="F22" s="28"/>
       <c r="G22" s="29"/>
       <c r="H22" s="29"/>
@@ -3343,12 +3350,12 @@
       <c r="AK22" s="32"/>
       <c r="AL22" s="33"/>
     </row>
-    <row r="23" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="93"/>
+    <row r="23" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="92"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="94"/>
       <c r="F23" s="34"/>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
@@ -3383,14 +3390,14 @@
       <c r="AK23" s="24"/>
       <c r="AL23" s="38"/>
     </row>
-    <row r="24" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="88" t="s">
+    <row r="24" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="90"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="91"/>
       <c r="F24" s="28"/>
       <c r="G24" s="29"/>
       <c r="H24" s="29"/>
@@ -3425,12 +3432,12 @@
       <c r="AK24" s="32"/>
       <c r="AL24" s="33"/>
     </row>
-    <row r="25" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="93"/>
+    <row r="25" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="92"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="94"/>
       <c r="F25" s="34"/>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
@@ -3465,14 +3472,14 @@
       <c r="AK25" s="24"/>
       <c r="AL25" s="38"/>
     </row>
-    <row r="26" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="88" t="s">
+    <row r="26" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="90"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="91"/>
       <c r="F26" s="28"/>
       <c r="G26" s="29"/>
       <c r="H26" s="29"/>
@@ -3507,12 +3514,12 @@
       <c r="AK26" s="32"/>
       <c r="AL26" s="33"/>
     </row>
-    <row r="27" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="93"/>
+    <row r="27" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="92"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="94"/>
       <c r="F27" s="34"/>
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
@@ -3547,14 +3554,14 @@
       <c r="AK27" s="24"/>
       <c r="AL27" s="38"/>
     </row>
-    <row r="28" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="88" t="s">
+    <row r="28" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="90"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="91"/>
       <c r="F28" s="28"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
@@ -3589,12 +3596,12 @@
       <c r="AK28" s="32"/>
       <c r="AL28" s="33"/>
     </row>
-    <row r="29" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="91"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="93"/>
+    <row r="29" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="92"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="94"/>
       <c r="F29" s="34"/>
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
@@ -3629,14 +3636,14 @@
       <c r="AK29" s="24"/>
       <c r="AL29" s="38"/>
     </row>
-    <row r="30" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="88" t="s">
+    <row r="30" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="90"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="91"/>
       <c r="F30" s="28"/>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -3671,12 +3678,12 @@
       <c r="AK30" s="32"/>
       <c r="AL30" s="33"/>
     </row>
-    <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="91"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="93"/>
+    <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="92"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="94"/>
       <c r="F31" s="34"/>
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
@@ -3711,14 +3718,14 @@
       <c r="AK31" s="24"/>
       <c r="AL31" s="38"/>
     </row>
-    <row r="32" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="88" t="s">
+    <row r="32" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="90"/>
       <c r="F32" s="28"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
@@ -3753,12 +3760,12 @@
       <c r="AK32" s="32"/>
       <c r="AL32" s="33"/>
     </row>
-    <row r="33" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
+    <row r="33" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="92"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
       <c r="F33" s="34"/>
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
@@ -3793,14 +3800,14 @@
       <c r="AK33" s="24"/>
       <c r="AL33" s="38"/>
     </row>
-    <row r="34" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="88" t="s">
+    <row r="34" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="90"/>
       <c r="F34" s="28"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29"/>
@@ -3835,12 +3842,12 @@
       <c r="AK34" s="32"/>
       <c r="AL34" s="33"/>
     </row>
-    <row r="35" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="91"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="93"/>
+    <row r="35" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="92"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="94"/>
       <c r="F35" s="34"/>
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
@@ -3875,14 +3882,14 @@
       <c r="AK35" s="24"/>
       <c r="AL35" s="38"/>
     </row>
-    <row r="36" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="94" t="s">
+    <row r="36" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="96"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="106"/>
       <c r="F36" s="28"/>
       <c r="G36" s="29"/>
       <c r="H36" s="29"/>
@@ -3917,12 +3924,12 @@
       <c r="AK36" s="32"/>
       <c r="AL36" s="33"/>
     </row>
-    <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="97"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="99"/>
+    <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="107"/>
+      <c r="B37" s="108"/>
+      <c r="C37" s="108"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="109"/>
       <c r="F37" s="34"/>
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
@@ -3957,7 +3964,7 @@
       <c r="AK37" s="24"/>
       <c r="AL37" s="38"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>38</v>
       </c>
@@ -3990,22 +3997,22 @@
       <c r="AE38" s="21"/>
       <c r="AF38" s="21"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A39" s="100" t="s">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A39" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="100"/>
-      <c r="C39" s="100"/>
-      <c r="D39" s="101" t="s">
+      <c r="B39" s="110"/>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="101"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="101"/>
-      <c r="H39" s="101"/>
-      <c r="I39" s="101"/>
-      <c r="J39" s="101"/>
-      <c r="K39" s="101"/>
+      <c r="E39" s="111"/>
+      <c r="F39" s="111"/>
+      <c r="G39" s="111"/>
+      <c r="H39" s="111"/>
+      <c r="I39" s="111"/>
+      <c r="J39" s="111"/>
+      <c r="K39" s="111"/>
       <c r="L39" s="21"/>
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
@@ -4028,20 +4035,20 @@
       <c r="AE39" s="21"/>
       <c r="AF39" s="21"/>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A40" s="100"/>
-      <c r="B40" s="100"/>
-      <c r="C40" s="100"/>
-      <c r="D40" s="102" t="s">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A40" s="110"/>
+      <c r="B40" s="110"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="102"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="102"/>
-      <c r="H40" s="102"/>
-      <c r="I40" s="102"/>
-      <c r="J40" s="102"/>
-      <c r="K40" s="102"/>
+      <c r="E40" s="112"/>
+      <c r="F40" s="112"/>
+      <c r="G40" s="112"/>
+      <c r="H40" s="112"/>
+      <c r="I40" s="112"/>
+      <c r="J40" s="112"/>
+      <c r="K40" s="112"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
@@ -4064,7 +4071,7 @@
       <c r="AE40" s="21"/>
       <c r="AF40" s="21"/>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>17</v>
       </c>
@@ -4097,7 +4104,7 @@
       <c r="AE41" s="21"/>
       <c r="AF41" s="21"/>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
@@ -4128,7 +4135,7 @@
       <c r="AE42" s="21"/>
       <c r="AF42" s="21"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="39"/>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
@@ -4159,7 +4166,7 @@
       <c r="AE43" s="21"/>
       <c r="AF43" s="21"/>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
@@ -4190,7 +4197,7 @@
       <c r="AE44" s="21"/>
       <c r="AF44" s="21"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
@@ -4221,7 +4228,7 @@
       <c r="AE45" s="21"/>
       <c r="AF45" s="21"/>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="21"/>
@@ -4252,14 +4259,26 @@
       <c r="AE46" s="21"/>
       <c r="AF46" s="21"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="A24:E25"/>
+    <mergeCell ref="A26:E27"/>
+    <mergeCell ref="A28:E29"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="A22:E23"/>
@@ -4276,18 +4295,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="A24:E25"/>
-    <mergeCell ref="A26:E27"/>
-    <mergeCell ref="A28:E29"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4307,15 +4314,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A966B5-BF06-44FD-908C-4467C7012DA9}">
   <dimension ref="A1:AL54"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="38" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="38" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4327,34 +4334,34 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
-    </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="119"/>
+      <c r="AJ1" s="119"/>
+      <c r="AK1" s="119"/>
+      <c r="AL1" s="119"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>44</v>
       </c>
@@ -4387,23 +4394,23 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="114"/>
+      <c r="O3" s="114"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -4420,17 +4427,17 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
+        <v>107</v>
+      </c>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="127"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -4454,7 +4461,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>46</v>
       </c>
@@ -4488,219 +4495,219 @@
       <c r="AF5" s="3"/>
       <c r="AK5" s="7"/>
     </row>
-    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="117" t="s">
+    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118" t="s">
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="118" t="s">
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="118"/>
-      <c r="O6" s="118"/>
-      <c r="P6" s="118"/>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="118"/>
-      <c r="S6" s="118"/>
-      <c r="T6" s="118"/>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
-      <c r="Z6" s="118"/>
-      <c r="AA6" s="118"/>
-      <c r="AB6" s="118"/>
-      <c r="AC6" s="118"/>
-      <c r="AD6" s="118"/>
-      <c r="AE6" s="118"/>
-      <c r="AF6" s="118"/>
-      <c r="AG6" s="118"/>
-      <c r="AH6" s="118"/>
-      <c r="AI6" s="118"/>
-      <c r="AJ6" s="118"/>
-      <c r="AK6" s="118"/>
-      <c r="AL6" s="118"/>
-    </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="117"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="122" t="s">
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115"/>
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115"/>
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115"/>
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115"/>
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115"/>
+    </row>
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="118"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
+      <c r="K7" s="115"/>
+      <c r="L7" s="115"/>
+      <c r="M7" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="123"/>
-      <c r="O7" s="123"/>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="123"/>
-      <c r="S7" s="123"/>
-      <c r="T7" s="123"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="122" t="s">
+      <c r="N7" s="122"/>
+      <c r="O7" s="122"/>
+      <c r="P7" s="122"/>
+      <c r="Q7" s="122"/>
+      <c r="R7" s="122"/>
+      <c r="S7" s="122"/>
+      <c r="T7" s="122"/>
+      <c r="U7" s="123"/>
+      <c r="V7" s="121" t="s">
         <v>51</v>
       </c>
-      <c r="W7" s="123"/>
-      <c r="X7" s="123"/>
-      <c r="Y7" s="123"/>
-      <c r="Z7" s="123"/>
-      <c r="AA7" s="123"/>
-      <c r="AB7" s="123"/>
-      <c r="AC7" s="123"/>
-      <c r="AD7" s="124"/>
-      <c r="AE7" s="119" t="s">
+      <c r="W7" s="122"/>
+      <c r="X7" s="122"/>
+      <c r="Y7" s="122"/>
+      <c r="Z7" s="122"/>
+      <c r="AA7" s="122"/>
+      <c r="AB7" s="122"/>
+      <c r="AC7" s="122"/>
+      <c r="AD7" s="123"/>
+      <c r="AE7" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="AF7" s="119"/>
-      <c r="AG7" s="119"/>
-      <c r="AH7" s="119"/>
-      <c r="AI7" s="119"/>
-      <c r="AJ7" s="119"/>
-      <c r="AK7" s="119"/>
-      <c r="AL7" s="119"/>
-    </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="116"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="86"/>
-      <c r="O8" s="86"/>
-      <c r="P8" s="86"/>
-      <c r="Q8" s="86"/>
-      <c r="R8" s="86"/>
-      <c r="S8" s="86"/>
-      <c r="T8" s="86"/>
-      <c r="U8" s="85"/>
-      <c r="V8" s="121"/>
-      <c r="W8" s="86"/>
-      <c r="X8" s="86"/>
-      <c r="Y8" s="86"/>
-      <c r="Z8" s="86"/>
-      <c r="AA8" s="86"/>
-      <c r="AB8" s="86"/>
-      <c r="AC8" s="86"/>
-      <c r="AD8" s="85"/>
-      <c r="AE8" s="114"/>
-      <c r="AF8" s="114"/>
-      <c r="AG8" s="114"/>
-      <c r="AH8" s="114"/>
-      <c r="AI8" s="114"/>
-      <c r="AJ8" s="114"/>
-      <c r="AK8" s="114"/>
-      <c r="AL8" s="114"/>
-    </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="116"/>
-      <c r="B9" s="116"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="116"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="114"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="86"/>
-      <c r="O9" s="86"/>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="86"/>
-      <c r="R9" s="86"/>
-      <c r="S9" s="86"/>
-      <c r="T9" s="86"/>
-      <c r="U9" s="85"/>
-      <c r="V9" s="121"/>
-      <c r="W9" s="86"/>
-      <c r="X9" s="86"/>
-      <c r="Y9" s="86"/>
-      <c r="Z9" s="86"/>
-      <c r="AA9" s="86"/>
-      <c r="AB9" s="86"/>
-      <c r="AC9" s="86"/>
-      <c r="AD9" s="85"/>
-      <c r="AE9" s="114"/>
-      <c r="AF9" s="114"/>
-      <c r="AG9" s="114"/>
-      <c r="AH9" s="114"/>
-      <c r="AI9" s="114"/>
-      <c r="AJ9" s="114"/>
-      <c r="AK9" s="114"/>
-      <c r="AL9" s="114"/>
-    </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="86"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="86"/>
-      <c r="Q10" s="86"/>
-      <c r="R10" s="86"/>
-      <c r="S10" s="86"/>
-      <c r="T10" s="86"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="121"/>
-      <c r="W10" s="86"/>
-      <c r="X10" s="86"/>
-      <c r="Y10" s="86"/>
-      <c r="Z10" s="86"/>
-      <c r="AA10" s="86"/>
-      <c r="AB10" s="86"/>
-      <c r="AC10" s="86"/>
-      <c r="AD10" s="85"/>
-      <c r="AE10" s="114"/>
-      <c r="AF10" s="114"/>
-      <c r="AG10" s="114"/>
-      <c r="AH10" s="114"/>
-      <c r="AI10" s="114"/>
-      <c r="AJ10" s="114"/>
-      <c r="AK10" s="114"/>
-      <c r="AL10" s="114"/>
-    </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AF7" s="124"/>
+      <c r="AG7" s="124"/>
+      <c r="AH7" s="124"/>
+      <c r="AI7" s="124"/>
+      <c r="AJ7" s="124"/>
+      <c r="AK7" s="124"/>
+      <c r="AL7" s="124"/>
+    </row>
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="125"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="83"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="120"/>
+      <c r="W8" s="83"/>
+      <c r="X8" s="83"/>
+      <c r="Y8" s="83"/>
+      <c r="Z8" s="83"/>
+      <c r="AA8" s="83"/>
+      <c r="AB8" s="83"/>
+      <c r="AC8" s="83"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="113"/>
+      <c r="AF8" s="113"/>
+      <c r="AG8" s="113"/>
+      <c r="AH8" s="113"/>
+      <c r="AI8" s="113"/>
+      <c r="AJ8" s="113"/>
+      <c r="AK8" s="113"/>
+      <c r="AL8" s="113"/>
+    </row>
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="125"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="120"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83"/>
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="113"/>
+      <c r="AF9" s="113"/>
+      <c r="AG9" s="113"/>
+      <c r="AH9" s="113"/>
+      <c r="AI9" s="113"/>
+      <c r="AJ9" s="113"/>
+      <c r="AK9" s="113"/>
+      <c r="AL9" s="113"/>
+    </row>
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="126"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="113"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
+      <c r="T10" s="83"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="120"/>
+      <c r="W10" s="83"/>
+      <c r="X10" s="83"/>
+      <c r="Y10" s="83"/>
+      <c r="Z10" s="83"/>
+      <c r="AA10" s="83"/>
+      <c r="AB10" s="83"/>
+      <c r="AC10" s="83"/>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="113"/>
+      <c r="AF10" s="113"/>
+      <c r="AG10" s="113"/>
+      <c r="AH10" s="113"/>
+      <c r="AI10" s="113"/>
+      <c r="AJ10" s="113"/>
+      <c r="AK10" s="113"/>
+      <c r="AL10" s="113"/>
+    </row>
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -4730,7 +4737,7 @@
       <c r="AF11" s="3"/>
       <c r="AK11" s="7"/>
     </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>44</v>
       </c>
@@ -4762,24 +4769,24 @@
       <c r="AF12" s="3"/>
       <c r="AK12" s="7"/>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="127"/>
-      <c r="O13" s="127"/>
-      <c r="P13" s="127"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="127"/>
-      <c r="S13" s="127"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
+      <c r="O13" s="117"/>
+      <c r="P13" s="117"/>
+      <c r="Q13" s="117"/>
+      <c r="R13" s="117"/>
+      <c r="S13" s="117"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -4793,17 +4800,17 @@
       <c r="AF13" s="3"/>
       <c r="AK13" s="7"/>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
+        <v>107</v>
+      </c>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -4827,7 +4834,7 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>46</v>
       </c>
@@ -4868,241 +4875,241 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="117" t="s">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="118" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="118" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="119" t="s">
+      <c r="I16" s="115"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="M16" s="119"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="119"/>
-      <c r="R16" s="119"/>
-      <c r="S16" s="119"/>
-      <c r="T16" s="119"/>
-      <c r="U16" s="119"/>
-      <c r="V16" s="119"/>
-      <c r="W16" s="119"/>
-      <c r="X16" s="118" t="s">
+      <c r="M16" s="124"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="124"/>
+      <c r="P16" s="124"/>
+      <c r="Q16" s="124"/>
+      <c r="R16" s="124"/>
+      <c r="S16" s="124"/>
+      <c r="T16" s="124"/>
+      <c r="U16" s="124"/>
+      <c r="V16" s="124"/>
+      <c r="W16" s="124"/>
+      <c r="X16" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="Y16" s="118"/>
-      <c r="Z16" s="118"/>
-      <c r="AA16" s="118"/>
-      <c r="AB16" s="119" t="s">
+      <c r="Y16" s="115"/>
+      <c r="Z16" s="115"/>
+      <c r="AA16" s="115"/>
+      <c r="AB16" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="AC16" s="119"/>
-      <c r="AD16" s="119"/>
-      <c r="AE16" s="119"/>
-      <c r="AF16" s="119"/>
-      <c r="AG16" s="119"/>
-      <c r="AH16" s="119"/>
-      <c r="AI16" s="119"/>
-      <c r="AJ16" s="119"/>
-      <c r="AK16" s="119"/>
-      <c r="AL16" s="119"/>
-    </row>
-    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="117"/>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="119" t="s">
+      <c r="AC16" s="124"/>
+      <c r="AD16" s="124"/>
+      <c r="AE16" s="124"/>
+      <c r="AF16" s="124"/>
+      <c r="AG16" s="124"/>
+      <c r="AH16" s="124"/>
+      <c r="AI16" s="124"/>
+      <c r="AJ16" s="124"/>
+      <c r="AK16" s="124"/>
+      <c r="AL16" s="124"/>
+    </row>
+    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="118"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="119"/>
-      <c r="N17" s="119"/>
-      <c r="O17" s="119"/>
-      <c r="P17" s="119" t="s">
+      <c r="M17" s="124"/>
+      <c r="N17" s="124"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="119"/>
-      <c r="R17" s="119"/>
-      <c r="S17" s="119"/>
-      <c r="T17" s="119" t="s">
+      <c r="Q17" s="124"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="U17" s="119"/>
-      <c r="V17" s="119"/>
-      <c r="W17" s="119"/>
-      <c r="X17" s="118"/>
-      <c r="Y17" s="118"/>
-      <c r="Z17" s="118"/>
-      <c r="AA17" s="118"/>
-      <c r="AB17" s="119" t="s">
+      <c r="U17" s="124"/>
+      <c r="V17" s="124"/>
+      <c r="W17" s="124"/>
+      <c r="X17" s="115"/>
+      <c r="Y17" s="115"/>
+      <c r="Z17" s="115"/>
+      <c r="AA17" s="115"/>
+      <c r="AB17" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="AC17" s="119"/>
-      <c r="AD17" s="119"/>
-      <c r="AE17" s="119"/>
-      <c r="AF17" s="119" t="s">
+      <c r="AC17" s="124"/>
+      <c r="AD17" s="124"/>
+      <c r="AE17" s="124"/>
+      <c r="AF17" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="AG17" s="119"/>
-      <c r="AH17" s="119"/>
-      <c r="AI17" s="119"/>
-      <c r="AJ17" s="119" t="s">
+      <c r="AG17" s="124"/>
+      <c r="AH17" s="124"/>
+      <c r="AI17" s="124"/>
+      <c r="AJ17" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="AK17" s="119"/>
-      <c r="AL17" s="119"/>
-    </row>
-    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="116"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="115">
+      <c r="AK17" s="124"/>
+      <c r="AL17" s="124"/>
+    </row>
+    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="125"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="116">
         <v>125</v>
       </c>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="114"/>
-      <c r="N18" s="114"/>
-      <c r="O18" s="114"/>
-      <c r="P18" s="114"/>
-      <c r="Q18" s="114"/>
-      <c r="R18" s="114"/>
-      <c r="S18" s="114"/>
-      <c r="T18" s="114"/>
-      <c r="U18" s="114"/>
-      <c r="V18" s="114"/>
-      <c r="W18" s="114"/>
-      <c r="X18" s="115">
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="116"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="113"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="113"/>
+      <c r="P18" s="113"/>
+      <c r="Q18" s="113"/>
+      <c r="R18" s="113"/>
+      <c r="S18" s="113"/>
+      <c r="T18" s="113"/>
+      <c r="U18" s="113"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="113"/>
+      <c r="X18" s="116">
         <v>2000</v>
       </c>
-      <c r="Y18" s="115"/>
-      <c r="Z18" s="115"/>
-      <c r="AA18" s="115"/>
-      <c r="AB18" s="114"/>
-      <c r="AC18" s="114"/>
-      <c r="AD18" s="114"/>
-      <c r="AE18" s="114"/>
-      <c r="AF18" s="114"/>
-      <c r="AG18" s="114"/>
-      <c r="AH18" s="114"/>
-      <c r="AI18" s="114"/>
-      <c r="AJ18" s="114"/>
-      <c r="AK18" s="114"/>
-      <c r="AL18" s="114"/>
-    </row>
-    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="115">
+      <c r="Y18" s="116"/>
+      <c r="Z18" s="116"/>
+      <c r="AA18" s="116"/>
+      <c r="AB18" s="113"/>
+      <c r="AC18" s="113"/>
+      <c r="AD18" s="113"/>
+      <c r="AE18" s="113"/>
+      <c r="AF18" s="113"/>
+      <c r="AG18" s="113"/>
+      <c r="AH18" s="113"/>
+      <c r="AI18" s="113"/>
+      <c r="AJ18" s="113"/>
+      <c r="AK18" s="113"/>
+      <c r="AL18" s="113"/>
+    </row>
+    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="125"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="116">
         <v>500</v>
       </c>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="114"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="114"/>
-      <c r="R19" s="114"/>
-      <c r="S19" s="114"/>
-      <c r="T19" s="114"/>
-      <c r="U19" s="114"/>
-      <c r="V19" s="114"/>
-      <c r="W19" s="114"/>
-      <c r="X19" s="115">
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="113"/>
+      <c r="N19" s="113"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="113"/>
+      <c r="Q19" s="113"/>
+      <c r="R19" s="113"/>
+      <c r="S19" s="113"/>
+      <c r="T19" s="113"/>
+      <c r="U19" s="113"/>
+      <c r="V19" s="113"/>
+      <c r="W19" s="113"/>
+      <c r="X19" s="116">
         <v>5000</v>
       </c>
-      <c r="Y19" s="115"/>
-      <c r="Z19" s="115"/>
-      <c r="AA19" s="115"/>
-      <c r="AB19" s="114"/>
-      <c r="AC19" s="114"/>
-      <c r="AD19" s="114"/>
-      <c r="AE19" s="114"/>
-      <c r="AF19" s="114"/>
-      <c r="AG19" s="114"/>
-      <c r="AH19" s="114"/>
-      <c r="AI19" s="114"/>
-      <c r="AJ19" s="114"/>
-      <c r="AK19" s="114"/>
-      <c r="AL19" s="114"/>
-    </row>
-    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="116"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="115">
+      <c r="Y19" s="116"/>
+      <c r="Z19" s="116"/>
+      <c r="AA19" s="116"/>
+      <c r="AB19" s="113"/>
+      <c r="AC19" s="113"/>
+      <c r="AD19" s="113"/>
+      <c r="AE19" s="113"/>
+      <c r="AF19" s="113"/>
+      <c r="AG19" s="113"/>
+      <c r="AH19" s="113"/>
+      <c r="AI19" s="113"/>
+      <c r="AJ19" s="113"/>
+      <c r="AK19" s="113"/>
+      <c r="AL19" s="113"/>
+    </row>
+    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="125"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="116">
         <v>1000</v>
       </c>
-      <c r="I20" s="115"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="114"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="114"/>
-      <c r="V20" s="114"/>
-      <c r="W20" s="114"/>
-      <c r="X20" s="115">
+      <c r="I20" s="116"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="113"/>
+      <c r="R20" s="113"/>
+      <c r="S20" s="113"/>
+      <c r="T20" s="113"/>
+      <c r="U20" s="113"/>
+      <c r="V20" s="113"/>
+      <c r="W20" s="113"/>
+      <c r="X20" s="116">
         <v>7000</v>
       </c>
-      <c r="Y20" s="115"/>
-      <c r="Z20" s="115"/>
-      <c r="AA20" s="115"/>
-      <c r="AB20" s="114"/>
-      <c r="AC20" s="114"/>
-      <c r="AD20" s="114"/>
-      <c r="AE20" s="114"/>
-      <c r="AF20" s="114"/>
-      <c r="AG20" s="114"/>
-      <c r="AH20" s="114"/>
-      <c r="AI20" s="114"/>
-      <c r="AJ20" s="114"/>
-      <c r="AK20" s="114"/>
-      <c r="AL20" s="114"/>
-    </row>
-    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y20" s="116"/>
+      <c r="Z20" s="116"/>
+      <c r="AA20" s="116"/>
+      <c r="AB20" s="113"/>
+      <c r="AC20" s="113"/>
+      <c r="AD20" s="113"/>
+      <c r="AE20" s="113"/>
+      <c r="AF20" s="113"/>
+      <c r="AG20" s="113"/>
+      <c r="AH20" s="113"/>
+      <c r="AI20" s="113"/>
+      <c r="AJ20" s="113"/>
+      <c r="AK20" s="113"/>
+      <c r="AL20" s="113"/>
+    </row>
+    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="D21" s="5"/>
       <c r="H21" s="3"/>
@@ -5137,7 +5144,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>46</v>
       </c>
@@ -5178,241 +5185,241 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="118" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="118" t="s">
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="119" t="s">
+      <c r="I23" s="115"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="115"/>
+      <c r="L23" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="M23" s="119"/>
-      <c r="N23" s="119"/>
-      <c r="O23" s="119"/>
-      <c r="P23" s="119"/>
-      <c r="Q23" s="119"/>
-      <c r="R23" s="119"/>
-      <c r="S23" s="119"/>
-      <c r="T23" s="119"/>
-      <c r="U23" s="119"/>
-      <c r="V23" s="119"/>
-      <c r="W23" s="119"/>
-      <c r="X23" s="118" t="s">
+      <c r="M23" s="124"/>
+      <c r="N23" s="124"/>
+      <c r="O23" s="124"/>
+      <c r="P23" s="124"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="124"/>
+      <c r="S23" s="124"/>
+      <c r="T23" s="124"/>
+      <c r="U23" s="124"/>
+      <c r="V23" s="124"/>
+      <c r="W23" s="124"/>
+      <c r="X23" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="Y23" s="118"/>
-      <c r="Z23" s="118"/>
-      <c r="AA23" s="118"/>
-      <c r="AB23" s="119" t="s">
+      <c r="Y23" s="115"/>
+      <c r="Z23" s="115"/>
+      <c r="AA23" s="115"/>
+      <c r="AB23" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="AC23" s="119"/>
-      <c r="AD23" s="119"/>
-      <c r="AE23" s="119"/>
-      <c r="AF23" s="119"/>
-      <c r="AG23" s="119"/>
-      <c r="AH23" s="119"/>
-      <c r="AI23" s="119"/>
-      <c r="AJ23" s="119"/>
-      <c r="AK23" s="119"/>
-      <c r="AL23" s="119"/>
-    </row>
-    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="117"/>
-      <c r="B24" s="117"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="119" t="s">
+      <c r="AC23" s="124"/>
+      <c r="AD23" s="124"/>
+      <c r="AE23" s="124"/>
+      <c r="AF23" s="124"/>
+      <c r="AG23" s="124"/>
+      <c r="AH23" s="124"/>
+      <c r="AI23" s="124"/>
+      <c r="AJ23" s="124"/>
+      <c r="AK23" s="124"/>
+      <c r="AL23" s="124"/>
+    </row>
+    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="118"/>
+      <c r="B24" s="118"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="115"/>
+      <c r="K24" s="115"/>
+      <c r="L24" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="119"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="119" t="s">
+      <c r="M24" s="124"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="124"/>
+      <c r="P24" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="119"/>
-      <c r="S24" s="119"/>
-      <c r="T24" s="119" t="s">
+      <c r="Q24" s="124"/>
+      <c r="R24" s="124"/>
+      <c r="S24" s="124"/>
+      <c r="T24" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="U24" s="119"/>
-      <c r="V24" s="119"/>
-      <c r="W24" s="119"/>
-      <c r="X24" s="118"/>
-      <c r="Y24" s="118"/>
-      <c r="Z24" s="118"/>
-      <c r="AA24" s="118"/>
-      <c r="AB24" s="119" t="s">
+      <c r="U24" s="124"/>
+      <c r="V24" s="124"/>
+      <c r="W24" s="124"/>
+      <c r="X24" s="115"/>
+      <c r="Y24" s="115"/>
+      <c r="Z24" s="115"/>
+      <c r="AA24" s="115"/>
+      <c r="AB24" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="AC24" s="119"/>
-      <c r="AD24" s="119"/>
-      <c r="AE24" s="119"/>
-      <c r="AF24" s="119" t="s">
+      <c r="AC24" s="124"/>
+      <c r="AD24" s="124"/>
+      <c r="AE24" s="124"/>
+      <c r="AF24" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="AG24" s="119"/>
-      <c r="AH24" s="119"/>
-      <c r="AI24" s="119"/>
-      <c r="AJ24" s="119" t="s">
+      <c r="AG24" s="124"/>
+      <c r="AH24" s="124"/>
+      <c r="AI24" s="124"/>
+      <c r="AJ24" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="AK24" s="119"/>
-      <c r="AL24" s="119"/>
-    </row>
-    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="116"/>
-      <c r="B25" s="116"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="115">
+      <c r="AK24" s="124"/>
+      <c r="AL24" s="124"/>
+    </row>
+    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="125"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="116">
         <v>125</v>
       </c>
-      <c r="I25" s="115"/>
-      <c r="J25" s="115"/>
-      <c r="K25" s="115"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="114"/>
-      <c r="N25" s="114"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="114"/>
-      <c r="Q25" s="114"/>
-      <c r="R25" s="114"/>
-      <c r="S25" s="114"/>
-      <c r="T25" s="114"/>
-      <c r="U25" s="114"/>
-      <c r="V25" s="114"/>
-      <c r="W25" s="114"/>
-      <c r="X25" s="115">
+      <c r="I25" s="116"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="116"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="113"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="R25" s="113"/>
+      <c r="S25" s="113"/>
+      <c r="T25" s="113"/>
+      <c r="U25" s="113"/>
+      <c r="V25" s="113"/>
+      <c r="W25" s="113"/>
+      <c r="X25" s="116">
         <v>2000</v>
       </c>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
-      <c r="AB25" s="114"/>
-      <c r="AC25" s="114"/>
-      <c r="AD25" s="114"/>
-      <c r="AE25" s="114"/>
-      <c r="AF25" s="114"/>
-      <c r="AG25" s="114"/>
-      <c r="AH25" s="114"/>
-      <c r="AI25" s="114"/>
-      <c r="AJ25" s="114"/>
-      <c r="AK25" s="114"/>
-      <c r="AL25" s="114"/>
-    </row>
-    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="116"/>
-      <c r="B26" s="116"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="116"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="115">
+      <c r="Y25" s="116"/>
+      <c r="Z25" s="116"/>
+      <c r="AA25" s="116"/>
+      <c r="AB25" s="113"/>
+      <c r="AC25" s="113"/>
+      <c r="AD25" s="113"/>
+      <c r="AE25" s="113"/>
+      <c r="AF25" s="113"/>
+      <c r="AG25" s="113"/>
+      <c r="AH25" s="113"/>
+      <c r="AI25" s="113"/>
+      <c r="AJ25" s="113"/>
+      <c r="AK25" s="113"/>
+      <c r="AL25" s="113"/>
+    </row>
+    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="125"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="116">
         <v>500</v>
       </c>
-      <c r="I26" s="115"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="114"/>
-      <c r="N26" s="114"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="114"/>
-      <c r="R26" s="114"/>
-      <c r="S26" s="114"/>
-      <c r="T26" s="114"/>
-      <c r="U26" s="114"/>
-      <c r="V26" s="114"/>
-      <c r="W26" s="114"/>
-      <c r="X26" s="115">
+      <c r="I26" s="116"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="113"/>
+      <c r="N26" s="113"/>
+      <c r="O26" s="113"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="113"/>
+      <c r="R26" s="113"/>
+      <c r="S26" s="113"/>
+      <c r="T26" s="113"/>
+      <c r="U26" s="113"/>
+      <c r="V26" s="113"/>
+      <c r="W26" s="113"/>
+      <c r="X26" s="116">
         <v>5000</v>
       </c>
-      <c r="Y26" s="115"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="115"/>
-      <c r="AB26" s="114"/>
-      <c r="AC26" s="114"/>
-      <c r="AD26" s="114"/>
-      <c r="AE26" s="114"/>
-      <c r="AF26" s="114"/>
-      <c r="AG26" s="114"/>
-      <c r="AH26" s="114"/>
-      <c r="AI26" s="114"/>
-      <c r="AJ26" s="114"/>
-      <c r="AK26" s="114"/>
-      <c r="AL26" s="114"/>
-    </row>
-    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="116"/>
-      <c r="B27" s="116"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="115">
+      <c r="Y26" s="116"/>
+      <c r="Z26" s="116"/>
+      <c r="AA26" s="116"/>
+      <c r="AB26" s="113"/>
+      <c r="AC26" s="113"/>
+      <c r="AD26" s="113"/>
+      <c r="AE26" s="113"/>
+      <c r="AF26" s="113"/>
+      <c r="AG26" s="113"/>
+      <c r="AH26" s="113"/>
+      <c r="AI26" s="113"/>
+      <c r="AJ26" s="113"/>
+      <c r="AK26" s="113"/>
+      <c r="AL26" s="113"/>
+    </row>
+    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="125"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="116">
         <v>1000</v>
       </c>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="114"/>
-      <c r="Q27" s="114"/>
-      <c r="R27" s="114"/>
-      <c r="S27" s="114"/>
-      <c r="T27" s="114"/>
-      <c r="U27" s="114"/>
-      <c r="V27" s="114"/>
-      <c r="W27" s="114"/>
-      <c r="X27" s="115">
+      <c r="I27" s="116"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="113"/>
+      <c r="O27" s="113"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="113"/>
+      <c r="R27" s="113"/>
+      <c r="S27" s="113"/>
+      <c r="T27" s="113"/>
+      <c r="U27" s="113"/>
+      <c r="V27" s="113"/>
+      <c r="W27" s="113"/>
+      <c r="X27" s="116">
         <v>7000</v>
       </c>
-      <c r="Y27" s="115"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="115"/>
-      <c r="AB27" s="114"/>
-      <c r="AC27" s="114"/>
-      <c r="AD27" s="114"/>
-      <c r="AE27" s="114"/>
-      <c r="AF27" s="114"/>
-      <c r="AG27" s="114"/>
-      <c r="AH27" s="114"/>
-      <c r="AI27" s="114"/>
-      <c r="AJ27" s="114"/>
-      <c r="AK27" s="114"/>
-      <c r="AL27" s="114"/>
-    </row>
-    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y27" s="116"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="116"/>
+      <c r="AB27" s="113"/>
+      <c r="AC27" s="113"/>
+      <c r="AD27" s="113"/>
+      <c r="AE27" s="113"/>
+      <c r="AF27" s="113"/>
+      <c r="AG27" s="113"/>
+      <c r="AH27" s="113"/>
+      <c r="AI27" s="113"/>
+      <c r="AJ27" s="113"/>
+      <c r="AK27" s="113"/>
+      <c r="AL27" s="113"/>
+    </row>
+    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -5443,7 +5450,7 @@
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="48" t="s">
         <v>17</v>
       </c>
@@ -5476,7 +5483,7 @@
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -5507,7 +5514,7 @@
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>54</v>
       </c>
@@ -5543,7 +5550,7 @@
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>53</v>
       </c>
@@ -5589,7 +5596,7 @@
       <c r="AK32" s="18"/>
       <c r="AL32" s="17"/>
     </row>
-    <row r="33" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>60</v>
       </c>
@@ -5635,7 +5642,7 @@
       <c r="AK33" s="18"/>
       <c r="AL33" s="17"/>
     </row>
-    <row r="34" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -5675,7 +5682,7 @@
       <c r="AK34" s="18"/>
       <c r="AL34" s="17"/>
     </row>
-    <row r="35" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>61</v>
       </c>
@@ -5721,7 +5728,7 @@
       <c r="AK35" s="18"/>
       <c r="AL35" s="17"/>
     </row>
-    <row r="36" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -5761,7 +5768,7 @@
       <c r="AK36" s="18"/>
       <c r="AL36" s="17"/>
     </row>
-    <row r="37" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>62</v>
       </c>
@@ -5807,7 +5814,7 @@
       <c r="AK37" s="18"/>
       <c r="AL37" s="17"/>
     </row>
-    <row r="38" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>63</v>
       </c>
@@ -5849,7 +5856,7 @@
       <c r="AK38" s="18"/>
       <c r="AL38" s="17"/>
     </row>
-    <row r="39" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>64</v>
       </c>
@@ -5891,7 +5898,7 @@
       <c r="AK39" s="18"/>
       <c r="AL39" s="17"/>
     </row>
-    <row r="40" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -5931,7 +5938,7 @@
       <c r="AK40" s="18"/>
       <c r="AL40" s="17"/>
     </row>
-    <row r="41" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>65</v>
       </c>
@@ -5977,7 +5984,7 @@
       <c r="AK41" s="18"/>
       <c r="AL41" s="17"/>
     </row>
-    <row r="42" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>66</v>
       </c>
@@ -6019,7 +6026,7 @@
       <c r="AK42" s="18"/>
       <c r="AL42" s="17"/>
     </row>
-    <row r="43" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>67</v>
       </c>
@@ -6061,7 +6068,7 @@
       <c r="AK43" s="18"/>
       <c r="AL43" s="17"/>
     </row>
-    <row r="44" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="18"/>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -6101,7 +6108,7 @@
       <c r="AK44" s="18"/>
       <c r="AL44" s="17"/>
     </row>
-    <row r="45" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>57</v>
       </c>
@@ -6147,7 +6154,7 @@
       <c r="AK45" s="18"/>
       <c r="AL45" s="17"/>
     </row>
-    <row r="46" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>59</v>
       </c>
@@ -6189,7 +6196,7 @@
       <c r="AK46" s="18"/>
       <c r="AL46" s="17"/>
     </row>
-    <row r="47" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>58</v>
       </c>
@@ -6231,7 +6238,7 @@
       <c r="AK47" s="18"/>
       <c r="AL47" s="17"/>
     </row>
-    <row r="48" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -6271,7 +6278,7 @@
       <c r="AK48" s="18"/>
       <c r="AL48" s="17"/>
     </row>
-    <row r="49" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -6311,7 +6318,7 @@
       <c r="AK49" s="17"/>
       <c r="AL49" s="17"/>
     </row>
-    <row r="50" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -6351,8 +6358,8 @@
       <c r="AK50" s="8"/>
       <c r="AL50" s="8"/>
     </row>
-    <row r="51" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -6368,7 +6375,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -6384,7 +6391,7 @@
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -6402,6 +6409,88 @@
     </row>
   </sheetData>
   <mergeCells count="98">
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="P27:S27"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="X27:AA27"/>
+    <mergeCell ref="AB27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="X26:AA26"/>
+    <mergeCell ref="AB26:AE26"/>
+    <mergeCell ref="A25:G27"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="A23:G24"/>
+    <mergeCell ref="H23:K24"/>
+    <mergeCell ref="L23:W23"/>
+    <mergeCell ref="X23:AA24"/>
+    <mergeCell ref="AB23:AL23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="AB24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="AJ24:AL24"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="H16:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="L16:W16"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="A16:G17"/>
+    <mergeCell ref="A18:G20"/>
+    <mergeCell ref="AB16:AL16"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AB18:AE18"/>
+    <mergeCell ref="AB19:AE19"/>
+    <mergeCell ref="AB20:AE20"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="A6:E7"/>
+    <mergeCell ref="F6:L7"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="M6:AL6"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AL7"/>
+    <mergeCell ref="V10:AD10"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="AE8:AL8"/>
     <mergeCell ref="AE9:AL9"/>
     <mergeCell ref="AE10:AL10"/>
@@ -6418,88 +6507,6 @@
     <mergeCell ref="X25:AA25"/>
     <mergeCell ref="AB25:AE25"/>
     <mergeCell ref="F13:S13"/>
-    <mergeCell ref="A6:E7"/>
-    <mergeCell ref="F6:L7"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="M6:AL6"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="V7:AD7"/>
-    <mergeCell ref="AE7:AL7"/>
-    <mergeCell ref="V10:AD10"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="V8:AD8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V9:AD9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A16:G17"/>
-    <mergeCell ref="A18:G20"/>
-    <mergeCell ref="AB16:AL16"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AB18:AE18"/>
-    <mergeCell ref="AB19:AE19"/>
-    <mergeCell ref="AB20:AE20"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="H16:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="L16:W16"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A23:G24"/>
-    <mergeCell ref="H23:K24"/>
-    <mergeCell ref="L23:W23"/>
-    <mergeCell ref="X23:AA24"/>
-    <mergeCell ref="AB23:AL23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="AB24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="AJ26:AL26"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="P27:S27"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="X27:AA27"/>
-    <mergeCell ref="AB27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="AJ27:AL27"/>
-    <mergeCell ref="X26:AA26"/>
-    <mergeCell ref="AB26:AE26"/>
-    <mergeCell ref="A25:G27"/>
-    <mergeCell ref="H25:K25"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6519,15 +6526,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626CC06E-9590-4323-BE24-60512668D6F0}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="38" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="38" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6539,34 +6546,34 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
-    </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="119"/>
+      <c r="AJ1" s="119"/>
+      <c r="AK1" s="119"/>
+      <c r="AL1" s="119"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>73</v>
       </c>
@@ -6599,18 +6606,18 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="84"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
       <c r="N3" s="3"/>
@@ -6633,7 +6640,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -6664,7 +6671,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
         <v>74</v>
       </c>
@@ -6697,7 +6704,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43" t="s">
         <v>75</v>
       </c>
@@ -6730,7 +6737,7 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
     </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="43"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -6770,271 +6777,271 @@
       <c r="AK7" s="15"/>
       <c r="AL7" s="15"/>
     </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="140" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
-      <c r="J8" s="131" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="131"/>
-      <c r="L8" s="131"/>
-      <c r="M8" s="131"/>
-      <c r="N8" s="131"/>
-      <c r="O8" s="131"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="131"/>
-      <c r="S8" s="131"/>
-      <c r="T8" s="131"/>
-      <c r="U8" s="131"/>
-      <c r="V8" s="131"/>
-      <c r="W8" s="131"/>
-      <c r="X8" s="131"/>
-      <c r="Y8" s="131"/>
-      <c r="Z8" s="131"/>
-      <c r="AA8" s="131"/>
-      <c r="AB8" s="131"/>
-      <c r="AC8" s="131"/>
-      <c r="AD8" s="131"/>
-      <c r="AE8" s="131"/>
-      <c r="AF8" s="131"/>
-      <c r="AG8" s="131"/>
-      <c r="AH8" s="131"/>
-      <c r="AI8" s="117" t="s">
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="128"/>
+      <c r="N8" s="128"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="128"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
+      <c r="S8" s="128"/>
+      <c r="T8" s="128"/>
+      <c r="U8" s="128"/>
+      <c r="V8" s="128"/>
+      <c r="W8" s="128"/>
+      <c r="X8" s="128"/>
+      <c r="Y8" s="128"/>
+      <c r="Z8" s="128"/>
+      <c r="AA8" s="128"/>
+      <c r="AB8" s="128"/>
+      <c r="AC8" s="128"/>
+      <c r="AD8" s="128"/>
+      <c r="AE8" s="128"/>
+      <c r="AF8" s="128"/>
+      <c r="AG8" s="128"/>
+      <c r="AH8" s="128"/>
+      <c r="AI8" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="AJ8" s="117"/>
-      <c r="AK8" s="117"/>
-      <c r="AL8" s="117"/>
-    </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="117"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="131" t="s">
+      <c r="AJ8" s="118"/>
+      <c r="AK8" s="118"/>
+      <c r="AL8" s="118"/>
+    </row>
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="118"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="128" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="128"/>
+      <c r="O9" s="128" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="131"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="131"/>
-      <c r="N9" s="131"/>
-      <c r="O9" s="131" t="s">
+      <c r="P9" s="128"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="128"/>
+      <c r="S9" s="128"/>
+      <c r="T9" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="131"/>
-      <c r="T9" s="131" t="s">
+      <c r="U9" s="128"/>
+      <c r="V9" s="128"/>
+      <c r="W9" s="128"/>
+      <c r="X9" s="128"/>
+      <c r="Y9" s="128" t="s">
         <v>81</v>
       </c>
-      <c r="U9" s="131"/>
-      <c r="V9" s="131"/>
-      <c r="W9" s="131"/>
-      <c r="X9" s="131"/>
-      <c r="Y9" s="131" t="s">
+      <c r="Z9" s="128"/>
+      <c r="AA9" s="128"/>
+      <c r="AB9" s="128"/>
+      <c r="AC9" s="128"/>
+      <c r="AD9" s="128" t="s">
         <v>82</v>
       </c>
-      <c r="Z9" s="131"/>
-      <c r="AA9" s="131"/>
-      <c r="AB9" s="131"/>
-      <c r="AC9" s="131"/>
-      <c r="AD9" s="131" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE9" s="131"/>
-      <c r="AF9" s="131"/>
-      <c r="AG9" s="131"/>
-      <c r="AH9" s="131"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="117"/>
-    </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="116"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="128" t="s">
+      <c r="AE9" s="128"/>
+      <c r="AF9" s="128"/>
+      <c r="AG9" s="128"/>
+      <c r="AH9" s="128"/>
+      <c r="AI9" s="118"/>
+      <c r="AJ9" s="118"/>
+      <c r="AK9" s="118"/>
+      <c r="AL9" s="118"/>
+    </row>
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="125"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="129" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="131"/>
-      <c r="V10" s="131"/>
-      <c r="W10" s="131"/>
-      <c r="X10" s="131"/>
-      <c r="Y10" s="131"/>
-      <c r="Z10" s="131"/>
-      <c r="AA10" s="131"/>
-      <c r="AB10" s="131"/>
-      <c r="AC10" s="131"/>
-      <c r="AD10" s="131"/>
-      <c r="AE10" s="131"/>
-      <c r="AF10" s="131"/>
-      <c r="AG10" s="131"/>
-      <c r="AH10" s="131"/>
-      <c r="AI10" s="117"/>
-      <c r="AJ10" s="117"/>
-      <c r="AK10" s="117"/>
-      <c r="AL10" s="117"/>
-    </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="128" t="s">
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
+      <c r="P10" s="128"/>
+      <c r="Q10" s="128"/>
+      <c r="R10" s="128"/>
+      <c r="S10" s="128"/>
+      <c r="T10" s="128"/>
+      <c r="U10" s="128"/>
+      <c r="V10" s="128"/>
+      <c r="W10" s="128"/>
+      <c r="X10" s="128"/>
+      <c r="Y10" s="128"/>
+      <c r="Z10" s="128"/>
+      <c r="AA10" s="128"/>
+      <c r="AB10" s="128"/>
+      <c r="AC10" s="128"/>
+      <c r="AD10" s="128"/>
+      <c r="AE10" s="128"/>
+      <c r="AF10" s="128"/>
+      <c r="AG10" s="128"/>
+      <c r="AH10" s="128"/>
+      <c r="AI10" s="118"/>
+      <c r="AJ10" s="118"/>
+      <c r="AK10" s="118"/>
+      <c r="AL10" s="118"/>
+    </row>
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="125"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="131"/>
-      <c r="N11" s="131"/>
-      <c r="O11" s="131"/>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="131"/>
-      <c r="R11" s="131"/>
-      <c r="S11" s="131"/>
-      <c r="T11" s="131"/>
-      <c r="U11" s="131"/>
-      <c r="V11" s="131"/>
-      <c r="W11" s="131"/>
-      <c r="X11" s="131"/>
-      <c r="Y11" s="131"/>
-      <c r="Z11" s="131"/>
-      <c r="AA11" s="131"/>
-      <c r="AB11" s="131"/>
-      <c r="AC11" s="131"/>
-      <c r="AD11" s="131"/>
-      <c r="AE11" s="131"/>
-      <c r="AF11" s="131"/>
-      <c r="AG11" s="131"/>
-      <c r="AH11" s="131"/>
-      <c r="AI11" s="117"/>
-      <c r="AJ11" s="117"/>
-      <c r="AK11" s="117"/>
-      <c r="AL11" s="117"/>
-    </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="116"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="128" t="s">
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="128"/>
+      <c r="P11" s="128"/>
+      <c r="Q11" s="128"/>
+      <c r="R11" s="128"/>
+      <c r="S11" s="128"/>
+      <c r="T11" s="128"/>
+      <c r="U11" s="128"/>
+      <c r="V11" s="128"/>
+      <c r="W11" s="128"/>
+      <c r="X11" s="128"/>
+      <c r="Y11" s="128"/>
+      <c r="Z11" s="128"/>
+      <c r="AA11" s="128"/>
+      <c r="AB11" s="128"/>
+      <c r="AC11" s="128"/>
+      <c r="AD11" s="128"/>
+      <c r="AE11" s="128"/>
+      <c r="AF11" s="128"/>
+      <c r="AG11" s="128"/>
+      <c r="AH11" s="128"/>
+      <c r="AI11" s="118"/>
+      <c r="AJ11" s="118"/>
+      <c r="AK11" s="118"/>
+      <c r="AL11" s="118"/>
+    </row>
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="125"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="129" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="131"/>
-      <c r="N12" s="131"/>
-      <c r="O12" s="131"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="131"/>
-      <c r="S12" s="131"/>
-      <c r="T12" s="131"/>
-      <c r="U12" s="131"/>
-      <c r="V12" s="131"/>
-      <c r="W12" s="131"/>
-      <c r="X12" s="131"/>
-      <c r="Y12" s="131"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="131"/>
-      <c r="AB12" s="131"/>
-      <c r="AC12" s="131"/>
-      <c r="AD12" s="131"/>
-      <c r="AE12" s="131"/>
-      <c r="AF12" s="131"/>
-      <c r="AG12" s="131"/>
-      <c r="AH12" s="131"/>
-      <c r="AI12" s="117"/>
-      <c r="AJ12" s="117"/>
-      <c r="AK12" s="117"/>
-      <c r="AL12" s="117"/>
-    </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="116"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="128" t="s">
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
+      <c r="M12" s="128"/>
+      <c r="N12" s="128"/>
+      <c r="O12" s="128"/>
+      <c r="P12" s="128"/>
+      <c r="Q12" s="128"/>
+      <c r="R12" s="128"/>
+      <c r="S12" s="128"/>
+      <c r="T12" s="128"/>
+      <c r="U12" s="128"/>
+      <c r="V12" s="128"/>
+      <c r="W12" s="128"/>
+      <c r="X12" s="128"/>
+      <c r="Y12" s="128"/>
+      <c r="Z12" s="128"/>
+      <c r="AA12" s="128"/>
+      <c r="AB12" s="128"/>
+      <c r="AC12" s="128"/>
+      <c r="AD12" s="128"/>
+      <c r="AE12" s="128"/>
+      <c r="AF12" s="128"/>
+      <c r="AG12" s="128"/>
+      <c r="AH12" s="128"/>
+      <c r="AI12" s="118"/>
+      <c r="AJ12" s="118"/>
+      <c r="AK12" s="118"/>
+      <c r="AL12" s="118"/>
+    </row>
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="125"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="131"/>
-      <c r="S13" s="131"/>
-      <c r="T13" s="131"/>
-      <c r="U13" s="131"/>
-      <c r="V13" s="131"/>
-      <c r="W13" s="131"/>
-      <c r="X13" s="131"/>
-      <c r="Y13" s="131"/>
-      <c r="Z13" s="131"/>
-      <c r="AA13" s="131"/>
-      <c r="AB13" s="131"/>
-      <c r="AC13" s="131"/>
-      <c r="AD13" s="131"/>
-      <c r="AE13" s="131"/>
-      <c r="AF13" s="131"/>
-      <c r="AG13" s="131"/>
-      <c r="AH13" s="131"/>
-      <c r="AI13" s="117"/>
-      <c r="AJ13" s="117"/>
-      <c r="AK13" s="117"/>
-      <c r="AL13" s="117"/>
-    </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="128"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="128"/>
+      <c r="U13" s="128"/>
+      <c r="V13" s="128"/>
+      <c r="W13" s="128"/>
+      <c r="X13" s="128"/>
+      <c r="Y13" s="128"/>
+      <c r="Z13" s="128"/>
+      <c r="AA13" s="128"/>
+      <c r="AB13" s="128"/>
+      <c r="AC13" s="128"/>
+      <c r="AD13" s="128"/>
+      <c r="AE13" s="128"/>
+      <c r="AF13" s="128"/>
+      <c r="AG13" s="128"/>
+      <c r="AH13" s="128"/>
+      <c r="AI13" s="118"/>
+      <c r="AJ13" s="118"/>
+      <c r="AK13" s="118"/>
+      <c r="AL13" s="118"/>
+    </row>
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="44"/>
       <c r="B14" s="44"/>
       <c r="C14" s="44"/>
@@ -7074,9 +7081,9 @@
       <c r="AK14" s="44"/>
       <c r="AL14" s="44"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="44"/>
       <c r="C15" s="44"/>
@@ -7116,9 +7123,9 @@
       <c r="AK15" s="15"/>
       <c r="AL15" s="15"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
@@ -7158,7 +7165,7 @@
       <c r="AK16" s="50"/>
       <c r="AL16" s="50"/>
     </row>
-    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="47"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -7189,9 +7196,9 @@
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -7222,9 +7229,9 @@
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -7255,9 +7262,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
@@ -7298,9 +7305,9 @@
       <c r="AL20" s="51"/>
       <c r="AM20" s="51"/>
     </row>
-    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="52" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B21" s="53"/>
       <c r="C21" s="53"/>
@@ -7341,9 +7348,9 @@
       <c r="AL21" s="51"/>
       <c r="AM21" s="51"/>
     </row>
-    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B22" s="53"/>
       <c r="C22" s="53"/>
@@ -7384,9 +7391,9 @@
       <c r="AL22" s="51"/>
       <c r="AM22" s="51"/>
     </row>
-    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" s="53"/>
       <c r="C23" s="53"/>
@@ -7427,7 +7434,7 @@
       <c r="AL23" s="51"/>
       <c r="AM23" s="51"/>
     </row>
-    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="47"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -7458,7 +7465,7 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="48" t="s">
         <v>17</v>
       </c>
@@ -7491,7 +7498,7 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="47"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -7522,7 +7529,7 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -7562,7 +7569,7 @@
       <c r="AK27" s="18"/>
       <c r="AL27" s="17"/>
     </row>
-    <row r="28" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -7602,7 +7609,7 @@
       <c r="AK28" s="18"/>
       <c r="AL28" s="17"/>
     </row>
-    <row r="29" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -7642,7 +7649,7 @@
       <c r="AK29" s="17"/>
       <c r="AL29" s="17"/>
     </row>
-    <row r="30" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -7682,8 +7689,8 @@
       <c r="AK30" s="8"/>
       <c r="AL30" s="8"/>
     </row>
-    <row r="31" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -7699,7 +7706,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7715,7 +7722,7 @@
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -7733,6 +7740,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="AI10:AL10"/>
+    <mergeCell ref="AI11:AL11"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="A8:I9"/>
+    <mergeCell ref="A10:C11"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="J11:N11"/>
     <mergeCell ref="A12:C13"/>
     <mergeCell ref="J10:N10"/>
     <mergeCell ref="J13:N13"/>
@@ -7749,30 +7780,6 @@
     <mergeCell ref="T12:X12"/>
     <mergeCell ref="Y12:AC12"/>
     <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="AI10:AL10"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="A8:I9"/>
-    <mergeCell ref="A10:C11"/>
-    <mergeCell ref="O11:S11"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7792,15 +7799,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DF6C1D-A8FC-4DBC-948C-47059EFC8040}">
   <dimension ref="A1:AM31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="39" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="39" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7812,37 +7819,37 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="119"/>
+      <c r="AJ1" s="119"/>
+      <c r="AK1" s="119"/>
+      <c r="AL1" s="119"/>
       <c r="AM1" s="56"/>
     </row>
-    <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -7873,9 +7880,9 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="132"/>
@@ -7906,7 +7913,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="47"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -7937,9 +7944,9 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
-        <v>91</v>
+    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="141" t="s">
+        <v>144</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -7973,9 +7980,9 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
-        <v>92</v>
+    <row r="6" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="141" t="s">
+        <v>145</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -8016,7 +8023,7 @@
       <c r="AL6" s="17"/>
       <c r="AM6" s="17"/>
     </row>
-    <row r="7" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -8057,363 +8064,363 @@
       <c r="AL7" s="17"/>
       <c r="AM7" s="17"/>
     </row>
-    <row r="8" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="117" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
-      <c r="J8" s="117"/>
-      <c r="K8" s="117"/>
-      <c r="L8" s="117"/>
-      <c r="M8" s="117"/>
-      <c r="N8" s="117"/>
-      <c r="O8" s="117"/>
-      <c r="P8" s="117" t="s">
+    <row r="8" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="140" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="118"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="117"/>
-      <c r="R8" s="117"/>
-      <c r="S8" s="117"/>
-      <c r="T8" s="117"/>
-      <c r="U8" s="117"/>
-      <c r="V8" s="117"/>
-      <c r="W8" s="117"/>
-      <c r="X8" s="117"/>
-      <c r="Y8" s="117"/>
-      <c r="Z8" s="117"/>
-      <c r="AA8" s="117"/>
-      <c r="AB8" s="117"/>
-      <c r="AC8" s="117"/>
-      <c r="AD8" s="117"/>
-      <c r="AE8" s="117"/>
-      <c r="AF8" s="117"/>
-      <c r="AG8" s="117"/>
-      <c r="AH8" s="117"/>
-      <c r="AI8" s="117"/>
-      <c r="AJ8" s="117" t="s">
+      <c r="Q8" s="118"/>
+      <c r="R8" s="118"/>
+      <c r="S8" s="118"/>
+      <c r="T8" s="118"/>
+      <c r="U8" s="118"/>
+      <c r="V8" s="118"/>
+      <c r="W8" s="118"/>
+      <c r="X8" s="118"/>
+      <c r="Y8" s="118"/>
+      <c r="Z8" s="118"/>
+      <c r="AA8" s="118"/>
+      <c r="AB8" s="118"/>
+      <c r="AC8" s="118"/>
+      <c r="AD8" s="118"/>
+      <c r="AE8" s="118"/>
+      <c r="AF8" s="118"/>
+      <c r="AG8" s="118"/>
+      <c r="AH8" s="118"/>
+      <c r="AI8" s="118"/>
+      <c r="AJ8" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="AK8" s="117"/>
-      <c r="AL8" s="117"/>
-      <c r="AM8" s="117"/>
-    </row>
-    <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="117"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117"/>
-      <c r="O9" s="117"/>
-      <c r="P9" s="117" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q9" s="117"/>
-      <c r="R9" s="117"/>
-      <c r="S9" s="117"/>
-      <c r="T9" s="117" t="s">
+      <c r="AK8" s="118"/>
+      <c r="AL8" s="118"/>
+      <c r="AM8" s="118"/>
+    </row>
+    <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="118"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="118" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118" t="s">
+        <v>79</v>
+      </c>
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="U9" s="117"/>
-      <c r="V9" s="117"/>
-      <c r="W9" s="117"/>
-      <c r="X9" s="117" t="s">
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118"/>
+      <c r="AA9" s="118"/>
+      <c r="AB9" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="Y9" s="117"/>
-      <c r="Z9" s="117"/>
-      <c r="AA9" s="117"/>
-      <c r="AB9" s="117" t="s">
+      <c r="AC9" s="118"/>
+      <c r="AD9" s="118"/>
+      <c r="AE9" s="118"/>
+      <c r="AF9" s="118" t="s">
         <v>82</v>
       </c>
-      <c r="AC9" s="117"/>
-      <c r="AD9" s="117"/>
-      <c r="AE9" s="117"/>
-      <c r="AF9" s="117" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG9" s="117"/>
-      <c r="AH9" s="117"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="117"/>
-      <c r="AM9" s="117"/>
-    </row>
-    <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="116"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="116"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="117" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="117"/>
-      <c r="K10" s="117"/>
-      <c r="L10" s="117"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="117"/>
-      <c r="O10" s="117"/>
-      <c r="P10" s="117"/>
-      <c r="Q10" s="117"/>
-      <c r="R10" s="117"/>
-      <c r="S10" s="117"/>
-      <c r="T10" s="117"/>
-      <c r="U10" s="117"/>
-      <c r="V10" s="117"/>
-      <c r="W10" s="117"/>
-      <c r="X10" s="117"/>
-      <c r="Y10" s="117"/>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="117"/>
-      <c r="AB10" s="117"/>
-      <c r="AC10" s="117"/>
-      <c r="AD10" s="117"/>
-      <c r="AE10" s="117"/>
-      <c r="AF10" s="117"/>
-      <c r="AG10" s="117"/>
-      <c r="AH10" s="117"/>
-      <c r="AI10" s="117"/>
-      <c r="AJ10" s="117"/>
-      <c r="AK10" s="117"/>
-      <c r="AL10" s="117"/>
-      <c r="AM10" s="117"/>
-    </row>
-    <row r="11" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="117"/>
-      <c r="H11" s="117"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="117"/>
-      <c r="K11" s="117"/>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="117"/>
-      <c r="O11" s="117"/>
-      <c r="P11" s="117"/>
-      <c r="Q11" s="117"/>
-      <c r="R11" s="117"/>
-      <c r="S11" s="117"/>
-      <c r="T11" s="117"/>
-      <c r="U11" s="117"/>
-      <c r="V11" s="117"/>
-      <c r="W11" s="117"/>
-      <c r="X11" s="117"/>
-      <c r="Y11" s="117"/>
-      <c r="Z11" s="117"/>
-      <c r="AA11" s="117"/>
-      <c r="AB11" s="117"/>
-      <c r="AC11" s="117"/>
-      <c r="AD11" s="117"/>
-      <c r="AE11" s="117"/>
-      <c r="AF11" s="117"/>
-      <c r="AG11" s="117"/>
-      <c r="AH11" s="117"/>
-      <c r="AI11" s="117"/>
-      <c r="AJ11" s="117"/>
-      <c r="AK11" s="117"/>
-      <c r="AL11" s="117"/>
-      <c r="AM11" s="117"/>
-    </row>
-    <row r="12" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="116"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="117" t="s">
-        <v>93</v>
-      </c>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
-      <c r="M12" s="117"/>
-      <c r="N12" s="117"/>
-      <c r="O12" s="117"/>
-      <c r="P12" s="117"/>
-      <c r="Q12" s="117"/>
-      <c r="R12" s="117"/>
-      <c r="S12" s="117"/>
-      <c r="T12" s="117"/>
-      <c r="U12" s="117"/>
-      <c r="V12" s="117"/>
-      <c r="W12" s="117"/>
-      <c r="X12" s="117"/>
-      <c r="Y12" s="117"/>
-      <c r="Z12" s="117"/>
-      <c r="AA12" s="117"/>
-      <c r="AB12" s="117"/>
-      <c r="AC12" s="117"/>
-      <c r="AD12" s="117"/>
-      <c r="AE12" s="117"/>
-      <c r="AF12" s="117"/>
-      <c r="AG12" s="117"/>
-      <c r="AH12" s="117"/>
-      <c r="AI12" s="117"/>
-      <c r="AJ12" s="117"/>
-      <c r="AK12" s="117"/>
-      <c r="AL12" s="117"/>
-      <c r="AM12" s="117"/>
-    </row>
-    <row r="13" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="116"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="117"/>
-      <c r="N13" s="117"/>
-      <c r="O13" s="117"/>
-      <c r="P13" s="117"/>
-      <c r="Q13" s="117"/>
-      <c r="R13" s="117"/>
-      <c r="S13" s="117"/>
-      <c r="T13" s="117"/>
-      <c r="U13" s="117"/>
-      <c r="V13" s="117"/>
-      <c r="W13" s="117"/>
-      <c r="X13" s="117"/>
-      <c r="Y13" s="117"/>
-      <c r="Z13" s="117"/>
-      <c r="AA13" s="117"/>
-      <c r="AB13" s="117"/>
-      <c r="AC13" s="117"/>
-      <c r="AD13" s="117"/>
-      <c r="AE13" s="117"/>
-      <c r="AF13" s="117"/>
-      <c r="AG13" s="117"/>
-      <c r="AH13" s="117"/>
-      <c r="AI13" s="117"/>
-      <c r="AJ13" s="117"/>
-      <c r="AK13" s="117"/>
-      <c r="AL13" s="117"/>
-      <c r="AM13" s="117"/>
-    </row>
-    <row r="14" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="116"/>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="117" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="117"/>
-      <c r="M14" s="117"/>
-      <c r="N14" s="117"/>
-      <c r="O14" s="117"/>
-      <c r="P14" s="117"/>
-      <c r="Q14" s="117"/>
-      <c r="R14" s="117"/>
-      <c r="S14" s="117"/>
-      <c r="T14" s="117"/>
-      <c r="U14" s="117"/>
-      <c r="V14" s="117"/>
-      <c r="W14" s="117"/>
-      <c r="X14" s="117"/>
-      <c r="Y14" s="117"/>
-      <c r="Z14" s="117"/>
-      <c r="AA14" s="117"/>
-      <c r="AB14" s="117"/>
-      <c r="AC14" s="117"/>
-      <c r="AD14" s="117"/>
-      <c r="AE14" s="117"/>
-      <c r="AF14" s="117"/>
-      <c r="AG14" s="117"/>
-      <c r="AH14" s="117"/>
-      <c r="AI14" s="117"/>
-      <c r="AJ14" s="117"/>
-      <c r="AK14" s="117"/>
-      <c r="AL14" s="117"/>
-      <c r="AM14" s="117"/>
-    </row>
-    <row r="15" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="116"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
-      <c r="T15" s="117"/>
-      <c r="U15" s="117"/>
-      <c r="V15" s="117"/>
-      <c r="W15" s="117"/>
-      <c r="X15" s="117"/>
-      <c r="Y15" s="117"/>
-      <c r="Z15" s="117"/>
-      <c r="AA15" s="117"/>
-      <c r="AB15" s="117"/>
-      <c r="AC15" s="117"/>
-      <c r="AD15" s="117"/>
-      <c r="AE15" s="117"/>
-      <c r="AF15" s="117"/>
-      <c r="AG15" s="117"/>
-      <c r="AH15" s="117"/>
-      <c r="AI15" s="117"/>
-      <c r="AJ15" s="117"/>
-      <c r="AK15" s="117"/>
-      <c r="AL15" s="117"/>
-      <c r="AM15" s="117"/>
-    </row>
-    <row r="16" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AG9" s="118"/>
+      <c r="AH9" s="118"/>
+      <c r="AI9" s="118"/>
+      <c r="AJ9" s="118"/>
+      <c r="AK9" s="118"/>
+      <c r="AL9" s="118"/>
+      <c r="AM9" s="118"/>
+    </row>
+    <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="125"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="118" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="118"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="118"/>
+      <c r="N10" s="118"/>
+      <c r="O10" s="118"/>
+      <c r="P10" s="118"/>
+      <c r="Q10" s="118"/>
+      <c r="R10" s="118"/>
+      <c r="S10" s="118"/>
+      <c r="T10" s="118"/>
+      <c r="U10" s="118"/>
+      <c r="V10" s="118"/>
+      <c r="W10" s="118"/>
+      <c r="X10" s="118"/>
+      <c r="Y10" s="118"/>
+      <c r="Z10" s="118"/>
+      <c r="AA10" s="118"/>
+      <c r="AB10" s="118"/>
+      <c r="AC10" s="118"/>
+      <c r="AD10" s="118"/>
+      <c r="AE10" s="118"/>
+      <c r="AF10" s="118"/>
+      <c r="AG10" s="118"/>
+      <c r="AH10" s="118"/>
+      <c r="AI10" s="118"/>
+      <c r="AJ10" s="118"/>
+      <c r="AK10" s="118"/>
+      <c r="AL10" s="118"/>
+      <c r="AM10" s="118"/>
+    </row>
+    <row r="11" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="125"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="118" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="118"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="118"/>
+      <c r="K11" s="118"/>
+      <c r="L11" s="118"/>
+      <c r="M11" s="118"/>
+      <c r="N11" s="118"/>
+      <c r="O11" s="118"/>
+      <c r="P11" s="118"/>
+      <c r="Q11" s="118"/>
+      <c r="R11" s="118"/>
+      <c r="S11" s="118"/>
+      <c r="T11" s="118"/>
+      <c r="U11" s="118"/>
+      <c r="V11" s="118"/>
+      <c r="W11" s="118"/>
+      <c r="X11" s="118"/>
+      <c r="Y11" s="118"/>
+      <c r="Z11" s="118"/>
+      <c r="AA11" s="118"/>
+      <c r="AB11" s="118"/>
+      <c r="AC11" s="118"/>
+      <c r="AD11" s="118"/>
+      <c r="AE11" s="118"/>
+      <c r="AF11" s="118"/>
+      <c r="AG11" s="118"/>
+      <c r="AH11" s="118"/>
+      <c r="AI11" s="118"/>
+      <c r="AJ11" s="118"/>
+      <c r="AK11" s="118"/>
+      <c r="AL11" s="118"/>
+      <c r="AM11" s="118"/>
+    </row>
+    <row r="12" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="125"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="118" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="118"/>
+      <c r="T12" s="118"/>
+      <c r="U12" s="118"/>
+      <c r="V12" s="118"/>
+      <c r="W12" s="118"/>
+      <c r="X12" s="118"/>
+      <c r="Y12" s="118"/>
+      <c r="Z12" s="118"/>
+      <c r="AA12" s="118"/>
+      <c r="AB12" s="118"/>
+      <c r="AC12" s="118"/>
+      <c r="AD12" s="118"/>
+      <c r="AE12" s="118"/>
+      <c r="AF12" s="118"/>
+      <c r="AG12" s="118"/>
+      <c r="AH12" s="118"/>
+      <c r="AI12" s="118"/>
+      <c r="AJ12" s="118"/>
+      <c r="AK12" s="118"/>
+      <c r="AL12" s="118"/>
+      <c r="AM12" s="118"/>
+    </row>
+    <row r="13" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="125"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="118" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="118"/>
+      <c r="O13" s="118"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="118"/>
+      <c r="T13" s="118"/>
+      <c r="U13" s="118"/>
+      <c r="V13" s="118"/>
+      <c r="W13" s="118"/>
+      <c r="X13" s="118"/>
+      <c r="Y13" s="118"/>
+      <c r="Z13" s="118"/>
+      <c r="AA13" s="118"/>
+      <c r="AB13" s="118"/>
+      <c r="AC13" s="118"/>
+      <c r="AD13" s="118"/>
+      <c r="AE13" s="118"/>
+      <c r="AF13" s="118"/>
+      <c r="AG13" s="118"/>
+      <c r="AH13" s="118"/>
+      <c r="AI13" s="118"/>
+      <c r="AJ13" s="118"/>
+      <c r="AK13" s="118"/>
+      <c r="AL13" s="118"/>
+      <c r="AM13" s="118"/>
+    </row>
+    <row r="14" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="125"/>
+      <c r="B14" s="125"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="118" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="118"/>
+      <c r="T14" s="118"/>
+      <c r="U14" s="118"/>
+      <c r="V14" s="118"/>
+      <c r="W14" s="118"/>
+      <c r="X14" s="118"/>
+      <c r="Y14" s="118"/>
+      <c r="Z14" s="118"/>
+      <c r="AA14" s="118"/>
+      <c r="AB14" s="118"/>
+      <c r="AC14" s="118"/>
+      <c r="AD14" s="118"/>
+      <c r="AE14" s="118"/>
+      <c r="AF14" s="118"/>
+      <c r="AG14" s="118"/>
+      <c r="AH14" s="118"/>
+      <c r="AI14" s="118"/>
+      <c r="AJ14" s="118"/>
+      <c r="AK14" s="118"/>
+      <c r="AL14" s="118"/>
+      <c r="AM14" s="118"/>
+    </row>
+    <row r="15" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="125"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="118" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="118"/>
+      <c r="L15" s="118"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="118"/>
+      <c r="T15" s="118"/>
+      <c r="U15" s="118"/>
+      <c r="V15" s="118"/>
+      <c r="W15" s="118"/>
+      <c r="X15" s="118"/>
+      <c r="Y15" s="118"/>
+      <c r="Z15" s="118"/>
+      <c r="AA15" s="118"/>
+      <c r="AB15" s="118"/>
+      <c r="AC15" s="118"/>
+      <c r="AD15" s="118"/>
+      <c r="AE15" s="118"/>
+      <c r="AF15" s="118"/>
+      <c r="AG15" s="118"/>
+      <c r="AH15" s="118"/>
+      <c r="AI15" s="118"/>
+      <c r="AJ15" s="118"/>
+      <c r="AK15" s="118"/>
+      <c r="AL15" s="118"/>
+      <c r="AM15" s="118"/>
+    </row>
+    <row r="16" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>38</v>
       </c>
@@ -8456,9 +8463,9 @@
       <c r="AL16" s="17"/>
       <c r="AM16" s="17"/>
     </row>
-    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -8490,7 +8497,7 @@
       <c r="AC17" s="18"/>
       <c r="AD17" s="18"/>
       <c r="AE17" s="15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AF17" s="18"/>
       <c r="AG17" s="18"/>
@@ -8501,9 +8508,9 @@
       <c r="AL17" s="17"/>
       <c r="AM17" s="17"/>
     </row>
-    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -8544,7 +8551,7 @@
       <c r="AL18" s="17"/>
       <c r="AM18" s="17"/>
     </row>
-    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -8585,7 +8592,7 @@
       <c r="AL19" s="17"/>
       <c r="AM19" s="17"/>
     </row>
-    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="48" t="s">
         <v>17</v>
       </c>
@@ -8628,7 +8635,7 @@
       <c r="AL20" s="17"/>
       <c r="AM20" s="17"/>
     </row>
-    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -8669,9 +8676,9 @@
       <c r="AL21" s="17"/>
       <c r="AM21" s="17"/>
     </row>
-    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -8685,56 +8692,56 @@
       <c r="K22" s="19"/>
       <c r="L22" s="19"/>
       <c r="M22" s="49" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O22" s="15"/>
       <c r="P22" s="18"/>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
       <c r="S22" s="49" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="T22" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="U22" s="18"/>
       <c r="V22" s="18"/>
       <c r="W22" s="18"/>
       <c r="X22" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y22" s="15" t="s">
         <v>100</v>
-      </c>
-      <c r="Y22" s="15" t="s">
-        <v>103</v>
       </c>
       <c r="Z22" s="15"/>
       <c r="AA22" s="18"/>
       <c r="AB22" s="15"/>
       <c r="AC22" s="49" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AD22" s="15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="AE22" s="49"/>
       <c r="AF22" s="15"/>
       <c r="AG22" s="18"/>
       <c r="AH22" s="49" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AI22" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AJ22" s="18"/>
       <c r="AK22" s="49"/>
       <c r="AL22" s="15"/>
       <c r="AM22" s="17"/>
     </row>
-    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -8775,7 +8782,7 @@
       <c r="AL23" s="17"/>
       <c r="AM23" s="17"/>
     </row>
-    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -8816,7 +8823,7 @@
       <c r="AL24" s="17"/>
       <c r="AM24" s="17"/>
     </row>
-    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -8857,7 +8864,7 @@
       <c r="AL25" s="17"/>
       <c r="AM25" s="17"/>
     </row>
-    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -8898,7 +8905,7 @@
       <c r="AL26" s="17"/>
       <c r="AM26" s="17"/>
     </row>
-    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -8939,8 +8946,8 @@
       <c r="AL27" s="8"/>
       <c r="AM27" s="8"/>
     </row>
-    <row r="28" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -8956,7 +8963,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -8972,7 +8979,7 @@
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -8990,6 +8997,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A8:O9"/>
+    <mergeCell ref="P8:AI8"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ8:AM9"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="AJ11:AM11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="F11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:W11"/>
+    <mergeCell ref="X11:AA11"/>
+    <mergeCell ref="AB11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:O12"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="T12:W12"/>
+    <mergeCell ref="X12:AA12"/>
+    <mergeCell ref="AB13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="AB12:AE12"/>
+    <mergeCell ref="AJ12:AM12"/>
+    <mergeCell ref="AJ13:AM13"/>
+    <mergeCell ref="A14:E15"/>
+    <mergeCell ref="F14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X14:AA14"/>
     <mergeCell ref="AJ14:AM14"/>
     <mergeCell ref="AJ15:AM15"/>
     <mergeCell ref="F3:R3"/>
@@ -9006,45 +9052,6 @@
     <mergeCell ref="P13:S13"/>
     <mergeCell ref="T13:W13"/>
     <mergeCell ref="X13:AA13"/>
-    <mergeCell ref="A14:E15"/>
-    <mergeCell ref="F14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="X14:AA14"/>
-    <mergeCell ref="AB13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="AB12:AE12"/>
-    <mergeCell ref="AJ12:AM12"/>
-    <mergeCell ref="AJ13:AM13"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:W12"/>
-    <mergeCell ref="X12:AA12"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="AJ11:AM11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="F11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:W11"/>
-    <mergeCell ref="X11:AA11"/>
-    <mergeCell ref="AB11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A8:O9"/>
-    <mergeCell ref="P8:AI8"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ8:AM9"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9064,15 +9071,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7E1E9E-D288-4FD7-BB39-0DBF9B2FAC5D}">
   <dimension ref="A1:AL48"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="38" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="38" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9114,17 +9121,17 @@
       <c r="AK1" s="135"/>
       <c r="AL1" s="135"/>
     </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="136" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="137" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -9156,7 +9163,7 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="132"/>
       <c r="B3" s="132"/>
       <c r="C3" s="132"/>
@@ -9196,7 +9203,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -9236,16 +9243,16 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="135"/>
       <c r="D5" s="135"/>
       <c r="E5" s="135"/>
       <c r="F5" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -9280,7 +9287,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9320,9 +9327,9 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -9362,91 +9369,91 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="137" t="s">
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="137"/>
-      <c r="C8" s="137"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="137"/>
-      <c r="G8" s="137"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
-      <c r="J8" s="138"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="138"/>
-      <c r="N8" s="138"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="138"/>
-      <c r="R8" s="138"/>
-      <c r="S8" s="138"/>
-      <c r="T8" s="138"/>
-      <c r="U8" s="138"/>
-      <c r="V8" s="138"/>
-      <c r="W8" s="138"/>
-      <c r="X8" s="138"/>
-      <c r="Y8" s="138"/>
-      <c r="Z8" s="138"/>
-      <c r="AA8" s="138"/>
-      <c r="AB8" s="138"/>
-      <c r="AC8" s="138"/>
-      <c r="AD8" s="138"/>
-      <c r="AE8" s="138"/>
-      <c r="AF8" s="138"/>
-      <c r="AG8" s="138"/>
-      <c r="AH8" s="138"/>
-      <c r="AI8" s="138"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="133"/>
+      <c r="U8" s="133"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="133"/>
+      <c r="Z8" s="133"/>
+      <c r="AA8" s="133"/>
+      <c r="AB8" s="133"/>
+      <c r="AC8" s="133"/>
+      <c r="AD8" s="133"/>
+      <c r="AE8" s="133"/>
+      <c r="AF8" s="133"/>
+      <c r="AG8" s="133"/>
+      <c r="AH8" s="133"/>
+      <c r="AI8" s="133"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="139" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="139"/>
-      <c r="C9" s="139"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="139"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="114"/>
-      <c r="M9" s="114"/>
-      <c r="N9" s="114"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="114"/>
-      <c r="R9" s="114"/>
-      <c r="S9" s="114"/>
-      <c r="T9" s="114"/>
-      <c r="U9" s="114"/>
-      <c r="V9" s="114"/>
-      <c r="W9" s="114"/>
-      <c r="X9" s="114"/>
-      <c r="Y9" s="114"/>
-      <c r="Z9" s="114"/>
-      <c r="AA9" s="114"/>
-      <c r="AB9" s="114"/>
-      <c r="AC9" s="114"/>
-      <c r="AD9" s="114"/>
-      <c r="AE9" s="114"/>
-      <c r="AF9" s="114"/>
-      <c r="AG9" s="114"/>
-      <c r="AH9" s="114"/>
-      <c r="AI9" s="114"/>
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="134" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="134"/>
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="134"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="113"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="113"/>
+      <c r="W9" s="113"/>
+      <c r="X9" s="113"/>
+      <c r="Y9" s="113"/>
+      <c r="Z9" s="113"/>
+      <c r="AA9" s="113"/>
+      <c r="AB9" s="113"/>
+      <c r="AC9" s="113"/>
+      <c r="AD9" s="113"/>
+      <c r="AE9" s="113"/>
+      <c r="AF9" s="113"/>
+      <c r="AG9" s="113"/>
+      <c r="AH9" s="113"/>
+      <c r="AI9" s="113"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -9486,16 +9493,16 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="135"/>
       <c r="D11" s="135"/>
       <c r="E11" s="135"/>
       <c r="F11" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -9530,9 +9537,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -9572,9 +9579,9 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -9614,9 +9621,9 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -9638,7 +9645,7 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -9658,12 +9665,12 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -9682,7 +9689,7 @@
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -9702,12 +9709,12 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -9726,7 +9733,7 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -9746,12 +9753,12 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -9770,7 +9777,7 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -9790,12 +9797,12 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -9814,7 +9821,7 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -9834,12 +9841,12 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -9876,7 +9883,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -9916,7 +9923,7 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>17</v>
       </c>
@@ -9958,7 +9965,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -9998,9 +10005,9 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -10030,28 +10037,28 @@
       <c r="AF23" s="3"/>
       <c r="AK23" s="58"/>
     </row>
-    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F24" s="59"/>
       <c r="G24" s="59"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
-      <c r="J24" s="134"/>
-      <c r="K24" s="134"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="134"/>
-      <c r="N24" s="134"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="134"/>
-      <c r="Q24" s="134"/>
-      <c r="R24" s="134"/>
-      <c r="S24" s="134"/>
-      <c r="T24" s="134"/>
-      <c r="U24" s="134"/>
-      <c r="V24" s="134"/>
-      <c r="W24" s="134"/>
+      <c r="J24" s="138"/>
+      <c r="K24" s="138"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="138"/>
+      <c r="N24" s="138"/>
+      <c r="O24" s="138"/>
+      <c r="P24" s="138"/>
+      <c r="Q24" s="138"/>
+      <c r="R24" s="138"/>
+      <c r="S24" s="138"/>
+      <c r="T24" s="138"/>
+      <c r="U24" s="138"/>
+      <c r="V24" s="138"/>
+      <c r="W24" s="138"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
@@ -10062,7 +10069,7 @@
       <c r="AF24" s="3"/>
       <c r="AK24" s="58"/>
     </row>
-    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="59"/>
       <c r="F25" s="59"/>
       <c r="G25" s="59"/>
@@ -10092,14 +10099,14 @@
       <c r="AF25" s="3"/>
       <c r="AK25" s="58"/>
     </row>
-    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="120"/>
-      <c r="D26" s="120"/>
+        <v>128</v>
+      </c>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
       <c r="E26" s="59" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F26" s="59"/>
       <c r="G26" s="59"/>
@@ -10129,7 +10136,7 @@
       <c r="AF26" s="3"/>
       <c r="AK26" s="58"/>
     </row>
-    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="59"/>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
@@ -10162,253 +10169,253 @@
       <c r="AF27" s="3"/>
       <c r="AK27" s="58"/>
     </row>
-    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="133" t="s">
+    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="133"/>
-      <c r="C28" s="133"/>
-      <c r="D28" s="133"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="133"/>
-      <c r="J28" s="133"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="116"/>
-      <c r="O28" s="116"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="116"/>
-      <c r="S28" s="116"/>
-      <c r="T28" s="116"/>
-      <c r="U28" s="116"/>
-      <c r="V28" s="116"/>
-      <c r="W28" s="116"/>
-      <c r="X28" s="116"/>
-      <c r="Y28" s="116"/>
-      <c r="Z28" s="116"/>
-      <c r="AA28" s="116"/>
-      <c r="AB28" s="116"/>
-      <c r="AC28" s="116"/>
-      <c r="AD28" s="116"/>
-      <c r="AE28" s="116"/>
-      <c r="AF28" s="116"/>
-      <c r="AG28" s="116"/>
-      <c r="AH28" s="116"/>
-      <c r="AI28" s="116"/>
-      <c r="AJ28" s="116"/>
-      <c r="AK28" s="116"/>
-      <c r="AL28" s="116"/>
-    </row>
-    <row r="29" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="133"/>
-      <c r="B29" s="133"/>
-      <c r="C29" s="133"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
-      <c r="H29" s="133"/>
-      <c r="I29" s="133"/>
-      <c r="J29" s="133"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="116"/>
-      <c r="N29" s="116"/>
-      <c r="O29" s="116"/>
-      <c r="P29" s="116"/>
-      <c r="Q29" s="116"/>
-      <c r="R29" s="116"/>
-      <c r="S29" s="116"/>
-      <c r="T29" s="116"/>
-      <c r="U29" s="116"/>
-      <c r="V29" s="116"/>
-      <c r="W29" s="116"/>
-      <c r="X29" s="116"/>
-      <c r="Y29" s="116"/>
-      <c r="Z29" s="116"/>
-      <c r="AA29" s="116"/>
-      <c r="AB29" s="116"/>
-      <c r="AC29" s="116"/>
-      <c r="AD29" s="116"/>
-      <c r="AE29" s="116"/>
-      <c r="AF29" s="116"/>
-      <c r="AG29" s="116"/>
-      <c r="AH29" s="116"/>
-      <c r="AI29" s="116"/>
-      <c r="AJ29" s="116"/>
-      <c r="AK29" s="116"/>
-      <c r="AL29" s="116"/>
-    </row>
-    <row r="30" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="133" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="133"/>
-      <c r="C30" s="133"/>
-      <c r="D30" s="133"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="133"/>
-      <c r="H30" s="133"/>
-      <c r="I30" s="133"/>
-      <c r="J30" s="133"/>
-      <c r="K30" s="133"/>
-      <c r="L30" s="133"/>
-      <c r="M30" s="133"/>
-      <c r="N30" s="133"/>
-      <c r="O30" s="133"/>
-      <c r="P30" s="133"/>
-      <c r="Q30" s="133"/>
-      <c r="R30" s="133"/>
-      <c r="S30" s="133"/>
-      <c r="T30" s="133"/>
-      <c r="U30" s="133"/>
-      <c r="V30" s="133"/>
-      <c r="W30" s="133"/>
-      <c r="X30" s="133"/>
-      <c r="Y30" s="133"/>
-      <c r="Z30" s="133"/>
-      <c r="AA30" s="133"/>
-      <c r="AB30" s="133"/>
-      <c r="AC30" s="133"/>
-      <c r="AD30" s="133"/>
-      <c r="AE30" s="133"/>
-      <c r="AF30" s="133"/>
-      <c r="AG30" s="133"/>
-      <c r="AH30" s="133"/>
-      <c r="AI30" s="133"/>
-      <c r="AJ30" s="133"/>
-      <c r="AK30" s="133"/>
-      <c r="AL30" s="133"/>
-    </row>
-    <row r="31" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="133"/>
-      <c r="B31" s="133"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="133"/>
-      <c r="I31" s="133"/>
-      <c r="J31" s="133"/>
-      <c r="K31" s="133"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="133"/>
-      <c r="N31" s="133"/>
-      <c r="O31" s="133"/>
-      <c r="P31" s="133"/>
-      <c r="Q31" s="133"/>
-      <c r="R31" s="133"/>
-      <c r="S31" s="133"/>
-      <c r="T31" s="133"/>
-      <c r="U31" s="133"/>
-      <c r="V31" s="133"/>
-      <c r="W31" s="133"/>
-      <c r="X31" s="133"/>
-      <c r="Y31" s="133"/>
-      <c r="Z31" s="133"/>
-      <c r="AA31" s="133"/>
-      <c r="AB31" s="133"/>
-      <c r="AC31" s="133"/>
-      <c r="AD31" s="133"/>
-      <c r="AE31" s="133"/>
-      <c r="AF31" s="133"/>
-      <c r="AG31" s="133"/>
-      <c r="AH31" s="133"/>
-      <c r="AI31" s="133"/>
-      <c r="AJ31" s="133"/>
-      <c r="AK31" s="133"/>
-      <c r="AL31" s="133"/>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A32" s="133" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="133"/>
-      <c r="C32" s="133"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="133"/>
-      <c r="H32" s="133"/>
-      <c r="I32" s="133"/>
-      <c r="J32" s="133"/>
-      <c r="K32" s="133"/>
-      <c r="L32" s="133"/>
-      <c r="M32" s="133"/>
-      <c r="N32" s="133"/>
-      <c r="O32" s="133"/>
-      <c r="P32" s="133"/>
-      <c r="Q32" s="133"/>
-      <c r="R32" s="133"/>
-      <c r="S32" s="133"/>
-      <c r="T32" s="133"/>
-      <c r="U32" s="133"/>
-      <c r="V32" s="133"/>
-      <c r="W32" s="133"/>
-      <c r="X32" s="133"/>
-      <c r="Y32" s="133"/>
-      <c r="Z32" s="133"/>
-      <c r="AA32" s="133"/>
-      <c r="AB32" s="133"/>
-      <c r="AC32" s="133"/>
-      <c r="AD32" s="133"/>
-      <c r="AE32" s="133"/>
-      <c r="AF32" s="133"/>
-      <c r="AG32" s="133"/>
-      <c r="AH32" s="133"/>
-      <c r="AI32" s="133"/>
-      <c r="AJ32" s="133"/>
-      <c r="AK32" s="133"/>
-      <c r="AL32" s="133"/>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A33" s="133"/>
-      <c r="B33" s="133"/>
-      <c r="C33" s="133"/>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="133"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
-      <c r="J33" s="133"/>
-      <c r="K33" s="133"/>
-      <c r="L33" s="133"/>
-      <c r="M33" s="133"/>
-      <c r="N33" s="133"/>
-      <c r="O33" s="133"/>
-      <c r="P33" s="133"/>
-      <c r="Q33" s="133"/>
-      <c r="R33" s="133"/>
-      <c r="S33" s="133"/>
-      <c r="T33" s="133"/>
-      <c r="U33" s="133"/>
-      <c r="V33" s="133"/>
-      <c r="W33" s="133"/>
-      <c r="X33" s="133"/>
-      <c r="Y33" s="133"/>
-      <c r="Z33" s="133"/>
-      <c r="AA33" s="133"/>
-      <c r="AB33" s="133"/>
-      <c r="AC33" s="133"/>
-      <c r="AD33" s="133"/>
-      <c r="AE33" s="133"/>
-      <c r="AF33" s="133"/>
-      <c r="AG33" s="133"/>
-      <c r="AH33" s="133"/>
-      <c r="AI33" s="133"/>
-      <c r="AJ33" s="133"/>
-      <c r="AK33" s="133"/>
-      <c r="AL33" s="133"/>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="B28" s="139"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="139"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="125"/>
+      <c r="N28" s="125"/>
+      <c r="O28" s="125"/>
+      <c r="P28" s="125"/>
+      <c r="Q28" s="125"/>
+      <c r="R28" s="125"/>
+      <c r="S28" s="125"/>
+      <c r="T28" s="125"/>
+      <c r="U28" s="125"/>
+      <c r="V28" s="125"/>
+      <c r="W28" s="125"/>
+      <c r="X28" s="125"/>
+      <c r="Y28" s="125"/>
+      <c r="Z28" s="125"/>
+      <c r="AA28" s="125"/>
+      <c r="AB28" s="125"/>
+      <c r="AC28" s="125"/>
+      <c r="AD28" s="125"/>
+      <c r="AE28" s="125"/>
+      <c r="AF28" s="125"/>
+      <c r="AG28" s="125"/>
+      <c r="AH28" s="125"/>
+      <c r="AI28" s="125"/>
+      <c r="AJ28" s="125"/>
+      <c r="AK28" s="125"/>
+      <c r="AL28" s="125"/>
+    </row>
+    <row r="29" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="139"/>
+      <c r="B29" s="139"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="139"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="139"/>
+      <c r="K29" s="125"/>
+      <c r="L29" s="125"/>
+      <c r="M29" s="125"/>
+      <c r="N29" s="125"/>
+      <c r="O29" s="125"/>
+      <c r="P29" s="125"/>
+      <c r="Q29" s="125"/>
+      <c r="R29" s="125"/>
+      <c r="S29" s="125"/>
+      <c r="T29" s="125"/>
+      <c r="U29" s="125"/>
+      <c r="V29" s="125"/>
+      <c r="W29" s="125"/>
+      <c r="X29" s="125"/>
+      <c r="Y29" s="125"/>
+      <c r="Z29" s="125"/>
+      <c r="AA29" s="125"/>
+      <c r="AB29" s="125"/>
+      <c r="AC29" s="125"/>
+      <c r="AD29" s="125"/>
+      <c r="AE29" s="125"/>
+      <c r="AF29" s="125"/>
+      <c r="AG29" s="125"/>
+      <c r="AH29" s="125"/>
+      <c r="AI29" s="125"/>
+      <c r="AJ29" s="125"/>
+      <c r="AK29" s="125"/>
+      <c r="AL29" s="125"/>
+    </row>
+    <row r="30" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="139" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="139"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="139"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="139"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="139"/>
+      <c r="M30" s="139"/>
+      <c r="N30" s="139"/>
+      <c r="O30" s="139"/>
+      <c r="P30" s="139"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="139"/>
+      <c r="S30" s="139"/>
+      <c r="T30" s="139"/>
+      <c r="U30" s="139"/>
+      <c r="V30" s="139"/>
+      <c r="W30" s="139"/>
+      <c r="X30" s="139"/>
+      <c r="Y30" s="139"/>
+      <c r="Z30" s="139"/>
+      <c r="AA30" s="139"/>
+      <c r="AB30" s="139"/>
+      <c r="AC30" s="139"/>
+      <c r="AD30" s="139"/>
+      <c r="AE30" s="139"/>
+      <c r="AF30" s="139"/>
+      <c r="AG30" s="139"/>
+      <c r="AH30" s="139"/>
+      <c r="AI30" s="139"/>
+      <c r="AJ30" s="139"/>
+      <c r="AK30" s="139"/>
+      <c r="AL30" s="139"/>
+    </row>
+    <row r="31" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="139"/>
+      <c r="B31" s="139"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="139"/>
+      <c r="K31" s="139"/>
+      <c r="L31" s="139"/>
+      <c r="M31" s="139"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="139"/>
+      <c r="P31" s="139"/>
+      <c r="Q31" s="139"/>
+      <c r="R31" s="139"/>
+      <c r="S31" s="139"/>
+      <c r="T31" s="139"/>
+      <c r="U31" s="139"/>
+      <c r="V31" s="139"/>
+      <c r="W31" s="139"/>
+      <c r="X31" s="139"/>
+      <c r="Y31" s="139"/>
+      <c r="Z31" s="139"/>
+      <c r="AA31" s="139"/>
+      <c r="AB31" s="139"/>
+      <c r="AC31" s="139"/>
+      <c r="AD31" s="139"/>
+      <c r="AE31" s="139"/>
+      <c r="AF31" s="139"/>
+      <c r="AG31" s="139"/>
+      <c r="AH31" s="139"/>
+      <c r="AI31" s="139"/>
+      <c r="AJ31" s="139"/>
+      <c r="AK31" s="139"/>
+      <c r="AL31" s="139"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A32" s="139" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="139"/>
+      <c r="C32" s="139"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139"/>
+      <c r="J32" s="139"/>
+      <c r="K32" s="139"/>
+      <c r="L32" s="139"/>
+      <c r="M32" s="139"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="139"/>
+      <c r="P32" s="139"/>
+      <c r="Q32" s="139"/>
+      <c r="R32" s="139"/>
+      <c r="S32" s="139"/>
+      <c r="T32" s="139"/>
+      <c r="U32" s="139"/>
+      <c r="V32" s="139"/>
+      <c r="W32" s="139"/>
+      <c r="X32" s="139"/>
+      <c r="Y32" s="139"/>
+      <c r="Z32" s="139"/>
+      <c r="AA32" s="139"/>
+      <c r="AB32" s="139"/>
+      <c r="AC32" s="139"/>
+      <c r="AD32" s="139"/>
+      <c r="AE32" s="139"/>
+      <c r="AF32" s="139"/>
+      <c r="AG32" s="139"/>
+      <c r="AH32" s="139"/>
+      <c r="AI32" s="139"/>
+      <c r="AJ32" s="139"/>
+      <c r="AK32" s="139"/>
+      <c r="AL32" s="139"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A33" s="139"/>
+      <c r="B33" s="139"/>
+      <c r="C33" s="139"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="139"/>
+      <c r="L33" s="139"/>
+      <c r="M33" s="139"/>
+      <c r="N33" s="139"/>
+      <c r="O33" s="139"/>
+      <c r="P33" s="139"/>
+      <c r="Q33" s="139"/>
+      <c r="R33" s="139"/>
+      <c r="S33" s="139"/>
+      <c r="T33" s="139"/>
+      <c r="U33" s="139"/>
+      <c r="V33" s="139"/>
+      <c r="W33" s="139"/>
+      <c r="X33" s="139"/>
+      <c r="Y33" s="139"/>
+      <c r="Z33" s="139"/>
+      <c r="AA33" s="139"/>
+      <c r="AB33" s="139"/>
+      <c r="AC33" s="139"/>
+      <c r="AD33" s="139"/>
+      <c r="AE33" s="139"/>
+      <c r="AF33" s="139"/>
+      <c r="AG33" s="139"/>
+      <c r="AH33" s="139"/>
+      <c r="AI33" s="139"/>
+      <c r="AJ33" s="139"/>
+      <c r="AK33" s="139"/>
+      <c r="AL33" s="139"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="59"/>
       <c r="F34" s="59"/>
       <c r="G34" s="59"/>
@@ -10444,7 +10451,7 @@
       <c r="AK34" s="62"/>
       <c r="AL34" s="61"/>
     </row>
-    <row r="35" spans="1:38" ht="15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A35" s="63" t="s">
         <v>17</v>
       </c>
@@ -10483,7 +10490,7 @@
       <c r="AK35" s="61"/>
       <c r="AL35" s="61"/>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="58"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -10520,7 +10527,7 @@
       <c r="AK36" s="61"/>
       <c r="AL36" s="61"/>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>54</v>
       </c>
@@ -10562,7 +10569,7 @@
       <c r="AK37" s="61"/>
       <c r="AL37" s="61"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="T38" s="61"/>
       <c r="U38" s="61"/>
       <c r="V38" s="61"/>
@@ -10579,9 +10586,9 @@
       <c r="AG38" s="61"/>
       <c r="AH38" s="61"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="59" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T39" s="61"/>
       <c r="U39" s="61"/>
@@ -10599,9 +10606,9 @@
       <c r="AG39" s="61"/>
       <c r="AH39" s="61"/>
     </row>
-    <row r="40" spans="1:38" ht="15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A40" s="64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="T40" s="61"/>
       <c r="U40" s="61"/>
@@ -10619,7 +10626,7 @@
       <c r="AG40" s="61"/>
       <c r="AH40" s="61"/>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="T41" s="61"/>
       <c r="U41" s="61"/>
       <c r="V41" s="61"/>
@@ -10636,12 +10643,12 @@
       <c r="AG41" s="61"/>
       <c r="AH41" s="61"/>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="T42" s="61" t="s">
         <v>136</v>
-      </c>
-      <c r="T42" s="61" t="s">
-        <v>139</v>
       </c>
       <c r="U42" s="61"/>
       <c r="V42" s="61"/>
@@ -10658,7 +10665,7 @@
       <c r="AG42" s="61"/>
       <c r="AH42" s="61"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="65"/>
       <c r="T43" s="61"/>
       <c r="U43" s="61"/>
@@ -10676,12 +10683,12 @@
       <c r="AG43" s="61"/>
       <c r="AH43" s="61"/>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="61" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="T44" s="61" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="U44" s="61"/>
       <c r="V44" s="61"/>
@@ -10698,7 +10705,7 @@
       <c r="AG44" s="61"/>
       <c r="AH44" s="61"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="T45" s="61"/>
       <c r="U45" s="61"/>
       <c r="V45" s="61"/>
@@ -10715,12 +10722,12 @@
       <c r="AG45" s="61"/>
       <c r="AH45" s="61"/>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" s="61" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="T46" s="61" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="U46" s="66"/>
       <c r="V46" s="66"/>
@@ -10737,7 +10744,7 @@
       <c r="AG46" s="61"/>
       <c r="AH46" s="61"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="T47" s="61"/>
       <c r="U47" s="61"/>
       <c r="V47" s="61"/>
@@ -10754,7 +10761,7 @@
       <c r="AG47" s="61"/>
       <c r="AH47" s="61"/>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="T48" s="61"/>
       <c r="U48" s="61"/>
       <c r="V48" s="61"/>
@@ -10773,27 +10780,11 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="AC8:AI8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="V9:AB9"/>
-    <mergeCell ref="AC9:AI9"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:U8"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="J24:W24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A28:J29"/>
-    <mergeCell ref="K28:Q29"/>
-    <mergeCell ref="R28:X29"/>
+    <mergeCell ref="A32:J33"/>
+    <mergeCell ref="K32:Q33"/>
+    <mergeCell ref="R32:X33"/>
+    <mergeCell ref="Y32:AE33"/>
+    <mergeCell ref="AF32:AL33"/>
     <mergeCell ref="Y28:AE29"/>
     <mergeCell ref="AF28:AL29"/>
     <mergeCell ref="A30:J31"/>
@@ -10801,11 +10792,27 @@
     <mergeCell ref="R30:X31"/>
     <mergeCell ref="Y30:AE31"/>
     <mergeCell ref="AF30:AL31"/>
-    <mergeCell ref="A32:J33"/>
-    <mergeCell ref="K32:Q33"/>
-    <mergeCell ref="R32:X33"/>
-    <mergeCell ref="Y32:AE33"/>
-    <mergeCell ref="AF32:AL33"/>
+    <mergeCell ref="J24:W24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A28:J29"/>
+    <mergeCell ref="K28:Q29"/>
+    <mergeCell ref="R28:X29"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:U8"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="AC8:AI8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="V9:AB9"/>
+    <mergeCell ref="AC9:AI9"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919BBC50-4755-4954-9940-827955AA76E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063AA031-2300-4AFF-8E7A-BE2B22022547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -315,42 +315,42 @@
   </si>
   <si>
     <t>Pilling Resistance</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>ICI Pilling Box:</t>
   </si>
   <si>
     <t>Original</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Sample</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Cycle</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Rating</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Pilling</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Fuzzing</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Matting</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Pilling grading scheme</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -375,73 +375,73 @@
       </rPr>
       <t>: Not applicable</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Fuzzing grading scheme</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Matting grading scheme</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">1 Severe pilling- pills of varying size </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> specimen surface</t>
   </si>
   <si>
     <t>and density covering the whole of the</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>5 No change</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>4 partially formed pills</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">3 Moderate pilling- pills of varying  </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">size and density partially covering </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>the specimen surface</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>2 Distinct pilling- pills of varying</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">size and density covering a large </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>proportion of the specimen surface</t>
   </si>
   <si>
     <t>4 Slight surface fuzzing</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>3Moderate surface fuzzing</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>2 Distinct surface fuzzing</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>1 Dense surface fuzzing</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Martindale:</t>
@@ -583,7 +583,7 @@
   </si>
   <si>
     <t>*1: Testing sample happened (Y.P.O./S.T.B./F.B./F.T.S) before achieving the (3mm/4mm/6mm/1/4inch ) opening</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
     <t>*2: Testing sample happened (Y.P.O./S.T.B./F.B./F.T.S) before achieving the (3mm/4mm/6mm/1/4inch ) opening</t>
@@ -618,7 +618,7 @@
   </si>
   <si>
     <t>Cycle：</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Abrasion Resistance</t>
@@ -715,31 +715,31 @@
   </si>
   <si>
     <t xml:space="preserve">Remark: </t>
-    <phoneticPr fontId="32" type="noConversion"/>
+    <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
     <t>Over 50001 rubs                   Every 10000 rubs</t>
-    <phoneticPr fontId="32" type="noConversion"/>
+    <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
     <t>Up to 6000 rubs                    Every 1000 rubs</t>
-    <phoneticPr fontId="32" type="noConversion"/>
+    <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
     <t>Sample  Unit(N)</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
     <t>Sample  Unit(gf)</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
-    <t>Warp /Length yarns torn (gf)</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weft / Width yarns torn (gf)</t>
-    <phoneticPr fontId="32" type="noConversion"/>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warp /Length yarns torn (N)</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weft / Width yarns torn (N)</t>
+    <phoneticPr fontId="33" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -749,12 +749,19 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1171,10 +1178,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1186,157 +1193,166 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1351,22 +1367,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1375,175 +1391,166 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1839,25 +1846,25 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="70"/>
+      <c r="T1" s="70"/>
+      <c r="U1" s="70"/>
+      <c r="V1" s="70"/>
+      <c r="W1" s="70"/>
+      <c r="X1" s="70"/>
+      <c r="Y1" s="70"/>
+      <c r="Z1" s="70"/>
+      <c r="AA1" s="70"/>
+      <c r="AB1" s="70"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1889,14 +1896,14 @@
       <c r="AB2" s="3"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2093,86 +2100,86 @@
       <c r="AB9" s="3"/>
     </row>
     <row r="10" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="68" t="s">
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="70" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="71"/>
-      <c r="AB10" s="72"/>
+      <c r="Z10" s="74"/>
+      <c r="AA10" s="74"/>
+      <c r="AB10" s="75"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="68" t="s">
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="68" t="s">
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="68" t="s">
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="68" t="s">
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="82"/>
-      <c r="U11" s="68" t="s">
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="69"/>
-      <c r="W11" s="69"/>
-      <c r="X11" s="83"/>
-      <c r="Y11" s="73"/>
-      <c r="Z11" s="74"/>
-      <c r="AA11" s="74"/>
-      <c r="AB11" s="75"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="72"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="76"/>
+      <c r="Z11" s="77"/>
+      <c r="AA11" s="77"/>
+      <c r="AB11" s="78"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="85"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="87"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2199,10 +2206,10 @@
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="85"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="87"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -2229,10 +2236,10 @@
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="85"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="87"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2259,10 +2266,10 @@
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="85"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="87"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2289,10 +2296,10 @@
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="85"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="87"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -2459,11 +2466,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="E10:X10"/>
     <mergeCell ref="Y10:AB11"/>
@@ -2474,8 +2476,13 @@
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -2514,32 +2521,32 @@
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="88"/>
-      <c r="Z1" s="88"/>
-      <c r="AA1" s="88"/>
-      <c r="AB1" s="88"/>
-      <c r="AC1" s="88"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="88"/>
-      <c r="AF1" s="88"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="88"/>
-      <c r="AJ1" s="88"/>
-      <c r="AK1" s="88"/>
-      <c r="AL1" s="88"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="103"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
+      <c r="Z1" s="103"/>
+      <c r="AA1" s="103"/>
+      <c r="AB1" s="103"/>
+      <c r="AC1" s="103"/>
+      <c r="AD1" s="103"/>
+      <c r="AE1" s="103"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="103"/>
+      <c r="AH1" s="103"/>
+      <c r="AI1" s="103"/>
+      <c r="AJ1" s="103"/>
+      <c r="AK1" s="103"/>
+      <c r="AL1" s="103"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -2575,17 +2582,17 @@
       <c r="AF2" s="21"/>
     </row>
     <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="103"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -2802,45 +2809,45 @@
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="95" t="s">
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="95" t="s">
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="96"/>
-      <c r="Y10" s="96"/>
-      <c r="Z10" s="96"/>
-      <c r="AA10" s="96"/>
-      <c r="AB10" s="96"/>
-      <c r="AC10" s="96"/>
-      <c r="AD10" s="96"/>
-      <c r="AE10" s="96"/>
-      <c r="AF10" s="96"/>
-      <c r="AG10" s="96"/>
-      <c r="AH10" s="96"/>
-      <c r="AI10" s="96"/>
-      <c r="AJ10" s="96"/>
-      <c r="AK10" s="96"/>
-      <c r="AL10" s="97"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="105"/>
+      <c r="S10" s="105"/>
+      <c r="T10" s="105"/>
+      <c r="U10" s="105"/>
+      <c r="V10" s="105"/>
+      <c r="W10" s="105"/>
+      <c r="X10" s="105"/>
+      <c r="Y10" s="105"/>
+      <c r="Z10" s="105"/>
+      <c r="AA10" s="105"/>
+      <c r="AB10" s="105"/>
+      <c r="AC10" s="105"/>
+      <c r="AD10" s="105"/>
+      <c r="AE10" s="105"/>
+      <c r="AF10" s="105"/>
+      <c r="AG10" s="105"/>
+      <c r="AH10" s="105"/>
+      <c r="AI10" s="105"/>
+      <c r="AJ10" s="105"/>
+      <c r="AK10" s="105"/>
+      <c r="AL10" s="106"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
@@ -2850,62 +2857,62 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="27"/>
-      <c r="F11" s="95" t="s">
+      <c r="F11" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="95" t="s">
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="95" t="s">
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="105"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="97"/>
-      <c r="U11" s="95" t="s">
+      <c r="Q11" s="105"/>
+      <c r="R11" s="105"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="106"/>
+      <c r="U11" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="96"/>
-      <c r="W11" s="96"/>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="97"/>
-      <c r="Z11" s="95" t="s">
+      <c r="V11" s="105"/>
+      <c r="W11" s="105"/>
+      <c r="X11" s="105"/>
+      <c r="Y11" s="106"/>
+      <c r="Z11" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="97"/>
-      <c r="AE11" s="95" t="s">
+      <c r="AA11" s="105"/>
+      <c r="AB11" s="105"/>
+      <c r="AC11" s="105"/>
+      <c r="AD11" s="106"/>
+      <c r="AE11" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="96"/>
-      <c r="AG11" s="96"/>
-      <c r="AH11" s="96"/>
-      <c r="AI11" s="97"/>
-      <c r="AJ11" s="98" t="s">
+      <c r="AF11" s="105"/>
+      <c r="AG11" s="105"/>
+      <c r="AH11" s="105"/>
+      <c r="AI11" s="106"/>
+      <c r="AJ11" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="99"/>
-      <c r="AL11" s="100"/>
+      <c r="AK11" s="108"/>
+      <c r="AL11" s="109"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="91"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="90"/>
       <c r="F12" s="28"/>
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
@@ -2941,11 +2948,11 @@
       <c r="AL12" s="33"/>
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="94"/>
+      <c r="A13" s="91"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
       <c r="F13" s="34"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
@@ -2981,13 +2988,13 @@
       <c r="AL13" s="38"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="91"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="90"/>
       <c r="F14" s="28"/>
       <c r="G14" s="29"/>
       <c r="H14" s="29"/>
@@ -3023,11 +3030,11 @@
       <c r="AL14" s="33"/>
     </row>
     <row r="15" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="92"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="94"/>
+      <c r="A15" s="91"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="93"/>
       <c r="F15" s="34"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
@@ -3063,13 +3070,13 @@
       <c r="AL15" s="38"/>
     </row>
     <row r="16" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="89" t="s">
+      <c r="A16" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="91"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="90"/>
       <c r="F16" s="28"/>
       <c r="G16" s="29"/>
       <c r="H16" s="29"/>
@@ -3105,11 +3112,11 @@
       <c r="AL16" s="33"/>
     </row>
     <row r="17" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="92"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94"/>
+      <c r="A17" s="91"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93"/>
       <c r="F17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
@@ -3145,13 +3152,13 @@
       <c r="AL17" s="38"/>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="90"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="90"/>
-      <c r="E18" s="91"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="90"/>
       <c r="F18" s="28"/>
       <c r="G18" s="29"/>
       <c r="H18" s="29"/>
@@ -3187,11 +3194,11 @@
       <c r="AL18" s="33"/>
     </row>
     <row r="19" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="92"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="94"/>
+      <c r="A19" s="91"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="93"/>
       <c r="F19" s="34"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
@@ -3227,13 +3234,13 @@
       <c r="AL19" s="38"/>
     </row>
     <row r="20" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="91"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="90"/>
       <c r="F20" s="28"/>
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
@@ -3269,11 +3276,11 @@
       <c r="AL20" s="33"/>
     </row>
     <row r="21" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="92"/>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="94"/>
+      <c r="A21" s="91"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93"/>
       <c r="F21" s="34"/>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
@@ -3309,13 +3316,13 @@
       <c r="AL21" s="38"/>
     </row>
     <row r="22" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="91"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="90"/>
       <c r="F22" s="28"/>
       <c r="G22" s="29"/>
       <c r="H22" s="29"/>
@@ -3351,11 +3358,11 @@
       <c r="AL22" s="33"/>
     </row>
     <row r="23" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="92"/>
-      <c r="B23" s="93"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="94"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="93"/>
       <c r="F23" s="34"/>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
@@ -3391,13 +3398,13 @@
       <c r="AL23" s="38"/>
     </row>
     <row r="24" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="91"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="90"/>
       <c r="F24" s="28"/>
       <c r="G24" s="29"/>
       <c r="H24" s="29"/>
@@ -3433,11 +3440,11 @@
       <c r="AL24" s="33"/>
     </row>
     <row r="25" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="92"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="94"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="93"/>
       <c r="F25" s="34"/>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
@@ -3473,13 +3480,13 @@
       <c r="AL25" s="38"/>
     </row>
     <row r="26" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="91"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="90"/>
       <c r="F26" s="28"/>
       <c r="G26" s="29"/>
       <c r="H26" s="29"/>
@@ -3515,11 +3522,11 @@
       <c r="AL26" s="33"/>
     </row>
     <row r="27" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="92"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="94"/>
+      <c r="A27" s="91"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="93"/>
       <c r="F27" s="34"/>
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
@@ -3555,13 +3562,13 @@
       <c r="AL27" s="38"/>
     </row>
     <row r="28" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="91"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="28"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
@@ -3597,11 +3604,11 @@
       <c r="AL28" s="33"/>
     </row>
     <row r="29" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="92"/>
-      <c r="B29" s="93"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="94"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="93"/>
       <c r="F29" s="34"/>
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
@@ -3637,13 +3644,13 @@
       <c r="AL29" s="38"/>
     </row>
     <row r="30" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="89" t="s">
+      <c r="A30" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="91"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="28"/>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -3679,11 +3686,11 @@
       <c r="AL30" s="33"/>
     </row>
     <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="92"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="94"/>
+      <c r="A31" s="91"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="93"/>
       <c r="F31" s="34"/>
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
@@ -3719,13 +3726,13 @@
       <c r="AL31" s="38"/>
     </row>
     <row r="32" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="89" t="s">
+      <c r="A32" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
       <c r="F32" s="28"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
@@ -3761,11 +3768,11 @@
       <c r="AL32" s="33"/>
     </row>
     <row r="33" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="92"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
       <c r="F33" s="34"/>
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
@@ -3801,13 +3808,13 @@
       <c r="AL33" s="38"/>
     </row>
     <row r="34" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="89" t="s">
+      <c r="A34" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="90"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
       <c r="F34" s="28"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29"/>
@@ -3843,11 +3850,11 @@
       <c r="AL34" s="33"/>
     </row>
     <row r="35" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="92"/>
-      <c r="B35" s="93"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="94"/>
+      <c r="A35" s="91"/>
+      <c r="B35" s="92"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="93"/>
       <c r="F35" s="34"/>
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
@@ -3883,13 +3890,13 @@
       <c r="AL35" s="38"/>
     </row>
     <row r="36" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="104" t="s">
+      <c r="A36" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="105"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="106"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="96"/>
       <c r="F36" s="28"/>
       <c r="G36" s="29"/>
       <c r="H36" s="29"/>
@@ -3925,11 +3932,11 @@
       <c r="AL36" s="33"/>
     </row>
     <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="107"/>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="109"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="99"/>
       <c r="F37" s="34"/>
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
@@ -3998,21 +4005,21 @@
       <c r="AF38" s="21"/>
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A39" s="110" t="s">
+      <c r="A39" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="110"/>
-      <c r="C39" s="110"/>
-      <c r="D39" s="111" t="s">
+      <c r="B39" s="100"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="111"/>
-      <c r="F39" s="111"/>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
-      <c r="I39" s="111"/>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="101"/>
+      <c r="H39" s="101"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
       <c r="L39" s="21"/>
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
@@ -4036,19 +4043,19 @@
       <c r="AF39" s="21"/>
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A40" s="110"/>
-      <c r="B40" s="110"/>
-      <c r="C40" s="110"/>
-      <c r="D40" s="112" t="s">
+      <c r="A40" s="100"/>
+      <c r="B40" s="100"/>
+      <c r="C40" s="100"/>
+      <c r="D40" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="112"/>
-      <c r="F40" s="112"/>
-      <c r="G40" s="112"/>
-      <c r="H40" s="112"/>
-      <c r="I40" s="112"/>
-      <c r="J40" s="112"/>
-      <c r="K40" s="112"/>
+      <c r="E40" s="102"/>
+      <c r="F40" s="102"/>
+      <c r="G40" s="102"/>
+      <c r="H40" s="102"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="102"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
@@ -4267,18 +4274,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="A24:E25"/>
-    <mergeCell ref="A26:E27"/>
-    <mergeCell ref="A28:E29"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="A22:E23"/>
@@ -4295,8 +4290,20 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="A24:E25"/>
+    <mergeCell ref="A26:E27"/>
+    <mergeCell ref="A28:E29"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -4334,32 +4341,32 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="119"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -4399,18 +4406,18 @@
         <v>45</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -4431,13 +4438,13 @@
       <c r="A4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -4496,216 +4503,216 @@
       <c r="AK5" s="7"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="115" t="s">
+      <c r="B6" s="117"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115" t="s">
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115"/>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115"/>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
-      <c r="AA6" s="115"/>
-      <c r="AB6" s="115"/>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115"/>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="115"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
+      <c r="S6" s="118"/>
+      <c r="T6" s="118"/>
+      <c r="U6" s="118"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="118"/>
+      <c r="X6" s="118"/>
+      <c r="Y6" s="118"/>
+      <c r="Z6" s="118"/>
+      <c r="AA6" s="118"/>
+      <c r="AB6" s="118"/>
+      <c r="AC6" s="118"/>
+      <c r="AD6" s="118"/>
+      <c r="AE6" s="118"/>
+      <c r="AF6" s="118"/>
+      <c r="AG6" s="118"/>
+      <c r="AH6" s="118"/>
+      <c r="AI6" s="118"/>
+      <c r="AJ6" s="118"/>
+      <c r="AK6" s="118"/>
+      <c r="AL6" s="118"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="118"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="121" t="s">
+      <c r="A7" s="117"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="122"/>
-      <c r="Q7" s="122"/>
-      <c r="R7" s="122"/>
-      <c r="S7" s="122"/>
-      <c r="T7" s="122"/>
-      <c r="U7" s="123"/>
-      <c r="V7" s="121" t="s">
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="123"/>
+      <c r="U7" s="124"/>
+      <c r="V7" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="W7" s="122"/>
-      <c r="X7" s="122"/>
-      <c r="Y7" s="122"/>
-      <c r="Z7" s="122"/>
-      <c r="AA7" s="122"/>
-      <c r="AB7" s="122"/>
-      <c r="AC7" s="122"/>
-      <c r="AD7" s="123"/>
-      <c r="AE7" s="124" t="s">
+      <c r="W7" s="123"/>
+      <c r="X7" s="123"/>
+      <c r="Y7" s="123"/>
+      <c r="Z7" s="123"/>
+      <c r="AA7" s="123"/>
+      <c r="AB7" s="123"/>
+      <c r="AC7" s="123"/>
+      <c r="AD7" s="124"/>
+      <c r="AE7" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="AF7" s="124"/>
-      <c r="AG7" s="124"/>
-      <c r="AH7" s="124"/>
-      <c r="AI7" s="124"/>
-      <c r="AJ7" s="124"/>
-      <c r="AK7" s="124"/>
-      <c r="AL7" s="124"/>
+      <c r="AF7" s="119"/>
+      <c r="AG7" s="119"/>
+      <c r="AH7" s="119"/>
+      <c r="AI7" s="119"/>
+      <c r="AJ7" s="119"/>
+      <c r="AK7" s="119"/>
+      <c r="AL7" s="119"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="125"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="120"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="82"/>
-      <c r="V8" s="120"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="83"/>
-      <c r="Y8" s="83"/>
-      <c r="Z8" s="83"/>
-      <c r="AA8" s="83"/>
-      <c r="AB8" s="83"/>
-      <c r="AC8" s="83"/>
-      <c r="AD8" s="82"/>
-      <c r="AE8" s="113"/>
-      <c r="AF8" s="113"/>
-      <c r="AG8" s="113"/>
-      <c r="AH8" s="113"/>
-      <c r="AI8" s="113"/>
-      <c r="AJ8" s="113"/>
-      <c r="AK8" s="113"/>
-      <c r="AL8" s="113"/>
+      <c r="A8" s="116"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="86"/>
+      <c r="O8" s="86"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="86"/>
+      <c r="R8" s="86"/>
+      <c r="S8" s="86"/>
+      <c r="T8" s="86"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="121"/>
+      <c r="W8" s="86"/>
+      <c r="X8" s="86"/>
+      <c r="Y8" s="86"/>
+      <c r="Z8" s="86"/>
+      <c r="AA8" s="86"/>
+      <c r="AB8" s="86"/>
+      <c r="AC8" s="86"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="114"/>
+      <c r="AF8" s="114"/>
+      <c r="AG8" s="114"/>
+      <c r="AH8" s="114"/>
+      <c r="AI8" s="114"/>
+      <c r="AJ8" s="114"/>
+      <c r="AK8" s="114"/>
+      <c r="AL8" s="114"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="125"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="113"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
-      <c r="L9" s="113"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="83"/>
-      <c r="U9" s="82"/>
-      <c r="V9" s="120"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="83"/>
-      <c r="Y9" s="83"/>
-      <c r="Z9" s="83"/>
-      <c r="AA9" s="83"/>
-      <c r="AB9" s="83"/>
-      <c r="AC9" s="83"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="113"/>
-      <c r="AF9" s="113"/>
-      <c r="AG9" s="113"/>
-      <c r="AH9" s="113"/>
-      <c r="AI9" s="113"/>
-      <c r="AJ9" s="113"/>
-      <c r="AK9" s="113"/>
-      <c r="AL9" s="113"/>
+      <c r="A9" s="116"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="114"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="86"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="86"/>
+      <c r="S9" s="86"/>
+      <c r="T9" s="86"/>
+      <c r="U9" s="85"/>
+      <c r="V9" s="121"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="86"/>
+      <c r="Z9" s="86"/>
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="86"/>
+      <c r="AC9" s="86"/>
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="114"/>
+      <c r="AF9" s="114"/>
+      <c r="AG9" s="114"/>
+      <c r="AH9" s="114"/>
+      <c r="AI9" s="114"/>
+      <c r="AJ9" s="114"/>
+      <c r="AK9" s="114"/>
+      <c r="AL9" s="114"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="126"/>
-      <c r="B10" s="126"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="126"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="113"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="83"/>
-      <c r="S10" s="83"/>
-      <c r="T10" s="83"/>
-      <c r="U10" s="82"/>
-      <c r="V10" s="120"/>
-      <c r="W10" s="83"/>
-      <c r="X10" s="83"/>
-      <c r="Y10" s="83"/>
-      <c r="Z10" s="83"/>
-      <c r="AA10" s="83"/>
-      <c r="AB10" s="83"/>
-      <c r="AC10" s="83"/>
-      <c r="AD10" s="82"/>
-      <c r="AE10" s="113"/>
-      <c r="AF10" s="113"/>
-      <c r="AG10" s="113"/>
-      <c r="AH10" s="113"/>
-      <c r="AI10" s="113"/>
-      <c r="AJ10" s="113"/>
-      <c r="AK10" s="113"/>
-      <c r="AL10" s="113"/>
+      <c r="A10" s="125"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="86"/>
+      <c r="O10" s="86"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="86"/>
+      <c r="R10" s="86"/>
+      <c r="S10" s="86"/>
+      <c r="T10" s="86"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="121"/>
+      <c r="W10" s="86"/>
+      <c r="X10" s="86"/>
+      <c r="Y10" s="86"/>
+      <c r="Z10" s="86"/>
+      <c r="AA10" s="86"/>
+      <c r="AB10" s="86"/>
+      <c r="AC10" s="86"/>
+      <c r="AD10" s="85"/>
+      <c r="AE10" s="114"/>
+      <c r="AF10" s="114"/>
+      <c r="AG10" s="114"/>
+      <c r="AH10" s="114"/>
+      <c r="AI10" s="114"/>
+      <c r="AJ10" s="114"/>
+      <c r="AK10" s="114"/>
+      <c r="AL10" s="114"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
@@ -4773,20 +4780,20 @@
       <c r="A13" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="117"/>
-      <c r="N13" s="117"/>
-      <c r="O13" s="117"/>
-      <c r="P13" s="117"/>
-      <c r="Q13" s="117"/>
-      <c r="R13" s="117"/>
-      <c r="S13" s="117"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="127"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="127"/>
+      <c r="O13" s="127"/>
+      <c r="P13" s="127"/>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -4804,13 +4811,13 @@
       <c r="A14" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -4876,238 +4883,238 @@
       <c r="AL15" s="3"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="115" t="s">
+      <c r="B16" s="117"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="115"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="124" t="s">
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="M16" s="124"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="124"/>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="124"/>
-      <c r="R16" s="124"/>
-      <c r="S16" s="124"/>
-      <c r="T16" s="124"/>
-      <c r="U16" s="124"/>
-      <c r="V16" s="124"/>
-      <c r="W16" s="124"/>
-      <c r="X16" s="115" t="s">
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="119"/>
+      <c r="R16" s="119"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="119"/>
+      <c r="U16" s="119"/>
+      <c r="V16" s="119"/>
+      <c r="W16" s="119"/>
+      <c r="X16" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="Y16" s="115"/>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="115"/>
-      <c r="AB16" s="124" t="s">
+      <c r="Y16" s="118"/>
+      <c r="Z16" s="118"/>
+      <c r="AA16" s="118"/>
+      <c r="AB16" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="AC16" s="124"/>
-      <c r="AD16" s="124"/>
-      <c r="AE16" s="124"/>
-      <c r="AF16" s="124"/>
-      <c r="AG16" s="124"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="124"/>
-      <c r="AJ16" s="124"/>
-      <c r="AK16" s="124"/>
-      <c r="AL16" s="124"/>
+      <c r="AC16" s="119"/>
+      <c r="AD16" s="119"/>
+      <c r="AE16" s="119"/>
+      <c r="AF16" s="119"/>
+      <c r="AG16" s="119"/>
+      <c r="AH16" s="119"/>
+      <c r="AI16" s="119"/>
+      <c r="AJ16" s="119"/>
+      <c r="AK16" s="119"/>
+      <c r="AL16" s="119"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="118"/>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="124" t="s">
+      <c r="A17" s="117"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124" t="s">
+      <c r="M17" s="119"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
+      <c r="P17" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124" t="s">
+      <c r="Q17" s="119"/>
+      <c r="R17" s="119"/>
+      <c r="S17" s="119"/>
+      <c r="T17" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="U17" s="124"/>
-      <c r="V17" s="124"/>
-      <c r="W17" s="124"/>
-      <c r="X17" s="115"/>
-      <c r="Y17" s="115"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="115"/>
-      <c r="AB17" s="124" t="s">
+      <c r="U17" s="119"/>
+      <c r="V17" s="119"/>
+      <c r="W17" s="119"/>
+      <c r="X17" s="118"/>
+      <c r="Y17" s="118"/>
+      <c r="Z17" s="118"/>
+      <c r="AA17" s="118"/>
+      <c r="AB17" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="AC17" s="124"/>
-      <c r="AD17" s="124"/>
-      <c r="AE17" s="124"/>
-      <c r="AF17" s="124" t="s">
+      <c r="AC17" s="119"/>
+      <c r="AD17" s="119"/>
+      <c r="AE17" s="119"/>
+      <c r="AF17" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="AG17" s="124"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="124"/>
-      <c r="AJ17" s="124" t="s">
+      <c r="AG17" s="119"/>
+      <c r="AH17" s="119"/>
+      <c r="AI17" s="119"/>
+      <c r="AJ17" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="AK17" s="124"/>
-      <c r="AL17" s="124"/>
+      <c r="AK17" s="119"/>
+      <c r="AL17" s="119"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="125"/>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="116">
+      <c r="A18" s="116"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="115">
         <v>125</v>
       </c>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="N18" s="113"/>
-      <c r="O18" s="113"/>
-      <c r="P18" s="113"/>
-      <c r="Q18" s="113"/>
-      <c r="R18" s="113"/>
-      <c r="S18" s="113"/>
-      <c r="T18" s="113"/>
-      <c r="U18" s="113"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="113"/>
-      <c r="X18" s="116">
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
+      <c r="U18" s="114"/>
+      <c r="V18" s="114"/>
+      <c r="W18" s="114"/>
+      <c r="X18" s="115">
         <v>2000</v>
       </c>
-      <c r="Y18" s="116"/>
-      <c r="Z18" s="116"/>
-      <c r="AA18" s="116"/>
-      <c r="AB18" s="113"/>
-      <c r="AC18" s="113"/>
-      <c r="AD18" s="113"/>
-      <c r="AE18" s="113"/>
-      <c r="AF18" s="113"/>
-      <c r="AG18" s="113"/>
-      <c r="AH18" s="113"/>
-      <c r="AI18" s="113"/>
-      <c r="AJ18" s="113"/>
-      <c r="AK18" s="113"/>
-      <c r="AL18" s="113"/>
+      <c r="Y18" s="115"/>
+      <c r="Z18" s="115"/>
+      <c r="AA18" s="115"/>
+      <c r="AB18" s="114"/>
+      <c r="AC18" s="114"/>
+      <c r="AD18" s="114"/>
+      <c r="AE18" s="114"/>
+      <c r="AF18" s="114"/>
+      <c r="AG18" s="114"/>
+      <c r="AH18" s="114"/>
+      <c r="AI18" s="114"/>
+      <c r="AJ18" s="114"/>
+      <c r="AK18" s="114"/>
+      <c r="AL18" s="114"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="125"/>
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="116">
+      <c r="A19" s="116"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="115">
         <v>500</v>
       </c>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="113"/>
-      <c r="N19" s="113"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="113"/>
-      <c r="Q19" s="113"/>
-      <c r="R19" s="113"/>
-      <c r="S19" s="113"/>
-      <c r="T19" s="113"/>
-      <c r="U19" s="113"/>
-      <c r="V19" s="113"/>
-      <c r="W19" s="113"/>
-      <c r="X19" s="116">
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="114"/>
+      <c r="V19" s="114"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="115">
         <v>5000</v>
       </c>
-      <c r="Y19" s="116"/>
-      <c r="Z19" s="116"/>
-      <c r="AA19" s="116"/>
-      <c r="AB19" s="113"/>
-      <c r="AC19" s="113"/>
-      <c r="AD19" s="113"/>
-      <c r="AE19" s="113"/>
-      <c r="AF19" s="113"/>
-      <c r="AG19" s="113"/>
-      <c r="AH19" s="113"/>
-      <c r="AI19" s="113"/>
-      <c r="AJ19" s="113"/>
-      <c r="AK19" s="113"/>
-      <c r="AL19" s="113"/>
+      <c r="Y19" s="115"/>
+      <c r="Z19" s="115"/>
+      <c r="AA19" s="115"/>
+      <c r="AB19" s="114"/>
+      <c r="AC19" s="114"/>
+      <c r="AD19" s="114"/>
+      <c r="AE19" s="114"/>
+      <c r="AF19" s="114"/>
+      <c r="AG19" s="114"/>
+      <c r="AH19" s="114"/>
+      <c r="AI19" s="114"/>
+      <c r="AJ19" s="114"/>
+      <c r="AK19" s="114"/>
+      <c r="AL19" s="114"/>
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="125"/>
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="116">
+      <c r="A20" s="116"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="115">
         <v>1000</v>
       </c>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="113"/>
-      <c r="R20" s="113"/>
-      <c r="S20" s="113"/>
-      <c r="T20" s="113"/>
-      <c r="U20" s="113"/>
-      <c r="V20" s="113"/>
-      <c r="W20" s="113"/>
-      <c r="X20" s="116">
+      <c r="I20" s="115"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="114"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="114"/>
+      <c r="V20" s="114"/>
+      <c r="W20" s="114"/>
+      <c r="X20" s="115">
         <v>7000</v>
       </c>
-      <c r="Y20" s="116"/>
-      <c r="Z20" s="116"/>
-      <c r="AA20" s="116"/>
-      <c r="AB20" s="113"/>
-      <c r="AC20" s="113"/>
-      <c r="AD20" s="113"/>
-      <c r="AE20" s="113"/>
-      <c r="AF20" s="113"/>
-      <c r="AG20" s="113"/>
-      <c r="AH20" s="113"/>
-      <c r="AI20" s="113"/>
-      <c r="AJ20" s="113"/>
-      <c r="AK20" s="113"/>
-      <c r="AL20" s="113"/>
+      <c r="Y20" s="115"/>
+      <c r="Z20" s="115"/>
+      <c r="AA20" s="115"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="114"/>
+      <c r="AD20" s="114"/>
+      <c r="AE20" s="114"/>
+      <c r="AF20" s="114"/>
+      <c r="AG20" s="114"/>
+      <c r="AH20" s="114"/>
+      <c r="AI20" s="114"/>
+      <c r="AJ20" s="114"/>
+      <c r="AK20" s="114"/>
+      <c r="AL20" s="114"/>
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
@@ -5186,238 +5193,238 @@
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="118" t="s">
+      <c r="A23" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="115" t="s">
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="124" t="s">
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="M23" s="124"/>
-      <c r="N23" s="124"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="124"/>
-      <c r="R23" s="124"/>
-      <c r="S23" s="124"/>
-      <c r="T23" s="124"/>
-      <c r="U23" s="124"/>
-      <c r="V23" s="124"/>
-      <c r="W23" s="124"/>
-      <c r="X23" s="115" t="s">
+      <c r="M23" s="119"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="119"/>
+      <c r="S23" s="119"/>
+      <c r="T23" s="119"/>
+      <c r="U23" s="119"/>
+      <c r="V23" s="119"/>
+      <c r="W23" s="119"/>
+      <c r="X23" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="Y23" s="115"/>
-      <c r="Z23" s="115"/>
-      <c r="AA23" s="115"/>
-      <c r="AB23" s="124" t="s">
+      <c r="Y23" s="118"/>
+      <c r="Z23" s="118"/>
+      <c r="AA23" s="118"/>
+      <c r="AB23" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="AC23" s="124"/>
-      <c r="AD23" s="124"/>
-      <c r="AE23" s="124"/>
-      <c r="AF23" s="124"/>
-      <c r="AG23" s="124"/>
-      <c r="AH23" s="124"/>
-      <c r="AI23" s="124"/>
-      <c r="AJ23" s="124"/>
-      <c r="AK23" s="124"/>
-      <c r="AL23" s="124"/>
+      <c r="AC23" s="119"/>
+      <c r="AD23" s="119"/>
+      <c r="AE23" s="119"/>
+      <c r="AF23" s="119"/>
+      <c r="AG23" s="119"/>
+      <c r="AH23" s="119"/>
+      <c r="AI23" s="119"/>
+      <c r="AJ23" s="119"/>
+      <c r="AK23" s="119"/>
+      <c r="AL23" s="119"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="118"/>
-      <c r="B24" s="118"/>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="115"/>
-      <c r="L24" s="124" t="s">
+      <c r="A24" s="117"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124" t="s">
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124" t="s">
+      <c r="Q24" s="119"/>
+      <c r="R24" s="119"/>
+      <c r="S24" s="119"/>
+      <c r="T24" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
-      <c r="X24" s="115"/>
-      <c r="Y24" s="115"/>
-      <c r="Z24" s="115"/>
-      <c r="AA24" s="115"/>
-      <c r="AB24" s="124" t="s">
+      <c r="U24" s="119"/>
+      <c r="V24" s="119"/>
+      <c r="W24" s="119"/>
+      <c r="X24" s="118"/>
+      <c r="Y24" s="118"/>
+      <c r="Z24" s="118"/>
+      <c r="AA24" s="118"/>
+      <c r="AB24" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="AC24" s="124"/>
-      <c r="AD24" s="124"/>
-      <c r="AE24" s="124"/>
-      <c r="AF24" s="124" t="s">
+      <c r="AC24" s="119"/>
+      <c r="AD24" s="119"/>
+      <c r="AE24" s="119"/>
+      <c r="AF24" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="AG24" s="124"/>
-      <c r="AH24" s="124"/>
-      <c r="AI24" s="124"/>
-      <c r="AJ24" s="124" t="s">
+      <c r="AG24" s="119"/>
+      <c r="AH24" s="119"/>
+      <c r="AI24" s="119"/>
+      <c r="AJ24" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="AK24" s="124"/>
-      <c r="AL24" s="124"/>
+      <c r="AK24" s="119"/>
+      <c r="AL24" s="119"/>
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="125"/>
-      <c r="B25" s="125"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="125"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="116">
+      <c r="A25" s="116"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="115">
         <v>125</v>
       </c>
-      <c r="I25" s="116"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="113"/>
-      <c r="N25" s="113"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="113"/>
-      <c r="S25" s="113"/>
-      <c r="T25" s="113"/>
-      <c r="U25" s="113"/>
-      <c r="V25" s="113"/>
-      <c r="W25" s="113"/>
-      <c r="X25" s="116">
+      <c r="I25" s="115"/>
+      <c r="J25" s="115"/>
+      <c r="K25" s="115"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
+      <c r="U25" s="114"/>
+      <c r="V25" s="114"/>
+      <c r="W25" s="114"/>
+      <c r="X25" s="115">
         <v>2000</v>
       </c>
-      <c r="Y25" s="116"/>
-      <c r="Z25" s="116"/>
-      <c r="AA25" s="116"/>
-      <c r="AB25" s="113"/>
-      <c r="AC25" s="113"/>
-      <c r="AD25" s="113"/>
-      <c r="AE25" s="113"/>
-      <c r="AF25" s="113"/>
-      <c r="AG25" s="113"/>
-      <c r="AH25" s="113"/>
-      <c r="AI25" s="113"/>
-      <c r="AJ25" s="113"/>
-      <c r="AK25" s="113"/>
-      <c r="AL25" s="113"/>
+      <c r="Y25" s="115"/>
+      <c r="Z25" s="115"/>
+      <c r="AA25" s="115"/>
+      <c r="AB25" s="114"/>
+      <c r="AC25" s="114"/>
+      <c r="AD25" s="114"/>
+      <c r="AE25" s="114"/>
+      <c r="AF25" s="114"/>
+      <c r="AG25" s="114"/>
+      <c r="AH25" s="114"/>
+      <c r="AI25" s="114"/>
+      <c r="AJ25" s="114"/>
+      <c r="AK25" s="114"/>
+      <c r="AL25" s="114"/>
     </row>
     <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="125"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="125"/>
-      <c r="G26" s="125"/>
-      <c r="H26" s="116">
+      <c r="A26" s="116"/>
+      <c r="B26" s="116"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="115">
         <v>500</v>
       </c>
-      <c r="I26" s="116"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="113"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="113"/>
-      <c r="S26" s="113"/>
-      <c r="T26" s="113"/>
-      <c r="U26" s="113"/>
-      <c r="V26" s="113"/>
-      <c r="W26" s="113"/>
-      <c r="X26" s="116">
+      <c r="I26" s="115"/>
+      <c r="J26" s="115"/>
+      <c r="K26" s="115"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="114"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="114"/>
+      <c r="T26" s="114"/>
+      <c r="U26" s="114"/>
+      <c r="V26" s="114"/>
+      <c r="W26" s="114"/>
+      <c r="X26" s="115">
         <v>5000</v>
       </c>
-      <c r="Y26" s="116"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="116"/>
-      <c r="AB26" s="113"/>
-      <c r="AC26" s="113"/>
-      <c r="AD26" s="113"/>
-      <c r="AE26" s="113"/>
-      <c r="AF26" s="113"/>
-      <c r="AG26" s="113"/>
-      <c r="AH26" s="113"/>
-      <c r="AI26" s="113"/>
-      <c r="AJ26" s="113"/>
-      <c r="AK26" s="113"/>
-      <c r="AL26" s="113"/>
+      <c r="Y26" s="115"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="115"/>
+      <c r="AB26" s="114"/>
+      <c r="AC26" s="114"/>
+      <c r="AD26" s="114"/>
+      <c r="AE26" s="114"/>
+      <c r="AF26" s="114"/>
+      <c r="AG26" s="114"/>
+      <c r="AH26" s="114"/>
+      <c r="AI26" s="114"/>
+      <c r="AJ26" s="114"/>
+      <c r="AK26" s="114"/>
+      <c r="AL26" s="114"/>
     </row>
     <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="125"/>
-      <c r="B27" s="125"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="125"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="116">
+      <c r="A27" s="116"/>
+      <c r="B27" s="116"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="115">
         <v>1000</v>
       </c>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="113"/>
-      <c r="M27" s="113"/>
-      <c r="N27" s="113"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="113"/>
-      <c r="R27" s="113"/>
-      <c r="S27" s="113"/>
-      <c r="T27" s="113"/>
-      <c r="U27" s="113"/>
-      <c r="V27" s="113"/>
-      <c r="W27" s="113"/>
-      <c r="X27" s="116">
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
+      <c r="U27" s="114"/>
+      <c r="V27" s="114"/>
+      <c r="W27" s="114"/>
+      <c r="X27" s="115">
         <v>7000</v>
       </c>
-      <c r="Y27" s="116"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="116"/>
-      <c r="AB27" s="113"/>
-      <c r="AC27" s="113"/>
-      <c r="AD27" s="113"/>
-      <c r="AE27" s="113"/>
-      <c r="AF27" s="113"/>
-      <c r="AG27" s="113"/>
-      <c r="AH27" s="113"/>
-      <c r="AI27" s="113"/>
-      <c r="AJ27" s="113"/>
-      <c r="AK27" s="113"/>
-      <c r="AL27" s="113"/>
+      <c r="Y27" s="115"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="115"/>
+      <c r="AB27" s="114"/>
+      <c r="AC27" s="114"/>
+      <c r="AD27" s="114"/>
+      <c r="AE27" s="114"/>
+      <c r="AF27" s="114"/>
+      <c r="AG27" s="114"/>
+      <c r="AH27" s="114"/>
+      <c r="AI27" s="114"/>
+      <c r="AJ27" s="114"/>
+      <c r="AK27" s="114"/>
+      <c r="AL27" s="114"/>
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
@@ -6409,6 +6416,88 @@
     </row>
   </sheetData>
   <mergeCells count="98">
+    <mergeCell ref="AE8:AL8"/>
+    <mergeCell ref="AE9:AL9"/>
+    <mergeCell ref="AE10:AL10"/>
+    <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="X16:AA17"/>
+    <mergeCell ref="X18:AA18"/>
+    <mergeCell ref="X19:AA19"/>
+    <mergeCell ref="X20:AA20"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="X25:AA25"/>
+    <mergeCell ref="AB25:AE25"/>
+    <mergeCell ref="F13:S13"/>
+    <mergeCell ref="A6:E7"/>
+    <mergeCell ref="F6:L7"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="M6:AL6"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AL7"/>
+    <mergeCell ref="V10:AD10"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A16:G17"/>
+    <mergeCell ref="A18:G20"/>
+    <mergeCell ref="AB16:AL16"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AB18:AE18"/>
+    <mergeCell ref="AB19:AE19"/>
+    <mergeCell ref="AB20:AE20"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="H16:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="L16:W16"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="A23:G24"/>
+    <mergeCell ref="H23:K24"/>
+    <mergeCell ref="L23:W23"/>
+    <mergeCell ref="X23:AA24"/>
+    <mergeCell ref="AB23:AL23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="AB24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="AJ24:AL24"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:W26"/>
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="AF26:AI26"/>
@@ -6425,90 +6514,8 @@
     <mergeCell ref="AB26:AE26"/>
     <mergeCell ref="A25:G27"/>
     <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="A23:G24"/>
-    <mergeCell ref="H23:K24"/>
-    <mergeCell ref="L23:W23"/>
-    <mergeCell ref="X23:AA24"/>
-    <mergeCell ref="AB23:AL23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="AB24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="H16:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="L16:W16"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A16:G17"/>
-    <mergeCell ref="A18:G20"/>
-    <mergeCell ref="AB16:AL16"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AB18:AE18"/>
-    <mergeCell ref="AB19:AE19"/>
-    <mergeCell ref="AB20:AE20"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="A6:E7"/>
-    <mergeCell ref="F6:L7"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="M6:AL6"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="V7:AD7"/>
-    <mergeCell ref="AE7:AL7"/>
-    <mergeCell ref="V10:AD10"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="V8:AD8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V9:AD9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="AE8:AL8"/>
-    <mergeCell ref="AE9:AL9"/>
-    <mergeCell ref="AE10:AL10"/>
-    <mergeCell ref="F3:Q3"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="X16:AA17"/>
-    <mergeCell ref="X18:AA18"/>
-    <mergeCell ref="X19:AA19"/>
-    <mergeCell ref="X20:AA20"/>
-    <mergeCell ref="F8:L8"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="F10:L10"/>
-    <mergeCell ref="X25:AA25"/>
-    <mergeCell ref="AB25:AE25"/>
-    <mergeCell ref="F13:S13"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -6546,32 +6553,32 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="119"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -6607,17 +6614,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
       <c r="N3" s="3"/>
@@ -6778,268 +6785,268 @@
       <c r="AL7" s="15"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="140" t="s">
+      <c r="A8" s="132" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="128" t="s">
+      <c r="B8" s="117"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="128"/>
-      <c r="L8" s="128"/>
-      <c r="M8" s="128"/>
-      <c r="N8" s="128"/>
-      <c r="O8" s="128"/>
-      <c r="P8" s="128"/>
-      <c r="Q8" s="128"/>
-      <c r="R8" s="128"/>
-      <c r="S8" s="128"/>
-      <c r="T8" s="128"/>
-      <c r="U8" s="128"/>
-      <c r="V8" s="128"/>
-      <c r="W8" s="128"/>
-      <c r="X8" s="128"/>
-      <c r="Y8" s="128"/>
-      <c r="Z8" s="128"/>
-      <c r="AA8" s="128"/>
-      <c r="AB8" s="128"/>
-      <c r="AC8" s="128"/>
-      <c r="AD8" s="128"/>
-      <c r="AE8" s="128"/>
-      <c r="AF8" s="128"/>
-      <c r="AG8" s="128"/>
-      <c r="AH8" s="128"/>
-      <c r="AI8" s="118" t="s">
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
+      <c r="M8" s="131"/>
+      <c r="N8" s="131"/>
+      <c r="O8" s="131"/>
+      <c r="P8" s="131"/>
+      <c r="Q8" s="131"/>
+      <c r="R8" s="131"/>
+      <c r="S8" s="131"/>
+      <c r="T8" s="131"/>
+      <c r="U8" s="131"/>
+      <c r="V8" s="131"/>
+      <c r="W8" s="131"/>
+      <c r="X8" s="131"/>
+      <c r="Y8" s="131"/>
+      <c r="Z8" s="131"/>
+      <c r="AA8" s="131"/>
+      <c r="AB8" s="131"/>
+      <c r="AC8" s="131"/>
+      <c r="AD8" s="131"/>
+      <c r="AE8" s="131"/>
+      <c r="AF8" s="131"/>
+      <c r="AG8" s="131"/>
+      <c r="AH8" s="131"/>
+      <c r="AI8" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="AJ8" s="118"/>
-      <c r="AK8" s="118"/>
-      <c r="AL8" s="118"/>
+      <c r="AJ8" s="117"/>
+      <c r="AK8" s="117"/>
+      <c r="AL8" s="117"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118"/>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="128" t="s">
+      <c r="A9" s="117"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="131" t="s">
         <v>78</v>
       </c>
-      <c r="K9" s="128"/>
-      <c r="L9" s="128"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="128" t="s">
+      <c r="K9" s="131"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="131"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="131" t="s">
         <v>79</v>
       </c>
-      <c r="P9" s="128"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="128"/>
-      <c r="S9" s="128"/>
-      <c r="T9" s="128" t="s">
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="131"/>
+      <c r="S9" s="131"/>
+      <c r="T9" s="131" t="s">
         <v>80</v>
       </c>
-      <c r="U9" s="128"/>
-      <c r="V9" s="128"/>
-      <c r="W9" s="128"/>
-      <c r="X9" s="128"/>
-      <c r="Y9" s="128" t="s">
+      <c r="U9" s="131"/>
+      <c r="V9" s="131"/>
+      <c r="W9" s="131"/>
+      <c r="X9" s="131"/>
+      <c r="Y9" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="Z9" s="128"/>
-      <c r="AA9" s="128"/>
-      <c r="AB9" s="128"/>
-      <c r="AC9" s="128"/>
-      <c r="AD9" s="128" t="s">
+      <c r="Z9" s="131"/>
+      <c r="AA9" s="131"/>
+      <c r="AB9" s="131"/>
+      <c r="AC9" s="131"/>
+      <c r="AD9" s="131" t="s">
         <v>82</v>
       </c>
-      <c r="AE9" s="128"/>
-      <c r="AF9" s="128"/>
-      <c r="AG9" s="128"/>
-      <c r="AH9" s="128"/>
-      <c r="AI9" s="118"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="118"/>
-      <c r="AL9" s="118"/>
+      <c r="AE9" s="131"/>
+      <c r="AF9" s="131"/>
+      <c r="AG9" s="131"/>
+      <c r="AH9" s="131"/>
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="129" t="s">
+      <c r="A10" s="116"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
-      <c r="P10" s="128"/>
-      <c r="Q10" s="128"/>
-      <c r="R10" s="128"/>
-      <c r="S10" s="128"/>
-      <c r="T10" s="128"/>
-      <c r="U10" s="128"/>
-      <c r="V10" s="128"/>
-      <c r="W10" s="128"/>
-      <c r="X10" s="128"/>
-      <c r="Y10" s="128"/>
-      <c r="Z10" s="128"/>
-      <c r="AA10" s="128"/>
-      <c r="AB10" s="128"/>
-      <c r="AC10" s="128"/>
-      <c r="AD10" s="128"/>
-      <c r="AE10" s="128"/>
-      <c r="AF10" s="128"/>
-      <c r="AG10" s="128"/>
-      <c r="AH10" s="128"/>
-      <c r="AI10" s="118"/>
-      <c r="AJ10" s="118"/>
-      <c r="AK10" s="118"/>
-      <c r="AL10" s="118"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="131"/>
+      <c r="T10" s="131"/>
+      <c r="U10" s="131"/>
+      <c r="V10" s="131"/>
+      <c r="W10" s="131"/>
+      <c r="X10" s="131"/>
+      <c r="Y10" s="131"/>
+      <c r="Z10" s="131"/>
+      <c r="AA10" s="131"/>
+      <c r="AB10" s="131"/>
+      <c r="AC10" s="131"/>
+      <c r="AD10" s="131"/>
+      <c r="AE10" s="131"/>
+      <c r="AF10" s="131"/>
+      <c r="AG10" s="131"/>
+      <c r="AH10" s="131"/>
+      <c r="AI10" s="117"/>
+      <c r="AJ10" s="117"/>
+      <c r="AK10" s="117"/>
+      <c r="AL10" s="117"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="125"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="129" t="s">
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="128"/>
-      <c r="N11" s="128"/>
-      <c r="O11" s="128"/>
-      <c r="P11" s="128"/>
-      <c r="Q11" s="128"/>
-      <c r="R11" s="128"/>
-      <c r="S11" s="128"/>
-      <c r="T11" s="128"/>
-      <c r="U11" s="128"/>
-      <c r="V11" s="128"/>
-      <c r="W11" s="128"/>
-      <c r="X11" s="128"/>
-      <c r="Y11" s="128"/>
-      <c r="Z11" s="128"/>
-      <c r="AA11" s="128"/>
-      <c r="AB11" s="128"/>
-      <c r="AC11" s="128"/>
-      <c r="AD11" s="128"/>
-      <c r="AE11" s="128"/>
-      <c r="AF11" s="128"/>
-      <c r="AG11" s="128"/>
-      <c r="AH11" s="128"/>
-      <c r="AI11" s="118"/>
-      <c r="AJ11" s="118"/>
-      <c r="AK11" s="118"/>
-      <c r="AL11" s="118"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="131"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="131"/>
+      <c r="U11" s="131"/>
+      <c r="V11" s="131"/>
+      <c r="W11" s="131"/>
+      <c r="X11" s="131"/>
+      <c r="Y11" s="131"/>
+      <c r="Z11" s="131"/>
+      <c r="AA11" s="131"/>
+      <c r="AB11" s="131"/>
+      <c r="AC11" s="131"/>
+      <c r="AD11" s="131"/>
+      <c r="AE11" s="131"/>
+      <c r="AF11" s="131"/>
+      <c r="AG11" s="131"/>
+      <c r="AH11" s="131"/>
+      <c r="AI11" s="117"/>
+      <c r="AJ11" s="117"/>
+      <c r="AK11" s="117"/>
+      <c r="AL11" s="117"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="125"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="129" t="s">
+      <c r="A12" s="116"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="128"/>
-      <c r="O12" s="128"/>
-      <c r="P12" s="128"/>
-      <c r="Q12" s="128"/>
-      <c r="R12" s="128"/>
-      <c r="S12" s="128"/>
-      <c r="T12" s="128"/>
-      <c r="U12" s="128"/>
-      <c r="V12" s="128"/>
-      <c r="W12" s="128"/>
-      <c r="X12" s="128"/>
-      <c r="Y12" s="128"/>
-      <c r="Z12" s="128"/>
-      <c r="AA12" s="128"/>
-      <c r="AB12" s="128"/>
-      <c r="AC12" s="128"/>
-      <c r="AD12" s="128"/>
-      <c r="AE12" s="128"/>
-      <c r="AF12" s="128"/>
-      <c r="AG12" s="128"/>
-      <c r="AH12" s="128"/>
-      <c r="AI12" s="118"/>
-      <c r="AJ12" s="118"/>
-      <c r="AK12" s="118"/>
-      <c r="AL12" s="118"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="131"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="131"/>
+      <c r="Q12" s="131"/>
+      <c r="R12" s="131"/>
+      <c r="S12" s="131"/>
+      <c r="T12" s="131"/>
+      <c r="U12" s="131"/>
+      <c r="V12" s="131"/>
+      <c r="W12" s="131"/>
+      <c r="X12" s="131"/>
+      <c r="Y12" s="131"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="131"/>
+      <c r="AB12" s="131"/>
+      <c r="AC12" s="131"/>
+      <c r="AD12" s="131"/>
+      <c r="AE12" s="131"/>
+      <c r="AF12" s="131"/>
+      <c r="AG12" s="131"/>
+      <c r="AH12" s="131"/>
+      <c r="AI12" s="117"/>
+      <c r="AJ12" s="117"/>
+      <c r="AK12" s="117"/>
+      <c r="AL12" s="117"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="125"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="129" t="s">
+      <c r="A13" s="116"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="128"/>
-      <c r="U13" s="128"/>
-      <c r="V13" s="128"/>
-      <c r="W13" s="128"/>
-      <c r="X13" s="128"/>
-      <c r="Y13" s="128"/>
-      <c r="Z13" s="128"/>
-      <c r="AA13" s="128"/>
-      <c r="AB13" s="128"/>
-      <c r="AC13" s="128"/>
-      <c r="AD13" s="128"/>
-      <c r="AE13" s="128"/>
-      <c r="AF13" s="128"/>
-      <c r="AG13" s="128"/>
-      <c r="AH13" s="128"/>
-      <c r="AI13" s="118"/>
-      <c r="AJ13" s="118"/>
-      <c r="AK13" s="118"/>
-      <c r="AL13" s="118"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="131"/>
+      <c r="P13" s="131"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="131"/>
+      <c r="S13" s="131"/>
+      <c r="T13" s="131"/>
+      <c r="U13" s="131"/>
+      <c r="V13" s="131"/>
+      <c r="W13" s="131"/>
+      <c r="X13" s="131"/>
+      <c r="Y13" s="131"/>
+      <c r="Z13" s="131"/>
+      <c r="AA13" s="131"/>
+      <c r="AB13" s="131"/>
+      <c r="AC13" s="131"/>
+      <c r="AD13" s="131"/>
+      <c r="AE13" s="131"/>
+      <c r="AF13" s="131"/>
+      <c r="AG13" s="131"/>
+      <c r="AH13" s="131"/>
+      <c r="AI13" s="117"/>
+      <c r="AJ13" s="117"/>
+      <c r="AK13" s="117"/>
+      <c r="AL13" s="117"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="44"/>
@@ -7740,6 +7747,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A12:C13"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="AI13:AL13"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="J11:N11"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="D10:I10"/>
@@ -7756,32 +7787,8 @@
     <mergeCell ref="A8:I9"/>
     <mergeCell ref="A10:C11"/>
     <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="A12:C13"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="AI13:AL13"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="O12:S12"/>
   </mergeCells>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="26" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -7819,32 +7826,32 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="119"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
       <c r="AM1" s="56"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7885,19 +7892,19 @@
         <v>89</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="132"/>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="132"/>
-      <c r="R3" s="132"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="133"/>
+      <c r="R3" s="133"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -8065,360 +8072,360 @@
       <c r="AM7" s="17"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="140" t="s">
+      <c r="A8" s="132" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118"/>
-      <c r="K8" s="118"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="118"/>
-      <c r="N8" s="118"/>
-      <c r="O8" s="118"/>
-      <c r="P8" s="118" t="s">
+      <c r="B8" s="117"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="117"/>
+      <c r="O8" s="117"/>
+      <c r="P8" s="117" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="118"/>
-      <c r="R8" s="118"/>
-      <c r="S8" s="118"/>
-      <c r="T8" s="118"/>
-      <c r="U8" s="118"/>
-      <c r="V8" s="118"/>
-      <c r="W8" s="118"/>
-      <c r="X8" s="118"/>
-      <c r="Y8" s="118"/>
-      <c r="Z8" s="118"/>
-      <c r="AA8" s="118"/>
-      <c r="AB8" s="118"/>
-      <c r="AC8" s="118"/>
-      <c r="AD8" s="118"/>
-      <c r="AE8" s="118"/>
-      <c r="AF8" s="118"/>
-      <c r="AG8" s="118"/>
-      <c r="AH8" s="118"/>
-      <c r="AI8" s="118"/>
-      <c r="AJ8" s="118" t="s">
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
+      <c r="U8" s="117"/>
+      <c r="V8" s="117"/>
+      <c r="W8" s="117"/>
+      <c r="X8" s="117"/>
+      <c r="Y8" s="117"/>
+      <c r="Z8" s="117"/>
+      <c r="AA8" s="117"/>
+      <c r="AB8" s="117"/>
+      <c r="AC8" s="117"/>
+      <c r="AD8" s="117"/>
+      <c r="AE8" s="117"/>
+      <c r="AF8" s="117"/>
+      <c r="AG8" s="117"/>
+      <c r="AH8" s="117"/>
+      <c r="AI8" s="117"/>
+      <c r="AJ8" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="AK8" s="118"/>
-      <c r="AL8" s="118"/>
-      <c r="AM8" s="118"/>
+      <c r="AK8" s="117"/>
+      <c r="AL8" s="117"/>
+      <c r="AM8" s="117"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118"/>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="118" t="s">
+      <c r="A9" s="117"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118" t="s">
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117"/>
+      <c r="S9" s="117"/>
+      <c r="T9" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118" t="s">
+      <c r="U9" s="117"/>
+      <c r="V9" s="117"/>
+      <c r="W9" s="117"/>
+      <c r="X9" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118"/>
-      <c r="AA9" s="118"/>
-      <c r="AB9" s="118" t="s">
+      <c r="Y9" s="117"/>
+      <c r="Z9" s="117"/>
+      <c r="AA9" s="117"/>
+      <c r="AB9" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="AC9" s="118"/>
-      <c r="AD9" s="118"/>
-      <c r="AE9" s="118"/>
-      <c r="AF9" s="118" t="s">
+      <c r="AC9" s="117"/>
+      <c r="AD9" s="117"/>
+      <c r="AE9" s="117"/>
+      <c r="AF9" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="AG9" s="118"/>
-      <c r="AH9" s="118"/>
-      <c r="AI9" s="118"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="118"/>
-      <c r="AL9" s="118"/>
-      <c r="AM9" s="118"/>
+      <c r="AG9" s="117"/>
+      <c r="AH9" s="117"/>
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
+      <c r="AM9" s="117"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="118" t="s">
+      <c r="A10" s="116"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="117" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="118"/>
-      <c r="O10" s="118"/>
-      <c r="P10" s="118"/>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="118"/>
-      <c r="S10" s="118"/>
-      <c r="T10" s="118"/>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
-      <c r="W10" s="118"/>
-      <c r="X10" s="118"/>
-      <c r="Y10" s="118"/>
-      <c r="Z10" s="118"/>
-      <c r="AA10" s="118"/>
-      <c r="AB10" s="118"/>
-      <c r="AC10" s="118"/>
-      <c r="AD10" s="118"/>
-      <c r="AE10" s="118"/>
-      <c r="AF10" s="118"/>
-      <c r="AG10" s="118"/>
-      <c r="AH10" s="118"/>
-      <c r="AI10" s="118"/>
-      <c r="AJ10" s="118"/>
-      <c r="AK10" s="118"/>
-      <c r="AL10" s="118"/>
-      <c r="AM10" s="118"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="117"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="117"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="117"/>
+      <c r="S10" s="117"/>
+      <c r="T10" s="117"/>
+      <c r="U10" s="117"/>
+      <c r="V10" s="117"/>
+      <c r="W10" s="117"/>
+      <c r="X10" s="117"/>
+      <c r="Y10" s="117"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="117"/>
+      <c r="AB10" s="117"/>
+      <c r="AC10" s="117"/>
+      <c r="AD10" s="117"/>
+      <c r="AE10" s="117"/>
+      <c r="AF10" s="117"/>
+      <c r="AG10" s="117"/>
+      <c r="AH10" s="117"/>
+      <c r="AI10" s="117"/>
+      <c r="AJ10" s="117"/>
+      <c r="AK10" s="117"/>
+      <c r="AL10" s="117"/>
+      <c r="AM10" s="117"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="125"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="118" t="s">
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="118"/>
-      <c r="N11" s="118"/>
-      <c r="O11" s="118"/>
-      <c r="P11" s="118"/>
-      <c r="Q11" s="118"/>
-      <c r="R11" s="118"/>
-      <c r="S11" s="118"/>
-      <c r="T11" s="118"/>
-      <c r="U11" s="118"/>
-      <c r="V11" s="118"/>
-      <c r="W11" s="118"/>
-      <c r="X11" s="118"/>
-      <c r="Y11" s="118"/>
-      <c r="Z11" s="118"/>
-      <c r="AA11" s="118"/>
-      <c r="AB11" s="118"/>
-      <c r="AC11" s="118"/>
-      <c r="AD11" s="118"/>
-      <c r="AE11" s="118"/>
-      <c r="AF11" s="118"/>
-      <c r="AG11" s="118"/>
-      <c r="AH11" s="118"/>
-      <c r="AI11" s="118"/>
-      <c r="AJ11" s="118"/>
-      <c r="AK11" s="118"/>
-      <c r="AL11" s="118"/>
-      <c r="AM11" s="118"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="117"/>
+      <c r="O11" s="117"/>
+      <c r="P11" s="117"/>
+      <c r="Q11" s="117"/>
+      <c r="R11" s="117"/>
+      <c r="S11" s="117"/>
+      <c r="T11" s="117"/>
+      <c r="U11" s="117"/>
+      <c r="V11" s="117"/>
+      <c r="W11" s="117"/>
+      <c r="X11" s="117"/>
+      <c r="Y11" s="117"/>
+      <c r="Z11" s="117"/>
+      <c r="AA11" s="117"/>
+      <c r="AB11" s="117"/>
+      <c r="AC11" s="117"/>
+      <c r="AD11" s="117"/>
+      <c r="AE11" s="117"/>
+      <c r="AF11" s="117"/>
+      <c r="AG11" s="117"/>
+      <c r="AH11" s="117"/>
+      <c r="AI11" s="117"/>
+      <c r="AJ11" s="117"/>
+      <c r="AK11" s="117"/>
+      <c r="AL11" s="117"/>
+      <c r="AM11" s="117"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="125"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="118" t="s">
+      <c r="A12" s="116"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="117" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="118"/>
-      <c r="L12" s="118"/>
-      <c r="M12" s="118"/>
-      <c r="N12" s="118"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="118"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
-      <c r="S12" s="118"/>
-      <c r="T12" s="118"/>
-      <c r="U12" s="118"/>
-      <c r="V12" s="118"/>
-      <c r="W12" s="118"/>
-      <c r="X12" s="118"/>
-      <c r="Y12" s="118"/>
-      <c r="Z12" s="118"/>
-      <c r="AA12" s="118"/>
-      <c r="AB12" s="118"/>
-      <c r="AC12" s="118"/>
-      <c r="AD12" s="118"/>
-      <c r="AE12" s="118"/>
-      <c r="AF12" s="118"/>
-      <c r="AG12" s="118"/>
-      <c r="AH12" s="118"/>
-      <c r="AI12" s="118"/>
-      <c r="AJ12" s="118"/>
-      <c r="AK12" s="118"/>
-      <c r="AL12" s="118"/>
-      <c r="AM12" s="118"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="117"/>
+      <c r="O12" s="117"/>
+      <c r="P12" s="117"/>
+      <c r="Q12" s="117"/>
+      <c r="R12" s="117"/>
+      <c r="S12" s="117"/>
+      <c r="T12" s="117"/>
+      <c r="U12" s="117"/>
+      <c r="V12" s="117"/>
+      <c r="W12" s="117"/>
+      <c r="X12" s="117"/>
+      <c r="Y12" s="117"/>
+      <c r="Z12" s="117"/>
+      <c r="AA12" s="117"/>
+      <c r="AB12" s="117"/>
+      <c r="AC12" s="117"/>
+      <c r="AD12" s="117"/>
+      <c r="AE12" s="117"/>
+      <c r="AF12" s="117"/>
+      <c r="AG12" s="117"/>
+      <c r="AH12" s="117"/>
+      <c r="AI12" s="117"/>
+      <c r="AJ12" s="117"/>
+      <c r="AK12" s="117"/>
+      <c r="AL12" s="117"/>
+      <c r="AM12" s="117"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="125"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="118" t="s">
+      <c r="A13" s="116"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="118"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="118"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
-      <c r="U13" s="118"/>
-      <c r="V13" s="118"/>
-      <c r="W13" s="118"/>
-      <c r="X13" s="118"/>
-      <c r="Y13" s="118"/>
-      <c r="Z13" s="118"/>
-      <c r="AA13" s="118"/>
-      <c r="AB13" s="118"/>
-      <c r="AC13" s="118"/>
-      <c r="AD13" s="118"/>
-      <c r="AE13" s="118"/>
-      <c r="AF13" s="118"/>
-      <c r="AG13" s="118"/>
-      <c r="AH13" s="118"/>
-      <c r="AI13" s="118"/>
-      <c r="AJ13" s="118"/>
-      <c r="AK13" s="118"/>
-      <c r="AL13" s="118"/>
-      <c r="AM13" s="118"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
+      <c r="O13" s="117"/>
+      <c r="P13" s="117"/>
+      <c r="Q13" s="117"/>
+      <c r="R13" s="117"/>
+      <c r="S13" s="117"/>
+      <c r="T13" s="117"/>
+      <c r="U13" s="117"/>
+      <c r="V13" s="117"/>
+      <c r="W13" s="117"/>
+      <c r="X13" s="117"/>
+      <c r="Y13" s="117"/>
+      <c r="Z13" s="117"/>
+      <c r="AA13" s="117"/>
+      <c r="AB13" s="117"/>
+      <c r="AC13" s="117"/>
+      <c r="AD13" s="117"/>
+      <c r="AE13" s="117"/>
+      <c r="AF13" s="117"/>
+      <c r="AG13" s="117"/>
+      <c r="AH13" s="117"/>
+      <c r="AI13" s="117"/>
+      <c r="AJ13" s="117"/>
+      <c r="AK13" s="117"/>
+      <c r="AL13" s="117"/>
+      <c r="AM13" s="117"/>
     </row>
     <row r="14" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="125"/>
-      <c r="B14" s="125"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="118" t="s">
+      <c r="A14" s="116"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="117" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="118"/>
-      <c r="N14" s="118"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="118"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
-      <c r="U14" s="118"/>
-      <c r="V14" s="118"/>
-      <c r="W14" s="118"/>
-      <c r="X14" s="118"/>
-      <c r="Y14" s="118"/>
-      <c r="Z14" s="118"/>
-      <c r="AA14" s="118"/>
-      <c r="AB14" s="118"/>
-      <c r="AC14" s="118"/>
-      <c r="AD14" s="118"/>
-      <c r="AE14" s="118"/>
-      <c r="AF14" s="118"/>
-      <c r="AG14" s="118"/>
-      <c r="AH14" s="118"/>
-      <c r="AI14" s="118"/>
-      <c r="AJ14" s="118"/>
-      <c r="AK14" s="118"/>
-      <c r="AL14" s="118"/>
-      <c r="AM14" s="118"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="117"/>
+      <c r="O14" s="117"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="117"/>
+      <c r="R14" s="117"/>
+      <c r="S14" s="117"/>
+      <c r="T14" s="117"/>
+      <c r="U14" s="117"/>
+      <c r="V14" s="117"/>
+      <c r="W14" s="117"/>
+      <c r="X14" s="117"/>
+      <c r="Y14" s="117"/>
+      <c r="Z14" s="117"/>
+      <c r="AA14" s="117"/>
+      <c r="AB14" s="117"/>
+      <c r="AC14" s="117"/>
+      <c r="AD14" s="117"/>
+      <c r="AE14" s="117"/>
+      <c r="AF14" s="117"/>
+      <c r="AG14" s="117"/>
+      <c r="AH14" s="117"/>
+      <c r="AI14" s="117"/>
+      <c r="AJ14" s="117"/>
+      <c r="AK14" s="117"/>
+      <c r="AL14" s="117"/>
+      <c r="AM14" s="117"/>
     </row>
     <row r="15" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="125"/>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="118" t="s">
+      <c r="A15" s="116"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
-      <c r="M15" s="118"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
-      <c r="U15" s="118"/>
-      <c r="V15" s="118"/>
-      <c r="W15" s="118"/>
-      <c r="X15" s="118"/>
-      <c r="Y15" s="118"/>
-      <c r="Z15" s="118"/>
-      <c r="AA15" s="118"/>
-      <c r="AB15" s="118"/>
-      <c r="AC15" s="118"/>
-      <c r="AD15" s="118"/>
-      <c r="AE15" s="118"/>
-      <c r="AF15" s="118"/>
-      <c r="AG15" s="118"/>
-      <c r="AH15" s="118"/>
-      <c r="AI15" s="118"/>
-      <c r="AJ15" s="118"/>
-      <c r="AK15" s="118"/>
-      <c r="AL15" s="118"/>
-      <c r="AM15" s="118"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="117"/>
+      <c r="V15" s="117"/>
+      <c r="W15" s="117"/>
+      <c r="X15" s="117"/>
+      <c r="Y15" s="117"/>
+      <c r="Z15" s="117"/>
+      <c r="AA15" s="117"/>
+      <c r="AB15" s="117"/>
+      <c r="AC15" s="117"/>
+      <c r="AD15" s="117"/>
+      <c r="AE15" s="117"/>
+      <c r="AF15" s="117"/>
+      <c r="AG15" s="117"/>
+      <c r="AH15" s="117"/>
+      <c r="AI15" s="117"/>
+      <c r="AJ15" s="117"/>
+      <c r="AK15" s="117"/>
+      <c r="AL15" s="117"/>
+      <c r="AM15" s="117"/>
     </row>
     <row r="16" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
@@ -8997,45 +9004,6 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A8:O9"/>
-    <mergeCell ref="P8:AI8"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ8:AM9"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="AJ11:AM11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="F11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:W11"/>
-    <mergeCell ref="X11:AA11"/>
-    <mergeCell ref="AB11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:W12"/>
-    <mergeCell ref="X12:AA12"/>
-    <mergeCell ref="AB13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="AB12:AE12"/>
-    <mergeCell ref="AJ12:AM12"/>
-    <mergeCell ref="AJ13:AM13"/>
-    <mergeCell ref="A14:E15"/>
-    <mergeCell ref="F14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="X14:AA14"/>
     <mergeCell ref="AJ14:AM14"/>
     <mergeCell ref="AJ15:AM15"/>
     <mergeCell ref="F3:R3"/>
@@ -9052,8 +9020,47 @@
     <mergeCell ref="P13:S13"/>
     <mergeCell ref="T13:W13"/>
     <mergeCell ref="X13:AA13"/>
+    <mergeCell ref="A14:E15"/>
+    <mergeCell ref="F14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X14:AA14"/>
+    <mergeCell ref="AB13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="AB12:AE12"/>
+    <mergeCell ref="AJ12:AM12"/>
+    <mergeCell ref="AJ13:AM13"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:O12"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="T12:W12"/>
+    <mergeCell ref="X12:AA12"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="AJ11:AM11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="F11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:W11"/>
+    <mergeCell ref="X11:AA11"/>
+    <mergeCell ref="AB11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A8:O9"/>
+    <mergeCell ref="P8:AI8"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ8:AM9"/>
   </mergeCells>
-  <phoneticPr fontId="32" type="noConversion"/>
+  <phoneticPr fontId="33" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -9094,32 +9101,32 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="135"/>
-      <c r="Z1" s="135"/>
-      <c r="AA1" s="135"/>
-      <c r="AB1" s="135"/>
-      <c r="AC1" s="135"/>
-      <c r="AD1" s="135"/>
-      <c r="AE1" s="135"/>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="135"/>
-      <c r="AI1" s="135"/>
-      <c r="AJ1" s="135"/>
-      <c r="AK1" s="135"/>
-      <c r="AL1" s="135"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
+      <c r="U1" s="136"/>
+      <c r="V1" s="136"/>
+      <c r="W1" s="136"/>
+      <c r="X1" s="136"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="136"/>
+      <c r="AA1" s="136"/>
+      <c r="AB1" s="136"/>
+      <c r="AC1" s="136"/>
+      <c r="AD1" s="136"/>
+      <c r="AE1" s="136"/>
+      <c r="AF1" s="136"/>
+      <c r="AG1" s="136"/>
+      <c r="AH1" s="136"/>
+      <c r="AI1" s="136"/>
+      <c r="AJ1" s="136"/>
+      <c r="AK1" s="136"/>
+      <c r="AL1" s="136"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="137" t="s">
@@ -9164,18 +9171,18 @@
       <c r="AL2" s="3"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="132"/>
-      <c r="B3" s="132"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -9248,18 +9255,18 @@
         <v>109</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
       <c r="F5" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -9370,85 +9377,85 @@
       <c r="AL7" s="3"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="133"/>
-      <c r="K8" s="133"/>
-      <c r="L8" s="133"/>
-      <c r="M8" s="133"/>
-      <c r="N8" s="133"/>
-      <c r="O8" s="133"/>
-      <c r="P8" s="133"/>
-      <c r="Q8" s="133"/>
-      <c r="R8" s="133"/>
-      <c r="S8" s="133"/>
-      <c r="T8" s="133"/>
-      <c r="U8" s="133"/>
-      <c r="V8" s="133"/>
-      <c r="W8" s="133"/>
-      <c r="X8" s="133"/>
-      <c r="Y8" s="133"/>
-      <c r="Z8" s="133"/>
-      <c r="AA8" s="133"/>
-      <c r="AB8" s="133"/>
-      <c r="AC8" s="133"/>
-      <c r="AD8" s="133"/>
-      <c r="AE8" s="133"/>
-      <c r="AF8" s="133"/>
-      <c r="AG8" s="133"/>
-      <c r="AH8" s="133"/>
-      <c r="AI8" s="133"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="139"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="139"/>
+      <c r="Q8" s="139"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="139"/>
+      <c r="T8" s="139"/>
+      <c r="U8" s="139"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="139"/>
+      <c r="X8" s="139"/>
+      <c r="Y8" s="139"/>
+      <c r="Z8" s="139"/>
+      <c r="AA8" s="139"/>
+      <c r="AB8" s="139"/>
+      <c r="AC8" s="139"/>
+      <c r="AD8" s="139"/>
+      <c r="AE8" s="139"/>
+      <c r="AF8" s="139"/>
+      <c r="AG8" s="139"/>
+      <c r="AH8" s="139"/>
+      <c r="AI8" s="139"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="134" t="s">
+      <c r="A9" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="134"/>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
-      <c r="L9" s="113"/>
-      <c r="M9" s="113"/>
-      <c r="N9" s="113"/>
-      <c r="O9" s="113"/>
-      <c r="P9" s="113"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="113"/>
-      <c r="S9" s="113"/>
-      <c r="T9" s="113"/>
-      <c r="U9" s="113"/>
-      <c r="V9" s="113"/>
-      <c r="W9" s="113"/>
-      <c r="X9" s="113"/>
-      <c r="Y9" s="113"/>
-      <c r="Z9" s="113"/>
-      <c r="AA9" s="113"/>
-      <c r="AB9" s="113"/>
-      <c r="AC9" s="113"/>
-      <c r="AD9" s="113"/>
-      <c r="AE9" s="113"/>
-      <c r="AF9" s="113"/>
-      <c r="AG9" s="113"/>
-      <c r="AH9" s="113"/>
-      <c r="AI9" s="113"/>
+      <c r="B9" s="140"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="114"/>
+      <c r="M9" s="114"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="114"/>
+      <c r="Q9" s="114"/>
+      <c r="R9" s="114"/>
+      <c r="S9" s="114"/>
+      <c r="T9" s="114"/>
+      <c r="U9" s="114"/>
+      <c r="V9" s="114"/>
+      <c r="W9" s="114"/>
+      <c r="X9" s="114"/>
+      <c r="Y9" s="114"/>
+      <c r="Z9" s="114"/>
+      <c r="AA9" s="114"/>
+      <c r="AB9" s="114"/>
+      <c r="AC9" s="114"/>
+      <c r="AD9" s="114"/>
+      <c r="AE9" s="114"/>
+      <c r="AF9" s="114"/>
+      <c r="AG9" s="114"/>
+      <c r="AH9" s="114"/>
+      <c r="AI9" s="114"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
@@ -9498,9 +9505,9 @@
         <v>113</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="135"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="135"/>
+      <c r="C11" s="136"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="136"/>
       <c r="F11" s="3" t="s">
         <v>114</v>
       </c>
@@ -10045,20 +10052,20 @@
       <c r="G24" s="59"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="138"/>
-      <c r="L24" s="138"/>
-      <c r="M24" s="138"/>
-      <c r="N24" s="138"/>
-      <c r="O24" s="138"/>
-      <c r="P24" s="138"/>
-      <c r="Q24" s="138"/>
-      <c r="R24" s="138"/>
-      <c r="S24" s="138"/>
-      <c r="T24" s="138"/>
-      <c r="U24" s="138"/>
-      <c r="V24" s="138"/>
-      <c r="W24" s="138"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="135"/>
+      <c r="L24" s="135"/>
+      <c r="M24" s="135"/>
+      <c r="N24" s="135"/>
+      <c r="O24" s="135"/>
+      <c r="P24" s="135"/>
+      <c r="Q24" s="135"/>
+      <c r="R24" s="135"/>
+      <c r="S24" s="135"/>
+      <c r="T24" s="135"/>
+      <c r="U24" s="135"/>
+      <c r="V24" s="135"/>
+      <c r="W24" s="135"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
@@ -10103,8 +10110,8 @@
       <c r="A26" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
       <c r="E26" s="59" t="s">
         <v>129</v>
       </c>
@@ -10170,250 +10177,250 @@
       <c r="AK27" s="58"/>
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="139" t="s">
+      <c r="A28" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="139"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="125"/>
-      <c r="L28" s="125"/>
-      <c r="M28" s="125"/>
-      <c r="N28" s="125"/>
-      <c r="O28" s="125"/>
-      <c r="P28" s="125"/>
-      <c r="Q28" s="125"/>
-      <c r="R28" s="125"/>
-      <c r="S28" s="125"/>
-      <c r="T28" s="125"/>
-      <c r="U28" s="125"/>
-      <c r="V28" s="125"/>
-      <c r="W28" s="125"/>
-      <c r="X28" s="125"/>
-      <c r="Y28" s="125"/>
-      <c r="Z28" s="125"/>
-      <c r="AA28" s="125"/>
-      <c r="AB28" s="125"/>
-      <c r="AC28" s="125"/>
-      <c r="AD28" s="125"/>
-      <c r="AE28" s="125"/>
-      <c r="AF28" s="125"/>
-      <c r="AG28" s="125"/>
-      <c r="AH28" s="125"/>
-      <c r="AI28" s="125"/>
-      <c r="AJ28" s="125"/>
-      <c r="AK28" s="125"/>
-      <c r="AL28" s="125"/>
+      <c r="B28" s="134"/>
+      <c r="C28" s="134"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="134"/>
+      <c r="I28" s="134"/>
+      <c r="J28" s="134"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="116"/>
+      <c r="N28" s="116"/>
+      <c r="O28" s="116"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="116"/>
+      <c r="S28" s="116"/>
+      <c r="T28" s="116"/>
+      <c r="U28" s="116"/>
+      <c r="V28" s="116"/>
+      <c r="W28" s="116"/>
+      <c r="X28" s="116"/>
+      <c r="Y28" s="116"/>
+      <c r="Z28" s="116"/>
+      <c r="AA28" s="116"/>
+      <c r="AB28" s="116"/>
+      <c r="AC28" s="116"/>
+      <c r="AD28" s="116"/>
+      <c r="AE28" s="116"/>
+      <c r="AF28" s="116"/>
+      <c r="AG28" s="116"/>
+      <c r="AH28" s="116"/>
+      <c r="AI28" s="116"/>
+      <c r="AJ28" s="116"/>
+      <c r="AK28" s="116"/>
+      <c r="AL28" s="116"/>
     </row>
     <row r="29" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="139"/>
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="139"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="125"/>
-      <c r="L29" s="125"/>
-      <c r="M29" s="125"/>
-      <c r="N29" s="125"/>
-      <c r="O29" s="125"/>
-      <c r="P29" s="125"/>
-      <c r="Q29" s="125"/>
-      <c r="R29" s="125"/>
-      <c r="S29" s="125"/>
-      <c r="T29" s="125"/>
-      <c r="U29" s="125"/>
-      <c r="V29" s="125"/>
-      <c r="W29" s="125"/>
-      <c r="X29" s="125"/>
-      <c r="Y29" s="125"/>
-      <c r="Z29" s="125"/>
-      <c r="AA29" s="125"/>
-      <c r="AB29" s="125"/>
-      <c r="AC29" s="125"/>
-      <c r="AD29" s="125"/>
-      <c r="AE29" s="125"/>
-      <c r="AF29" s="125"/>
-      <c r="AG29" s="125"/>
-      <c r="AH29" s="125"/>
-      <c r="AI29" s="125"/>
-      <c r="AJ29" s="125"/>
-      <c r="AK29" s="125"/>
-      <c r="AL29" s="125"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="134"/>
+      <c r="C29" s="134"/>
+      <c r="D29" s="134"/>
+      <c r="E29" s="134"/>
+      <c r="F29" s="134"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="134"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="116"/>
+      <c r="L29" s="116"/>
+      <c r="M29" s="116"/>
+      <c r="N29" s="116"/>
+      <c r="O29" s="116"/>
+      <c r="P29" s="116"/>
+      <c r="Q29" s="116"/>
+      <c r="R29" s="116"/>
+      <c r="S29" s="116"/>
+      <c r="T29" s="116"/>
+      <c r="U29" s="116"/>
+      <c r="V29" s="116"/>
+      <c r="W29" s="116"/>
+      <c r="X29" s="116"/>
+      <c r="Y29" s="116"/>
+      <c r="Z29" s="116"/>
+      <c r="AA29" s="116"/>
+      <c r="AB29" s="116"/>
+      <c r="AC29" s="116"/>
+      <c r="AD29" s="116"/>
+      <c r="AE29" s="116"/>
+      <c r="AF29" s="116"/>
+      <c r="AG29" s="116"/>
+      <c r="AH29" s="116"/>
+      <c r="AI29" s="116"/>
+      <c r="AJ29" s="116"/>
+      <c r="AK29" s="116"/>
+      <c r="AL29" s="116"/>
     </row>
     <row r="30" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="139" t="s">
+      <c r="A30" s="134" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="139"/>
-      <c r="C30" s="139"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="139"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="139"/>
-      <c r="L30" s="139"/>
-      <c r="M30" s="139"/>
-      <c r="N30" s="139"/>
-      <c r="O30" s="139"/>
-      <c r="P30" s="139"/>
-      <c r="Q30" s="139"/>
-      <c r="R30" s="139"/>
-      <c r="S30" s="139"/>
-      <c r="T30" s="139"/>
-      <c r="U30" s="139"/>
-      <c r="V30" s="139"/>
-      <c r="W30" s="139"/>
-      <c r="X30" s="139"/>
-      <c r="Y30" s="139"/>
-      <c r="Z30" s="139"/>
-      <c r="AA30" s="139"/>
-      <c r="AB30" s="139"/>
-      <c r="AC30" s="139"/>
-      <c r="AD30" s="139"/>
-      <c r="AE30" s="139"/>
-      <c r="AF30" s="139"/>
-      <c r="AG30" s="139"/>
-      <c r="AH30" s="139"/>
-      <c r="AI30" s="139"/>
-      <c r="AJ30" s="139"/>
-      <c r="AK30" s="139"/>
-      <c r="AL30" s="139"/>
+      <c r="B30" s="134"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="134"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="134"/>
+      <c r="H30" s="134"/>
+      <c r="I30" s="134"/>
+      <c r="J30" s="134"/>
+      <c r="K30" s="134"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="134"/>
+      <c r="N30" s="134"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="134"/>
+      <c r="Q30" s="134"/>
+      <c r="R30" s="134"/>
+      <c r="S30" s="134"/>
+      <c r="T30" s="134"/>
+      <c r="U30" s="134"/>
+      <c r="V30" s="134"/>
+      <c r="W30" s="134"/>
+      <c r="X30" s="134"/>
+      <c r="Y30" s="134"/>
+      <c r="Z30" s="134"/>
+      <c r="AA30" s="134"/>
+      <c r="AB30" s="134"/>
+      <c r="AC30" s="134"/>
+      <c r="AD30" s="134"/>
+      <c r="AE30" s="134"/>
+      <c r="AF30" s="134"/>
+      <c r="AG30" s="134"/>
+      <c r="AH30" s="134"/>
+      <c r="AI30" s="134"/>
+      <c r="AJ30" s="134"/>
+      <c r="AK30" s="134"/>
+      <c r="AL30" s="134"/>
     </row>
     <row r="31" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="139"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
-      <c r="J31" s="139"/>
-      <c r="K31" s="139"/>
-      <c r="L31" s="139"/>
-      <c r="M31" s="139"/>
-      <c r="N31" s="139"/>
-      <c r="O31" s="139"/>
-      <c r="P31" s="139"/>
-      <c r="Q31" s="139"/>
-      <c r="R31" s="139"/>
-      <c r="S31" s="139"/>
-      <c r="T31" s="139"/>
-      <c r="U31" s="139"/>
-      <c r="V31" s="139"/>
-      <c r="W31" s="139"/>
-      <c r="X31" s="139"/>
-      <c r="Y31" s="139"/>
-      <c r="Z31" s="139"/>
-      <c r="AA31" s="139"/>
-      <c r="AB31" s="139"/>
-      <c r="AC31" s="139"/>
-      <c r="AD31" s="139"/>
-      <c r="AE31" s="139"/>
-      <c r="AF31" s="139"/>
-      <c r="AG31" s="139"/>
-      <c r="AH31" s="139"/>
-      <c r="AI31" s="139"/>
-      <c r="AJ31" s="139"/>
-      <c r="AK31" s="139"/>
-      <c r="AL31" s="139"/>
+      <c r="A31" s="134"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="134"/>
+      <c r="E31" s="134"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="134"/>
+      <c r="I31" s="134"/>
+      <c r="J31" s="134"/>
+      <c r="K31" s="134"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="134"/>
+      <c r="N31" s="134"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="134"/>
+      <c r="Q31" s="134"/>
+      <c r="R31" s="134"/>
+      <c r="S31" s="134"/>
+      <c r="T31" s="134"/>
+      <c r="U31" s="134"/>
+      <c r="V31" s="134"/>
+      <c r="W31" s="134"/>
+      <c r="X31" s="134"/>
+      <c r="Y31" s="134"/>
+      <c r="Z31" s="134"/>
+      <c r="AA31" s="134"/>
+      <c r="AB31" s="134"/>
+      <c r="AC31" s="134"/>
+      <c r="AD31" s="134"/>
+      <c r="AE31" s="134"/>
+      <c r="AF31" s="134"/>
+      <c r="AG31" s="134"/>
+      <c r="AH31" s="134"/>
+      <c r="AI31" s="134"/>
+      <c r="AJ31" s="134"/>
+      <c r="AK31" s="134"/>
+      <c r="AL31" s="134"/>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="134" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="139"/>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="139"/>
-      <c r="L32" s="139"/>
-      <c r="M32" s="139"/>
-      <c r="N32" s="139"/>
-      <c r="O32" s="139"/>
-      <c r="P32" s="139"/>
-      <c r="Q32" s="139"/>
-      <c r="R32" s="139"/>
-      <c r="S32" s="139"/>
-      <c r="T32" s="139"/>
-      <c r="U32" s="139"/>
-      <c r="V32" s="139"/>
-      <c r="W32" s="139"/>
-      <c r="X32" s="139"/>
-      <c r="Y32" s="139"/>
-      <c r="Z32" s="139"/>
-      <c r="AA32" s="139"/>
-      <c r="AB32" s="139"/>
-      <c r="AC32" s="139"/>
-      <c r="AD32" s="139"/>
-      <c r="AE32" s="139"/>
-      <c r="AF32" s="139"/>
-      <c r="AG32" s="139"/>
-      <c r="AH32" s="139"/>
-      <c r="AI32" s="139"/>
-      <c r="AJ32" s="139"/>
-      <c r="AK32" s="139"/>
-      <c r="AL32" s="139"/>
+      <c r="B32" s="134"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="134"/>
+      <c r="F32" s="134"/>
+      <c r="G32" s="134"/>
+      <c r="H32" s="134"/>
+      <c r="I32" s="134"/>
+      <c r="J32" s="134"/>
+      <c r="K32" s="134"/>
+      <c r="L32" s="134"/>
+      <c r="M32" s="134"/>
+      <c r="N32" s="134"/>
+      <c r="O32" s="134"/>
+      <c r="P32" s="134"/>
+      <c r="Q32" s="134"/>
+      <c r="R32" s="134"/>
+      <c r="S32" s="134"/>
+      <c r="T32" s="134"/>
+      <c r="U32" s="134"/>
+      <c r="V32" s="134"/>
+      <c r="W32" s="134"/>
+      <c r="X32" s="134"/>
+      <c r="Y32" s="134"/>
+      <c r="Z32" s="134"/>
+      <c r="AA32" s="134"/>
+      <c r="AB32" s="134"/>
+      <c r="AC32" s="134"/>
+      <c r="AD32" s="134"/>
+      <c r="AE32" s="134"/>
+      <c r="AF32" s="134"/>
+      <c r="AG32" s="134"/>
+      <c r="AH32" s="134"/>
+      <c r="AI32" s="134"/>
+      <c r="AJ32" s="134"/>
+      <c r="AK32" s="134"/>
+      <c r="AL32" s="134"/>
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A33" s="139"/>
-      <c r="B33" s="139"/>
-      <c r="C33" s="139"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="139"/>
-      <c r="K33" s="139"/>
-      <c r="L33" s="139"/>
-      <c r="M33" s="139"/>
-      <c r="N33" s="139"/>
-      <c r="O33" s="139"/>
-      <c r="P33" s="139"/>
-      <c r="Q33" s="139"/>
-      <c r="R33" s="139"/>
-      <c r="S33" s="139"/>
-      <c r="T33" s="139"/>
-      <c r="U33" s="139"/>
-      <c r="V33" s="139"/>
-      <c r="W33" s="139"/>
-      <c r="X33" s="139"/>
-      <c r="Y33" s="139"/>
-      <c r="Z33" s="139"/>
-      <c r="AA33" s="139"/>
-      <c r="AB33" s="139"/>
-      <c r="AC33" s="139"/>
-      <c r="AD33" s="139"/>
-      <c r="AE33" s="139"/>
-      <c r="AF33" s="139"/>
-      <c r="AG33" s="139"/>
-      <c r="AH33" s="139"/>
-      <c r="AI33" s="139"/>
-      <c r="AJ33" s="139"/>
-      <c r="AK33" s="139"/>
-      <c r="AL33" s="139"/>
+      <c r="A33" s="134"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="134"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="134"/>
+      <c r="I33" s="134"/>
+      <c r="J33" s="134"/>
+      <c r="K33" s="134"/>
+      <c r="L33" s="134"/>
+      <c r="M33" s="134"/>
+      <c r="N33" s="134"/>
+      <c r="O33" s="134"/>
+      <c r="P33" s="134"/>
+      <c r="Q33" s="134"/>
+      <c r="R33" s="134"/>
+      <c r="S33" s="134"/>
+      <c r="T33" s="134"/>
+      <c r="U33" s="134"/>
+      <c r="V33" s="134"/>
+      <c r="W33" s="134"/>
+      <c r="X33" s="134"/>
+      <c r="Y33" s="134"/>
+      <c r="Z33" s="134"/>
+      <c r="AA33" s="134"/>
+      <c r="AB33" s="134"/>
+      <c r="AC33" s="134"/>
+      <c r="AD33" s="134"/>
+      <c r="AE33" s="134"/>
+      <c r="AF33" s="134"/>
+      <c r="AG33" s="134"/>
+      <c r="AH33" s="134"/>
+      <c r="AI33" s="134"/>
+      <c r="AJ33" s="134"/>
+      <c r="AK33" s="134"/>
+      <c r="AL33" s="134"/>
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="59"/>
@@ -10780,11 +10787,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A32:J33"/>
-    <mergeCell ref="K32:Q33"/>
-    <mergeCell ref="R32:X33"/>
-    <mergeCell ref="Y32:AE33"/>
-    <mergeCell ref="AF32:AL33"/>
+    <mergeCell ref="AC8:AI8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="V9:AB9"/>
+    <mergeCell ref="AC9:AI9"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:U8"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="J24:W24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A28:J29"/>
+    <mergeCell ref="K28:Q29"/>
+    <mergeCell ref="R28:X29"/>
     <mergeCell ref="Y28:AE29"/>
     <mergeCell ref="AF28:AL29"/>
     <mergeCell ref="A30:J31"/>
@@ -10792,29 +10815,13 @@
     <mergeCell ref="R30:X31"/>
     <mergeCell ref="Y30:AE31"/>
     <mergeCell ref="AF30:AL31"/>
-    <mergeCell ref="J24:W24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A28:J29"/>
-    <mergeCell ref="K28:Q29"/>
-    <mergeCell ref="R28:X29"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:U8"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="AC8:AI8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="V9:AB9"/>
-    <mergeCell ref="AC9:AI9"/>
+    <mergeCell ref="A32:J33"/>
+    <mergeCell ref="K32:Q33"/>
+    <mergeCell ref="R32:X33"/>
+    <mergeCell ref="Y32:AE33"/>
+    <mergeCell ref="AF32:AL33"/>
   </mergeCells>
-  <phoneticPr fontId="32" type="noConversion"/>
+  <phoneticPr fontId="33" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Mango_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063AA031-2300-4AFF-8E7A-BE2B22022547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA436980-99D9-47BC-9BDC-187F6F12DF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -19,9 +19,11 @@
     <sheet name="Seam Slippage" sheetId="21" r:id="rId4"/>
     <sheet name="Tear Strength" sheetId="22" r:id="rId5"/>
     <sheet name="Abrasion&amp;Snagging Resistance" sheetId="23" r:id="rId6"/>
+    <sheet name="Elongation" sheetId="24" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="ReportNumber" localSheetId="5">'Abrasion&amp;Snagging Resistance'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="6">Elongation!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="2">'Pilling Resistance'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="3">'Seam Slippage'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="4">'Tear Strength'!$M$1</definedName>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="170">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -315,42 +317,42 @@
   </si>
   <si>
     <t>Pilling Resistance</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>ICI Pilling Box:</t>
   </si>
   <si>
     <t>Original</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Sample</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Cycle</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Rating</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Pilling</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Fuzzing</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Matting</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Pilling grading scheme</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -375,73 +377,73 @@
       </rPr>
       <t>: Not applicable</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Fuzzing grading scheme</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Matting grading scheme</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">1 Severe pilling- pills of varying size </t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> specimen surface</t>
   </si>
   <si>
     <t>and density covering the whole of the</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>5 No change</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>4 partially formed pills</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">3 Moderate pilling- pills of varying  </t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">size and density partially covering </t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>the specimen surface</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>2 Distinct pilling- pills of varying</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">size and density covering a large </t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>proportion of the specimen surface</t>
   </si>
   <si>
     <t>4 Slight surface fuzzing</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>3Moderate surface fuzzing</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>2 Distinct surface fuzzing</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>1 Dense surface fuzzing</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Martindale:</t>
@@ -583,7 +585,7 @@
   </si>
   <si>
     <t>*1: Testing sample happened (Y.P.O./S.T.B./F.B./F.T.S) before achieving the (3mm/4mm/6mm/1/4inch ) opening</t>
-    <phoneticPr fontId="26" type="noConversion"/>
+    <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
     <t>*2: Testing sample happened (Y.P.O./S.T.B./F.B./F.T.S) before achieving the (3mm/4mm/6mm/1/4inch ) opening</t>
@@ -618,7 +620,7 @@
   </si>
   <si>
     <t>Cycle：</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Abrasion Resistance</t>
@@ -715,31 +717,149 @@
   </si>
   <si>
     <t xml:space="preserve">Remark: </t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>Over 50001 rubs                   Every 10000 rubs</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>Up to 6000 rubs                    Every 1000 rubs</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>Sample  Unit(N)</t>
-    <phoneticPr fontId="26" type="noConversion"/>
+    <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
     <t>Sample  Unit(gf)</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>Warp /Length yarns torn (N)</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>Weft / Width yarns torn (N)</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Elongation and Recovery of Elastic </t>
+  </si>
+  <si>
+    <t>Extension at</t>
+  </si>
+  <si>
+    <t>N;</t>
+  </si>
+  <si>
+    <t>At</t>
+  </si>
+  <si>
+    <t>cycle.</t>
+  </si>
+  <si>
+    <t>Warp/Lengthwise(%)</t>
+  </si>
+  <si>
+    <t>Weft/Widthwise(%)</t>
+  </si>
+  <si>
+    <t>Residual Extension after 1 min. Relaxation</t>
+  </si>
+  <si>
+    <t>Residual Extension after 30 mins. Relaxation</t>
+  </si>
+  <si>
+    <t>Recovery after 1 min. Relaxation</t>
+  </si>
+  <si>
+    <t>Recovery after 30 mins. Relaxation</t>
+  </si>
+  <si>
+    <t>L1(mm)</t>
+  </si>
+  <si>
+    <t>L2(mm)</t>
+  </si>
+  <si>
+    <t>L3(mm)</t>
+  </si>
+  <si>
+    <t>E(%)</t>
+  </si>
+  <si>
+    <t>R1(%)</t>
+  </si>
+  <si>
+    <t>R2(%)</t>
+  </si>
+  <si>
+    <t>R3(%)</t>
+  </si>
+  <si>
+    <t>R4(%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: L1: original length;     L2: after 1min. length;     L3: after 30mins length; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1: Residual Extension after 1 min Relaxation; R2: Residual Extension after 30 mins Relaxation; </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>=L2-L1  ; C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>30min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>=L3-L1    Recovery% =</t>
+    </r>
+  </si>
+  <si>
+    <t>(E-C)/E *100</t>
+  </si>
+  <si>
+    <t>Equipment No:SFL-NGB-EQP-</t>
   </si>
 </sst>
 </file>
@@ -749,12 +869,19 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1042,6 +1169,75 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9.5"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1051,7 +1247,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1173,19 +1369,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1193,166 +1410,175 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1367,22 +1593,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1391,173 +1617,301 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="2" xr:uid="{B926554C-D793-41B2-A366-631BCC55C3AD}"/>
+    <cellStyle name="常规 3" xfId="3" xr:uid="{BAF1A318-C259-4EC9-A5F6-D9379DECD6A5}"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1832,12 +2186,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="28" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1846,27 +2200,27 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="70"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="70"/>
-      <c r="AB1" s="70"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1895,15 +2249,15 @@
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -1925,7 +2279,7 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
-    <row r="4" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -1954,7 +2308,7 @@
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
@@ -1983,7 +2337,7 @@
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
@@ -2012,7 +2366,7 @@
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>4</v>
       </c>
@@ -2041,7 +2395,7 @@
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -2068,7 +2422,7 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
     </row>
-    <row r="9" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
@@ -2099,87 +2453,87 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
     </row>
-    <row r="10" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="79" t="s">
+    <row r="10" spans="1:28" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="71" t="s">
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="73" t="s">
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
+      <c r="V10" s="75"/>
+      <c r="W10" s="75"/>
+      <c r="X10" s="75"/>
+      <c r="Y10" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="74"/>
-      <c r="AA10" s="74"/>
-      <c r="AB10" s="75"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="71" t="s">
+      <c r="Z10" s="77"/>
+      <c r="AA10" s="77"/>
+      <c r="AB10" s="78"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A11" s="85"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="71" t="s">
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="71" t="s">
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="71" t="s">
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="85"/>
-      <c r="U11" s="71" t="s">
+      <c r="R11" s="75"/>
+      <c r="S11" s="75"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="86"/>
-      <c r="Y11" s="76"/>
-      <c r="Z11" s="77"/>
-      <c r="AA11" s="77"/>
-      <c r="AB11" s="78"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="67"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
+      <c r="V11" s="75"/>
+      <c r="W11" s="75"/>
+      <c r="X11" s="89"/>
+      <c r="Y11" s="79"/>
+      <c r="Z11" s="80"/>
+      <c r="AA11" s="80"/>
+      <c r="AB11" s="81"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A12" s="91"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2205,11 +2559,11 @@
       <c r="AA12" s="4"/>
       <c r="AB12" s="2"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="67"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A13" s="91"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -2235,11 +2589,11 @@
       <c r="AA13" s="4"/>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="69"/>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A14" s="91"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="93"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2265,11 +2619,11 @@
       <c r="AA14" s="4"/>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="67"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A15" s="91"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="93"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2295,11 +2649,11 @@
       <c r="AA15" s="4"/>
       <c r="AB15" s="2"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A16" s="91"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="93"/>
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -2325,7 +2679,7 @@
       <c r="AA16" s="4"/>
       <c r="AB16" s="2"/>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>16</v>
       </c>
@@ -2354,7 +2708,7 @@
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2381,7 +2735,7 @@
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>17</v>
       </c>
@@ -2410,7 +2764,7 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2437,7 +2791,7 @@
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2466,6 +2820,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="E10:X10"/>
     <mergeCell ref="Y10:AB11"/>
@@ -2476,13 +2835,8 @@
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
   </mergeCells>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -2500,16 +2854,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD6E72E-6B16-4A5A-8E3F-434228BD81B4}">
   <dimension ref="A1:AL48"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="2.33203125" style="22" customWidth="1"/>
+    <col min="1" max="7" width="2.375" style="22" customWidth="1"/>
     <col min="8" max="8" width="2" style="22" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" style="22" customWidth="1"/>
-    <col min="32" max="38" width="2.33203125" style="22" customWidth="1"/>
-    <col min="39" max="16384" width="8.88671875" style="22"/>
+    <col min="9" max="31" width="2.125" style="22" customWidth="1"/>
+    <col min="32" max="38" width="2.375" style="22" customWidth="1"/>
+    <col min="39" max="16384" width="8.875" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -2521,34 +2875,34 @@
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="103"/>
-      <c r="AH1" s="103"/>
-      <c r="AI1" s="103"/>
-      <c r="AJ1" s="103"/>
-      <c r="AK1" s="103"/>
-      <c r="AL1" s="103"/>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+      <c r="W1" s="94"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="94"/>
+      <c r="AA1" s="94"/>
+      <c r="AB1" s="94"/>
+      <c r="AC1" s="94"/>
+      <c r="AD1" s="94"/>
+      <c r="AE1" s="94"/>
+      <c r="AF1" s="94"/>
+      <c r="AG1" s="94"/>
+      <c r="AH1" s="94"/>
+      <c r="AI1" s="94"/>
+      <c r="AJ1" s="94"/>
+      <c r="AK1" s="94"/>
+      <c r="AL1" s="94"/>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
         <v>19</v>
       </c>
@@ -2581,18 +2935,18 @@
       <c r="AE2" s="21"/>
       <c r="AF2" s="21"/>
     </row>
-    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="112"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
+    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="109"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -2615,7 +2969,7 @@
       <c r="AE3" s="21"/>
       <c r="AF3" s="21"/>
     </row>
-    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
@@ -2646,7 +3000,7 @@
       <c r="AE4" s="21"/>
       <c r="AF4" s="21"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
         <v>20</v>
       </c>
@@ -2678,7 +3032,7 @@
       <c r="AF5" s="21"/>
       <c r="AK5" s="21"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>21</v>
       </c>
@@ -2710,7 +3064,7 @@
       <c r="AF6" s="21"/>
       <c r="AK6" s="21"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -2740,7 +3094,7 @@
       <c r="AF7" s="21"/>
       <c r="AK7" s="21"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>22</v>
       </c>
@@ -2772,7 +3126,7 @@
       <c r="AF8" s="21"/>
       <c r="AK8" s="21"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="21"/>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
@@ -2803,53 +3157,53 @@
       <c r="AE9" s="21"/>
       <c r="AF9" s="21"/>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="104" t="s">
+      <c r="D10" s="107"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="105"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="104" t="s">
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
+      <c r="K10" s="102"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="102"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="103"/>
+      <c r="P10" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="Q10" s="105"/>
-      <c r="R10" s="105"/>
-      <c r="S10" s="105"/>
-      <c r="T10" s="105"/>
-      <c r="U10" s="105"/>
-      <c r="V10" s="105"/>
-      <c r="W10" s="105"/>
-      <c r="X10" s="105"/>
-      <c r="Y10" s="105"/>
-      <c r="Z10" s="105"/>
-      <c r="AA10" s="105"/>
-      <c r="AB10" s="105"/>
-      <c r="AC10" s="105"/>
-      <c r="AD10" s="105"/>
-      <c r="AE10" s="105"/>
-      <c r="AF10" s="105"/>
-      <c r="AG10" s="105"/>
-      <c r="AH10" s="105"/>
-      <c r="AI10" s="105"/>
-      <c r="AJ10" s="105"/>
-      <c r="AK10" s="105"/>
-      <c r="AL10" s="106"/>
-    </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="Q10" s="102"/>
+      <c r="R10" s="102"/>
+      <c r="S10" s="102"/>
+      <c r="T10" s="102"/>
+      <c r="U10" s="102"/>
+      <c r="V10" s="102"/>
+      <c r="W10" s="102"/>
+      <c r="X10" s="102"/>
+      <c r="Y10" s="102"/>
+      <c r="Z10" s="102"/>
+      <c r="AA10" s="102"/>
+      <c r="AB10" s="102"/>
+      <c r="AC10" s="102"/>
+      <c r="AD10" s="102"/>
+      <c r="AE10" s="102"/>
+      <c r="AF10" s="102"/>
+      <c r="AG10" s="102"/>
+      <c r="AH10" s="102"/>
+      <c r="AI10" s="102"/>
+      <c r="AJ10" s="102"/>
+      <c r="AK10" s="102"/>
+      <c r="AL10" s="103"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
         <v>26</v>
       </c>
@@ -2857,62 +3211,62 @@
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="27"/>
-      <c r="F11" s="104" t="s">
+      <c r="F11" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="104" t="s">
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="105"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="105"/>
-      <c r="O11" s="106"/>
-      <c r="P11" s="104" t="s">
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
+      <c r="N11" s="102"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="106"/>
-      <c r="U11" s="104" t="s">
+      <c r="Q11" s="102"/>
+      <c r="R11" s="102"/>
+      <c r="S11" s="102"/>
+      <c r="T11" s="103"/>
+      <c r="U11" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="V11" s="105"/>
-      <c r="W11" s="105"/>
-      <c r="X11" s="105"/>
-      <c r="Y11" s="106"/>
-      <c r="Z11" s="104" t="s">
+      <c r="V11" s="102"/>
+      <c r="W11" s="102"/>
+      <c r="X11" s="102"/>
+      <c r="Y11" s="103"/>
+      <c r="Z11" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="AA11" s="105"/>
-      <c r="AB11" s="105"/>
-      <c r="AC11" s="105"/>
-      <c r="AD11" s="106"/>
-      <c r="AE11" s="104" t="s">
+      <c r="AA11" s="102"/>
+      <c r="AB11" s="102"/>
+      <c r="AC11" s="102"/>
+      <c r="AD11" s="103"/>
+      <c r="AE11" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="AF11" s="105"/>
-      <c r="AG11" s="105"/>
-      <c r="AH11" s="105"/>
-      <c r="AI11" s="106"/>
-      <c r="AJ11" s="107" t="s">
+      <c r="AF11" s="102"/>
+      <c r="AG11" s="102"/>
+      <c r="AH11" s="102"/>
+      <c r="AI11" s="103"/>
+      <c r="AJ11" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="108"/>
-      <c r="AL11" s="109"/>
-    </row>
-    <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="88" t="s">
+      <c r="AK11" s="105"/>
+      <c r="AL11" s="106"/>
+    </row>
+    <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="90"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="97"/>
       <c r="F12" s="28"/>
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
@@ -2947,12 +3301,12 @@
       <c r="AK12" s="32"/>
       <c r="AL12" s="33"/>
     </row>
-    <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="91"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
+    <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="100"/>
       <c r="F13" s="34"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
@@ -2987,14 +3341,14 @@
       <c r="AK13" s="24"/>
       <c r="AL13" s="38"/>
     </row>
-    <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="88" t="s">
+    <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="90"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="97"/>
       <c r="F14" s="28"/>
       <c r="G14" s="29"/>
       <c r="H14" s="29"/>
@@ -3029,12 +3383,12 @@
       <c r="AK14" s="32"/>
       <c r="AL14" s="33"/>
     </row>
-    <row r="15" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="93"/>
+    <row r="15" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="98"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="100"/>
       <c r="F15" s="34"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
@@ -3069,14 +3423,14 @@
       <c r="AK15" s="24"/>
       <c r="AL15" s="38"/>
     </row>
-    <row r="16" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="88" t="s">
+    <row r="16" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="90"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="97"/>
       <c r="F16" s="28"/>
       <c r="G16" s="29"/>
       <c r="H16" s="29"/>
@@ -3111,12 +3465,12 @@
       <c r="AK16" s="32"/>
       <c r="AL16" s="33"/>
     </row>
-    <row r="17" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="93"/>
+    <row r="17" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="98"/>
+      <c r="B17" s="99"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="100"/>
       <c r="F17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
@@ -3151,14 +3505,14 @@
       <c r="AK17" s="24"/>
       <c r="AL17" s="38"/>
     </row>
-    <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="88" t="s">
+    <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="90"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="97"/>
       <c r="F18" s="28"/>
       <c r="G18" s="29"/>
       <c r="H18" s="29"/>
@@ -3193,12 +3547,12 @@
       <c r="AK18" s="32"/>
       <c r="AL18" s="33"/>
     </row>
-    <row r="19" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="91"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="93"/>
+    <row r="19" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="98"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="100"/>
       <c r="F19" s="34"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
@@ -3233,14 +3587,14 @@
       <c r="AK19" s="24"/>
       <c r="AL19" s="38"/>
     </row>
-    <row r="20" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="88" t="s">
+    <row r="20" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="90"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="97"/>
       <c r="F20" s="28"/>
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
@@ -3275,12 +3629,12 @@
       <c r="AK20" s="32"/>
       <c r="AL20" s="33"/>
     </row>
-    <row r="21" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="93"/>
+    <row r="21" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="98"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="100"/>
       <c r="F21" s="34"/>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
@@ -3315,14 +3669,14 @@
       <c r="AK21" s="24"/>
       <c r="AL21" s="38"/>
     </row>
-    <row r="22" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="88" t="s">
+    <row r="22" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="90"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="97"/>
       <c r="F22" s="28"/>
       <c r="G22" s="29"/>
       <c r="H22" s="29"/>
@@ -3357,12 +3711,12 @@
       <c r="AK22" s="32"/>
       <c r="AL22" s="33"/>
     </row>
-    <row r="23" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="93"/>
+    <row r="23" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="98"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="100"/>
       <c r="F23" s="34"/>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
@@ -3397,14 +3751,14 @@
       <c r="AK23" s="24"/>
       <c r="AL23" s="38"/>
     </row>
-    <row r="24" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="88" t="s">
+    <row r="24" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="90"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="97"/>
       <c r="F24" s="28"/>
       <c r="G24" s="29"/>
       <c r="H24" s="29"/>
@@ -3439,12 +3793,12 @@
       <c r="AK24" s="32"/>
       <c r="AL24" s="33"/>
     </row>
-    <row r="25" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="93"/>
+    <row r="25" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="98"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="100"/>
       <c r="F25" s="34"/>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
@@ -3479,14 +3833,14 @@
       <c r="AK25" s="24"/>
       <c r="AL25" s="38"/>
     </row>
-    <row r="26" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="88" t="s">
+    <row r="26" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="90"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="97"/>
       <c r="F26" s="28"/>
       <c r="G26" s="29"/>
       <c r="H26" s="29"/>
@@ -3521,12 +3875,12 @@
       <c r="AK26" s="32"/>
       <c r="AL26" s="33"/>
     </row>
-    <row r="27" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="93"/>
+    <row r="27" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="98"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="100"/>
       <c r="F27" s="34"/>
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
@@ -3561,14 +3915,14 @@
       <c r="AK27" s="24"/>
       <c r="AL27" s="38"/>
     </row>
-    <row r="28" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="88" t="s">
+    <row r="28" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="90"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="97"/>
       <c r="F28" s="28"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
@@ -3603,12 +3957,12 @@
       <c r="AK28" s="32"/>
       <c r="AL28" s="33"/>
     </row>
-    <row r="29" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="91"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="93"/>
+    <row r="29" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="98"/>
+      <c r="B29" s="99"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="100"/>
       <c r="F29" s="34"/>
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
@@ -3643,14 +3997,14 @@
       <c r="AK29" s="24"/>
       <c r="AL29" s="38"/>
     </row>
-    <row r="30" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="88" t="s">
+    <row r="30" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="90"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="97"/>
       <c r="F30" s="28"/>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -3685,12 +4039,12 @@
       <c r="AK30" s="32"/>
       <c r="AL30" s="33"/>
     </row>
-    <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="91"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="93"/>
+    <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="98"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="100"/>
       <c r="F31" s="34"/>
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
@@ -3725,14 +4079,14 @@
       <c r="AK31" s="24"/>
       <c r="AL31" s="38"/>
     </row>
-    <row r="32" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="88" t="s">
+    <row r="32" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
       <c r="F32" s="28"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
@@ -3767,12 +4121,12 @@
       <c r="AK32" s="32"/>
       <c r="AL32" s="33"/>
     </row>
-    <row r="33" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
+    <row r="33" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="98"/>
+      <c r="B33" s="99"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
       <c r="F33" s="34"/>
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
@@ -3807,14 +4161,14 @@
       <c r="AK33" s="24"/>
       <c r="AL33" s="38"/>
     </row>
-    <row r="34" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="88" t="s">
+    <row r="34" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
+      <c r="B34" s="96"/>
+      <c r="C34" s="96"/>
+      <c r="D34" s="96"/>
+      <c r="E34" s="96"/>
       <c r="F34" s="28"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29"/>
@@ -3849,12 +4203,12 @@
       <c r="AK34" s="32"/>
       <c r="AL34" s="33"/>
     </row>
-    <row r="35" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="93"/>
+    <row r="35" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="98"/>
+      <c r="B35" s="99"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="100"/>
       <c r="F35" s="34"/>
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
@@ -3889,14 +4243,14 @@
       <c r="AK35" s="24"/>
       <c r="AL35" s="38"/>
     </row>
-    <row r="36" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="94" t="s">
+    <row r="36" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="96"/>
+      <c r="B36" s="111"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
       <c r="F36" s="28"/>
       <c r="G36" s="29"/>
       <c r="H36" s="29"/>
@@ -3931,12 +4285,12 @@
       <c r="AK36" s="32"/>
       <c r="AL36" s="33"/>
     </row>
-    <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="97"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="99"/>
+    <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="113"/>
+      <c r="B37" s="114"/>
+      <c r="C37" s="114"/>
+      <c r="D37" s="114"/>
+      <c r="E37" s="115"/>
       <c r="F37" s="34"/>
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
@@ -3971,7 +4325,7 @@
       <c r="AK37" s="24"/>
       <c r="AL37" s="38"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A38" s="21" t="s">
         <v>38</v>
       </c>
@@ -4004,22 +4358,22 @@
       <c r="AE38" s="21"/>
       <c r="AF38" s="21"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A39" s="100" t="s">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A39" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="100"/>
-      <c r="C39" s="100"/>
-      <c r="D39" s="101" t="s">
+      <c r="B39" s="116"/>
+      <c r="C39" s="116"/>
+      <c r="D39" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="101"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="101"/>
-      <c r="H39" s="101"/>
-      <c r="I39" s="101"/>
-      <c r="J39" s="101"/>
-      <c r="K39" s="101"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="117"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="117"/>
       <c r="L39" s="21"/>
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
@@ -4042,20 +4396,20 @@
       <c r="AE39" s="21"/>
       <c r="AF39" s="21"/>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A40" s="100"/>
-      <c r="B40" s="100"/>
-      <c r="C40" s="100"/>
-      <c r="D40" s="102" t="s">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A40" s="116"/>
+      <c r="B40" s="116"/>
+      <c r="C40" s="116"/>
+      <c r="D40" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="102"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="102"/>
-      <c r="H40" s="102"/>
-      <c r="I40" s="102"/>
-      <c r="J40" s="102"/>
-      <c r="K40" s="102"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
@@ -4078,7 +4432,7 @@
       <c r="AE40" s="21"/>
       <c r="AF40" s="21"/>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A41" s="21" t="s">
         <v>17</v>
       </c>
@@ -4111,7 +4465,7 @@
       <c r="AE41" s="21"/>
       <c r="AF41" s="21"/>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
@@ -4142,7 +4496,7 @@
       <c r="AE42" s="21"/>
       <c r="AF42" s="21"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A43" s="39"/>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
@@ -4173,7 +4527,7 @@
       <c r="AE43" s="21"/>
       <c r="AF43" s="21"/>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A44" s="23"/>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
@@ -4204,7 +4558,7 @@
       <c r="AE44" s="21"/>
       <c r="AF44" s="21"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
@@ -4235,7 +4589,7 @@
       <c r="AE45" s="21"/>
       <c r="AF45" s="21"/>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="21"/>
@@ -4266,14 +4620,26 @@
       <c r="AE46" s="21"/>
       <c r="AF46" s="21"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A47" s="21"/>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A48" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A16:E17"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="D39:K39"/>
+    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="A24:E25"/>
+    <mergeCell ref="A26:E27"/>
+    <mergeCell ref="A28:E29"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="A32:E33"/>
+    <mergeCell ref="A34:E35"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="A22:E23"/>
@@ -4290,20 +4656,8 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A12:E13"/>
     <mergeCell ref="A14:E15"/>
-    <mergeCell ref="A16:E17"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="A24:E25"/>
-    <mergeCell ref="A26:E27"/>
-    <mergeCell ref="A28:E29"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="A32:E33"/>
-    <mergeCell ref="A34:E35"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -4321,15 +4675,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A966B5-BF06-44FD-908C-4467C7012DA9}">
   <dimension ref="A1:AL54"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="2.33203125" customWidth="1"/>
+    <col min="1" max="7" width="2.375" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" customWidth="1"/>
-    <col min="32" max="38" width="2.33203125" customWidth="1"/>
+    <col min="9" max="31" width="2.125" customWidth="1"/>
+    <col min="32" max="38" width="2.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4341,34 +4695,34 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
-    </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
+      <c r="AI1" s="71"/>
+      <c r="AJ1" s="71"/>
+      <c r="AK1" s="71"/>
+      <c r="AL1" s="71"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>44</v>
       </c>
@@ -4401,23 +4755,23 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="120"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -4434,17 +4788,17 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -4468,7 +4822,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>46</v>
       </c>
@@ -4502,219 +4856,219 @@
       <c r="AF5" s="3"/>
       <c r="AK5" s="7"/>
     </row>
-    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="117" t="s">
+    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="118" t="s">
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="118"/>
-      <c r="O6" s="118"/>
-      <c r="P6" s="118"/>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="118"/>
-      <c r="S6" s="118"/>
-      <c r="T6" s="118"/>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
-      <c r="Z6" s="118"/>
-      <c r="AA6" s="118"/>
-      <c r="AB6" s="118"/>
-      <c r="AC6" s="118"/>
-      <c r="AD6" s="118"/>
-      <c r="AE6" s="118"/>
-      <c r="AF6" s="118"/>
-      <c r="AG6" s="118"/>
-      <c r="AH6" s="118"/>
-      <c r="AI6" s="118"/>
-      <c r="AJ6" s="118"/>
-      <c r="AK6" s="118"/>
-      <c r="AL6" s="118"/>
-    </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="117"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="122" t="s">
+      <c r="N6" s="121"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="121"/>
+      <c r="S6" s="121"/>
+      <c r="T6" s="121"/>
+      <c r="U6" s="121"/>
+      <c r="V6" s="121"/>
+      <c r="W6" s="121"/>
+      <c r="X6" s="121"/>
+      <c r="Y6" s="121"/>
+      <c r="Z6" s="121"/>
+      <c r="AA6" s="121"/>
+      <c r="AB6" s="121"/>
+      <c r="AC6" s="121"/>
+      <c r="AD6" s="121"/>
+      <c r="AE6" s="121"/>
+      <c r="AF6" s="121"/>
+      <c r="AG6" s="121"/>
+      <c r="AH6" s="121"/>
+      <c r="AI6" s="121"/>
+      <c r="AJ6" s="121"/>
+      <c r="AK6" s="121"/>
+      <c r="AL6" s="121"/>
+    </row>
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="68"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="121"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="123"/>
-      <c r="O7" s="123"/>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="123"/>
-      <c r="S7" s="123"/>
-      <c r="T7" s="123"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="122" t="s">
+      <c r="N7" s="126"/>
+      <c r="O7" s="126"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="126"/>
+      <c r="U7" s="127"/>
+      <c r="V7" s="125" t="s">
         <v>51</v>
       </c>
-      <c r="W7" s="123"/>
-      <c r="X7" s="123"/>
-      <c r="Y7" s="123"/>
-      <c r="Z7" s="123"/>
-      <c r="AA7" s="123"/>
-      <c r="AB7" s="123"/>
-      <c r="AC7" s="123"/>
-      <c r="AD7" s="124"/>
-      <c r="AE7" s="119" t="s">
+      <c r="W7" s="126"/>
+      <c r="X7" s="126"/>
+      <c r="Y7" s="126"/>
+      <c r="Z7" s="126"/>
+      <c r="AA7" s="126"/>
+      <c r="AB7" s="126"/>
+      <c r="AC7" s="126"/>
+      <c r="AD7" s="127"/>
+      <c r="AE7" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="AF7" s="119"/>
-      <c r="AG7" s="119"/>
-      <c r="AH7" s="119"/>
-      <c r="AI7" s="119"/>
-      <c r="AJ7" s="119"/>
-      <c r="AK7" s="119"/>
-      <c r="AL7" s="119"/>
-    </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="116"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="86"/>
-      <c r="O8" s="86"/>
-      <c r="P8" s="86"/>
-      <c r="Q8" s="86"/>
-      <c r="R8" s="86"/>
-      <c r="S8" s="86"/>
-      <c r="T8" s="86"/>
-      <c r="U8" s="85"/>
-      <c r="V8" s="121"/>
-      <c r="W8" s="86"/>
-      <c r="X8" s="86"/>
-      <c r="Y8" s="86"/>
-      <c r="Z8" s="86"/>
-      <c r="AA8" s="86"/>
-      <c r="AB8" s="86"/>
-      <c r="AC8" s="86"/>
-      <c r="AD8" s="85"/>
-      <c r="AE8" s="114"/>
-      <c r="AF8" s="114"/>
-      <c r="AG8" s="114"/>
-      <c r="AH8" s="114"/>
-      <c r="AI8" s="114"/>
-      <c r="AJ8" s="114"/>
-      <c r="AK8" s="114"/>
-      <c r="AL8" s="114"/>
-    </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="116"/>
-      <c r="B9" s="116"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="116"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="114"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="86"/>
-      <c r="O9" s="86"/>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="86"/>
-      <c r="R9" s="86"/>
-      <c r="S9" s="86"/>
-      <c r="T9" s="86"/>
-      <c r="U9" s="85"/>
-      <c r="V9" s="121"/>
-      <c r="W9" s="86"/>
-      <c r="X9" s="86"/>
-      <c r="Y9" s="86"/>
-      <c r="Z9" s="86"/>
-      <c r="AA9" s="86"/>
-      <c r="AB9" s="86"/>
-      <c r="AC9" s="86"/>
-      <c r="AD9" s="85"/>
-      <c r="AE9" s="114"/>
-      <c r="AF9" s="114"/>
-      <c r="AG9" s="114"/>
-      <c r="AH9" s="114"/>
-      <c r="AI9" s="114"/>
-      <c r="AJ9" s="114"/>
-      <c r="AK9" s="114"/>
-      <c r="AL9" s="114"/>
-    </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="86"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="86"/>
-      <c r="Q10" s="86"/>
-      <c r="R10" s="86"/>
-      <c r="S10" s="86"/>
-      <c r="T10" s="86"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="121"/>
-      <c r="W10" s="86"/>
-      <c r="X10" s="86"/>
-      <c r="Y10" s="86"/>
-      <c r="Z10" s="86"/>
-      <c r="AA10" s="86"/>
-      <c r="AB10" s="86"/>
-      <c r="AC10" s="86"/>
-      <c r="AD10" s="85"/>
-      <c r="AE10" s="114"/>
-      <c r="AF10" s="114"/>
-      <c r="AG10" s="114"/>
-      <c r="AH10" s="114"/>
-      <c r="AI10" s="114"/>
-      <c r="AJ10" s="114"/>
-      <c r="AK10" s="114"/>
-      <c r="AL10" s="114"/>
-    </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF7" s="128"/>
+      <c r="AG7" s="128"/>
+      <c r="AH7" s="128"/>
+      <c r="AI7" s="128"/>
+      <c r="AJ7" s="128"/>
+      <c r="AK7" s="128"/>
+      <c r="AL7" s="128"/>
+    </row>
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="70"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="124"/>
+      <c r="N8" s="89"/>
+      <c r="O8" s="89"/>
+      <c r="P8" s="89"/>
+      <c r="Q8" s="89"/>
+      <c r="R8" s="89"/>
+      <c r="S8" s="89"/>
+      <c r="T8" s="89"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="124"/>
+      <c r="W8" s="89"/>
+      <c r="X8" s="89"/>
+      <c r="Y8" s="89"/>
+      <c r="Z8" s="89"/>
+      <c r="AA8" s="89"/>
+      <c r="AB8" s="89"/>
+      <c r="AC8" s="89"/>
+      <c r="AD8" s="88"/>
+      <c r="AE8" s="119"/>
+      <c r="AF8" s="119"/>
+      <c r="AG8" s="119"/>
+      <c r="AH8" s="119"/>
+      <c r="AI8" s="119"/>
+      <c r="AJ8" s="119"/>
+      <c r="AK8" s="119"/>
+      <c r="AL8" s="119"/>
+    </row>
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="70"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="124"/>
+      <c r="N9" s="89"/>
+      <c r="O9" s="89"/>
+      <c r="P9" s="89"/>
+      <c r="Q9" s="89"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89"/>
+      <c r="T9" s="89"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="124"/>
+      <c r="W9" s="89"/>
+      <c r="X9" s="89"/>
+      <c r="Y9" s="89"/>
+      <c r="Z9" s="89"/>
+      <c r="AA9" s="89"/>
+      <c r="AB9" s="89"/>
+      <c r="AC9" s="89"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="119"/>
+      <c r="AG9" s="119"/>
+      <c r="AH9" s="119"/>
+      <c r="AI9" s="119"/>
+      <c r="AJ9" s="119"/>
+      <c r="AK9" s="119"/>
+      <c r="AL9" s="119"/>
+    </row>
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="129"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="124"/>
+      <c r="N10" s="89"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="89"/>
+      <c r="R10" s="89"/>
+      <c r="S10" s="89"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="124"/>
+      <c r="W10" s="89"/>
+      <c r="X10" s="89"/>
+      <c r="Y10" s="89"/>
+      <c r="Z10" s="89"/>
+      <c r="AA10" s="89"/>
+      <c r="AB10" s="89"/>
+      <c r="AC10" s="89"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="119"/>
+      <c r="AF10" s="119"/>
+      <c r="AG10" s="119"/>
+      <c r="AH10" s="119"/>
+      <c r="AI10" s="119"/>
+      <c r="AJ10" s="119"/>
+      <c r="AK10" s="119"/>
+      <c r="AL10" s="119"/>
+    </row>
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -4744,7 +5098,7 @@
       <c r="AF11" s="3"/>
       <c r="AK11" s="7"/>
     </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>44</v>
       </c>
@@ -4776,24 +5130,24 @@
       <c r="AF12" s="3"/>
       <c r="AK12" s="7"/>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="127"/>
-      <c r="O13" s="127"/>
-      <c r="P13" s="127"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="127"/>
-      <c r="S13" s="127"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="123"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="123"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="123"/>
+      <c r="M13" s="123"/>
+      <c r="N13" s="123"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="123"/>
+      <c r="S13" s="123"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -4807,17 +5161,17 @@
       <c r="AF13" s="3"/>
       <c r="AK13" s="7"/>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -4841,7 +5195,7 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>46</v>
       </c>
@@ -4882,241 +5236,241 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="117" t="s">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="118" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="119" t="s">
+      <c r="I16" s="121"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="M16" s="119"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="119"/>
-      <c r="R16" s="119"/>
-      <c r="S16" s="119"/>
-      <c r="T16" s="119"/>
-      <c r="U16" s="119"/>
-      <c r="V16" s="119"/>
-      <c r="W16" s="119"/>
-      <c r="X16" s="118" t="s">
+      <c r="M16" s="128"/>
+      <c r="N16" s="128"/>
+      <c r="O16" s="128"/>
+      <c r="P16" s="128"/>
+      <c r="Q16" s="128"/>
+      <c r="R16" s="128"/>
+      <c r="S16" s="128"/>
+      <c r="T16" s="128"/>
+      <c r="U16" s="128"/>
+      <c r="V16" s="128"/>
+      <c r="W16" s="128"/>
+      <c r="X16" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="Y16" s="118"/>
-      <c r="Z16" s="118"/>
-      <c r="AA16" s="118"/>
-      <c r="AB16" s="119" t="s">
+      <c r="Y16" s="121"/>
+      <c r="Z16" s="121"/>
+      <c r="AA16" s="121"/>
+      <c r="AB16" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="AC16" s="119"/>
-      <c r="AD16" s="119"/>
-      <c r="AE16" s="119"/>
-      <c r="AF16" s="119"/>
-      <c r="AG16" s="119"/>
-      <c r="AH16" s="119"/>
-      <c r="AI16" s="119"/>
-      <c r="AJ16" s="119"/>
-      <c r="AK16" s="119"/>
-      <c r="AL16" s="119"/>
-    </row>
-    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="117"/>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="119" t="s">
+      <c r="AC16" s="128"/>
+      <c r="AD16" s="128"/>
+      <c r="AE16" s="128"/>
+      <c r="AF16" s="128"/>
+      <c r="AG16" s="128"/>
+      <c r="AH16" s="128"/>
+      <c r="AI16" s="128"/>
+      <c r="AJ16" s="128"/>
+      <c r="AK16" s="128"/>
+      <c r="AL16" s="128"/>
+    </row>
+    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="68"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="119"/>
-      <c r="N17" s="119"/>
-      <c r="O17" s="119"/>
-      <c r="P17" s="119" t="s">
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="128"/>
+      <c r="P17" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="119"/>
-      <c r="R17" s="119"/>
-      <c r="S17" s="119"/>
-      <c r="T17" s="119" t="s">
+      <c r="Q17" s="128"/>
+      <c r="R17" s="128"/>
+      <c r="S17" s="128"/>
+      <c r="T17" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="U17" s="119"/>
-      <c r="V17" s="119"/>
-      <c r="W17" s="119"/>
-      <c r="X17" s="118"/>
-      <c r="Y17" s="118"/>
-      <c r="Z17" s="118"/>
-      <c r="AA17" s="118"/>
-      <c r="AB17" s="119" t="s">
+      <c r="U17" s="128"/>
+      <c r="V17" s="128"/>
+      <c r="W17" s="128"/>
+      <c r="X17" s="121"/>
+      <c r="Y17" s="121"/>
+      <c r="Z17" s="121"/>
+      <c r="AA17" s="121"/>
+      <c r="AB17" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="AC17" s="119"/>
-      <c r="AD17" s="119"/>
-      <c r="AE17" s="119"/>
-      <c r="AF17" s="119" t="s">
+      <c r="AC17" s="128"/>
+      <c r="AD17" s="128"/>
+      <c r="AE17" s="128"/>
+      <c r="AF17" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="AG17" s="119"/>
-      <c r="AH17" s="119"/>
-      <c r="AI17" s="119"/>
-      <c r="AJ17" s="119" t="s">
+      <c r="AG17" s="128"/>
+      <c r="AH17" s="128"/>
+      <c r="AI17" s="128"/>
+      <c r="AJ17" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="AK17" s="119"/>
-      <c r="AL17" s="119"/>
-    </row>
-    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="116"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="115">
+      <c r="AK17" s="128"/>
+      <c r="AL17" s="128"/>
+    </row>
+    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="70"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="122">
         <v>125</v>
       </c>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="114"/>
-      <c r="N18" s="114"/>
-      <c r="O18" s="114"/>
-      <c r="P18" s="114"/>
-      <c r="Q18" s="114"/>
-      <c r="R18" s="114"/>
-      <c r="S18" s="114"/>
-      <c r="T18" s="114"/>
-      <c r="U18" s="114"/>
-      <c r="V18" s="114"/>
-      <c r="W18" s="114"/>
-      <c r="X18" s="115">
+      <c r="I18" s="122"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="119"/>
+      <c r="N18" s="119"/>
+      <c r="O18" s="119"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
+      <c r="U18" s="119"/>
+      <c r="V18" s="119"/>
+      <c r="W18" s="119"/>
+      <c r="X18" s="122">
         <v>2000</v>
       </c>
-      <c r="Y18" s="115"/>
-      <c r="Z18" s="115"/>
-      <c r="AA18" s="115"/>
-      <c r="AB18" s="114"/>
-      <c r="AC18" s="114"/>
-      <c r="AD18" s="114"/>
-      <c r="AE18" s="114"/>
-      <c r="AF18" s="114"/>
-      <c r="AG18" s="114"/>
-      <c r="AH18" s="114"/>
-      <c r="AI18" s="114"/>
-      <c r="AJ18" s="114"/>
-      <c r="AK18" s="114"/>
-      <c r="AL18" s="114"/>
-    </row>
-    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="115">
+      <c r="Y18" s="122"/>
+      <c r="Z18" s="122"/>
+      <c r="AA18" s="122"/>
+      <c r="AB18" s="119"/>
+      <c r="AC18" s="119"/>
+      <c r="AD18" s="119"/>
+      <c r="AE18" s="119"/>
+      <c r="AF18" s="119"/>
+      <c r="AG18" s="119"/>
+      <c r="AH18" s="119"/>
+      <c r="AI18" s="119"/>
+      <c r="AJ18" s="119"/>
+      <c r="AK18" s="119"/>
+      <c r="AL18" s="119"/>
+    </row>
+    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="70"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="122">
         <v>500</v>
       </c>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="114"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="114"/>
-      <c r="R19" s="114"/>
-      <c r="S19" s="114"/>
-      <c r="T19" s="114"/>
-      <c r="U19" s="114"/>
-      <c r="V19" s="114"/>
-      <c r="W19" s="114"/>
-      <c r="X19" s="115">
+      <c r="I19" s="122"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="119"/>
+      <c r="R19" s="119"/>
+      <c r="S19" s="119"/>
+      <c r="T19" s="119"/>
+      <c r="U19" s="119"/>
+      <c r="V19" s="119"/>
+      <c r="W19" s="119"/>
+      <c r="X19" s="122">
         <v>5000</v>
       </c>
-      <c r="Y19" s="115"/>
-      <c r="Z19" s="115"/>
-      <c r="AA19" s="115"/>
-      <c r="AB19" s="114"/>
-      <c r="AC19" s="114"/>
-      <c r="AD19" s="114"/>
-      <c r="AE19" s="114"/>
-      <c r="AF19" s="114"/>
-      <c r="AG19" s="114"/>
-      <c r="AH19" s="114"/>
-      <c r="AI19" s="114"/>
-      <c r="AJ19" s="114"/>
-      <c r="AK19" s="114"/>
-      <c r="AL19" s="114"/>
-    </row>
-    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="116"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="115">
+      <c r="Y19" s="122"/>
+      <c r="Z19" s="122"/>
+      <c r="AA19" s="122"/>
+      <c r="AB19" s="119"/>
+      <c r="AC19" s="119"/>
+      <c r="AD19" s="119"/>
+      <c r="AE19" s="119"/>
+      <c r="AF19" s="119"/>
+      <c r="AG19" s="119"/>
+      <c r="AH19" s="119"/>
+      <c r="AI19" s="119"/>
+      <c r="AJ19" s="119"/>
+      <c r="AK19" s="119"/>
+      <c r="AL19" s="119"/>
+    </row>
+    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="70"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="122">
         <v>1000</v>
       </c>
-      <c r="I20" s="115"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="114"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="114"/>
-      <c r="V20" s="114"/>
-      <c r="W20" s="114"/>
-      <c r="X20" s="115">
+      <c r="I20" s="122"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="119"/>
+      <c r="R20" s="119"/>
+      <c r="S20" s="119"/>
+      <c r="T20" s="119"/>
+      <c r="U20" s="119"/>
+      <c r="V20" s="119"/>
+      <c r="W20" s="119"/>
+      <c r="X20" s="122">
         <v>7000</v>
       </c>
-      <c r="Y20" s="115"/>
-      <c r="Z20" s="115"/>
-      <c r="AA20" s="115"/>
-      <c r="AB20" s="114"/>
-      <c r="AC20" s="114"/>
-      <c r="AD20" s="114"/>
-      <c r="AE20" s="114"/>
-      <c r="AF20" s="114"/>
-      <c r="AG20" s="114"/>
-      <c r="AH20" s="114"/>
-      <c r="AI20" s="114"/>
-      <c r="AJ20" s="114"/>
-      <c r="AK20" s="114"/>
-      <c r="AL20" s="114"/>
-    </row>
-    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y20" s="122"/>
+      <c r="Z20" s="122"/>
+      <c r="AA20" s="122"/>
+      <c r="AB20" s="119"/>
+      <c r="AC20" s="119"/>
+      <c r="AD20" s="119"/>
+      <c r="AE20" s="119"/>
+      <c r="AF20" s="119"/>
+      <c r="AG20" s="119"/>
+      <c r="AH20" s="119"/>
+      <c r="AI20" s="119"/>
+      <c r="AJ20" s="119"/>
+      <c r="AK20" s="119"/>
+      <c r="AL20" s="119"/>
+    </row>
+    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="D21" s="5"/>
       <c r="H21" s="3"/>
@@ -5151,7 +5505,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>46</v>
       </c>
@@ -5192,241 +5546,241 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="117" t="s">
+    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="118" t="s">
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="119" t="s">
+      <c r="I23" s="121"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="M23" s="119"/>
-      <c r="N23" s="119"/>
-      <c r="O23" s="119"/>
-      <c r="P23" s="119"/>
-      <c r="Q23" s="119"/>
-      <c r="R23" s="119"/>
-      <c r="S23" s="119"/>
-      <c r="T23" s="119"/>
-      <c r="U23" s="119"/>
-      <c r="V23" s="119"/>
-      <c r="W23" s="119"/>
-      <c r="X23" s="118" t="s">
+      <c r="M23" s="128"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="128"/>
+      <c r="T23" s="128"/>
+      <c r="U23" s="128"/>
+      <c r="V23" s="128"/>
+      <c r="W23" s="128"/>
+      <c r="X23" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="Y23" s="118"/>
-      <c r="Z23" s="118"/>
-      <c r="AA23" s="118"/>
-      <c r="AB23" s="119" t="s">
+      <c r="Y23" s="121"/>
+      <c r="Z23" s="121"/>
+      <c r="AA23" s="121"/>
+      <c r="AB23" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="AC23" s="119"/>
-      <c r="AD23" s="119"/>
-      <c r="AE23" s="119"/>
-      <c r="AF23" s="119"/>
-      <c r="AG23" s="119"/>
-      <c r="AH23" s="119"/>
-      <c r="AI23" s="119"/>
-      <c r="AJ23" s="119"/>
-      <c r="AK23" s="119"/>
-      <c r="AL23" s="119"/>
-    </row>
-    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="117"/>
-      <c r="B24" s="117"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="119" t="s">
+      <c r="AC23" s="128"/>
+      <c r="AD23" s="128"/>
+      <c r="AE23" s="128"/>
+      <c r="AF23" s="128"/>
+      <c r="AG23" s="128"/>
+      <c r="AH23" s="128"/>
+      <c r="AI23" s="128"/>
+      <c r="AJ23" s="128"/>
+      <c r="AK23" s="128"/>
+      <c r="AL23" s="128"/>
+    </row>
+    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="68"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="119"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="119" t="s">
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="119"/>
-      <c r="S24" s="119"/>
-      <c r="T24" s="119" t="s">
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="U24" s="119"/>
-      <c r="V24" s="119"/>
-      <c r="W24" s="119"/>
-      <c r="X24" s="118"/>
-      <c r="Y24" s="118"/>
-      <c r="Z24" s="118"/>
-      <c r="AA24" s="118"/>
-      <c r="AB24" s="119" t="s">
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="121"/>
+      <c r="Y24" s="121"/>
+      <c r="Z24" s="121"/>
+      <c r="AA24" s="121"/>
+      <c r="AB24" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="AC24" s="119"/>
-      <c r="AD24" s="119"/>
-      <c r="AE24" s="119"/>
-      <c r="AF24" s="119" t="s">
+      <c r="AC24" s="128"/>
+      <c r="AD24" s="128"/>
+      <c r="AE24" s="128"/>
+      <c r="AF24" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="AG24" s="119"/>
-      <c r="AH24" s="119"/>
-      <c r="AI24" s="119"/>
-      <c r="AJ24" s="119" t="s">
+      <c r="AG24" s="128"/>
+      <c r="AH24" s="128"/>
+      <c r="AI24" s="128"/>
+      <c r="AJ24" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="AK24" s="119"/>
-      <c r="AL24" s="119"/>
-    </row>
-    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="116"/>
-      <c r="B25" s="116"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="115">
+      <c r="AK24" s="128"/>
+      <c r="AL24" s="128"/>
+    </row>
+    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="70"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="122">
         <v>125</v>
       </c>
-      <c r="I25" s="115"/>
-      <c r="J25" s="115"/>
-      <c r="K25" s="115"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="114"/>
-      <c r="N25" s="114"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="114"/>
-      <c r="Q25" s="114"/>
-      <c r="R25" s="114"/>
-      <c r="S25" s="114"/>
-      <c r="T25" s="114"/>
-      <c r="U25" s="114"/>
-      <c r="V25" s="114"/>
-      <c r="W25" s="114"/>
-      <c r="X25" s="115">
+      <c r="I25" s="122"/>
+      <c r="J25" s="122"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="119"/>
+      <c r="N25" s="119"/>
+      <c r="O25" s="119"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119"/>
+      <c r="R25" s="119"/>
+      <c r="S25" s="119"/>
+      <c r="T25" s="119"/>
+      <c r="U25" s="119"/>
+      <c r="V25" s="119"/>
+      <c r="W25" s="119"/>
+      <c r="X25" s="122">
         <v>2000</v>
       </c>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
-      <c r="AB25" s="114"/>
-      <c r="AC25" s="114"/>
-      <c r="AD25" s="114"/>
-      <c r="AE25" s="114"/>
-      <c r="AF25" s="114"/>
-      <c r="AG25" s="114"/>
-      <c r="AH25" s="114"/>
-      <c r="AI25" s="114"/>
-      <c r="AJ25" s="114"/>
-      <c r="AK25" s="114"/>
-      <c r="AL25" s="114"/>
-    </row>
-    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="116"/>
-      <c r="B26" s="116"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="116"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="115">
+      <c r="Y25" s="122"/>
+      <c r="Z25" s="122"/>
+      <c r="AA25" s="122"/>
+      <c r="AB25" s="119"/>
+      <c r="AC25" s="119"/>
+      <c r="AD25" s="119"/>
+      <c r="AE25" s="119"/>
+      <c r="AF25" s="119"/>
+      <c r="AG25" s="119"/>
+      <c r="AH25" s="119"/>
+      <c r="AI25" s="119"/>
+      <c r="AJ25" s="119"/>
+      <c r="AK25" s="119"/>
+      <c r="AL25" s="119"/>
+    </row>
+    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="70"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="122">
         <v>500</v>
       </c>
-      <c r="I26" s="115"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="114"/>
-      <c r="N26" s="114"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="114"/>
-      <c r="R26" s="114"/>
-      <c r="S26" s="114"/>
-      <c r="T26" s="114"/>
-      <c r="U26" s="114"/>
-      <c r="V26" s="114"/>
-      <c r="W26" s="114"/>
-      <c r="X26" s="115">
+      <c r="I26" s="122"/>
+      <c r="J26" s="122"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="119"/>
+      <c r="N26" s="119"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="119"/>
+      <c r="R26" s="119"/>
+      <c r="S26" s="119"/>
+      <c r="T26" s="119"/>
+      <c r="U26" s="119"/>
+      <c r="V26" s="119"/>
+      <c r="W26" s="119"/>
+      <c r="X26" s="122">
         <v>5000</v>
       </c>
-      <c r="Y26" s="115"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="115"/>
-      <c r="AB26" s="114"/>
-      <c r="AC26" s="114"/>
-      <c r="AD26" s="114"/>
-      <c r="AE26" s="114"/>
-      <c r="AF26" s="114"/>
-      <c r="AG26" s="114"/>
-      <c r="AH26" s="114"/>
-      <c r="AI26" s="114"/>
-      <c r="AJ26" s="114"/>
-      <c r="AK26" s="114"/>
-      <c r="AL26" s="114"/>
-    </row>
-    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="116"/>
-      <c r="B27" s="116"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="115">
+      <c r="Y26" s="122"/>
+      <c r="Z26" s="122"/>
+      <c r="AA26" s="122"/>
+      <c r="AB26" s="119"/>
+      <c r="AC26" s="119"/>
+      <c r="AD26" s="119"/>
+      <c r="AE26" s="119"/>
+      <c r="AF26" s="119"/>
+      <c r="AG26" s="119"/>
+      <c r="AH26" s="119"/>
+      <c r="AI26" s="119"/>
+      <c r="AJ26" s="119"/>
+      <c r="AK26" s="119"/>
+      <c r="AL26" s="119"/>
+    </row>
+    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="70"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="122">
         <v>1000</v>
       </c>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="114"/>
-      <c r="Q27" s="114"/>
-      <c r="R27" s="114"/>
-      <c r="S27" s="114"/>
-      <c r="T27" s="114"/>
-      <c r="U27" s="114"/>
-      <c r="V27" s="114"/>
-      <c r="W27" s="114"/>
-      <c r="X27" s="115">
+      <c r="I27" s="122"/>
+      <c r="J27" s="122"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="119"/>
+      <c r="N27" s="119"/>
+      <c r="O27" s="119"/>
+      <c r="P27" s="119"/>
+      <c r="Q27" s="119"/>
+      <c r="R27" s="119"/>
+      <c r="S27" s="119"/>
+      <c r="T27" s="119"/>
+      <c r="U27" s="119"/>
+      <c r="V27" s="119"/>
+      <c r="W27" s="119"/>
+      <c r="X27" s="122">
         <v>7000</v>
       </c>
-      <c r="Y27" s="115"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="115"/>
-      <c r="AB27" s="114"/>
-      <c r="AC27" s="114"/>
-      <c r="AD27" s="114"/>
-      <c r="AE27" s="114"/>
-      <c r="AF27" s="114"/>
-      <c r="AG27" s="114"/>
-      <c r="AH27" s="114"/>
-      <c r="AI27" s="114"/>
-      <c r="AJ27" s="114"/>
-      <c r="AK27" s="114"/>
-      <c r="AL27" s="114"/>
-    </row>
-    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y27" s="122"/>
+      <c r="Z27" s="122"/>
+      <c r="AA27" s="122"/>
+      <c r="AB27" s="119"/>
+      <c r="AC27" s="119"/>
+      <c r="AD27" s="119"/>
+      <c r="AE27" s="119"/>
+      <c r="AF27" s="119"/>
+      <c r="AG27" s="119"/>
+      <c r="AH27" s="119"/>
+      <c r="AI27" s="119"/>
+      <c r="AJ27" s="119"/>
+      <c r="AK27" s="119"/>
+      <c r="AL27" s="119"/>
+    </row>
+    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -5457,7 +5811,7 @@
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="48" t="s">
         <v>17</v>
       </c>
@@ -5490,7 +5844,7 @@
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -5521,7 +5875,7 @@
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
         <v>54</v>
       </c>
@@ -5557,7 +5911,7 @@
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>53</v>
       </c>
@@ -5603,7 +5957,7 @@
       <c r="AK32" s="18"/>
       <c r="AL32" s="17"/>
     </row>
-    <row r="33" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>60</v>
       </c>
@@ -5649,7 +6003,7 @@
       <c r="AK33" s="18"/>
       <c r="AL33" s="17"/>
     </row>
-    <row r="34" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -5689,7 +6043,7 @@
       <c r="AK34" s="18"/>
       <c r="AL34" s="17"/>
     </row>
-    <row r="35" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>61</v>
       </c>
@@ -5735,7 +6089,7 @@
       <c r="AK35" s="18"/>
       <c r="AL35" s="17"/>
     </row>
-    <row r="36" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -5775,7 +6129,7 @@
       <c r="AK36" s="18"/>
       <c r="AL36" s="17"/>
     </row>
-    <row r="37" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>62</v>
       </c>
@@ -5821,7 +6175,7 @@
       <c r="AK37" s="18"/>
       <c r="AL37" s="17"/>
     </row>
-    <row r="38" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>63</v>
       </c>
@@ -5863,7 +6217,7 @@
       <c r="AK38" s="18"/>
       <c r="AL38" s="17"/>
     </row>
-    <row r="39" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>64</v>
       </c>
@@ -5905,7 +6259,7 @@
       <c r="AK39" s="18"/>
       <c r="AL39" s="17"/>
     </row>
-    <row r="40" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="18"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -5945,7 +6299,7 @@
       <c r="AK40" s="18"/>
       <c r="AL40" s="17"/>
     </row>
-    <row r="41" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
         <v>65</v>
       </c>
@@ -5991,7 +6345,7 @@
       <c r="AK41" s="18"/>
       <c r="AL41" s="17"/>
     </row>
-    <row r="42" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>66</v>
       </c>
@@ -6033,7 +6387,7 @@
       <c r="AK42" s="18"/>
       <c r="AL42" s="17"/>
     </row>
-    <row r="43" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
         <v>67</v>
       </c>
@@ -6075,7 +6429,7 @@
       <c r="AK43" s="18"/>
       <c r="AL43" s="17"/>
     </row>
-    <row r="44" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="18"/>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -6115,7 +6469,7 @@
       <c r="AK44" s="18"/>
       <c r="AL44" s="17"/>
     </row>
-    <row r="45" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
         <v>57</v>
       </c>
@@ -6161,7 +6515,7 @@
       <c r="AK45" s="18"/>
       <c r="AL45" s="17"/>
     </row>
-    <row r="46" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
         <v>59</v>
       </c>
@@ -6203,7 +6557,7 @@
       <c r="AK46" s="18"/>
       <c r="AL46" s="17"/>
     </row>
-    <row r="47" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
         <v>58</v>
       </c>
@@ -6245,7 +6599,7 @@
       <c r="AK47" s="18"/>
       <c r="AL47" s="17"/>
     </row>
-    <row r="48" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15"/>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -6285,7 +6639,7 @@
       <c r="AK48" s="18"/>
       <c r="AL48" s="17"/>
     </row>
-    <row r="49" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -6325,7 +6679,7 @@
       <c r="AK49" s="17"/>
       <c r="AL49" s="17"/>
     </row>
-    <row r="50" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -6365,8 +6719,8 @@
       <c r="AK50" s="8"/>
       <c r="AL50" s="8"/>
     </row>
-    <row r="51" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="11"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -6382,7 +6736,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="11"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -6398,7 +6752,7 @@
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A54" s="11"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -6416,6 +6770,88 @@
     </row>
   </sheetData>
   <mergeCells count="98">
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="P27:S27"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="X27:AA27"/>
+    <mergeCell ref="AB27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="X26:AA26"/>
+    <mergeCell ref="AB26:AE26"/>
+    <mergeCell ref="A25:G27"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="A23:G24"/>
+    <mergeCell ref="H23:K24"/>
+    <mergeCell ref="L23:W23"/>
+    <mergeCell ref="X23:AA24"/>
+    <mergeCell ref="AB23:AL23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="AB24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="AJ24:AL24"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="H16:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="L16:W16"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="A16:G17"/>
+    <mergeCell ref="A18:G20"/>
+    <mergeCell ref="AB16:AL16"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AB18:AE18"/>
+    <mergeCell ref="AB19:AE19"/>
+    <mergeCell ref="AB20:AE20"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="A6:E7"/>
+    <mergeCell ref="F6:L7"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="M6:AL6"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AL7"/>
+    <mergeCell ref="V10:AD10"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="AE8:AL8"/>
     <mergeCell ref="AE9:AL9"/>
     <mergeCell ref="AE10:AL10"/>
@@ -6432,90 +6868,8 @@
     <mergeCell ref="X25:AA25"/>
     <mergeCell ref="AB25:AE25"/>
     <mergeCell ref="F13:S13"/>
-    <mergeCell ref="A6:E7"/>
-    <mergeCell ref="F6:L7"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="M6:AL6"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="V7:AD7"/>
-    <mergeCell ref="AE7:AL7"/>
-    <mergeCell ref="V10:AD10"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="V8:AD8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V9:AD9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A16:G17"/>
-    <mergeCell ref="A18:G20"/>
-    <mergeCell ref="AB16:AL16"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AB18:AE18"/>
-    <mergeCell ref="AB19:AE19"/>
-    <mergeCell ref="AB20:AE20"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="H16:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="L16:W16"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A23:G24"/>
-    <mergeCell ref="H23:K24"/>
-    <mergeCell ref="L23:W23"/>
-    <mergeCell ref="X23:AA24"/>
-    <mergeCell ref="AB23:AL23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="AB24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="AJ26:AL26"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="P27:S27"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="X27:AA27"/>
-    <mergeCell ref="AB27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="AJ27:AL27"/>
-    <mergeCell ref="X26:AA26"/>
-    <mergeCell ref="AB26:AE26"/>
-    <mergeCell ref="A25:G27"/>
-    <mergeCell ref="H25:K25"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -6533,15 +6887,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626CC06E-9590-4323-BE24-60512668D6F0}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="2.33203125" customWidth="1"/>
+    <col min="1" max="7" width="2.375" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" customWidth="1"/>
-    <col min="32" max="38" width="2.33203125" customWidth="1"/>
+    <col min="9" max="31" width="2.125" customWidth="1"/>
+    <col min="32" max="38" width="2.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6553,34 +6907,34 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
-    </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
+      <c r="AI1" s="71"/>
+      <c r="AJ1" s="71"/>
+      <c r="AK1" s="71"/>
+      <c r="AL1" s="71"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>73</v>
       </c>
@@ -6613,18 +6967,18 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
       <c r="N3" s="3"/>
@@ -6647,7 +7001,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -6678,7 +7032,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>74</v>
       </c>
@@ -6711,7 +7065,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="43" t="s">
         <v>75</v>
       </c>
@@ -6744,7 +7098,7 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
     </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="43"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -6784,18 +7138,18 @@
       <c r="AK7" s="15"/>
       <c r="AL7" s="15"/>
     </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="132" t="s">
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
       <c r="J8" s="131" t="s">
         <v>18</v>
       </c>
@@ -6823,23 +7177,23 @@
       <c r="AF8" s="131"/>
       <c r="AG8" s="131"/>
       <c r="AH8" s="131"/>
-      <c r="AI8" s="117" t="s">
+      <c r="AI8" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="AJ8" s="117"/>
-      <c r="AK8" s="117"/>
-      <c r="AL8" s="117"/>
-    </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
+      <c r="AJ8" s="68"/>
+      <c r="AK8" s="68"/>
+      <c r="AL8" s="68"/>
+    </row>
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
       <c r="J9" s="131" t="s">
         <v>78</v>
       </c>
@@ -6875,23 +7229,23 @@
       <c r="AF9" s="131"/>
       <c r="AG9" s="131"/>
       <c r="AH9" s="131"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="117"/>
-    </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="116"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="128" t="s">
+      <c r="AI9" s="68"/>
+      <c r="AJ9" s="68"/>
+      <c r="AK9" s="68"/>
+      <c r="AL9" s="68"/>
+    </row>
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="130"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="134"/>
       <c r="J10" s="131"/>
       <c r="K10" s="131"/>
       <c r="L10" s="131"/>
@@ -6917,23 +7271,23 @@
       <c r="AF10" s="131"/>
       <c r="AG10" s="131"/>
       <c r="AH10" s="131"/>
-      <c r="AI10" s="117"/>
-      <c r="AJ10" s="117"/>
-      <c r="AK10" s="117"/>
-      <c r="AL10" s="117"/>
-    </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="128" t="s">
+      <c r="AI10" s="68"/>
+      <c r="AJ10" s="68"/>
+      <c r="AK10" s="68"/>
+      <c r="AL10" s="68"/>
+    </row>
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="130"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="134"/>
       <c r="J11" s="131"/>
       <c r="K11" s="131"/>
       <c r="L11" s="131"/>
@@ -6959,23 +7313,23 @@
       <c r="AF11" s="131"/>
       <c r="AG11" s="131"/>
       <c r="AH11" s="131"/>
-      <c r="AI11" s="117"/>
-      <c r="AJ11" s="117"/>
-      <c r="AK11" s="117"/>
-      <c r="AL11" s="117"/>
-    </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="116"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="128" t="s">
+      <c r="AI11" s="68"/>
+      <c r="AJ11" s="68"/>
+      <c r="AK11" s="68"/>
+      <c r="AL11" s="68"/>
+    </row>
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="130"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="134"/>
       <c r="J12" s="131"/>
       <c r="K12" s="131"/>
       <c r="L12" s="131"/>
@@ -7001,23 +7355,23 @@
       <c r="AF12" s="131"/>
       <c r="AG12" s="131"/>
       <c r="AH12" s="131"/>
-      <c r="AI12" s="117"/>
-      <c r="AJ12" s="117"/>
-      <c r="AK12" s="117"/>
-      <c r="AL12" s="117"/>
-    </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="116"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="128" t="s">
+      <c r="AI12" s="68"/>
+      <c r="AJ12" s="68"/>
+      <c r="AK12" s="68"/>
+      <c r="AL12" s="68"/>
+    </row>
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="130"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="134"/>
       <c r="J13" s="131"/>
       <c r="K13" s="131"/>
       <c r="L13" s="131"/>
@@ -7043,12 +7397,12 @@
       <c r="AF13" s="131"/>
       <c r="AG13" s="131"/>
       <c r="AH13" s="131"/>
-      <c r="AI13" s="117"/>
-      <c r="AJ13" s="117"/>
-      <c r="AK13" s="117"/>
-      <c r="AL13" s="117"/>
-    </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI13" s="68"/>
+      <c r="AJ13" s="68"/>
+      <c r="AK13" s="68"/>
+      <c r="AL13" s="68"/>
+    </row>
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="44"/>
       <c r="B14" s="44"/>
       <c r="C14" s="44"/>
@@ -7088,7 +7442,7 @@
       <c r="AK14" s="44"/>
       <c r="AL14" s="44"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45" t="s">
         <v>83</v>
       </c>
@@ -7130,7 +7484,7 @@
       <c r="AK15" s="15"/>
       <c r="AL15" s="15"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="55" t="s">
         <v>84</v>
       </c>
@@ -7172,7 +7526,7 @@
       <c r="AK16" s="50"/>
       <c r="AL16" s="50"/>
     </row>
-    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="47"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -7203,7 +7557,7 @@
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="47" t="s">
         <v>85</v>
       </c>
@@ -7236,7 +7590,7 @@
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="47" t="s">
         <v>86</v>
       </c>
@@ -7269,7 +7623,7 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="52" t="s">
         <v>104</v>
       </c>
@@ -7312,7 +7666,7 @@
       <c r="AL20" s="51"/>
       <c r="AM20" s="51"/>
     </row>
-    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="52" t="s">
         <v>105</v>
       </c>
@@ -7355,7 +7709,7 @@
       <c r="AL21" s="51"/>
       <c r="AM21" s="51"/>
     </row>
-    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="52" t="s">
         <v>106</v>
       </c>
@@ -7398,7 +7752,7 @@
       <c r="AL22" s="51"/>
       <c r="AM22" s="51"/>
     </row>
-    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="54" t="s">
         <v>87</v>
       </c>
@@ -7441,7 +7795,7 @@
       <c r="AL23" s="51"/>
       <c r="AM23" s="51"/>
     </row>
-    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="47"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -7472,7 +7826,7 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="48" t="s">
         <v>17</v>
       </c>
@@ -7505,7 +7859,7 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="47"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -7536,7 +7890,7 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -7576,7 +7930,7 @@
       <c r="AK27" s="18"/>
       <c r="AL27" s="17"/>
     </row>
-    <row r="28" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -7616,7 +7970,7 @@
       <c r="AK28" s="18"/>
       <c r="AL28" s="17"/>
     </row>
-    <row r="29" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -7656,7 +8010,7 @@
       <c r="AK29" s="17"/>
       <c r="AL29" s="17"/>
     </row>
-    <row r="30" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -7696,8 +8050,8 @@
       <c r="AK30" s="8"/>
       <c r="AL30" s="8"/>
     </row>
-    <row r="31" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="13.9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:39" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -7713,7 +8067,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="11"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7729,7 +8083,7 @@
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="11"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -7747,6 +8101,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="AI10:AL10"/>
+    <mergeCell ref="AI11:AL11"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="A8:I9"/>
+    <mergeCell ref="A10:C11"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="J11:N11"/>
     <mergeCell ref="A12:C13"/>
     <mergeCell ref="J10:N10"/>
     <mergeCell ref="J13:N13"/>
@@ -7763,32 +8141,8 @@
     <mergeCell ref="T12:X12"/>
     <mergeCell ref="Y12:AC12"/>
     <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="AI10:AL10"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="A8:I9"/>
-    <mergeCell ref="A10:C11"/>
-    <mergeCell ref="O11:S11"/>
   </mergeCells>
-  <phoneticPr fontId="26" type="noConversion"/>
+  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -7806,15 +8160,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DF6C1D-A8FC-4DBC-948C-47059EFC8040}">
   <dimension ref="A1:AM31"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="2.33203125" customWidth="1"/>
+    <col min="1" max="7" width="2.375" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" customWidth="1"/>
-    <col min="32" max="39" width="2.33203125" customWidth="1"/>
+    <col min="9" max="31" width="2.125" customWidth="1"/>
+    <col min="32" max="39" width="2.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7826,35 +8180,35 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
+      <c r="AI1" s="71"/>
+      <c r="AJ1" s="71"/>
+      <c r="AK1" s="71"/>
+      <c r="AL1" s="71"/>
       <c r="AM1" s="56"/>
     </row>
-    <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>88</v>
       </c>
@@ -7887,24 +8241,24 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>89</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="N3" s="133"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="133"/>
-      <c r="R3" s="133"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -7920,7 +8274,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="47"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -7951,8 +8305,8 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="141" t="s">
+    <row r="5" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="67" t="s">
         <v>144</v>
       </c>
       <c r="B5" s="7"/>
@@ -7987,8 +8341,8 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="141" t="s">
+    <row r="6" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="67" t="s">
         <v>145</v>
       </c>
       <c r="B6" s="18"/>
@@ -8030,7 +8384,7 @@
       <c r="AL6" s="17"/>
       <c r="AM6" s="17"/>
     </row>
-    <row r="7" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -8071,363 +8425,363 @@
       <c r="AL7" s="17"/>
       <c r="AM7" s="17"/>
     </row>
-    <row r="8" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="132" t="s">
+    <row r="8" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
-      <c r="J8" s="117"/>
-      <c r="K8" s="117"/>
-      <c r="L8" s="117"/>
-      <c r="M8" s="117"/>
-      <c r="N8" s="117"/>
-      <c r="O8" s="117"/>
-      <c r="P8" s="117" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="117"/>
-      <c r="R8" s="117"/>
-      <c r="S8" s="117"/>
-      <c r="T8" s="117"/>
-      <c r="U8" s="117"/>
-      <c r="V8" s="117"/>
-      <c r="W8" s="117"/>
-      <c r="X8" s="117"/>
-      <c r="Y8" s="117"/>
-      <c r="Z8" s="117"/>
-      <c r="AA8" s="117"/>
-      <c r="AB8" s="117"/>
-      <c r="AC8" s="117"/>
-      <c r="AD8" s="117"/>
-      <c r="AE8" s="117"/>
-      <c r="AF8" s="117"/>
-      <c r="AG8" s="117"/>
-      <c r="AH8" s="117"/>
-      <c r="AI8" s="117"/>
-      <c r="AJ8" s="117" t="s">
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="68"/>
+      <c r="U8" s="68"/>
+      <c r="V8" s="68"/>
+      <c r="W8" s="68"/>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="68"/>
+      <c r="Z8" s="68"/>
+      <c r="AA8" s="68"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="68"/>
+      <c r="AD8" s="68"/>
+      <c r="AE8" s="68"/>
+      <c r="AF8" s="68"/>
+      <c r="AG8" s="68"/>
+      <c r="AH8" s="68"/>
+      <c r="AI8" s="68"/>
+      <c r="AJ8" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="AK8" s="117"/>
-      <c r="AL8" s="117"/>
-      <c r="AM8" s="117"/>
-    </row>
-    <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117"/>
-      <c r="O9" s="117"/>
-      <c r="P9" s="117" t="s">
+      <c r="AK8" s="68"/>
+      <c r="AL8" s="68"/>
+      <c r="AM8" s="68"/>
+    </row>
+    <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="Q9" s="117"/>
-      <c r="R9" s="117"/>
-      <c r="S9" s="117"/>
-      <c r="T9" s="117" t="s">
+      <c r="Q9" s="68"/>
+      <c r="R9" s="68"/>
+      <c r="S9" s="68"/>
+      <c r="T9" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="117"/>
-      <c r="V9" s="117"/>
-      <c r="W9" s="117"/>
-      <c r="X9" s="117" t="s">
+      <c r="U9" s="68"/>
+      <c r="V9" s="68"/>
+      <c r="W9" s="68"/>
+      <c r="X9" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="Y9" s="117"/>
-      <c r="Z9" s="117"/>
-      <c r="AA9" s="117"/>
-      <c r="AB9" s="117" t="s">
+      <c r="Y9" s="68"/>
+      <c r="Z9" s="68"/>
+      <c r="AA9" s="68"/>
+      <c r="AB9" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="AC9" s="117"/>
-      <c r="AD9" s="117"/>
-      <c r="AE9" s="117"/>
-      <c r="AF9" s="117" t="s">
+      <c r="AC9" s="68"/>
+      <c r="AD9" s="68"/>
+      <c r="AE9" s="68"/>
+      <c r="AF9" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="AG9" s="117"/>
-      <c r="AH9" s="117"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="117"/>
-      <c r="AM9" s="117"/>
-    </row>
-    <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="116"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="116"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="117" t="s">
+      <c r="AG9" s="68"/>
+      <c r="AH9" s="68"/>
+      <c r="AI9" s="68"/>
+      <c r="AJ9" s="68"/>
+      <c r="AK9" s="68"/>
+      <c r="AL9" s="68"/>
+      <c r="AM9" s="68"/>
+    </row>
+    <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="117"/>
-      <c r="K10" s="117"/>
-      <c r="L10" s="117"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="117"/>
-      <c r="O10" s="117"/>
-      <c r="P10" s="117"/>
-      <c r="Q10" s="117"/>
-      <c r="R10" s="117"/>
-      <c r="S10" s="117"/>
-      <c r="T10" s="117"/>
-      <c r="U10" s="117"/>
-      <c r="V10" s="117"/>
-      <c r="W10" s="117"/>
-      <c r="X10" s="117"/>
-      <c r="Y10" s="117"/>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="117"/>
-      <c r="AB10" s="117"/>
-      <c r="AC10" s="117"/>
-      <c r="AD10" s="117"/>
-      <c r="AE10" s="117"/>
-      <c r="AF10" s="117"/>
-      <c r="AG10" s="117"/>
-      <c r="AH10" s="117"/>
-      <c r="AI10" s="117"/>
-      <c r="AJ10" s="117"/>
-      <c r="AK10" s="117"/>
-      <c r="AL10" s="117"/>
-      <c r="AM10" s="117"/>
-    </row>
-    <row r="11" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="117" t="s">
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="68"/>
+      <c r="U10" s="68"/>
+      <c r="V10" s="68"/>
+      <c r="W10" s="68"/>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="68"/>
+      <c r="Z10" s="68"/>
+      <c r="AA10" s="68"/>
+      <c r="AB10" s="68"/>
+      <c r="AC10" s="68"/>
+      <c r="AD10" s="68"/>
+      <c r="AE10" s="68"/>
+      <c r="AF10" s="68"/>
+      <c r="AG10" s="68"/>
+      <c r="AH10" s="68"/>
+      <c r="AI10" s="68"/>
+      <c r="AJ10" s="68"/>
+      <c r="AK10" s="68"/>
+      <c r="AL10" s="68"/>
+      <c r="AM10" s="68"/>
+    </row>
+    <row r="11" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="117"/>
-      <c r="H11" s="117"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="117"/>
-      <c r="K11" s="117"/>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="117"/>
-      <c r="O11" s="117"/>
-      <c r="P11" s="117"/>
-      <c r="Q11" s="117"/>
-      <c r="R11" s="117"/>
-      <c r="S11" s="117"/>
-      <c r="T11" s="117"/>
-      <c r="U11" s="117"/>
-      <c r="V11" s="117"/>
-      <c r="W11" s="117"/>
-      <c r="X11" s="117"/>
-      <c r="Y11" s="117"/>
-      <c r="Z11" s="117"/>
-      <c r="AA11" s="117"/>
-      <c r="AB11" s="117"/>
-      <c r="AC11" s="117"/>
-      <c r="AD11" s="117"/>
-      <c r="AE11" s="117"/>
-      <c r="AF11" s="117"/>
-      <c r="AG11" s="117"/>
-      <c r="AH11" s="117"/>
-      <c r="AI11" s="117"/>
-      <c r="AJ11" s="117"/>
-      <c r="AK11" s="117"/>
-      <c r="AL11" s="117"/>
-      <c r="AM11" s="117"/>
-    </row>
-    <row r="12" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="116"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="117" t="s">
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="68"/>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
+      <c r="T11" s="68"/>
+      <c r="U11" s="68"/>
+      <c r="V11" s="68"/>
+      <c r="W11" s="68"/>
+      <c r="X11" s="68"/>
+      <c r="Y11" s="68"/>
+      <c r="Z11" s="68"/>
+      <c r="AA11" s="68"/>
+      <c r="AB11" s="68"/>
+      <c r="AC11" s="68"/>
+      <c r="AD11" s="68"/>
+      <c r="AE11" s="68"/>
+      <c r="AF11" s="68"/>
+      <c r="AG11" s="68"/>
+      <c r="AH11" s="68"/>
+      <c r="AI11" s="68"/>
+      <c r="AJ11" s="68"/>
+      <c r="AK11" s="68"/>
+      <c r="AL11" s="68"/>
+      <c r="AM11" s="68"/>
+    </row>
+    <row r="12" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
-      <c r="M12" s="117"/>
-      <c r="N12" s="117"/>
-      <c r="O12" s="117"/>
-      <c r="P12" s="117"/>
-      <c r="Q12" s="117"/>
-      <c r="R12" s="117"/>
-      <c r="S12" s="117"/>
-      <c r="T12" s="117"/>
-      <c r="U12" s="117"/>
-      <c r="V12" s="117"/>
-      <c r="W12" s="117"/>
-      <c r="X12" s="117"/>
-      <c r="Y12" s="117"/>
-      <c r="Z12" s="117"/>
-      <c r="AA12" s="117"/>
-      <c r="AB12" s="117"/>
-      <c r="AC12" s="117"/>
-      <c r="AD12" s="117"/>
-      <c r="AE12" s="117"/>
-      <c r="AF12" s="117"/>
-      <c r="AG12" s="117"/>
-      <c r="AH12" s="117"/>
-      <c r="AI12" s="117"/>
-      <c r="AJ12" s="117"/>
-      <c r="AK12" s="117"/>
-      <c r="AL12" s="117"/>
-      <c r="AM12" s="117"/>
-    </row>
-    <row r="13" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="116"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117" t="s">
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="68"/>
+      <c r="T12" s="68"/>
+      <c r="U12" s="68"/>
+      <c r="V12" s="68"/>
+      <c r="W12" s="68"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="68"/>
+      <c r="Z12" s="68"/>
+      <c r="AA12" s="68"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="68"/>
+      <c r="AD12" s="68"/>
+      <c r="AE12" s="68"/>
+      <c r="AF12" s="68"/>
+      <c r="AG12" s="68"/>
+      <c r="AH12" s="68"/>
+      <c r="AI12" s="68"/>
+      <c r="AJ12" s="68"/>
+      <c r="AK12" s="68"/>
+      <c r="AL12" s="68"/>
+      <c r="AM12" s="68"/>
+    </row>
+    <row r="13" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="117"/>
-      <c r="N13" s="117"/>
-      <c r="O13" s="117"/>
-      <c r="P13" s="117"/>
-      <c r="Q13" s="117"/>
-      <c r="R13" s="117"/>
-      <c r="S13" s="117"/>
-      <c r="T13" s="117"/>
-      <c r="U13" s="117"/>
-      <c r="V13" s="117"/>
-      <c r="W13" s="117"/>
-      <c r="X13" s="117"/>
-      <c r="Y13" s="117"/>
-      <c r="Z13" s="117"/>
-      <c r="AA13" s="117"/>
-      <c r="AB13" s="117"/>
-      <c r="AC13" s="117"/>
-      <c r="AD13" s="117"/>
-      <c r="AE13" s="117"/>
-      <c r="AF13" s="117"/>
-      <c r="AG13" s="117"/>
-      <c r="AH13" s="117"/>
-      <c r="AI13" s="117"/>
-      <c r="AJ13" s="117"/>
-      <c r="AK13" s="117"/>
-      <c r="AL13" s="117"/>
-      <c r="AM13" s="117"/>
-    </row>
-    <row r="14" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="116"/>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="117" t="s">
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="68"/>
+      <c r="T13" s="68"/>
+      <c r="U13" s="68"/>
+      <c r="V13" s="68"/>
+      <c r="W13" s="68"/>
+      <c r="X13" s="68"/>
+      <c r="Y13" s="68"/>
+      <c r="Z13" s="68"/>
+      <c r="AA13" s="68"/>
+      <c r="AB13" s="68"/>
+      <c r="AC13" s="68"/>
+      <c r="AD13" s="68"/>
+      <c r="AE13" s="68"/>
+      <c r="AF13" s="68"/>
+      <c r="AG13" s="68"/>
+      <c r="AH13" s="68"/>
+      <c r="AI13" s="68"/>
+      <c r="AJ13" s="68"/>
+      <c r="AK13" s="68"/>
+      <c r="AL13" s="68"/>
+      <c r="AM13" s="68"/>
+    </row>
+    <row r="14" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="117"/>
-      <c r="M14" s="117"/>
-      <c r="N14" s="117"/>
-      <c r="O14" s="117"/>
-      <c r="P14" s="117"/>
-      <c r="Q14" s="117"/>
-      <c r="R14" s="117"/>
-      <c r="S14" s="117"/>
-      <c r="T14" s="117"/>
-      <c r="U14" s="117"/>
-      <c r="V14" s="117"/>
-      <c r="W14" s="117"/>
-      <c r="X14" s="117"/>
-      <c r="Y14" s="117"/>
-      <c r="Z14" s="117"/>
-      <c r="AA14" s="117"/>
-      <c r="AB14" s="117"/>
-      <c r="AC14" s="117"/>
-      <c r="AD14" s="117"/>
-      <c r="AE14" s="117"/>
-      <c r="AF14" s="117"/>
-      <c r="AG14" s="117"/>
-      <c r="AH14" s="117"/>
-      <c r="AI14" s="117"/>
-      <c r="AJ14" s="117"/>
-      <c r="AK14" s="117"/>
-      <c r="AL14" s="117"/>
-      <c r="AM14" s="117"/>
-    </row>
-    <row r="15" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="116"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117" t="s">
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="68"/>
+      <c r="W14" s="68"/>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="68"/>
+      <c r="Z14" s="68"/>
+      <c r="AA14" s="68"/>
+      <c r="AB14" s="68"/>
+      <c r="AC14" s="68"/>
+      <c r="AD14" s="68"/>
+      <c r="AE14" s="68"/>
+      <c r="AF14" s="68"/>
+      <c r="AG14" s="68"/>
+      <c r="AH14" s="68"/>
+      <c r="AI14" s="68"/>
+      <c r="AJ14" s="68"/>
+      <c r="AK14" s="68"/>
+      <c r="AL14" s="68"/>
+      <c r="AM14" s="68"/>
+    </row>
+    <row r="15" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="70"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
-      <c r="T15" s="117"/>
-      <c r="U15" s="117"/>
-      <c r="V15" s="117"/>
-      <c r="W15" s="117"/>
-      <c r="X15" s="117"/>
-      <c r="Y15" s="117"/>
-      <c r="Z15" s="117"/>
-      <c r="AA15" s="117"/>
-      <c r="AB15" s="117"/>
-      <c r="AC15" s="117"/>
-      <c r="AD15" s="117"/>
-      <c r="AE15" s="117"/>
-      <c r="AF15" s="117"/>
-      <c r="AG15" s="117"/>
-      <c r="AH15" s="117"/>
-      <c r="AI15" s="117"/>
-      <c r="AJ15" s="117"/>
-      <c r="AK15" s="117"/>
-      <c r="AL15" s="117"/>
-      <c r="AM15" s="117"/>
-    </row>
-    <row r="16" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="68"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="68"/>
+      <c r="X15" s="68"/>
+      <c r="Y15" s="68"/>
+      <c r="Z15" s="68"/>
+      <c r="AA15" s="68"/>
+      <c r="AB15" s="68"/>
+      <c r="AC15" s="68"/>
+      <c r="AD15" s="68"/>
+      <c r="AE15" s="68"/>
+      <c r="AF15" s="68"/>
+      <c r="AG15" s="68"/>
+      <c r="AH15" s="68"/>
+      <c r="AI15" s="68"/>
+      <c r="AJ15" s="68"/>
+      <c r="AK15" s="68"/>
+      <c r="AL15" s="68"/>
+      <c r="AM15" s="68"/>
+    </row>
+    <row r="16" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>38</v>
       </c>
@@ -8470,7 +8824,7 @@
       <c r="AL16" s="17"/>
       <c r="AM16" s="17"/>
     </row>
-    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>93</v>
       </c>
@@ -8515,7 +8869,7 @@
       <c r="AL17" s="17"/>
       <c r="AM17" s="17"/>
     </row>
-    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>94</v>
       </c>
@@ -8558,7 +8912,7 @@
       <c r="AL18" s="17"/>
       <c r="AM18" s="17"/>
     </row>
-    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -8599,7 +8953,7 @@
       <c r="AL19" s="17"/>
       <c r="AM19" s="17"/>
     </row>
-    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="48" t="s">
         <v>17</v>
       </c>
@@ -8642,7 +8996,7 @@
       <c r="AL20" s="17"/>
       <c r="AM20" s="17"/>
     </row>
-    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -8683,7 +9037,7 @@
       <c r="AL21" s="17"/>
       <c r="AM21" s="17"/>
     </row>
-    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>96</v>
       </c>
@@ -8746,7 +9100,7 @@
       <c r="AL22" s="15"/>
       <c r="AM22" s="17"/>
     </row>
-    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>103</v>
       </c>
@@ -8789,7 +9143,7 @@
       <c r="AL23" s="17"/>
       <c r="AM23" s="17"/>
     </row>
-    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="15"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -8830,7 +9184,7 @@
       <c r="AL24" s="17"/>
       <c r="AM24" s="17"/>
     </row>
-    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -8871,7 +9225,7 @@
       <c r="AL25" s="17"/>
       <c r="AM25" s="17"/>
     </row>
-    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -8912,7 +9266,7 @@
       <c r="AL26" s="17"/>
       <c r="AM26" s="17"/>
     </row>
-    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -8953,8 +9307,8 @@
       <c r="AL27" s="8"/>
       <c r="AM27" s="8"/>
     </row>
-    <row r="28" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="13.9" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:39" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="11"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -8970,7 +9324,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:39" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -8986,7 +9340,7 @@
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -9004,6 +9358,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A8:O9"/>
+    <mergeCell ref="P8:AI8"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ8:AM9"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="AJ11:AM11"/>
+    <mergeCell ref="A10:E11"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X10:AA10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="F11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:W11"/>
+    <mergeCell ref="X11:AA11"/>
+    <mergeCell ref="AB11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="AB10:AE10"/>
+    <mergeCell ref="A12:E13"/>
+    <mergeCell ref="F12:O12"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="T12:W12"/>
+    <mergeCell ref="X12:AA12"/>
+    <mergeCell ref="AB13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="AB12:AE12"/>
+    <mergeCell ref="AJ12:AM12"/>
+    <mergeCell ref="AJ13:AM13"/>
+    <mergeCell ref="A14:E15"/>
+    <mergeCell ref="F14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X14:AA14"/>
     <mergeCell ref="AJ14:AM14"/>
     <mergeCell ref="AJ15:AM15"/>
     <mergeCell ref="F3:R3"/>
@@ -9020,47 +9413,8 @@
     <mergeCell ref="P13:S13"/>
     <mergeCell ref="T13:W13"/>
     <mergeCell ref="X13:AA13"/>
-    <mergeCell ref="A14:E15"/>
-    <mergeCell ref="F14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="X14:AA14"/>
-    <mergeCell ref="AB13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="AB12:AE12"/>
-    <mergeCell ref="AJ12:AM12"/>
-    <mergeCell ref="AJ13:AM13"/>
-    <mergeCell ref="A12:E13"/>
-    <mergeCell ref="F12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:W12"/>
-    <mergeCell ref="X12:AA12"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="AJ11:AM11"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X10:AA10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="F11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:W11"/>
-    <mergeCell ref="X11:AA11"/>
-    <mergeCell ref="AB11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="AB10:AE10"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A8:O9"/>
-    <mergeCell ref="P8:AI8"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ8:AM9"/>
   </mergeCells>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="34" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -9078,15 +9432,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7E1E9E-D288-4FD7-BB39-0DBF9B2FAC5D}">
   <dimension ref="A1:AL48"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="2.33203125" customWidth="1"/>
+    <col min="1" max="7" width="2.375" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" customWidth="1"/>
-    <col min="32" max="38" width="2.33203125" customWidth="1"/>
+    <col min="9" max="31" width="2.125" customWidth="1"/>
+    <col min="32" max="38" width="2.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9101,44 +9455,44 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="136"/>
-      <c r="U1" s="136"/>
-      <c r="V1" s="136"/>
-      <c r="W1" s="136"/>
-      <c r="X1" s="136"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="136"/>
-      <c r="AA1" s="136"/>
-      <c r="AB1" s="136"/>
-      <c r="AC1" s="136"/>
-      <c r="AD1" s="136"/>
-      <c r="AE1" s="136"/>
-      <c r="AF1" s="136"/>
-      <c r="AG1" s="136"/>
-      <c r="AH1" s="136"/>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="136"/>
-      <c r="AK1" s="136"/>
-      <c r="AL1" s="136"/>
-    </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="137" t="s">
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
+      <c r="AJ1" s="137"/>
+      <c r="AK1" s="137"/>
+      <c r="AL1" s="137"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -9170,19 +9524,19 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="133"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -9210,7 +9564,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -9250,23 +9604,23 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
       <c r="F5" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
+      <c r="L5" s="137"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -9294,7 +9648,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9334,7 +9688,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>111</v>
       </c>
@@ -9376,7 +9730,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="138" t="s">
         <v>8</v>
       </c>
@@ -9386,81 +9740,81 @@
       <c r="E8" s="138"/>
       <c r="F8" s="138"/>
       <c r="G8" s="138"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="139"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="139"/>
-      <c r="T8" s="139"/>
-      <c r="U8" s="139"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="139"/>
-      <c r="X8" s="139"/>
-      <c r="Y8" s="139"/>
-      <c r="Z8" s="139"/>
-      <c r="AA8" s="139"/>
-      <c r="AB8" s="139"/>
-      <c r="AC8" s="139"/>
-      <c r="AD8" s="139"/>
-      <c r="AE8" s="139"/>
-      <c r="AF8" s="139"/>
-      <c r="AG8" s="139"/>
-      <c r="AH8" s="139"/>
-      <c r="AI8" s="139"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="135"/>
+      <c r="O8" s="135"/>
+      <c r="P8" s="135"/>
+      <c r="Q8" s="135"/>
+      <c r="R8" s="135"/>
+      <c r="S8" s="135"/>
+      <c r="T8" s="135"/>
+      <c r="U8" s="135"/>
+      <c r="V8" s="135"/>
+      <c r="W8" s="135"/>
+      <c r="X8" s="135"/>
+      <c r="Y8" s="135"/>
+      <c r="Z8" s="135"/>
+      <c r="AA8" s="135"/>
+      <c r="AB8" s="135"/>
+      <c r="AC8" s="135"/>
+      <c r="AD8" s="135"/>
+      <c r="AE8" s="135"/>
+      <c r="AF8" s="135"/>
+      <c r="AG8" s="135"/>
+      <c r="AH8" s="135"/>
+      <c r="AI8" s="135"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="140" t="s">
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="136" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="140"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="114"/>
-      <c r="M9" s="114"/>
-      <c r="N9" s="114"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="114"/>
-      <c r="R9" s="114"/>
-      <c r="S9" s="114"/>
-      <c r="T9" s="114"/>
-      <c r="U9" s="114"/>
-      <c r="V9" s="114"/>
-      <c r="W9" s="114"/>
-      <c r="X9" s="114"/>
-      <c r="Y9" s="114"/>
-      <c r="Z9" s="114"/>
-      <c r="AA9" s="114"/>
-      <c r="AB9" s="114"/>
-      <c r="AC9" s="114"/>
-      <c r="AD9" s="114"/>
-      <c r="AE9" s="114"/>
-      <c r="AF9" s="114"/>
-      <c r="AG9" s="114"/>
-      <c r="AH9" s="114"/>
-      <c r="AI9" s="114"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="119"/>
+      <c r="R9" s="119"/>
+      <c r="S9" s="119"/>
+      <c r="T9" s="119"/>
+      <c r="U9" s="119"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="119"/>
+      <c r="X9" s="119"/>
+      <c r="Y9" s="119"/>
+      <c r="Z9" s="119"/>
+      <c r="AA9" s="119"/>
+      <c r="AB9" s="119"/>
+      <c r="AC9" s="119"/>
+      <c r="AD9" s="119"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="119"/>
+      <c r="AG9" s="119"/>
+      <c r="AH9" s="119"/>
+      <c r="AI9" s="119"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -9500,14 +9854,14 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
       <c r="F11" s="3" t="s">
         <v>114</v>
       </c>
@@ -9544,7 +9898,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>115</v>
       </c>
@@ -9586,7 +9940,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>116</v>
       </c>
@@ -9628,7 +9982,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>117</v>
       </c>
@@ -9672,7 +10026,7 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -9716,7 +10070,7 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -9760,7 +10114,7 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -9804,7 +10158,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -9848,7 +10202,7 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -9890,7 +10244,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -9930,7 +10284,7 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>17</v>
       </c>
@@ -9972,7 +10326,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -10012,7 +10366,7 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="20" t="s">
         <v>126</v>
       </c>
@@ -10044,7 +10398,7 @@
       <c r="AF23" s="3"/>
       <c r="AK23" s="58"/>
     </row>
-    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="59" t="s">
         <v>127</v>
       </c>
@@ -10052,20 +10406,20 @@
       <c r="G24" s="59"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
-      <c r="J24" s="135"/>
-      <c r="K24" s="135"/>
-      <c r="L24" s="135"/>
-      <c r="M24" s="135"/>
-      <c r="N24" s="135"/>
-      <c r="O24" s="135"/>
-      <c r="P24" s="135"/>
-      <c r="Q24" s="135"/>
-      <c r="R24" s="135"/>
-      <c r="S24" s="135"/>
-      <c r="T24" s="135"/>
-      <c r="U24" s="135"/>
-      <c r="V24" s="135"/>
-      <c r="W24" s="135"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="140"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="140"/>
+      <c r="N24" s="140"/>
+      <c r="O24" s="140"/>
+      <c r="P24" s="140"/>
+      <c r="Q24" s="140"/>
+      <c r="R24" s="140"/>
+      <c r="S24" s="140"/>
+      <c r="T24" s="140"/>
+      <c r="U24" s="140"/>
+      <c r="V24" s="140"/>
+      <c r="W24" s="140"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
@@ -10076,7 +10430,7 @@
       <c r="AF24" s="3"/>
       <c r="AK24" s="58"/>
     </row>
-    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="59"/>
       <c r="F25" s="59"/>
       <c r="G25" s="59"/>
@@ -10106,12 +10460,12 @@
       <c r="AF25" s="3"/>
       <c r="AK25" s="58"/>
     </row>
-    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="120"/>
-      <c r="D26" s="120"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
       <c r="E26" s="59" t="s">
         <v>129</v>
       </c>
@@ -10143,7 +10497,7 @@
       <c r="AF26" s="3"/>
       <c r="AK26" s="58"/>
     </row>
-    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="59"/>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
@@ -10176,253 +10530,253 @@
       <c r="AF27" s="3"/>
       <c r="AK27" s="58"/>
     </row>
-    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="134" t="s">
+    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="134"/>
-      <c r="C28" s="134"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="134"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="134"/>
-      <c r="I28" s="134"/>
-      <c r="J28" s="134"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="116"/>
-      <c r="O28" s="116"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="116"/>
-      <c r="S28" s="116"/>
-      <c r="T28" s="116"/>
-      <c r="U28" s="116"/>
-      <c r="V28" s="116"/>
-      <c r="W28" s="116"/>
-      <c r="X28" s="116"/>
-      <c r="Y28" s="116"/>
-      <c r="Z28" s="116"/>
-      <c r="AA28" s="116"/>
-      <c r="AB28" s="116"/>
-      <c r="AC28" s="116"/>
-      <c r="AD28" s="116"/>
-      <c r="AE28" s="116"/>
-      <c r="AF28" s="116"/>
-      <c r="AG28" s="116"/>
-      <c r="AH28" s="116"/>
-      <c r="AI28" s="116"/>
-      <c r="AJ28" s="116"/>
-      <c r="AK28" s="116"/>
-      <c r="AL28" s="116"/>
-    </row>
-    <row r="29" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="134"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="134"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="134"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="134"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="116"/>
-      <c r="N29" s="116"/>
-      <c r="O29" s="116"/>
-      <c r="P29" s="116"/>
-      <c r="Q29" s="116"/>
-      <c r="R29" s="116"/>
-      <c r="S29" s="116"/>
-      <c r="T29" s="116"/>
-      <c r="U29" s="116"/>
-      <c r="V29" s="116"/>
-      <c r="W29" s="116"/>
-      <c r="X29" s="116"/>
-      <c r="Y29" s="116"/>
-      <c r="Z29" s="116"/>
-      <c r="AA29" s="116"/>
-      <c r="AB29" s="116"/>
-      <c r="AC29" s="116"/>
-      <c r="AD29" s="116"/>
-      <c r="AE29" s="116"/>
-      <c r="AF29" s="116"/>
-      <c r="AG29" s="116"/>
-      <c r="AH29" s="116"/>
-      <c r="AI29" s="116"/>
-      <c r="AJ29" s="116"/>
-      <c r="AK29" s="116"/>
-      <c r="AL29" s="116"/>
-    </row>
-    <row r="30" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="134" t="s">
+      <c r="B28" s="141"/>
+      <c r="C28" s="141"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="70"/>
+      <c r="R28" s="70"/>
+      <c r="S28" s="70"/>
+      <c r="T28" s="70"/>
+      <c r="U28" s="70"/>
+      <c r="V28" s="70"/>
+      <c r="W28" s="70"/>
+      <c r="X28" s="70"/>
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="70"/>
+      <c r="AA28" s="70"/>
+      <c r="AB28" s="70"/>
+      <c r="AC28" s="70"/>
+      <c r="AD28" s="70"/>
+      <c r="AE28" s="70"/>
+      <c r="AF28" s="70"/>
+      <c r="AG28" s="70"/>
+      <c r="AH28" s="70"/>
+      <c r="AI28" s="70"/>
+      <c r="AJ28" s="70"/>
+      <c r="AK28" s="70"/>
+      <c r="AL28" s="70"/>
+    </row>
+    <row r="29" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="141"/>
+      <c r="B29" s="141"/>
+      <c r="C29" s="141"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="70"/>
+      <c r="R29" s="70"/>
+      <c r="S29" s="70"/>
+      <c r="T29" s="70"/>
+      <c r="U29" s="70"/>
+      <c r="V29" s="70"/>
+      <c r="W29" s="70"/>
+      <c r="X29" s="70"/>
+      <c r="Y29" s="70"/>
+      <c r="Z29" s="70"/>
+      <c r="AA29" s="70"/>
+      <c r="AB29" s="70"/>
+      <c r="AC29" s="70"/>
+      <c r="AD29" s="70"/>
+      <c r="AE29" s="70"/>
+      <c r="AF29" s="70"/>
+      <c r="AG29" s="70"/>
+      <c r="AH29" s="70"/>
+      <c r="AI29" s="70"/>
+      <c r="AJ29" s="70"/>
+      <c r="AK29" s="70"/>
+      <c r="AL29" s="70"/>
+    </row>
+    <row r="30" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="134"/>
-      <c r="C30" s="134"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="134"/>
-      <c r="F30" s="134"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="134"/>
-      <c r="I30" s="134"/>
-      <c r="J30" s="134"/>
-      <c r="K30" s="134"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="134"/>
-      <c r="N30" s="134"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="134"/>
-      <c r="Q30" s="134"/>
-      <c r="R30" s="134"/>
-      <c r="S30" s="134"/>
-      <c r="T30" s="134"/>
-      <c r="U30" s="134"/>
-      <c r="V30" s="134"/>
-      <c r="W30" s="134"/>
-      <c r="X30" s="134"/>
-      <c r="Y30" s="134"/>
-      <c r="Z30" s="134"/>
-      <c r="AA30" s="134"/>
-      <c r="AB30" s="134"/>
-      <c r="AC30" s="134"/>
-      <c r="AD30" s="134"/>
-      <c r="AE30" s="134"/>
-      <c r="AF30" s="134"/>
-      <c r="AG30" s="134"/>
-      <c r="AH30" s="134"/>
-      <c r="AI30" s="134"/>
-      <c r="AJ30" s="134"/>
-      <c r="AK30" s="134"/>
-      <c r="AL30" s="134"/>
-    </row>
-    <row r="31" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="134"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="134"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="134"/>
-      <c r="F31" s="134"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="134"/>
-      <c r="J31" s="134"/>
-      <c r="K31" s="134"/>
-      <c r="L31" s="134"/>
-      <c r="M31" s="134"/>
-      <c r="N31" s="134"/>
-      <c r="O31" s="134"/>
-      <c r="P31" s="134"/>
-      <c r="Q31" s="134"/>
-      <c r="R31" s="134"/>
-      <c r="S31" s="134"/>
-      <c r="T31" s="134"/>
-      <c r="U31" s="134"/>
-      <c r="V31" s="134"/>
-      <c r="W31" s="134"/>
-      <c r="X31" s="134"/>
-      <c r="Y31" s="134"/>
-      <c r="Z31" s="134"/>
-      <c r="AA31" s="134"/>
-      <c r="AB31" s="134"/>
-      <c r="AC31" s="134"/>
-      <c r="AD31" s="134"/>
-      <c r="AE31" s="134"/>
-      <c r="AF31" s="134"/>
-      <c r="AG31" s="134"/>
-      <c r="AH31" s="134"/>
-      <c r="AI31" s="134"/>
-      <c r="AJ31" s="134"/>
-      <c r="AK31" s="134"/>
-      <c r="AL31" s="134"/>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A32" s="134" t="s">
+      <c r="B30" s="141"/>
+      <c r="C30" s="141"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="141"/>
+      <c r="I30" s="141"/>
+      <c r="J30" s="141"/>
+      <c r="K30" s="141"/>
+      <c r="L30" s="141"/>
+      <c r="M30" s="141"/>
+      <c r="N30" s="141"/>
+      <c r="O30" s="141"/>
+      <c r="P30" s="141"/>
+      <c r="Q30" s="141"/>
+      <c r="R30" s="141"/>
+      <c r="S30" s="141"/>
+      <c r="T30" s="141"/>
+      <c r="U30" s="141"/>
+      <c r="V30" s="141"/>
+      <c r="W30" s="141"/>
+      <c r="X30" s="141"/>
+      <c r="Y30" s="141"/>
+      <c r="Z30" s="141"/>
+      <c r="AA30" s="141"/>
+      <c r="AB30" s="141"/>
+      <c r="AC30" s="141"/>
+      <c r="AD30" s="141"/>
+      <c r="AE30" s="141"/>
+      <c r="AF30" s="141"/>
+      <c r="AG30" s="141"/>
+      <c r="AH30" s="141"/>
+      <c r="AI30" s="141"/>
+      <c r="AJ30" s="141"/>
+      <c r="AK30" s="141"/>
+      <c r="AL30" s="141"/>
+    </row>
+    <row r="31" spans="1:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="141"/>
+      <c r="B31" s="141"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="141"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="141"/>
+      <c r="M31" s="141"/>
+      <c r="N31" s="141"/>
+      <c r="O31" s="141"/>
+      <c r="P31" s="141"/>
+      <c r="Q31" s="141"/>
+      <c r="R31" s="141"/>
+      <c r="S31" s="141"/>
+      <c r="T31" s="141"/>
+      <c r="U31" s="141"/>
+      <c r="V31" s="141"/>
+      <c r="W31" s="141"/>
+      <c r="X31" s="141"/>
+      <c r="Y31" s="141"/>
+      <c r="Z31" s="141"/>
+      <c r="AA31" s="141"/>
+      <c r="AB31" s="141"/>
+      <c r="AC31" s="141"/>
+      <c r="AD31" s="141"/>
+      <c r="AE31" s="141"/>
+      <c r="AF31" s="141"/>
+      <c r="AG31" s="141"/>
+      <c r="AH31" s="141"/>
+      <c r="AI31" s="141"/>
+      <c r="AJ31" s="141"/>
+      <c r="AK31" s="141"/>
+      <c r="AL31" s="141"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A32" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="134"/>
-      <c r="C32" s="134"/>
-      <c r="D32" s="134"/>
-      <c r="E32" s="134"/>
-      <c r="F32" s="134"/>
-      <c r="G32" s="134"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="134"/>
-      <c r="J32" s="134"/>
-      <c r="K32" s="134"/>
-      <c r="L32" s="134"/>
-      <c r="M32" s="134"/>
-      <c r="N32" s="134"/>
-      <c r="O32" s="134"/>
-      <c r="P32" s="134"/>
-      <c r="Q32" s="134"/>
-      <c r="R32" s="134"/>
-      <c r="S32" s="134"/>
-      <c r="T32" s="134"/>
-      <c r="U32" s="134"/>
-      <c r="V32" s="134"/>
-      <c r="W32" s="134"/>
-      <c r="X32" s="134"/>
-      <c r="Y32" s="134"/>
-      <c r="Z32" s="134"/>
-      <c r="AA32" s="134"/>
-      <c r="AB32" s="134"/>
-      <c r="AC32" s="134"/>
-      <c r="AD32" s="134"/>
-      <c r="AE32" s="134"/>
-      <c r="AF32" s="134"/>
-      <c r="AG32" s="134"/>
-      <c r="AH32" s="134"/>
-      <c r="AI32" s="134"/>
-      <c r="AJ32" s="134"/>
-      <c r="AK32" s="134"/>
-      <c r="AL32" s="134"/>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A33" s="134"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="134"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="134"/>
-      <c r="F33" s="134"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="134"/>
-      <c r="J33" s="134"/>
-      <c r="K33" s="134"/>
-      <c r="L33" s="134"/>
-      <c r="M33" s="134"/>
-      <c r="N33" s="134"/>
-      <c r="O33" s="134"/>
-      <c r="P33" s="134"/>
-      <c r="Q33" s="134"/>
-      <c r="R33" s="134"/>
-      <c r="S33" s="134"/>
-      <c r="T33" s="134"/>
-      <c r="U33" s="134"/>
-      <c r="V33" s="134"/>
-      <c r="W33" s="134"/>
-      <c r="X33" s="134"/>
-      <c r="Y33" s="134"/>
-      <c r="Z33" s="134"/>
-      <c r="AA33" s="134"/>
-      <c r="AB33" s="134"/>
-      <c r="AC33" s="134"/>
-      <c r="AD33" s="134"/>
-      <c r="AE33" s="134"/>
-      <c r="AF33" s="134"/>
-      <c r="AG33" s="134"/>
-      <c r="AH33" s="134"/>
-      <c r="AI33" s="134"/>
-      <c r="AJ33" s="134"/>
-      <c r="AK33" s="134"/>
-      <c r="AL33" s="134"/>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="B32" s="141"/>
+      <c r="C32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="141"/>
+      <c r="H32" s="141"/>
+      <c r="I32" s="141"/>
+      <c r="J32" s="141"/>
+      <c r="K32" s="141"/>
+      <c r="L32" s="141"/>
+      <c r="M32" s="141"/>
+      <c r="N32" s="141"/>
+      <c r="O32" s="141"/>
+      <c r="P32" s="141"/>
+      <c r="Q32" s="141"/>
+      <c r="R32" s="141"/>
+      <c r="S32" s="141"/>
+      <c r="T32" s="141"/>
+      <c r="U32" s="141"/>
+      <c r="V32" s="141"/>
+      <c r="W32" s="141"/>
+      <c r="X32" s="141"/>
+      <c r="Y32" s="141"/>
+      <c r="Z32" s="141"/>
+      <c r="AA32" s="141"/>
+      <c r="AB32" s="141"/>
+      <c r="AC32" s="141"/>
+      <c r="AD32" s="141"/>
+      <c r="AE32" s="141"/>
+      <c r="AF32" s="141"/>
+      <c r="AG32" s="141"/>
+      <c r="AH32" s="141"/>
+      <c r="AI32" s="141"/>
+      <c r="AJ32" s="141"/>
+      <c r="AK32" s="141"/>
+      <c r="AL32" s="141"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A33" s="141"/>
+      <c r="B33" s="141"/>
+      <c r="C33" s="141"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="141"/>
+      <c r="H33" s="141"/>
+      <c r="I33" s="141"/>
+      <c r="J33" s="141"/>
+      <c r="K33" s="141"/>
+      <c r="L33" s="141"/>
+      <c r="M33" s="141"/>
+      <c r="N33" s="141"/>
+      <c r="O33" s="141"/>
+      <c r="P33" s="141"/>
+      <c r="Q33" s="141"/>
+      <c r="R33" s="141"/>
+      <c r="S33" s="141"/>
+      <c r="T33" s="141"/>
+      <c r="U33" s="141"/>
+      <c r="V33" s="141"/>
+      <c r="W33" s="141"/>
+      <c r="X33" s="141"/>
+      <c r="Y33" s="141"/>
+      <c r="Z33" s="141"/>
+      <c r="AA33" s="141"/>
+      <c r="AB33" s="141"/>
+      <c r="AC33" s="141"/>
+      <c r="AD33" s="141"/>
+      <c r="AE33" s="141"/>
+      <c r="AF33" s="141"/>
+      <c r="AG33" s="141"/>
+      <c r="AH33" s="141"/>
+      <c r="AI33" s="141"/>
+      <c r="AJ33" s="141"/>
+      <c r="AK33" s="141"/>
+      <c r="AL33" s="141"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A34" s="59"/>
       <c r="F34" s="59"/>
       <c r="G34" s="59"/>
@@ -10458,7 +10812,7 @@
       <c r="AK34" s="62"/>
       <c r="AL34" s="61"/>
     </row>
-    <row r="35" spans="1:38" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A35" s="63" t="s">
         <v>17</v>
       </c>
@@ -10497,7 +10851,7 @@
       <c r="AK35" s="61"/>
       <c r="AL35" s="61"/>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A36" s="58"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -10534,7 +10888,7 @@
       <c r="AK36" s="61"/>
       <c r="AL36" s="61"/>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
         <v>54</v>
       </c>
@@ -10576,7 +10930,7 @@
       <c r="AK37" s="61"/>
       <c r="AL37" s="61"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.2">
       <c r="T38" s="61"/>
       <c r="U38" s="61"/>
       <c r="V38" s="61"/>
@@ -10593,7 +10947,7 @@
       <c r="AG38" s="61"/>
       <c r="AH38" s="61"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A39" s="59" t="s">
         <v>139</v>
       </c>
@@ -10613,7 +10967,7 @@
       <c r="AG39" s="61"/>
       <c r="AH39" s="61"/>
     </row>
-    <row r="40" spans="1:38" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A40" s="64" t="s">
         <v>132</v>
       </c>
@@ -10633,7 +10987,7 @@
       <c r="AG40" s="61"/>
       <c r="AH40" s="61"/>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.2">
       <c r="T41" s="61"/>
       <c r="U41" s="61"/>
       <c r="V41" s="61"/>
@@ -10650,7 +11004,7 @@
       <c r="AG41" s="61"/>
       <c r="AH41" s="61"/>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A42" s="65" t="s">
         <v>133</v>
       </c>
@@ -10672,7 +11026,7 @@
       <c r="AG42" s="61"/>
       <c r="AH42" s="61"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A43" s="65"/>
       <c r="T43" s="61"/>
       <c r="U43" s="61"/>
@@ -10690,7 +11044,7 @@
       <c r="AG43" s="61"/>
       <c r="AH43" s="61"/>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A44" s="61" t="s">
         <v>138</v>
       </c>
@@ -10712,7 +11066,7 @@
       <c r="AG44" s="61"/>
       <c r="AH44" s="61"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.2">
       <c r="T45" s="61"/>
       <c r="U45" s="61"/>
       <c r="V45" s="61"/>
@@ -10729,7 +11083,7 @@
       <c r="AG45" s="61"/>
       <c r="AH45" s="61"/>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A46" s="61" t="s">
         <v>137</v>
       </c>
@@ -10751,7 +11105,7 @@
       <c r="AG46" s="61"/>
       <c r="AH46" s="61"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.2">
       <c r="T47" s="61"/>
       <c r="U47" s="61"/>
       <c r="V47" s="61"/>
@@ -10768,7 +11122,7 @@
       <c r="AG47" s="61"/>
       <c r="AH47" s="61"/>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.2">
       <c r="T48" s="61"/>
       <c r="U48" s="61"/>
       <c r="V48" s="61"/>
@@ -10787,27 +11141,11 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="AC8:AI8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="V9:AB9"/>
-    <mergeCell ref="AC9:AI9"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:U8"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="J24:W24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A28:J29"/>
-    <mergeCell ref="K28:Q29"/>
-    <mergeCell ref="R28:X29"/>
+    <mergeCell ref="A32:J33"/>
+    <mergeCell ref="K32:Q33"/>
+    <mergeCell ref="R32:X33"/>
+    <mergeCell ref="Y32:AE33"/>
+    <mergeCell ref="AF32:AL33"/>
     <mergeCell ref="Y28:AE29"/>
     <mergeCell ref="AF28:AL29"/>
     <mergeCell ref="A30:J31"/>
@@ -10815,13 +11153,29 @@
     <mergeCell ref="R30:X31"/>
     <mergeCell ref="Y30:AE31"/>
     <mergeCell ref="AF30:AL31"/>
-    <mergeCell ref="A32:J33"/>
-    <mergeCell ref="K32:Q33"/>
-    <mergeCell ref="R32:X33"/>
-    <mergeCell ref="Y32:AE33"/>
-    <mergeCell ref="AF32:AL33"/>
+    <mergeCell ref="J24:W24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A28:J29"/>
+    <mergeCell ref="K28:Q29"/>
+    <mergeCell ref="R28:X29"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:U8"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="AC8:AI8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="V9:AB9"/>
+    <mergeCell ref="AC9:AI9"/>
   </mergeCells>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="34" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -10836,6 +11190,2371 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CB20BC-425A-4A65-A6D2-E0DAF0CC9C68}">
+  <dimension ref="A1:AL56"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="2.375" style="143" customWidth="1"/>
+    <col min="4" max="4" width="3" style="143" customWidth="1"/>
+    <col min="5" max="7" width="2.375" style="143" customWidth="1"/>
+    <col min="8" max="8" width="2" style="143" customWidth="1"/>
+    <col min="9" max="31" width="2.125" style="143" customWidth="1"/>
+    <col min="32" max="38" width="2.375" style="143" customWidth="1"/>
+    <col min="39" max="16384" width="8.875" style="143"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="142" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="145"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="145"/>
+      <c r="Z1" s="145"/>
+      <c r="AA1" s="145"/>
+      <c r="AB1" s="145"/>
+      <c r="AC1" s="145"/>
+      <c r="AD1" s="145"/>
+      <c r="AE1" s="145"/>
+      <c r="AF1" s="145"/>
+      <c r="AG1" s="145"/>
+      <c r="AH1" s="145"/>
+      <c r="AI1" s="145"/>
+      <c r="AJ1" s="145"/>
+      <c r="AK1" s="145"/>
+      <c r="AL1" s="145"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="146" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
+      <c r="U2" s="147"/>
+      <c r="V2" s="147"/>
+      <c r="W2" s="147"/>
+      <c r="X2" s="147"/>
+      <c r="Y2" s="147"/>
+      <c r="Z2" s="147"/>
+      <c r="AA2" s="147"/>
+      <c r="AB2" s="147"/>
+      <c r="AC2" s="147"/>
+      <c r="AD2" s="147"/>
+      <c r="AE2" s="147"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="147"/>
+      <c r="AH2" s="147"/>
+      <c r="AI2" s="147"/>
+      <c r="AJ2" s="147"/>
+      <c r="AK2" s="147"/>
+      <c r="AL2" s="147"/>
+    </row>
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="148"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="148"/>
+      <c r="K3" s="148"/>
+      <c r="L3" s="148"/>
+      <c r="M3" s="148"/>
+      <c r="N3" s="148"/>
+      <c r="O3" s="148"/>
+      <c r="P3" s="148"/>
+      <c r="Q3" s="148"/>
+      <c r="R3" s="148"/>
+      <c r="S3" s="148"/>
+      <c r="T3" s="148"/>
+      <c r="U3" s="147"/>
+      <c r="V3" s="147"/>
+      <c r="W3" s="147"/>
+      <c r="X3" s="147"/>
+      <c r="Y3" s="147"/>
+      <c r="Z3" s="149"/>
+      <c r="AA3" s="147"/>
+      <c r="AB3" s="147"/>
+      <c r="AC3" s="147"/>
+      <c r="AD3" s="147"/>
+      <c r="AE3" s="147"/>
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="147"/>
+      <c r="AH3" s="147"/>
+      <c r="AI3" s="147"/>
+      <c r="AJ3" s="147"/>
+      <c r="AK3" s="147"/>
+      <c r="AL3" s="147"/>
+    </row>
+    <row r="4" spans="1:38" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="150"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="152"/>
+      <c r="J4" s="152"/>
+      <c r="K4" s="152"/>
+      <c r="L4" s="152"/>
+      <c r="M4" s="153"/>
+      <c r="N4" s="153"/>
+      <c r="O4" s="153"/>
+      <c r="P4" s="153"/>
+      <c r="Q4" s="153"/>
+      <c r="R4" s="153"/>
+      <c r="S4" s="153"/>
+      <c r="T4" s="153"/>
+      <c r="U4" s="153"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="153"/>
+      <c r="X4" s="153"/>
+      <c r="Y4" s="153"/>
+      <c r="Z4" s="153"/>
+      <c r="AA4" s="153"/>
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="153"/>
+      <c r="AD4" s="153"/>
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="153"/>
+      <c r="AG4" s="153"/>
+      <c r="AH4" s="153"/>
+      <c r="AI4" s="153"/>
+      <c r="AJ4" s="153"/>
+      <c r="AK4" s="153"/>
+      <c r="AL4" s="153"/>
+    </row>
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="154"/>
+      <c r="B5" s="151"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="153"/>
+      <c r="N5" s="153"/>
+      <c r="O5" s="153"/>
+      <c r="P5" s="153"/>
+      <c r="Q5" s="153"/>
+      <c r="R5" s="153"/>
+      <c r="S5" s="153"/>
+      <c r="T5" s="153"/>
+      <c r="U5" s="153"/>
+      <c r="V5" s="153"/>
+      <c r="W5" s="153"/>
+      <c r="X5" s="153"/>
+      <c r="Y5" s="153"/>
+      <c r="Z5" s="153"/>
+      <c r="AA5" s="153"/>
+      <c r="AB5" s="153"/>
+      <c r="AC5" s="153"/>
+      <c r="AD5" s="153"/>
+      <c r="AE5" s="153"/>
+      <c r="AF5" s="153"/>
+      <c r="AG5" s="153"/>
+      <c r="AH5" s="153"/>
+      <c r="AI5" s="153"/>
+      <c r="AJ5" s="153"/>
+      <c r="AK5" s="153"/>
+      <c r="AL5" s="153"/>
+    </row>
+    <row r="6" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="155"/>
+      <c r="B6" s="151"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="151"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="152"/>
+      <c r="J6" s="152"/>
+      <c r="K6" s="152"/>
+      <c r="L6" s="152"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="153"/>
+      <c r="R6" s="153"/>
+      <c r="S6" s="153"/>
+      <c r="T6" s="153"/>
+      <c r="U6" s="153"/>
+      <c r="V6" s="153"/>
+      <c r="W6" s="153"/>
+      <c r="X6" s="153"/>
+      <c r="Y6" s="153"/>
+      <c r="Z6" s="153"/>
+      <c r="AA6" s="153"/>
+      <c r="AB6" s="153"/>
+      <c r="AC6" s="153"/>
+      <c r="AD6" s="153"/>
+      <c r="AE6" s="153"/>
+      <c r="AF6" s="153"/>
+      <c r="AG6" s="153"/>
+      <c r="AH6" s="153"/>
+      <c r="AI6" s="153"/>
+      <c r="AJ6" s="153"/>
+      <c r="AK6" s="153"/>
+      <c r="AL6" s="153"/>
+    </row>
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="143" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="142"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="142" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="142"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="157" t="s">
+        <v>149</v>
+      </c>
+      <c r="L7" s="145"/>
+      <c r="M7" s="145"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="145"/>
+      <c r="P7" s="158" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q7" s="157"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="157"/>
+      <c r="T7" s="157"/>
+      <c r="U7" s="157"/>
+      <c r="V7" s="157"/>
+      <c r="W7" s="157"/>
+      <c r="X7" s="157"/>
+      <c r="Y7" s="157"/>
+      <c r="Z7" s="157"/>
+      <c r="AA7" s="157"/>
+      <c r="AB7" s="157"/>
+      <c r="AC7" s="157"/>
+      <c r="AD7" s="157"/>
+      <c r="AE7" s="157"/>
+      <c r="AF7" s="157"/>
+      <c r="AG7" s="157"/>
+      <c r="AH7" s="157"/>
+      <c r="AI7" s="157"/>
+      <c r="AJ7" s="157"/>
+      <c r="AK7" s="157"/>
+      <c r="AL7" s="157"/>
+    </row>
+    <row r="8" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="142"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="144"/>
+      <c r="L8" s="144"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="142"/>
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="147"/>
+      <c r="U8" s="147"/>
+      <c r="V8" s="147"/>
+      <c r="W8" s="147"/>
+      <c r="X8" s="147"/>
+      <c r="Y8" s="147"/>
+      <c r="Z8" s="147"/>
+      <c r="AA8" s="147"/>
+      <c r="AB8" s="147"/>
+      <c r="AC8" s="147"/>
+      <c r="AD8" s="147"/>
+      <c r="AE8" s="147"/>
+      <c r="AF8" s="147"/>
+      <c r="AG8" s="147"/>
+      <c r="AH8" s="147"/>
+      <c r="AI8" s="147"/>
+      <c r="AJ8" s="147"/>
+      <c r="AK8" s="147"/>
+      <c r="AL8" s="147"/>
+    </row>
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="143" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="142"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="142"/>
+      <c r="I9" s="142"/>
+      <c r="J9" s="147"/>
+      <c r="K9" s="147"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="147"/>
+      <c r="N9" s="147"/>
+      <c r="O9" s="147"/>
+      <c r="P9" s="147"/>
+      <c r="Q9" s="147"/>
+      <c r="R9" s="147"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="147"/>
+      <c r="U9" s="147"/>
+      <c r="V9" s="147"/>
+      <c r="W9" s="147"/>
+      <c r="X9" s="147"/>
+      <c r="Y9" s="147"/>
+      <c r="Z9" s="147"/>
+      <c r="AA9" s="147"/>
+      <c r="AB9" s="147"/>
+      <c r="AC9" s="147"/>
+      <c r="AD9" s="147"/>
+      <c r="AE9" s="159"/>
+      <c r="AF9" s="159"/>
+      <c r="AG9" s="159"/>
+      <c r="AH9" s="159"/>
+      <c r="AI9" s="147"/>
+      <c r="AJ9" s="147"/>
+      <c r="AK9" s="147"/>
+      <c r="AL9" s="147"/>
+    </row>
+    <row r="10" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="142"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="144"/>
+      <c r="L10" s="144"/>
+      <c r="M10" s="147"/>
+      <c r="N10" s="147"/>
+      <c r="O10" s="147"/>
+      <c r="P10" s="147"/>
+      <c r="Q10" s="142"/>
+      <c r="R10" s="147"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="147"/>
+      <c r="U10" s="147"/>
+      <c r="V10" s="147"/>
+      <c r="W10" s="147"/>
+      <c r="X10" s="147"/>
+      <c r="Y10" s="147"/>
+      <c r="Z10" s="147"/>
+      <c r="AA10" s="147"/>
+      <c r="AB10" s="147"/>
+      <c r="AC10" s="147"/>
+      <c r="AD10" s="147"/>
+      <c r="AE10" s="159"/>
+      <c r="AF10" s="159"/>
+      <c r="AG10" s="159"/>
+      <c r="AH10" s="159"/>
+      <c r="AI10" s="147"/>
+      <c r="AJ10" s="147"/>
+      <c r="AK10" s="147"/>
+      <c r="AL10" s="147"/>
+    </row>
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="143" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="147"/>
+      <c r="O11" s="147"/>
+      <c r="P11" s="147"/>
+      <c r="Q11" s="142"/>
+      <c r="R11" s="147"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="147"/>
+      <c r="U11" s="147"/>
+      <c r="V11" s="147"/>
+      <c r="W11" s="147"/>
+      <c r="X11" s="147"/>
+      <c r="Y11" s="147"/>
+      <c r="Z11" s="147"/>
+      <c r="AA11" s="147"/>
+      <c r="AB11" s="147"/>
+      <c r="AC11" s="147"/>
+      <c r="AD11" s="147"/>
+      <c r="AE11" s="159"/>
+      <c r="AF11" s="159"/>
+      <c r="AG11" s="159"/>
+      <c r="AH11" s="159"/>
+      <c r="AI11" s="147"/>
+      <c r="AJ11" s="147"/>
+      <c r="AK11" s="147"/>
+      <c r="AL11" s="147"/>
+    </row>
+    <row r="12" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="147"/>
+      <c r="O12" s="147"/>
+      <c r="P12" s="147"/>
+      <c r="Q12" s="142"/>
+      <c r="R12" s="147"/>
+      <c r="S12" s="147"/>
+      <c r="T12" s="147"/>
+      <c r="U12" s="147"/>
+      <c r="V12" s="147"/>
+      <c r="W12" s="147"/>
+      <c r="X12" s="147"/>
+      <c r="Y12" s="147"/>
+      <c r="Z12" s="147"/>
+      <c r="AA12" s="147"/>
+      <c r="AB12" s="147"/>
+      <c r="AC12" s="147"/>
+      <c r="AD12" s="147"/>
+      <c r="AE12" s="159"/>
+      <c r="AF12" s="159"/>
+      <c r="AG12" s="159"/>
+      <c r="AH12" s="159"/>
+      <c r="AI12" s="147"/>
+      <c r="AJ12" s="147"/>
+      <c r="AK12" s="147"/>
+      <c r="AL12" s="147"/>
+    </row>
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="160" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="147"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="147"/>
+      <c r="U13" s="147"/>
+      <c r="V13" s="147"/>
+      <c r="W13" s="147"/>
+      <c r="X13" s="147"/>
+      <c r="Y13" s="147"/>
+      <c r="Z13" s="147"/>
+      <c r="AA13" s="147"/>
+      <c r="AB13" s="147"/>
+      <c r="AC13" s="147"/>
+      <c r="AD13" s="147"/>
+      <c r="AE13" s="147"/>
+      <c r="AF13" s="147"/>
+      <c r="AG13" s="147"/>
+      <c r="AH13" s="147"/>
+      <c r="AI13" s="147"/>
+      <c r="AJ13" s="147"/>
+      <c r="AK13" s="147"/>
+      <c r="AL13" s="147"/>
+    </row>
+    <row r="14" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="160"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="147"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
+      <c r="Q14" s="142"/>
+      <c r="R14" s="147"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="147"/>
+      <c r="U14" s="147"/>
+      <c r="V14" s="147"/>
+      <c r="W14" s="147"/>
+      <c r="X14" s="147"/>
+      <c r="Y14" s="147"/>
+      <c r="Z14" s="147"/>
+      <c r="AA14" s="147"/>
+      <c r="AB14" s="147"/>
+      <c r="AC14" s="147"/>
+      <c r="AD14" s="147"/>
+      <c r="AE14" s="147"/>
+      <c r="AF14" s="147"/>
+      <c r="AG14" s="147"/>
+      <c r="AH14" s="147"/>
+      <c r="AI14" s="147"/>
+      <c r="AJ14" s="147"/>
+      <c r="AK14" s="147"/>
+      <c r="AL14" s="147"/>
+    </row>
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="143" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="147"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="147"/>
+      <c r="P15" s="147"/>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="147"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="147"/>
+      <c r="U15" s="147"/>
+      <c r="V15" s="147"/>
+      <c r="W15" s="147"/>
+      <c r="X15" s="147"/>
+      <c r="Y15" s="147"/>
+      <c r="Z15" s="147"/>
+      <c r="AA15" s="147"/>
+      <c r="AB15" s="147"/>
+      <c r="AC15" s="147"/>
+      <c r="AD15" s="147"/>
+      <c r="AE15" s="147"/>
+      <c r="AF15" s="147"/>
+      <c r="AG15" s="147"/>
+      <c r="AH15" s="147"/>
+      <c r="AI15" s="147"/>
+      <c r="AJ15" s="147"/>
+      <c r="AK15" s="147"/>
+      <c r="AL15" s="147"/>
+    </row>
+    <row r="16" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="142"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="142"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="147"/>
+      <c r="N16" s="147"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="147"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="147"/>
+      <c r="U16" s="147"/>
+      <c r="V16" s="147"/>
+      <c r="W16" s="147"/>
+      <c r="X16" s="147"/>
+      <c r="Y16" s="147"/>
+      <c r="Z16" s="147"/>
+      <c r="AA16" s="147"/>
+      <c r="AB16" s="147"/>
+      <c r="AC16" s="147"/>
+      <c r="AD16" s="147"/>
+      <c r="AE16" s="147"/>
+      <c r="AF16" s="147"/>
+      <c r="AG16" s="147"/>
+      <c r="AH16" s="147"/>
+      <c r="AI16" s="147"/>
+      <c r="AJ16" s="147"/>
+      <c r="AK16" s="147"/>
+      <c r="AL16" s="147"/>
+    </row>
+    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="143" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="142"/>
+      <c r="J17" s="144"/>
+      <c r="K17" s="144"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="147"/>
+      <c r="O17" s="147"/>
+      <c r="P17" s="147"/>
+      <c r="Q17" s="142"/>
+      <c r="R17" s="147"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="147"/>
+      <c r="U17" s="147"/>
+      <c r="V17" s="147"/>
+      <c r="W17" s="147"/>
+      <c r="X17" s="147"/>
+      <c r="Y17" s="147"/>
+      <c r="Z17" s="147"/>
+      <c r="AA17" s="147"/>
+      <c r="AB17" s="147"/>
+      <c r="AC17" s="147"/>
+      <c r="AD17" s="147"/>
+      <c r="AE17" s="147"/>
+      <c r="AF17" s="147"/>
+      <c r="AG17" s="147"/>
+      <c r="AH17" s="147"/>
+      <c r="AI17" s="147"/>
+      <c r="AJ17" s="147"/>
+      <c r="AK17" s="147"/>
+      <c r="AL17" s="147"/>
+    </row>
+    <row r="18" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="142"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142"/>
+      <c r="J18" s="144"/>
+      <c r="K18" s="144"/>
+      <c r="L18" s="144"/>
+      <c r="M18" s="147"/>
+      <c r="N18" s="147"/>
+      <c r="O18" s="147"/>
+      <c r="P18" s="147"/>
+      <c r="Q18" s="142"/>
+      <c r="R18" s="147"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="147"/>
+      <c r="U18" s="147"/>
+      <c r="V18" s="147"/>
+      <c r="W18" s="147"/>
+      <c r="X18" s="147"/>
+      <c r="Y18" s="147"/>
+      <c r="Z18" s="147"/>
+      <c r="AA18" s="147"/>
+      <c r="AB18" s="147"/>
+      <c r="AC18" s="147"/>
+      <c r="AD18" s="147"/>
+      <c r="AE18" s="147"/>
+      <c r="AF18" s="147"/>
+      <c r="AG18" s="147"/>
+      <c r="AH18" s="147"/>
+      <c r="AI18" s="147"/>
+      <c r="AJ18" s="147"/>
+      <c r="AK18" s="147"/>
+      <c r="AL18" s="147"/>
+    </row>
+    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="160" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="144"/>
+      <c r="K19" s="144"/>
+      <c r="L19" s="144"/>
+      <c r="M19" s="147"/>
+      <c r="N19" s="147"/>
+      <c r="O19" s="147"/>
+      <c r="P19" s="147"/>
+      <c r="Q19" s="142"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="147"/>
+      <c r="U19" s="147"/>
+      <c r="V19" s="147"/>
+      <c r="W19" s="147"/>
+      <c r="X19" s="147"/>
+      <c r="Y19" s="147"/>
+      <c r="Z19" s="147"/>
+      <c r="AA19" s="147"/>
+      <c r="AB19" s="147"/>
+      <c r="AC19" s="147"/>
+      <c r="AD19" s="147"/>
+      <c r="AE19" s="147"/>
+      <c r="AF19" s="147"/>
+      <c r="AG19" s="147"/>
+      <c r="AH19" s="147"/>
+      <c r="AI19" s="147"/>
+      <c r="AJ19" s="147"/>
+      <c r="AK19" s="147"/>
+      <c r="AL19" s="147"/>
+    </row>
+    <row r="20" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="142"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="144"/>
+      <c r="K20" s="144"/>
+      <c r="L20" s="144"/>
+      <c r="M20" s="147"/>
+      <c r="N20" s="147"/>
+      <c r="O20" s="147"/>
+      <c r="P20" s="147"/>
+      <c r="Q20" s="142"/>
+      <c r="R20" s="147"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="147"/>
+      <c r="U20" s="147"/>
+      <c r="V20" s="147"/>
+      <c r="W20" s="147"/>
+      <c r="X20" s="147"/>
+      <c r="Y20" s="147"/>
+      <c r="Z20" s="147"/>
+      <c r="AA20" s="147"/>
+      <c r="AB20" s="147"/>
+      <c r="AC20" s="147"/>
+      <c r="AD20" s="147"/>
+      <c r="AE20" s="147"/>
+      <c r="AF20" s="147"/>
+      <c r="AG20" s="147"/>
+      <c r="AH20" s="147"/>
+      <c r="AI20" s="147"/>
+      <c r="AJ20" s="147"/>
+      <c r="AK20" s="147"/>
+      <c r="AL20" s="147"/>
+    </row>
+    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="143" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="142"/>
+      <c r="F21" s="142"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="142"/>
+      <c r="I21" s="142"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="147"/>
+      <c r="N21" s="147"/>
+      <c r="O21" s="147"/>
+      <c r="P21" s="147"/>
+      <c r="Q21" s="142"/>
+      <c r="R21" s="147"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="147"/>
+      <c r="U21" s="147"/>
+      <c r="V21" s="147"/>
+      <c r="W21" s="147"/>
+      <c r="X21" s="147"/>
+      <c r="Y21" s="147"/>
+      <c r="Z21" s="147"/>
+      <c r="AA21" s="147"/>
+      <c r="AB21" s="147"/>
+      <c r="AC21" s="147"/>
+      <c r="AD21" s="147"/>
+      <c r="AE21" s="147"/>
+      <c r="AF21" s="147"/>
+      <c r="AG21" s="147"/>
+      <c r="AH21" s="147"/>
+      <c r="AI21" s="147"/>
+      <c r="AJ21" s="147"/>
+      <c r="AK21" s="147"/>
+      <c r="AL21" s="147"/>
+    </row>
+    <row r="22" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E22" s="142"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="142"/>
+      <c r="J22" s="144"/>
+      <c r="K22" s="144"/>
+      <c r="L22" s="144"/>
+      <c r="M22" s="147"/>
+      <c r="N22" s="147"/>
+      <c r="O22" s="147"/>
+      <c r="P22" s="147"/>
+      <c r="Q22" s="142"/>
+      <c r="R22" s="147"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="147"/>
+      <c r="U22" s="147"/>
+      <c r="V22" s="147"/>
+      <c r="W22" s="147"/>
+      <c r="X22" s="147"/>
+      <c r="Y22" s="147"/>
+      <c r="Z22" s="147"/>
+      <c r="AA22" s="147"/>
+      <c r="AB22" s="147"/>
+      <c r="AC22" s="147"/>
+      <c r="AD22" s="147"/>
+      <c r="AE22" s="147"/>
+      <c r="AF22" s="147"/>
+      <c r="AG22" s="147"/>
+      <c r="AH22" s="147"/>
+      <c r="AI22" s="147"/>
+      <c r="AJ22" s="147"/>
+      <c r="AK22" s="147"/>
+      <c r="AL22" s="147"/>
+    </row>
+    <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="143" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="142"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="142"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="144"/>
+      <c r="K23" s="144"/>
+      <c r="L23" s="144"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="147"/>
+      <c r="P23" s="147"/>
+      <c r="Q23" s="142"/>
+      <c r="R23" s="147"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="147"/>
+      <c r="U23" s="147"/>
+      <c r="V23" s="147"/>
+      <c r="W23" s="147"/>
+      <c r="X23" s="147"/>
+      <c r="Y23" s="147"/>
+      <c r="Z23" s="147"/>
+      <c r="AA23" s="147"/>
+      <c r="AB23" s="147"/>
+      <c r="AC23" s="147"/>
+      <c r="AD23" s="147"/>
+      <c r="AE23" s="147"/>
+      <c r="AF23" s="147"/>
+      <c r="AG23" s="147"/>
+      <c r="AH23" s="147"/>
+      <c r="AI23" s="147"/>
+      <c r="AJ23" s="147"/>
+      <c r="AK23" s="147"/>
+      <c r="AL23" s="147"/>
+    </row>
+    <row r="24" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="142"/>
+      <c r="F24" s="142"/>
+      <c r="G24" s="142"/>
+      <c r="H24" s="142"/>
+      <c r="I24" s="142"/>
+      <c r="J24" s="144"/>
+      <c r="K24" s="144"/>
+      <c r="L24" s="144"/>
+      <c r="M24" s="147"/>
+      <c r="N24" s="147"/>
+      <c r="O24" s="147"/>
+      <c r="P24" s="147"/>
+      <c r="Q24" s="142"/>
+      <c r="R24" s="147"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="147"/>
+      <c r="U24" s="147"/>
+      <c r="V24" s="147"/>
+      <c r="W24" s="147"/>
+      <c r="X24" s="147"/>
+      <c r="Y24" s="147"/>
+      <c r="Z24" s="147"/>
+      <c r="AA24" s="147"/>
+      <c r="AB24" s="147"/>
+      <c r="AC24" s="147"/>
+      <c r="AD24" s="147"/>
+      <c r="AE24" s="147"/>
+      <c r="AF24" s="147"/>
+      <c r="AG24" s="147"/>
+      <c r="AH24" s="147"/>
+      <c r="AI24" s="147"/>
+      <c r="AJ24" s="147"/>
+      <c r="AK24" s="147"/>
+      <c r="AL24" s="147"/>
+    </row>
+    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="160" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="142"/>
+      <c r="F25" s="142"/>
+      <c r="G25" s="142"/>
+      <c r="H25" s="142"/>
+      <c r="I25" s="142"/>
+      <c r="J25" s="144"/>
+      <c r="K25" s="144"/>
+      <c r="L25" s="144"/>
+      <c r="M25" s="147"/>
+      <c r="N25" s="147"/>
+      <c r="O25" s="147"/>
+      <c r="P25" s="147"/>
+      <c r="Q25" s="142"/>
+      <c r="R25" s="147"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="147"/>
+      <c r="U25" s="147"/>
+      <c r="V25" s="147"/>
+      <c r="W25" s="147"/>
+      <c r="X25" s="147"/>
+      <c r="Y25" s="147"/>
+      <c r="Z25" s="147"/>
+      <c r="AA25" s="147"/>
+      <c r="AB25" s="147"/>
+      <c r="AC25" s="147"/>
+      <c r="AD25" s="147"/>
+      <c r="AE25" s="147"/>
+      <c r="AF25" s="147"/>
+      <c r="AG25" s="147"/>
+      <c r="AH25" s="147"/>
+      <c r="AI25" s="147"/>
+      <c r="AJ25" s="147"/>
+      <c r="AK25" s="147"/>
+      <c r="AL25" s="147"/>
+    </row>
+    <row r="26" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="142"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="142"/>
+      <c r="J26" s="144"/>
+      <c r="K26" s="144"/>
+      <c r="L26" s="144"/>
+      <c r="M26" s="147"/>
+      <c r="N26" s="147"/>
+      <c r="O26" s="147"/>
+      <c r="P26" s="147"/>
+      <c r="Q26" s="142"/>
+      <c r="R26" s="147"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="147"/>
+      <c r="U26" s="147"/>
+      <c r="V26" s="147"/>
+      <c r="W26" s="147"/>
+      <c r="X26" s="147"/>
+      <c r="Y26" s="147"/>
+      <c r="Z26" s="147"/>
+      <c r="AA26" s="147"/>
+      <c r="AB26" s="147"/>
+      <c r="AC26" s="147"/>
+      <c r="AD26" s="147"/>
+      <c r="AE26" s="147"/>
+      <c r="AF26" s="147"/>
+      <c r="AG26" s="147"/>
+      <c r="AH26" s="147"/>
+      <c r="AI26" s="147"/>
+      <c r="AJ26" s="147"/>
+      <c r="AK26" s="147"/>
+      <c r="AL26" s="147"/>
+    </row>
+    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="143" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="142"/>
+      <c r="F27" s="142"/>
+      <c r="G27" s="142"/>
+      <c r="H27" s="142"/>
+      <c r="I27" s="142"/>
+      <c r="J27" s="144"/>
+      <c r="K27" s="144"/>
+      <c r="L27" s="144"/>
+      <c r="M27" s="147"/>
+      <c r="N27" s="147"/>
+      <c r="O27" s="147"/>
+      <c r="P27" s="147"/>
+      <c r="Q27" s="142"/>
+      <c r="R27" s="147"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="147"/>
+      <c r="U27" s="147"/>
+      <c r="V27" s="147"/>
+      <c r="W27" s="147"/>
+      <c r="X27" s="147"/>
+      <c r="Y27" s="147"/>
+      <c r="Z27" s="147"/>
+      <c r="AA27" s="147"/>
+      <c r="AB27" s="147"/>
+      <c r="AC27" s="147"/>
+      <c r="AD27" s="147"/>
+      <c r="AE27" s="147"/>
+      <c r="AF27" s="147"/>
+      <c r="AG27" s="147"/>
+      <c r="AH27" s="147"/>
+      <c r="AI27" s="147"/>
+      <c r="AJ27" s="147"/>
+      <c r="AK27" s="147"/>
+      <c r="AL27" s="147"/>
+    </row>
+    <row r="28" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="142"/>
+      <c r="J28" s="144"/>
+      <c r="K28" s="144"/>
+      <c r="L28" s="144"/>
+      <c r="M28" s="147"/>
+      <c r="N28" s="147"/>
+      <c r="O28" s="147"/>
+      <c r="P28" s="147"/>
+      <c r="Q28" s="142"/>
+      <c r="R28" s="147"/>
+      <c r="S28" s="147"/>
+      <c r="T28" s="147"/>
+      <c r="U28" s="147"/>
+      <c r="V28" s="147"/>
+      <c r="W28" s="147"/>
+      <c r="X28" s="147"/>
+      <c r="Y28" s="147"/>
+      <c r="Z28" s="147"/>
+      <c r="AA28" s="147"/>
+      <c r="AB28" s="147"/>
+      <c r="AC28" s="147"/>
+      <c r="AD28" s="147"/>
+      <c r="AE28" s="147"/>
+      <c r="AF28" s="147"/>
+      <c r="AG28" s="147"/>
+      <c r="AH28" s="147"/>
+      <c r="AI28" s="147"/>
+      <c r="AJ28" s="147"/>
+      <c r="AK28" s="147"/>
+      <c r="AL28" s="147"/>
+    </row>
+    <row r="29" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="143" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="142"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="144"/>
+      <c r="K29" s="144"/>
+      <c r="L29" s="144"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="147"/>
+      <c r="O29" s="147"/>
+      <c r="P29" s="147"/>
+      <c r="Q29" s="142"/>
+      <c r="R29" s="147"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="147"/>
+      <c r="U29" s="147"/>
+      <c r="V29" s="147"/>
+      <c r="W29" s="147"/>
+      <c r="X29" s="147"/>
+      <c r="Y29" s="147"/>
+      <c r="Z29" s="147"/>
+      <c r="AA29" s="147"/>
+      <c r="AB29" s="147"/>
+      <c r="AC29" s="147"/>
+      <c r="AD29" s="147"/>
+      <c r="AE29" s="147"/>
+      <c r="AF29" s="147"/>
+      <c r="AG29" s="147"/>
+      <c r="AH29" s="147"/>
+      <c r="AI29" s="147"/>
+      <c r="AJ29" s="147"/>
+      <c r="AK29" s="147"/>
+      <c r="AL29" s="147"/>
+    </row>
+    <row r="30" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="142"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="142"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="144"/>
+      <c r="K30" s="144"/>
+      <c r="L30" s="144"/>
+      <c r="M30" s="147"/>
+      <c r="N30" s="147"/>
+      <c r="O30" s="147"/>
+      <c r="P30" s="147"/>
+      <c r="Q30" s="142"/>
+      <c r="R30" s="147"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="147"/>
+      <c r="U30" s="147"/>
+      <c r="V30" s="147"/>
+      <c r="W30" s="147"/>
+      <c r="X30" s="147"/>
+      <c r="Y30" s="147"/>
+      <c r="Z30" s="147"/>
+      <c r="AA30" s="147"/>
+      <c r="AB30" s="147"/>
+      <c r="AC30" s="147"/>
+      <c r="AD30" s="147"/>
+      <c r="AE30" s="147"/>
+      <c r="AF30" s="147"/>
+      <c r="AG30" s="147"/>
+      <c r="AH30" s="147"/>
+      <c r="AI30" s="147"/>
+      <c r="AJ30" s="147"/>
+      <c r="AK30" s="147"/>
+      <c r="AL30" s="147"/>
+    </row>
+    <row r="31" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="160" t="s">
+        <v>156</v>
+      </c>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="142"/>
+      <c r="J31" s="144"/>
+      <c r="K31" s="144"/>
+      <c r="L31" s="144"/>
+      <c r="M31" s="147"/>
+      <c r="N31" s="147"/>
+      <c r="O31" s="147"/>
+      <c r="P31" s="147"/>
+      <c r="Q31" s="142"/>
+      <c r="R31" s="147"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="147"/>
+      <c r="U31" s="147"/>
+      <c r="V31" s="147"/>
+      <c r="W31" s="147"/>
+      <c r="X31" s="147"/>
+      <c r="Y31" s="147"/>
+      <c r="Z31" s="147"/>
+      <c r="AA31" s="147"/>
+      <c r="AB31" s="147"/>
+      <c r="AC31" s="147"/>
+      <c r="AD31" s="147"/>
+      <c r="AE31" s="147"/>
+      <c r="AF31" s="147"/>
+      <c r="AG31" s="147"/>
+      <c r="AH31" s="147"/>
+      <c r="AI31" s="147"/>
+      <c r="AJ31" s="147"/>
+      <c r="AK31" s="147"/>
+      <c r="AL31" s="147"/>
+    </row>
+    <row r="32" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E32" s="142"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="142"/>
+      <c r="I32" s="142"/>
+      <c r="J32" s="144"/>
+      <c r="K32" s="144"/>
+      <c r="L32" s="144"/>
+      <c r="M32" s="147"/>
+      <c r="N32" s="147"/>
+      <c r="O32" s="147"/>
+      <c r="P32" s="147"/>
+      <c r="Q32" s="142"/>
+      <c r="R32" s="147"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="147"/>
+      <c r="U32" s="147"/>
+      <c r="V32" s="147"/>
+      <c r="W32" s="147"/>
+      <c r="X32" s="147"/>
+      <c r="Y32" s="147"/>
+      <c r="Z32" s="147"/>
+      <c r="AA32" s="147"/>
+      <c r="AB32" s="147"/>
+      <c r="AC32" s="147"/>
+      <c r="AD32" s="147"/>
+      <c r="AE32" s="147"/>
+      <c r="AF32" s="147"/>
+      <c r="AG32" s="147"/>
+      <c r="AH32" s="147"/>
+      <c r="AI32" s="147"/>
+      <c r="AJ32" s="147"/>
+      <c r="AK32" s="147"/>
+      <c r="AL32" s="147"/>
+    </row>
+    <row r="33" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="143" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="142"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="142"/>
+      <c r="I33" s="142"/>
+      <c r="J33" s="144"/>
+      <c r="K33" s="144"/>
+      <c r="L33" s="144"/>
+      <c r="M33" s="147"/>
+      <c r="N33" s="147"/>
+      <c r="O33" s="147"/>
+      <c r="P33" s="147"/>
+      <c r="Q33" s="142"/>
+      <c r="R33" s="147"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="147"/>
+      <c r="U33" s="147"/>
+      <c r="V33" s="147"/>
+      <c r="W33" s="147"/>
+      <c r="X33" s="147"/>
+      <c r="Y33" s="147"/>
+      <c r="Z33" s="147"/>
+      <c r="AA33" s="147"/>
+      <c r="AB33" s="147"/>
+      <c r="AC33" s="147"/>
+      <c r="AD33" s="147"/>
+      <c r="AE33" s="147"/>
+      <c r="AF33" s="147"/>
+      <c r="AG33" s="147"/>
+      <c r="AH33" s="147"/>
+      <c r="AI33" s="147"/>
+      <c r="AJ33" s="147"/>
+      <c r="AK33" s="147"/>
+      <c r="AL33" s="147"/>
+    </row>
+    <row r="34" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="142"/>
+      <c r="F34" s="142"/>
+      <c r="G34" s="142"/>
+      <c r="H34" s="142"/>
+      <c r="I34" s="142"/>
+      <c r="J34" s="144"/>
+      <c r="K34" s="144"/>
+      <c r="L34" s="144"/>
+      <c r="M34" s="147"/>
+      <c r="N34" s="147"/>
+      <c r="O34" s="147"/>
+      <c r="P34" s="147"/>
+      <c r="Q34" s="142"/>
+      <c r="R34" s="147"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="147"/>
+      <c r="U34" s="147"/>
+      <c r="V34" s="147"/>
+      <c r="W34" s="147"/>
+      <c r="X34" s="147"/>
+      <c r="Y34" s="147"/>
+      <c r="Z34" s="147"/>
+      <c r="AA34" s="147"/>
+      <c r="AB34" s="147"/>
+      <c r="AC34" s="147"/>
+      <c r="AD34" s="147"/>
+      <c r="AE34" s="147"/>
+      <c r="AF34" s="147"/>
+      <c r="AG34" s="147"/>
+      <c r="AH34" s="147"/>
+      <c r="AI34" s="147"/>
+      <c r="AJ34" s="147"/>
+      <c r="AK34" s="147"/>
+      <c r="AL34" s="147"/>
+    </row>
+    <row r="35" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="143" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="142"/>
+      <c r="F35" s="142"/>
+      <c r="G35" s="142"/>
+      <c r="H35" s="142"/>
+      <c r="I35" s="142"/>
+      <c r="J35" s="144"/>
+      <c r="K35" s="144"/>
+      <c r="L35" s="144"/>
+      <c r="M35" s="147"/>
+      <c r="N35" s="147"/>
+      <c r="O35" s="147"/>
+      <c r="P35" s="147"/>
+      <c r="Q35" s="142"/>
+      <c r="R35" s="147"/>
+      <c r="S35" s="147"/>
+      <c r="T35" s="147"/>
+      <c r="U35" s="147"/>
+      <c r="V35" s="147"/>
+      <c r="W35" s="147"/>
+      <c r="X35" s="147"/>
+      <c r="Y35" s="147"/>
+      <c r="Z35" s="147"/>
+      <c r="AA35" s="147"/>
+      <c r="AB35" s="147"/>
+      <c r="AC35" s="147"/>
+      <c r="AD35" s="147"/>
+      <c r="AE35" s="147"/>
+      <c r="AF35" s="147"/>
+      <c r="AG35" s="147"/>
+      <c r="AH35" s="147"/>
+      <c r="AI35" s="147"/>
+      <c r="AJ35" s="147"/>
+      <c r="AK35" s="147"/>
+      <c r="AL35" s="147"/>
+    </row>
+    <row r="36" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="142"/>
+      <c r="F36" s="142"/>
+      <c r="G36" s="142"/>
+      <c r="H36" s="142"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="144"/>
+      <c r="K36" s="144"/>
+      <c r="L36" s="144"/>
+      <c r="M36" s="147"/>
+      <c r="N36" s="147"/>
+      <c r="O36" s="147"/>
+      <c r="P36" s="147"/>
+      <c r="Q36" s="142"/>
+      <c r="R36" s="147"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="147"/>
+      <c r="U36" s="147"/>
+      <c r="V36" s="147"/>
+      <c r="W36" s="147"/>
+      <c r="X36" s="147"/>
+      <c r="Y36" s="147"/>
+      <c r="Z36" s="147"/>
+      <c r="AA36" s="147"/>
+      <c r="AB36" s="147"/>
+      <c r="AC36" s="147"/>
+      <c r="AD36" s="147"/>
+      <c r="AE36" s="147"/>
+      <c r="AF36" s="147"/>
+      <c r="AG36" s="147"/>
+      <c r="AH36" s="147"/>
+      <c r="AI36" s="147"/>
+      <c r="AJ36" s="147"/>
+      <c r="AK36" s="147"/>
+      <c r="AL36" s="147"/>
+    </row>
+    <row r="37" spans="1:38" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="161"/>
+      <c r="B37" s="162"/>
+      <c r="C37" s="162"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="164" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="165"/>
+      <c r="G37" s="165"/>
+      <c r="H37" s="166"/>
+      <c r="I37" s="167" t="s">
+        <v>157</v>
+      </c>
+      <c r="J37" s="168"/>
+      <c r="K37" s="169"/>
+      <c r="L37" s="164" t="s">
+        <v>158</v>
+      </c>
+      <c r="M37" s="165"/>
+      <c r="N37" s="165"/>
+      <c r="O37" s="166"/>
+      <c r="P37" s="164" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q37" s="165"/>
+      <c r="R37" s="165"/>
+      <c r="S37" s="166"/>
+      <c r="T37" s="164" t="s">
+        <v>160</v>
+      </c>
+      <c r="U37" s="165"/>
+      <c r="V37" s="165"/>
+      <c r="W37" s="166"/>
+      <c r="X37" s="164" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y37" s="165"/>
+      <c r="Z37" s="165"/>
+      <c r="AA37" s="166"/>
+      <c r="AB37" s="164" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC37" s="165"/>
+      <c r="AD37" s="165"/>
+      <c r="AE37" s="166"/>
+      <c r="AF37" s="164" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG37" s="165"/>
+      <c r="AH37" s="165"/>
+      <c r="AI37" s="166"/>
+      <c r="AJ37" s="164" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK37" s="165"/>
+      <c r="AL37" s="166"/>
+    </row>
+    <row r="38" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="170" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="171"/>
+      <c r="C38" s="171"/>
+      <c r="D38" s="172"/>
+      <c r="E38" s="173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="173"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="175"/>
+      <c r="K38" s="176"/>
+      <c r="L38" s="164"/>
+      <c r="M38" s="165"/>
+      <c r="N38" s="165"/>
+      <c r="O38" s="166"/>
+      <c r="P38" s="164"/>
+      <c r="Q38" s="165"/>
+      <c r="R38" s="165"/>
+      <c r="S38" s="166"/>
+      <c r="T38" s="164"/>
+      <c r="U38" s="165"/>
+      <c r="V38" s="165"/>
+      <c r="W38" s="166"/>
+      <c r="X38" s="164"/>
+      <c r="Y38" s="165"/>
+      <c r="Z38" s="165"/>
+      <c r="AA38" s="166"/>
+      <c r="AB38" s="164"/>
+      <c r="AC38" s="165"/>
+      <c r="AD38" s="165"/>
+      <c r="AE38" s="166"/>
+      <c r="AF38" s="164"/>
+      <c r="AG38" s="165"/>
+      <c r="AH38" s="165"/>
+      <c r="AI38" s="166"/>
+      <c r="AJ38" s="164"/>
+      <c r="AK38" s="165"/>
+      <c r="AL38" s="166"/>
+    </row>
+    <row r="39" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="177"/>
+      <c r="B39" s="178"/>
+      <c r="C39" s="178"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="173" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="173"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="180"/>
+      <c r="J39" s="181"/>
+      <c r="K39" s="182"/>
+      <c r="L39" s="164"/>
+      <c r="M39" s="165"/>
+      <c r="N39" s="165"/>
+      <c r="O39" s="166"/>
+      <c r="P39" s="164"/>
+      <c r="Q39" s="165"/>
+      <c r="R39" s="165"/>
+      <c r="S39" s="166"/>
+      <c r="T39" s="164"/>
+      <c r="U39" s="165"/>
+      <c r="V39" s="165"/>
+      <c r="W39" s="166"/>
+      <c r="X39" s="164"/>
+      <c r="Y39" s="165"/>
+      <c r="Z39" s="165"/>
+      <c r="AA39" s="166"/>
+      <c r="AB39" s="164"/>
+      <c r="AC39" s="165"/>
+      <c r="AD39" s="165"/>
+      <c r="AE39" s="166"/>
+      <c r="AF39" s="164"/>
+      <c r="AG39" s="165"/>
+      <c r="AH39" s="165"/>
+      <c r="AI39" s="166"/>
+      <c r="AJ39" s="164"/>
+      <c r="AK39" s="165"/>
+      <c r="AL39" s="166"/>
+    </row>
+    <row r="40" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="177"/>
+      <c r="B40" s="178"/>
+      <c r="C40" s="178"/>
+      <c r="D40" s="179"/>
+      <c r="E40" s="173" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="173"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="180"/>
+      <c r="J40" s="181"/>
+      <c r="K40" s="182"/>
+      <c r="L40" s="164"/>
+      <c r="M40" s="165"/>
+      <c r="N40" s="165"/>
+      <c r="O40" s="166"/>
+      <c r="P40" s="164"/>
+      <c r="Q40" s="165"/>
+      <c r="R40" s="165"/>
+      <c r="S40" s="166"/>
+      <c r="T40" s="164"/>
+      <c r="U40" s="165"/>
+      <c r="V40" s="165"/>
+      <c r="W40" s="166"/>
+      <c r="X40" s="164"/>
+      <c r="Y40" s="165"/>
+      <c r="Z40" s="165"/>
+      <c r="AA40" s="166"/>
+      <c r="AB40" s="164"/>
+      <c r="AC40" s="165"/>
+      <c r="AD40" s="165"/>
+      <c r="AE40" s="166"/>
+      <c r="AF40" s="164"/>
+      <c r="AG40" s="165"/>
+      <c r="AH40" s="165"/>
+      <c r="AI40" s="166"/>
+      <c r="AJ40" s="164"/>
+      <c r="AK40" s="165"/>
+      <c r="AL40" s="166"/>
+    </row>
+    <row r="41" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="177"/>
+      <c r="B41" s="178"/>
+      <c r="C41" s="178"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="173" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="173"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="173"/>
+      <c r="I41" s="180"/>
+      <c r="J41" s="181"/>
+      <c r="K41" s="182"/>
+      <c r="L41" s="164"/>
+      <c r="M41" s="165"/>
+      <c r="N41" s="165"/>
+      <c r="O41" s="166"/>
+      <c r="P41" s="164"/>
+      <c r="Q41" s="165"/>
+      <c r="R41" s="165"/>
+      <c r="S41" s="166"/>
+      <c r="T41" s="164"/>
+      <c r="U41" s="165"/>
+      <c r="V41" s="165"/>
+      <c r="W41" s="166"/>
+      <c r="X41" s="164"/>
+      <c r="Y41" s="165"/>
+      <c r="Z41" s="165"/>
+      <c r="AA41" s="166"/>
+      <c r="AB41" s="164"/>
+      <c r="AC41" s="165"/>
+      <c r="AD41" s="165"/>
+      <c r="AE41" s="166"/>
+      <c r="AF41" s="164"/>
+      <c r="AG41" s="165"/>
+      <c r="AH41" s="165"/>
+      <c r="AI41" s="166"/>
+      <c r="AJ41" s="164"/>
+      <c r="AK41" s="165"/>
+      <c r="AL41" s="166"/>
+    </row>
+    <row r="42" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="177"/>
+      <c r="B42" s="178"/>
+      <c r="C42" s="178"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="173" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="173"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="173"/>
+      <c r="I42" s="180"/>
+      <c r="J42" s="181"/>
+      <c r="K42" s="182"/>
+      <c r="L42" s="164"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="166"/>
+      <c r="P42" s="164"/>
+      <c r="Q42" s="165"/>
+      <c r="R42" s="165"/>
+      <c r="S42" s="166"/>
+      <c r="T42" s="164"/>
+      <c r="U42" s="165"/>
+      <c r="V42" s="165"/>
+      <c r="W42" s="166"/>
+      <c r="X42" s="164"/>
+      <c r="Y42" s="165"/>
+      <c r="Z42" s="165"/>
+      <c r="AA42" s="166"/>
+      <c r="AB42" s="164"/>
+      <c r="AC42" s="165"/>
+      <c r="AD42" s="165"/>
+      <c r="AE42" s="166"/>
+      <c r="AF42" s="164"/>
+      <c r="AG42" s="165"/>
+      <c r="AH42" s="165"/>
+      <c r="AI42" s="166"/>
+      <c r="AJ42" s="164"/>
+      <c r="AK42" s="165"/>
+      <c r="AL42" s="166"/>
+    </row>
+    <row r="43" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="183"/>
+      <c r="B43" s="184"/>
+      <c r="C43" s="184"/>
+      <c r="D43" s="185"/>
+      <c r="E43" s="173" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="173"/>
+      <c r="G43" s="173"/>
+      <c r="H43" s="173"/>
+      <c r="I43" s="180"/>
+      <c r="J43" s="181"/>
+      <c r="K43" s="182"/>
+      <c r="L43" s="164"/>
+      <c r="M43" s="165"/>
+      <c r="N43" s="165"/>
+      <c r="O43" s="166"/>
+      <c r="P43" s="164"/>
+      <c r="Q43" s="165"/>
+      <c r="R43" s="165"/>
+      <c r="S43" s="166"/>
+      <c r="T43" s="164"/>
+      <c r="U43" s="165"/>
+      <c r="V43" s="165"/>
+      <c r="W43" s="166"/>
+      <c r="X43" s="164"/>
+      <c r="Y43" s="165"/>
+      <c r="Z43" s="165"/>
+      <c r="AA43" s="166"/>
+      <c r="AB43" s="164"/>
+      <c r="AC43" s="165"/>
+      <c r="AD43" s="165"/>
+      <c r="AE43" s="166"/>
+      <c r="AF43" s="164"/>
+      <c r="AG43" s="165"/>
+      <c r="AH43" s="165"/>
+      <c r="AI43" s="166"/>
+      <c r="AJ43" s="164"/>
+      <c r="AK43" s="165"/>
+      <c r="AL43" s="166"/>
+    </row>
+    <row r="44" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="170" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="171"/>
+      <c r="C44" s="171"/>
+      <c r="D44" s="172"/>
+      <c r="E44" s="173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="173"/>
+      <c r="G44" s="173"/>
+      <c r="H44" s="173"/>
+      <c r="I44" s="180"/>
+      <c r="J44" s="181"/>
+      <c r="K44" s="182"/>
+      <c r="L44" s="164"/>
+      <c r="M44" s="165"/>
+      <c r="N44" s="165"/>
+      <c r="O44" s="166"/>
+      <c r="P44" s="164"/>
+      <c r="Q44" s="165"/>
+      <c r="R44" s="165"/>
+      <c r="S44" s="166"/>
+      <c r="T44" s="164"/>
+      <c r="U44" s="165"/>
+      <c r="V44" s="165"/>
+      <c r="W44" s="166"/>
+      <c r="X44" s="164"/>
+      <c r="Y44" s="165"/>
+      <c r="Z44" s="165"/>
+      <c r="AA44" s="166"/>
+      <c r="AB44" s="164"/>
+      <c r="AC44" s="165"/>
+      <c r="AD44" s="165"/>
+      <c r="AE44" s="166"/>
+      <c r="AF44" s="164"/>
+      <c r="AG44" s="165"/>
+      <c r="AH44" s="165"/>
+      <c r="AI44" s="166"/>
+      <c r="AJ44" s="164"/>
+      <c r="AK44" s="165"/>
+      <c r="AL44" s="166"/>
+    </row>
+    <row r="45" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="177"/>
+      <c r="B45" s="178"/>
+      <c r="C45" s="178"/>
+      <c r="D45" s="179"/>
+      <c r="E45" s="173" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="173"/>
+      <c r="G45" s="173"/>
+      <c r="H45" s="173"/>
+      <c r="I45" s="180"/>
+      <c r="J45" s="181"/>
+      <c r="K45" s="182"/>
+      <c r="L45" s="164"/>
+      <c r="M45" s="165"/>
+      <c r="N45" s="165"/>
+      <c r="O45" s="166"/>
+      <c r="P45" s="164"/>
+      <c r="Q45" s="165"/>
+      <c r="R45" s="165"/>
+      <c r="S45" s="166"/>
+      <c r="T45" s="164"/>
+      <c r="U45" s="165"/>
+      <c r="V45" s="165"/>
+      <c r="W45" s="166"/>
+      <c r="X45" s="164"/>
+      <c r="Y45" s="165"/>
+      <c r="Z45" s="165"/>
+      <c r="AA45" s="166"/>
+      <c r="AB45" s="164"/>
+      <c r="AC45" s="165"/>
+      <c r="AD45" s="165"/>
+      <c r="AE45" s="166"/>
+      <c r="AF45" s="164"/>
+      <c r="AG45" s="165"/>
+      <c r="AH45" s="165"/>
+      <c r="AI45" s="166"/>
+      <c r="AJ45" s="164"/>
+      <c r="AK45" s="165"/>
+      <c r="AL45" s="166"/>
+    </row>
+    <row r="46" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="177"/>
+      <c r="B46" s="178"/>
+      <c r="C46" s="178"/>
+      <c r="D46" s="179"/>
+      <c r="E46" s="173" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="173"/>
+      <c r="G46" s="173"/>
+      <c r="H46" s="173"/>
+      <c r="I46" s="180"/>
+      <c r="J46" s="181"/>
+      <c r="K46" s="182"/>
+      <c r="L46" s="164"/>
+      <c r="M46" s="165"/>
+      <c r="N46" s="165"/>
+      <c r="O46" s="166"/>
+      <c r="P46" s="164"/>
+      <c r="Q46" s="165"/>
+      <c r="R46" s="165"/>
+      <c r="S46" s="166"/>
+      <c r="T46" s="164"/>
+      <c r="U46" s="165"/>
+      <c r="V46" s="165"/>
+      <c r="W46" s="166"/>
+      <c r="X46" s="164"/>
+      <c r="Y46" s="165"/>
+      <c r="Z46" s="165"/>
+      <c r="AA46" s="166"/>
+      <c r="AB46" s="164"/>
+      <c r="AC46" s="165"/>
+      <c r="AD46" s="165"/>
+      <c r="AE46" s="166"/>
+      <c r="AF46" s="164"/>
+      <c r="AG46" s="165"/>
+      <c r="AH46" s="165"/>
+      <c r="AI46" s="166"/>
+      <c r="AJ46" s="164"/>
+      <c r="AK46" s="165"/>
+      <c r="AL46" s="166"/>
+    </row>
+    <row r="47" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="177"/>
+      <c r="B47" s="178"/>
+      <c r="C47" s="178"/>
+      <c r="D47" s="179"/>
+      <c r="E47" s="173" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="173"/>
+      <c r="G47" s="173"/>
+      <c r="H47" s="173"/>
+      <c r="I47" s="180"/>
+      <c r="J47" s="181"/>
+      <c r="K47" s="182"/>
+      <c r="L47" s="164"/>
+      <c r="M47" s="165"/>
+      <c r="N47" s="165"/>
+      <c r="O47" s="166"/>
+      <c r="P47" s="164"/>
+      <c r="Q47" s="165"/>
+      <c r="R47" s="165"/>
+      <c r="S47" s="166"/>
+      <c r="T47" s="164"/>
+      <c r="U47" s="165"/>
+      <c r="V47" s="165"/>
+      <c r="W47" s="166"/>
+      <c r="X47" s="164"/>
+      <c r="Y47" s="165"/>
+      <c r="Z47" s="165"/>
+      <c r="AA47" s="166"/>
+      <c r="AB47" s="164"/>
+      <c r="AC47" s="165"/>
+      <c r="AD47" s="165"/>
+      <c r="AE47" s="166"/>
+      <c r="AF47" s="164"/>
+      <c r="AG47" s="165"/>
+      <c r="AH47" s="165"/>
+      <c r="AI47" s="166"/>
+      <c r="AJ47" s="164"/>
+      <c r="AK47" s="165"/>
+      <c r="AL47" s="166"/>
+    </row>
+    <row r="48" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="177"/>
+      <c r="B48" s="178"/>
+      <c r="C48" s="178"/>
+      <c r="D48" s="179"/>
+      <c r="E48" s="173" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="173"/>
+      <c r="G48" s="173"/>
+      <c r="H48" s="173"/>
+      <c r="I48" s="180"/>
+      <c r="J48" s="181"/>
+      <c r="K48" s="182"/>
+      <c r="L48" s="164"/>
+      <c r="M48" s="165"/>
+      <c r="N48" s="165"/>
+      <c r="O48" s="166"/>
+      <c r="P48" s="164"/>
+      <c r="Q48" s="165"/>
+      <c r="R48" s="165"/>
+      <c r="S48" s="166"/>
+      <c r="T48" s="164"/>
+      <c r="U48" s="165"/>
+      <c r="V48" s="165"/>
+      <c r="W48" s="166"/>
+      <c r="X48" s="164"/>
+      <c r="Y48" s="165"/>
+      <c r="Z48" s="165"/>
+      <c r="AA48" s="166"/>
+      <c r="AB48" s="164"/>
+      <c r="AC48" s="165"/>
+      <c r="AD48" s="165"/>
+      <c r="AE48" s="166"/>
+      <c r="AF48" s="164"/>
+      <c r="AG48" s="165"/>
+      <c r="AH48" s="165"/>
+      <c r="AI48" s="166"/>
+      <c r="AJ48" s="164"/>
+      <c r="AK48" s="165"/>
+      <c r="AL48" s="166"/>
+    </row>
+    <row r="49" spans="1:38" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="183"/>
+      <c r="B49" s="184"/>
+      <c r="C49" s="184"/>
+      <c r="D49" s="185"/>
+      <c r="E49" s="173" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" s="173"/>
+      <c r="G49" s="173"/>
+      <c r="H49" s="173"/>
+      <c r="I49" s="186"/>
+      <c r="J49" s="187"/>
+      <c r="K49" s="188"/>
+      <c r="L49" s="164"/>
+      <c r="M49" s="165"/>
+      <c r="N49" s="165"/>
+      <c r="O49" s="166"/>
+      <c r="P49" s="164"/>
+      <c r="Q49" s="165"/>
+      <c r="R49" s="165"/>
+      <c r="S49" s="166"/>
+      <c r="T49" s="164"/>
+      <c r="U49" s="165"/>
+      <c r="V49" s="165"/>
+      <c r="W49" s="166"/>
+      <c r="X49" s="164"/>
+      <c r="Y49" s="165"/>
+      <c r="Z49" s="165"/>
+      <c r="AA49" s="166"/>
+      <c r="AB49" s="164"/>
+      <c r="AC49" s="165"/>
+      <c r="AD49" s="165"/>
+      <c r="AE49" s="166"/>
+      <c r="AF49" s="164"/>
+      <c r="AG49" s="165"/>
+      <c r="AH49" s="165"/>
+      <c r="AI49" s="166"/>
+      <c r="AJ49" s="164"/>
+      <c r="AK49" s="165"/>
+      <c r="AL49" s="166"/>
+    </row>
+    <row r="50" spans="1:38" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="157"/>
+      <c r="B50" s="157"/>
+      <c r="C50" s="157"/>
+      <c r="D50" s="157"/>
+      <c r="E50" s="157"/>
+      <c r="F50" s="157"/>
+      <c r="G50" s="157"/>
+      <c r="H50" s="157"/>
+      <c r="I50" s="189"/>
+      <c r="J50" s="189"/>
+      <c r="K50" s="189"/>
+      <c r="L50" s="157"/>
+      <c r="M50" s="157"/>
+      <c r="N50" s="157"/>
+      <c r="O50" s="157"/>
+      <c r="P50" s="157"/>
+      <c r="Q50" s="157"/>
+      <c r="R50" s="157"/>
+      <c r="S50" s="157"/>
+      <c r="T50" s="157"/>
+      <c r="U50" s="157"/>
+      <c r="V50" s="157"/>
+      <c r="W50" s="157"/>
+      <c r="X50" s="157"/>
+      <c r="Y50" s="157"/>
+      <c r="Z50" s="157"/>
+      <c r="AA50" s="157"/>
+      <c r="AB50" s="157"/>
+      <c r="AC50" s="157"/>
+      <c r="AD50" s="157"/>
+      <c r="AE50" s="157"/>
+      <c r="AF50" s="157"/>
+      <c r="AG50" s="157"/>
+      <c r="AH50" s="157"/>
+      <c r="AI50" s="157"/>
+      <c r="AJ50" s="157"/>
+      <c r="AK50" s="157"/>
+      <c r="AL50" s="157"/>
+    </row>
+    <row r="51" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="155" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="157"/>
+      <c r="C51" s="157"/>
+      <c r="D51" s="157"/>
+      <c r="E51" s="157"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="157"/>
+      <c r="K51" s="157"/>
+      <c r="L51" s="157"/>
+      <c r="M51" s="157"/>
+      <c r="N51" s="157"/>
+      <c r="O51" s="157"/>
+      <c r="P51" s="157"/>
+      <c r="Q51" s="157"/>
+      <c r="R51" s="157"/>
+      <c r="S51" s="147"/>
+      <c r="T51" s="147"/>
+      <c r="U51" s="147"/>
+      <c r="V51" s="147"/>
+      <c r="W51" s="147"/>
+      <c r="X51" s="147"/>
+      <c r="Y51" s="147"/>
+      <c r="Z51" s="147"/>
+      <c r="AA51" s="147"/>
+      <c r="AB51" s="147"/>
+      <c r="AC51" s="147"/>
+      <c r="AD51" s="147"/>
+      <c r="AE51" s="147"/>
+      <c r="AF51" s="147"/>
+      <c r="AG51" s="147"/>
+      <c r="AH51" s="147"/>
+      <c r="AI51" s="147"/>
+      <c r="AJ51" s="147"/>
+      <c r="AK51" s="147"/>
+      <c r="AL51" s="147"/>
+    </row>
+    <row r="52" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="155" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" s="157"/>
+      <c r="C52" s="157"/>
+      <c r="D52" s="157"/>
+      <c r="E52" s="157"/>
+      <c r="F52" s="157"/>
+      <c r="G52" s="157"/>
+      <c r="H52" s="157"/>
+      <c r="I52" s="157"/>
+      <c r="J52" s="157"/>
+      <c r="K52" s="157"/>
+      <c r="L52" s="157"/>
+      <c r="M52" s="157"/>
+      <c r="N52" s="157"/>
+      <c r="O52" s="157"/>
+      <c r="P52" s="157"/>
+      <c r="Q52" s="157"/>
+      <c r="R52" s="157"/>
+      <c r="S52" s="147"/>
+      <c r="T52" s="147"/>
+      <c r="U52" s="147"/>
+      <c r="V52" s="147"/>
+      <c r="W52" s="147"/>
+      <c r="X52" s="147"/>
+      <c r="Y52" s="147"/>
+      <c r="Z52" s="147"/>
+      <c r="AA52" s="147"/>
+      <c r="AB52" s="147"/>
+      <c r="AC52" s="147"/>
+      <c r="AD52" s="147"/>
+      <c r="AE52" s="147"/>
+      <c r="AF52" s="147"/>
+      <c r="AG52" s="147"/>
+      <c r="AH52" s="147"/>
+      <c r="AI52" s="147"/>
+      <c r="AJ52" s="147"/>
+      <c r="AK52" s="147"/>
+      <c r="AL52" s="147"/>
+    </row>
+    <row r="53" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="155" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" s="157"/>
+      <c r="C53" s="157"/>
+      <c r="D53" s="157"/>
+      <c r="E53" s="157"/>
+      <c r="F53" s="157"/>
+      <c r="G53" s="157"/>
+      <c r="H53" s="157"/>
+      <c r="I53" s="157"/>
+      <c r="J53" s="157"/>
+      <c r="K53" s="157"/>
+      <c r="L53" s="157"/>
+      <c r="M53" s="157"/>
+      <c r="N53" s="157"/>
+      <c r="O53" s="157"/>
+      <c r="P53" s="157"/>
+      <c r="Q53" s="155" t="s">
+        <v>168</v>
+      </c>
+      <c r="R53" s="157"/>
+      <c r="S53" s="147"/>
+      <c r="T53" s="155"/>
+      <c r="U53" s="157"/>
+      <c r="V53" s="147"/>
+      <c r="W53" s="147"/>
+      <c r="X53" s="147"/>
+      <c r="Y53" s="147"/>
+      <c r="Z53" s="147"/>
+      <c r="AA53" s="147"/>
+      <c r="AB53" s="147"/>
+      <c r="AC53" s="147"/>
+      <c r="AD53" s="147"/>
+      <c r="AE53" s="147"/>
+      <c r="AF53" s="147"/>
+      <c r="AG53" s="147"/>
+      <c r="AH53" s="147"/>
+      <c r="AI53" s="147"/>
+      <c r="AJ53" s="147"/>
+      <c r="AK53" s="147"/>
+      <c r="AL53" s="147"/>
+    </row>
+    <row r="54" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="143" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" s="157"/>
+      <c r="C54" s="157"/>
+      <c r="D54" s="157"/>
+      <c r="E54" s="157"/>
+      <c r="F54" s="157"/>
+      <c r="G54" s="157"/>
+      <c r="H54" s="157"/>
+      <c r="I54" s="157"/>
+      <c r="J54" s="157"/>
+      <c r="K54" s="157"/>
+      <c r="L54" s="157"/>
+      <c r="M54" s="157"/>
+      <c r="N54" s="157"/>
+      <c r="O54" s="157"/>
+      <c r="P54" s="157"/>
+      <c r="Q54" s="157"/>
+      <c r="R54" s="157"/>
+      <c r="S54" s="147"/>
+      <c r="T54" s="147"/>
+      <c r="U54" s="147"/>
+      <c r="V54" s="147"/>
+      <c r="W54" s="147"/>
+      <c r="X54" s="147"/>
+      <c r="Y54" s="147"/>
+      <c r="Z54" s="147"/>
+      <c r="AA54" s="147"/>
+      <c r="AB54" s="147"/>
+      <c r="AC54" s="147"/>
+      <c r="AD54" s="147"/>
+      <c r="AE54" s="147"/>
+      <c r="AF54" s="147"/>
+      <c r="AG54" s="147"/>
+      <c r="AH54" s="147"/>
+      <c r="AI54" s="147"/>
+      <c r="AJ54" s="147"/>
+      <c r="AK54" s="147"/>
+      <c r="AL54" s="147"/>
+    </row>
+    <row r="55" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E55" s="142"/>
+      <c r="F55" s="142"/>
+      <c r="G55" s="142"/>
+      <c r="H55" s="142"/>
+      <c r="I55" s="142"/>
+      <c r="J55" s="144"/>
+      <c r="K55" s="144"/>
+      <c r="L55" s="144"/>
+      <c r="M55" s="147"/>
+      <c r="N55" s="147"/>
+      <c r="O55" s="147"/>
+      <c r="P55" s="147"/>
+      <c r="Q55" s="147"/>
+      <c r="R55" s="147"/>
+      <c r="S55" s="147"/>
+      <c r="T55" s="147"/>
+      <c r="U55" s="147"/>
+      <c r="V55" s="147"/>
+      <c r="W55" s="147"/>
+      <c r="X55" s="147"/>
+      <c r="Y55" s="147"/>
+      <c r="Z55" s="147"/>
+      <c r="AA55" s="147"/>
+      <c r="AB55" s="147"/>
+      <c r="AC55" s="147"/>
+      <c r="AD55" s="147"/>
+      <c r="AE55" s="147"/>
+      <c r="AF55" s="147"/>
+      <c r="AG55" s="147"/>
+      <c r="AH55" s="147"/>
+      <c r="AI55" s="147"/>
+      <c r="AJ55" s="147"/>
+      <c r="AK55" s="147"/>
+      <c r="AL55" s="147"/>
+    </row>
+    <row r="56" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="142"/>
+      <c r="E56" s="142"/>
+      <c r="F56" s="142"/>
+      <c r="G56" s="142"/>
+      <c r="H56" s="142"/>
+      <c r="I56" s="142"/>
+      <c r="J56" s="144"/>
+      <c r="K56" s="144"/>
+      <c r="L56" s="144"/>
+      <c r="M56" s="147"/>
+      <c r="N56" s="147"/>
+      <c r="O56" s="147"/>
+      <c r="P56" s="147"/>
+      <c r="Q56" s="147"/>
+      <c r="R56" s="147"/>
+      <c r="S56" s="147"/>
+      <c r="T56" s="147"/>
+      <c r="U56" s="147"/>
+      <c r="V56" s="147"/>
+      <c r="W56" s="147"/>
+      <c r="X56" s="147"/>
+      <c r="Y56" s="147"/>
+      <c r="Z56" s="147"/>
+      <c r="AA56" s="147"/>
+      <c r="AB56" s="147"/>
+      <c r="AC56" s="147"/>
+      <c r="AD56" s="147"/>
+      <c r="AE56" s="147"/>
+      <c r="AF56" s="147"/>
+      <c r="AG56" s="147"/>
+      <c r="AH56" s="147"/>
+      <c r="AI56" s="147"/>
+      <c r="AJ56" s="147"/>
+      <c r="AK56" s="147"/>
+      <c r="AL56" s="147"/>
+    </row>
+  </sheetData>
+  <mergeCells count="114">
+    <mergeCell ref="AF48:AI48"/>
+    <mergeCell ref="AJ48:AL48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="L49:O49"/>
+    <mergeCell ref="P49:S49"/>
+    <mergeCell ref="T49:W49"/>
+    <mergeCell ref="X49:AA49"/>
+    <mergeCell ref="AB49:AE49"/>
+    <mergeCell ref="AF49:AI49"/>
+    <mergeCell ref="AJ49:AL49"/>
+    <mergeCell ref="X47:AA47"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AJ47:AL47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="L48:O48"/>
+    <mergeCell ref="P48:S48"/>
+    <mergeCell ref="T48:W48"/>
+    <mergeCell ref="X48:AA48"/>
+    <mergeCell ref="AB48:AE48"/>
+    <mergeCell ref="AJ45:AL45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="L46:O46"/>
+    <mergeCell ref="P46:S46"/>
+    <mergeCell ref="T46:W46"/>
+    <mergeCell ref="X46:AA46"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="AF46:AI46"/>
+    <mergeCell ref="AJ46:AL46"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="AF44:AI44"/>
+    <mergeCell ref="AJ44:AL44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="L45:O45"/>
+    <mergeCell ref="P45:S45"/>
+    <mergeCell ref="T45:W45"/>
+    <mergeCell ref="X45:AA45"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="AF45:AI45"/>
+    <mergeCell ref="A44:D49"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="L44:O44"/>
+    <mergeCell ref="P44:S44"/>
+    <mergeCell ref="T44:W44"/>
+    <mergeCell ref="X44:AA44"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="L47:O47"/>
+    <mergeCell ref="P47:S47"/>
+    <mergeCell ref="T47:W47"/>
+    <mergeCell ref="AF42:AI42"/>
+    <mergeCell ref="AJ42:AL42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="L43:O43"/>
+    <mergeCell ref="P43:S43"/>
+    <mergeCell ref="T43:W43"/>
+    <mergeCell ref="X43:AA43"/>
+    <mergeCell ref="AB43:AE43"/>
+    <mergeCell ref="AF43:AI43"/>
+    <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="L42:O42"/>
+    <mergeCell ref="P42:S42"/>
+    <mergeCell ref="T42:W42"/>
+    <mergeCell ref="X42:AA42"/>
+    <mergeCell ref="AB42:AE42"/>
+    <mergeCell ref="AJ40:AL40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="L41:O41"/>
+    <mergeCell ref="P41:S41"/>
+    <mergeCell ref="T41:W41"/>
+    <mergeCell ref="X41:AA41"/>
+    <mergeCell ref="AB41:AE41"/>
+    <mergeCell ref="AF41:AI41"/>
+    <mergeCell ref="AJ41:AL41"/>
+    <mergeCell ref="AB39:AE39"/>
+    <mergeCell ref="AF39:AI39"/>
+    <mergeCell ref="AJ39:AL39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="L40:O40"/>
+    <mergeCell ref="P40:S40"/>
+    <mergeCell ref="T40:W40"/>
+    <mergeCell ref="X40:AA40"/>
+    <mergeCell ref="AB40:AE40"/>
+    <mergeCell ref="AF40:AI40"/>
+    <mergeCell ref="T38:W38"/>
+    <mergeCell ref="X38:AA38"/>
+    <mergeCell ref="AB38:AE38"/>
+    <mergeCell ref="AF38:AI38"/>
+    <mergeCell ref="AJ38:AL38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="P39:S39"/>
+    <mergeCell ref="T39:W39"/>
+    <mergeCell ref="X39:AA39"/>
+    <mergeCell ref="T37:W37"/>
+    <mergeCell ref="X37:AA37"/>
+    <mergeCell ref="AB37:AE37"/>
+    <mergeCell ref="AF37:AI37"/>
+    <mergeCell ref="AJ37:AL37"/>
+    <mergeCell ref="A38:D43"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K49"/>
+    <mergeCell ref="L38:O38"/>
+    <mergeCell ref="P38:S38"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="AE9:AH12"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="P37:S37"/>
+  </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L
+Form Code表格编号: NGB_SFL_F_7.8_Mango-PHY_0006_CS_A.0&amp;R&amp;G</oddHeader>
+    <oddFooter>&amp;L测试/日期Conducted by/Date:
+&amp;U                                                   &amp;U.&amp;C复核/日期Checked by/Date:
+&amp;U                                            &amp;U.&amp;R测试环境Test Condition:
+&amp;U                &amp;U ℃,&amp;U                 &amp;U%RH</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{948094c8-480e-400b-91c4-c984b7e20814}" enabled="1" method="Standard" siteId="{a1109567-0815-4e1f-88af-e23555482aaa}" contentBits="0" removed="0"/>
